--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="783">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825943946838</t>
+    <t xml:space="preserve">1.85825955867767</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9132376909256</t>
+    <t xml:space="preserve">1.91323757171631</t>
   </si>
   <si>
     <t xml:space="preserve">1.92109167575836</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">1.80642306804657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82998490333557</t>
+    <t xml:space="preserve">1.82998478412628</t>
   </si>
   <si>
     <t xml:space="preserve">1.79856908321381</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">1.76715278625488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85354697704315</t>
+    <t xml:space="preserve">1.85354685783386</t>
   </si>
   <si>
     <t xml:space="preserve">1.86925518512726</t>
@@ -80,19 +80,19 @@
     <t xml:space="preserve">1.89281713962555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86768424510956</t>
+    <t xml:space="preserve">1.86768436431885</t>
   </si>
   <si>
     <t xml:space="preserve">1.81584763526917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83783900737762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87553811073303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684338092804</t>
+    <t xml:space="preserve">1.83783888816833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553822994232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684314250946</t>
   </si>
   <si>
     <t xml:space="preserve">1.84569275379181</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">1.81898939609528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8362683057785</t>
+    <t xml:space="preserve">1.83626818656921</t>
   </si>
   <si>
     <t xml:space="preserve">1.85983002185822</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">1.80485212802887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82056033611298</t>
+    <t xml:space="preserve">1.82056021690369</t>
   </si>
   <si>
     <t xml:space="preserve">1.81741857528687</t>
@@ -125,10 +125,10 @@
     <t xml:space="preserve">1.81427705287933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85197627544403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84412205219269</t>
+    <t xml:space="preserve">1.85197639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84412217140198</t>
   </si>
   <si>
     <t xml:space="preserve">1.84098064899445</t>
@@ -143,19 +143,19 @@
     <t xml:space="preserve">1.8221310377121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93679976463318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622421264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407855510712</t>
+    <t xml:space="preserve">1.9367995262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622433185577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407843589783</t>
   </si>
   <si>
     <t xml:space="preserve">1.96350336074829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9650741815567</t>
+    <t xml:space="preserve">1.96507394313812</t>
   </si>
   <si>
     <t xml:space="preserve">1.99334859848022</t>
@@ -164,34 +164,34 @@
     <t xml:space="preserve">2.00434398651123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98706543445587</t>
+    <t xml:space="preserve">1.98706531524658</t>
   </si>
   <si>
     <t xml:space="preserve">2.00905680656433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02476477622986</t>
+    <t xml:space="preserve">2.0247642993927</t>
   </si>
   <si>
     <t xml:space="preserve">1.93051624298096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96193218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994128704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564925670624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637909412384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87396728992462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378734588623</t>
+    <t xml:space="preserve">1.96193253993988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564901828766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637921333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87396740913391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378722667694</t>
   </si>
   <si>
     <t xml:space="preserve">1.95017540454865</t>
@@ -200,10 +200,10 @@
     <t xml:space="preserve">1.92231559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93050968647003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656334400177</t>
+    <t xml:space="preserve">1.93050956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656322479248</t>
   </si>
   <si>
     <t xml:space="preserve">1.95509147644043</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">1.91739904880524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93542611598969</t>
+    <t xml:space="preserve">1.93542587757111</t>
   </si>
   <si>
     <t xml:space="preserve">1.9419811964035</t>
@@ -224,16 +224,16 @@
     <t xml:space="preserve">1.91248285770416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91084396839142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545899391174</t>
+    <t xml:space="preserve">1.91084408760071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545887470245</t>
   </si>
   <si>
     <t xml:space="preserve">1.80268287658691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84201431274414</t>
+    <t xml:space="preserve">1.84201419353485</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218145370483</t>
@@ -242,22 +242,22 @@
     <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86823499202728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90756642818451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88462316989899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920507907867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87151253223419</t>
+    <t xml:space="preserve">1.86823523044586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9075665473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90592741966248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88462293148041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920519828796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87151277065277</t>
   </si>
   <si>
     <t xml:space="preserve">1.89773344993591</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">1.82398748397827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75843524932861</t>
+    <t xml:space="preserve">1.75843513011932</t>
   </si>
   <si>
     <t xml:space="preserve">1.76662921905518</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">1.77646219730377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75187993049622</t>
+    <t xml:space="preserve">1.75188004970551</t>
   </si>
   <si>
     <t xml:space="preserve">1.75351893901825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77973985671997</t>
+    <t xml:space="preserve">1.77973973751068</t>
   </si>
   <si>
     <t xml:space="preserve">1.75024116039276</t>
@@ -299,13 +299,13 @@
     <t xml:space="preserve">1.72893667221069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69616079330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76007413864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70435464382172</t>
+    <t xml:space="preserve">1.69616067409515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76007401943207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70435476303101</t>
   </si>
   <si>
     <t xml:space="preserve">1.73549211025238</t>
@@ -314,10 +314,10 @@
     <t xml:space="preserve">1.73385322093964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71254873275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63060879707336</t>
+    <t xml:space="preserve">1.71254861354828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63060867786407</t>
   </si>
   <si>
     <t xml:space="preserve">1.67157864570618</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">1.62241458892822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6633847951889</t>
+    <t xml:space="preserve">1.66338467597961</t>
   </si>
   <si>
     <t xml:space="preserve">1.67321753501892</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">1.64535784721375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63880264759064</t>
+    <t xml:space="preserve">1.63880276679993</t>
   </si>
   <si>
     <t xml:space="preserve">1.62569212913513</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">1.66830110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65519082546234</t>
+    <t xml:space="preserve">1.65519070625305</t>
   </si>
   <si>
     <t xml:space="preserve">1.64699673652649</t>
@@ -362,37 +362,37 @@
     <t xml:space="preserve">1.59865200519562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62978935241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58308351039886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59537446498871</t>
+    <t xml:space="preserve">1.6297892332077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58308339118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59537434577942</t>
   </si>
   <si>
     <t xml:space="preserve">1.57898640632629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59127736091614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54047453403473</t>
+    <t xml:space="preserve">1.59127748012543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54047441482544</t>
   </si>
   <si>
     <t xml:space="preserve">1.56751477718353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56997299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56669545173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55850112438202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60274887084961</t>
+    <t xml:space="preserve">1.56997287273407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56669533252716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55850124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6027489900589</t>
   </si>
   <si>
     <t xml:space="preserve">1.60356855392456</t>
@@ -401,28 +401,28 @@
     <t xml:space="preserve">1.6060266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51917016506195</t>
+    <t xml:space="preserve">1.51917004585266</t>
   </si>
   <si>
     <t xml:space="preserve">1.56177890300751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54539084434509</t>
+    <t xml:space="preserve">1.54539096355438</t>
   </si>
   <si>
     <t xml:space="preserve">1.37659418582916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4126478433609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39462113380432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45771503448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47082555294037</t>
+    <t xml:space="preserve">1.41264796257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39462101459503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45771491527557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47082543373108</t>
   </si>
   <si>
     <t xml:space="preserve">1.53391933441162</t>
@@ -434,28 +434,28 @@
     <t xml:space="preserve">1.61176240444183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59783279895782</t>
+    <t xml:space="preserve">1.59783267974854</t>
   </si>
   <si>
     <t xml:space="preserve">1.54211330413818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51179540157318</t>
+    <t xml:space="preserve">1.51179552078247</t>
   </si>
   <si>
     <t xml:space="preserve">1.55522382259369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.565056681633</t>
+    <t xml:space="preserve">1.56505644321442</t>
   </si>
   <si>
     <t xml:space="preserve">1.56423711776733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59291613101959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55686247348785</t>
+    <t xml:space="preserve">1.59291625022888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55686259269714</t>
   </si>
   <si>
     <t xml:space="preserve">1.52162826061249</t>
@@ -464,19 +464,19 @@
     <t xml:space="preserve">1.54129385948181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50442087650299</t>
+    <t xml:space="preserve">1.5044207572937</t>
   </si>
   <si>
     <t xml:space="preserve">1.51097619533539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55112683773041</t>
+    <t xml:space="preserve">1.55112671852112</t>
   </si>
   <si>
     <t xml:space="preserve">1.51589250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55194616317749</t>
+    <t xml:space="preserve">1.55194628238678</t>
   </si>
   <si>
     <t xml:space="preserve">1.50851774215698</t>
@@ -491,28 +491,28 @@
     <t xml:space="preserve">1.50769853591919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50278210639954</t>
+    <t xml:space="preserve">1.50278198719025</t>
   </si>
   <si>
     <t xml:space="preserve">1.49540746212006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51015663146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57325053215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58554136753082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59455490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60684597492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62159514427185</t>
+    <t xml:space="preserve">1.51015675067902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57325065135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58554148674011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59455513954163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60684585571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62159526348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.57161176204681</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">1.58799982070923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53473877906799</t>
+    <t xml:space="preserve">1.5347386598587</t>
   </si>
   <si>
     <t xml:space="preserve">1.58226406574249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54702961444855</t>
+    <t xml:space="preserve">1.54702973365784</t>
   </si>
   <si>
     <t xml:space="preserve">1.53883576393127</t>
@@ -554,43 +554,43 @@
     <t xml:space="preserve">1.55276548862457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54948806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53801643848419</t>
+    <t xml:space="preserve">1.54948794841766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5380163192749</t>
   </si>
   <si>
     <t xml:space="preserve">1.54866850376129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53637766838074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53965520858765</t>
+    <t xml:space="preserve">1.53637742996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53965508937836</t>
   </si>
   <si>
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191316604614</t>
+    <t xml:space="preserve">1.65191304683685</t>
   </si>
   <si>
     <t xml:space="preserve">1.69288313388824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65355181694031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82070970535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82890391349792</t>
+    <t xml:space="preserve">1.65355169773102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82070958614349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82890379428864</t>
   </si>
   <si>
     <t xml:space="preserve">1.81743204593658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81579351425171</t>
+    <t xml:space="preserve">1.815793633461</t>
   </si>
   <si>
     <t xml:space="preserve">1.87970650196075</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">1.79448890686035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80104398727417</t>
+    <t xml:space="preserve">1.80104410648346</t>
   </si>
   <si>
     <t xml:space="preserve">1.73876953125</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">1.81251573562622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86168003082275</t>
+    <t xml:space="preserve">1.86168015003204</t>
   </si>
   <si>
     <t xml:space="preserve">1.86495745182037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840225219727</t>
+    <t xml:space="preserve">1.85840213298798</t>
   </si>
   <si>
     <t xml:space="preserve">1.87642896175385</t>
@@ -644,28 +644,28 @@
     <t xml:space="preserve">1.84856939315796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92479634284973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679392337799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850827217102</t>
+    <t xml:space="preserve">1.92479622364044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679416179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850839138031</t>
   </si>
   <si>
     <t xml:space="preserve">1.97107374668121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92822420597076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94193613529205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94364988803864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95907592773438</t>
+    <t xml:space="preserve">1.92822432518005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94193625450134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94365000724792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95907580852509</t>
   </si>
   <si>
     <t xml:space="preserve">1.96764576435089</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">1.92651033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95393395423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93336606025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90594255924225</t>
+    <t xml:space="preserve">1.95393407344818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93336617946625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90594267845154</t>
   </si>
   <si>
     <t xml:space="preserve">1.8939448595047</t>
@@ -689,16 +689,16 @@
     <t xml:space="preserve">1.8716629743576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9299384355545</t>
+    <t xml:space="preserve">1.92993831634521</t>
   </si>
   <si>
     <t xml:space="preserve">1.90080046653748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91451239585876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88708889484406</t>
+    <t xml:space="preserve">1.91451251506805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">1.87680494785309</t>
@@ -710,31 +710,31 @@
     <t xml:space="preserve">1.8853747844696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86994910240173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88880264759064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90937042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90251469612122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96421778202057</t>
+    <t xml:space="preserve">1.86994886398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88880288600922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90937054157257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90251457691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96421790122986</t>
   </si>
   <si>
     <t xml:space="preserve">1.96250379085541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821365833282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98649954795837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964358329773</t>
+    <t xml:space="preserve">1.98821353912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98649966716766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97964346408844</t>
   </si>
   <si>
     <t xml:space="preserve">2.12533164024353</t>
@@ -743,28 +743,28 @@
     <t xml:space="preserve">2.08591032028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05677247047424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07905459403992</t>
+    <t xml:space="preserve">2.0567729473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07905435562134</t>
   </si>
   <si>
     <t xml:space="preserve">2.0807683467865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06534242630005</t>
+    <t xml:space="preserve">2.06534266471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.06020045280457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07219862937927</t>
+    <t xml:space="preserve">2.07219839096069</t>
   </si>
   <si>
     <t xml:space="preserve">2.13390159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10819220542908</t>
+    <t xml:space="preserve">2.10819172859192</t>
   </si>
   <si>
     <t xml:space="preserve">2.09962201118469</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">2.10304975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03963303565979</t>
+    <t xml:space="preserve">2.03963279724121</t>
   </si>
   <si>
     <t xml:space="preserve">2.06877040863037</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">2.09790778160095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1167619228363</t>
+    <t xml:space="preserve">2.11676168441772</t>
   </si>
   <si>
     <t xml:space="preserve">2.08248209953308</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">2.06705665588379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12190365791321</t>
+    <t xml:space="preserve">2.12190389633179</t>
   </si>
   <si>
     <t xml:space="preserve">2.10647797584534</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">2.17675089836121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14247131347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1321873664856</t>
+    <t xml:space="preserve">2.14247155189514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13218760490417</t>
   </si>
   <si>
     <t xml:space="preserve">2.13047361373901</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">2.11847543716431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09105181694031</t>
+    <t xml:space="preserve">2.09105205535889</t>
   </si>
   <si>
     <t xml:space="preserve">2.12361764907837</t>
@@ -836,43 +836,43 @@
     <t xml:space="preserve">2.11161994934082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10133576393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15789699554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15618348121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14418530464172</t>
+    <t xml:space="preserve">2.10133600234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15789723396301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15618324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1441855430603</t>
   </si>
   <si>
     <t xml:space="preserve">2.1407573223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14932727813721</t>
+    <t xml:space="preserve">2.14932703971863</t>
   </si>
   <si>
     <t xml:space="preserve">2.13904333114624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17503690719604</t>
+    <t xml:space="preserve">2.17503714561462</t>
   </si>
   <si>
     <t xml:space="preserve">2.15104126930237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12018990516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1047637462616</t>
+    <t xml:space="preserve">2.12018966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10476398468018</t>
   </si>
   <si>
     <t xml:space="preserve">2.06362843513489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03277707099915</t>
+    <t xml:space="preserve">2.03277683258057</t>
   </si>
   <si>
     <t xml:space="preserve">2.04820275306702</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">2.0499165058136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12875962257385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08762431144714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02077889442444</t>
+    <t xml:space="preserve">2.12875938415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08762407302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02077913284302</t>
   </si>
   <si>
     <t xml:space="preserve">2.08419609069824</t>
@@ -917,13 +917,13 @@
     <t xml:space="preserve">2.33100891113281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32243895530701</t>
+    <t xml:space="preserve">2.32243919372559</t>
   </si>
   <si>
     <t xml:space="preserve">2.35671830177307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44241738319397</t>
+    <t xml:space="preserve">2.44241714477539</t>
   </si>
   <si>
     <t xml:space="preserve">2.49383664131165</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">2.47669696807861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48526668548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53668618202209</t>
+    <t xml:space="preserve">2.48526692390442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53668642044067</t>
   </si>
   <si>
     <t xml:space="preserve">2.57953572273254</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">2.59667539596558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61381483078003</t>
+    <t xml:space="preserve">2.61381506919861</t>
   </si>
   <si>
     <t xml:space="preserve">2.55382585525513</t>
@@ -968,13 +968,13 @@
     <t xml:space="preserve">2.52694344520569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43733549118042</t>
+    <t xml:space="preserve">2.437335729599</t>
   </si>
   <si>
     <t xml:space="preserve">2.46421790122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50006103515625</t>
+    <t xml:space="preserve">2.50006127357483</t>
   </si>
   <si>
     <t xml:space="preserve">2.45525717735291</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">2.51798272132874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56278657913208</t>
+    <t xml:space="preserve">2.56278681755066</t>
   </si>
   <si>
     <t xml:space="preserve">2.53590416908264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4911003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48213982582092</t>
+    <t xml:space="preserve">2.49110054969788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48213958740234</t>
   </si>
   <si>
     <t xml:space="preserve">2.50902199745178</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">2.78680658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75992441177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77784562110901</t>
+    <t xml:space="preserve">2.7599241733551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77784585952759</t>
   </si>
   <si>
     <t xml:space="preserve">2.74200248718262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76888489723206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71512007713318</t>
+    <t xml:space="preserve">2.76888513565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71512031555176</t>
   </si>
   <si>
     <t xml:space="preserve">2.75096321105957</t>
@@ -1055,13 +1055,13 @@
     <t xml:space="preserve">2.86745381355286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83161044120789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6434338092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62551236152649</t>
+    <t xml:space="preserve">2.83161067962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64343404769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62551259994507</t>
   </si>
   <si>
     <t xml:space="preserve">2.58070850372314</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">2.607590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41941428184509</t>
+    <t xml:space="preserve">2.41941404342651</t>
   </si>
   <si>
     <t xml:space="preserve">2.66135549545288</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">2.81368899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84057140350342</t>
+    <t xml:space="preserve">2.840571641922</t>
   </si>
   <si>
     <t xml:space="preserve">2.93914008140564</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">2.80472826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90329670906067</t>
+    <t xml:space="preserve">2.90329694747925</t>
   </si>
   <si>
     <t xml:space="preserve">3.12731671333313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16315984725952</t>
+    <t xml:space="preserve">3.16315960884094</t>
   </si>
   <si>
     <t xml:space="preserve">3.13627743721008</t>
@@ -1118,19 +1118,19 @@
     <t xml:space="preserve">3.28861093521118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29757189750671</t>
+    <t xml:space="preserve">3.29757165908813</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33341503143311</t>
+    <t xml:space="preserve">3.33341479301453</t>
   </si>
   <si>
     <t xml:space="preserve">3.34237575531006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42302298545837</t>
+    <t xml:space="preserve">3.42302274703979</t>
   </si>
   <si>
     <t xml:space="preserve">3.3871796131134</t>
@@ -1148,10 +1148,10 @@
     <t xml:space="preserve">3.37821888923645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45886564254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48574876785278</t>
+    <t xml:space="preserve">3.45886588096619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4857485294342</t>
   </si>
   <si>
     <t xml:space="preserve">3.47678756713867</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">3.67392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58431696891785</t>
+    <t xml:space="preserve">3.58431720733643</t>
   </si>
   <si>
     <t xml:space="preserve">3.53055238723755</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">3.55743479728699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52159142494202</t>
+    <t xml:space="preserve">3.5215916633606</t>
   </si>
   <si>
     <t xml:space="preserve">3.51263093948364</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">3.80833721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79041504859924</t>
+    <t xml:space="preserve">3.79041528701782</t>
   </si>
   <si>
     <t xml:space="preserve">3.95170950889587</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">3.97005581855774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00759792327881</t>
+    <t xml:space="preserve">4.00759744644165</t>
   </si>
   <si>
     <t xml:space="preserve">4.0920672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81988835334778</t>
+    <t xml:space="preserve">3.81988859176636</t>
   </si>
   <si>
     <t xml:space="preserve">3.87620115280151</t>
@@ -1259,40 +1259,40 @@
     <t xml:space="preserve">4.03575468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99821257591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97944092750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85743021965027</t>
+    <t xml:space="preserve">3.9982123374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97944116592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85743045806885</t>
   </si>
   <si>
     <t xml:space="preserve">3.84804463386536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81050252914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7448046207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89497232437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94189953804016</t>
+    <t xml:space="preserve">3.81050276756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74480438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89497208595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.941899061203</t>
   </si>
   <si>
     <t xml:space="preserve">3.8668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93251395225525</t>
+    <t xml:space="preserve">3.93251419067383</t>
   </si>
   <si>
     <t xml:space="preserve">4.08268165588379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11083793640137</t>
+    <t xml:space="preserve">4.11083841323853</t>
   </si>
   <si>
     <t xml:space="preserve">4.12022304534912</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">4.18592166900635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19530725479126</t>
+    <t xml:space="preserve">4.1953067779541</t>
   </si>
   <si>
     <t xml:space="preserve">4.20469284057617</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">4.28916215896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26100587844849</t>
+    <t xml:space="preserve">4.26100540161133</t>
   </si>
   <si>
     <t xml:space="preserve">4.2703914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34547472000122</t>
+    <t xml:space="preserve">4.34547519683838</t>
   </si>
   <si>
     <t xml:space="preserve">4.36424589157104</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">4.50502824783325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49564266204834</t>
+    <t xml:space="preserve">4.49564218521118</t>
   </si>
   <si>
     <t xml:space="preserve">4.43932962417603</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">4.5519552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54257011413574</t>
+    <t xml:space="preserve">4.54256963729858</t>
   </si>
   <si>
     <t xml:space="preserve">4.48625707626343</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">4.40178775787354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44871520996094</t>
+    <t xml:space="preserve">4.44871473312378</t>
   </si>
   <si>
     <t xml:space="preserve">4.42994403839111</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">4.41117334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39240169525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24223470687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30793333053589</t>
+    <t xml:space="preserve">4.39240217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2422342300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30793285369873</t>
   </si>
   <si>
     <t xml:space="preserve">4.17653608322144</t>
@@ -1394,28 +1394,28 @@
     <t xml:space="preserve">4.62703895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61765336990356</t>
+    <t xml:space="preserve">4.61765384674072</t>
   </si>
   <si>
     <t xml:space="preserve">4.51441335678101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57072591781616</t>
+    <t xml:space="preserve">4.57072639465332</t>
   </si>
   <si>
     <t xml:space="preserve">4.67396640777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80536270141602</t>
+    <t xml:space="preserve">4.80536317825317</t>
   </si>
   <si>
     <t xml:space="preserve">4.78659200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86167621612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84290504455566</t>
+    <t xml:space="preserve">4.86167573928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84290456771851</t>
   </si>
   <si>
     <t xml:space="preserve">4.89921760559082</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">4.5988826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53318405151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58011150360107</t>
+    <t xml:space="preserve">4.53318452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58011198043823</t>
   </si>
   <si>
     <t xml:space="preserve">4.6927375793457</t>
@@ -1439,16 +1439,16 @@
     <t xml:space="preserve">4.74905014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73027944564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71150827407837</t>
+    <t xml:space="preserve">4.73027896881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71150875091553</t>
   </si>
   <si>
     <t xml:space="preserve">4.76782131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95553112030029</t>
+    <t xml:space="preserve">4.95553064346313</t>
   </si>
   <si>
     <t xml:space="preserve">4.88044691085815</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">4.91798877716064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99307250976562</t>
+    <t xml:space="preserve">4.99307298660278</t>
   </si>
   <si>
     <t xml:space="preserve">4.93675994873047</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">6.60737419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28826808929443</t>
+    <t xml:space="preserve">6.28826761245728</t>
   </si>
   <si>
     <t xml:space="preserve">6.1568717956543</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">5.96916246414185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70636892318726</t>
+    <t xml:space="preserve">5.7063684463501</t>
   </si>
   <si>
     <t xml:space="preserve">5.53743028640747</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">5.87530755996704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66882658004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68759727478027</t>
+    <t xml:space="preserve">5.66882705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68759775161743</t>
   </si>
   <si>
     <t xml:space="preserve">5.83776521682739</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59374284744263</t>
+    <t xml:space="preserve">5.59374332427979</t>
   </si>
   <si>
     <t xml:space="preserve">5.38726234436035</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">5.10569858551025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68335199356079</t>
+    <t xml:space="preserve">4.68335151672363</t>
   </si>
   <si>
     <t xml:space="preserve">4.14837980270386</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">3.62279319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55709481239319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37877082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50078225135803</t>
+    <t xml:space="preserve">3.55709505081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37877106666565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50078201293945</t>
   </si>
   <si>
     <t xml:space="preserve">3.5664803981781</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">3.75418996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70726251602173</t>
+    <t xml:space="preserve">3.70726275444031</t>
   </si>
   <si>
     <t xml:space="preserve">3.71664810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8386595249176</t>
+    <t xml:space="preserve">3.83865928649902</t>
   </si>
   <si>
     <t xml:space="preserve">4.25162029266357</t>
@@ -1580,25 +1580,25 @@
     <t xml:space="preserve">4.12960910797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16715049743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05452537536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76357555389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66972064971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65094995498657</t>
+    <t xml:space="preserve">4.16715097427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05452489852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76357579231262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66972088813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65094971656799</t>
   </si>
   <si>
     <t xml:space="preserve">3.66033530235291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95128512382507</t>
+    <t xml:space="preserve">3.95128488540649</t>
   </si>
   <si>
     <t xml:space="preserve">4.29854726791382</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">4.31731843948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15776491165161</t>
+    <t xml:space="preserve">4.15776538848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.10145235061646</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">4.13899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88558626174927</t>
+    <t xml:space="preserve">3.88558650016785</t>
   </si>
   <si>
     <t xml:space="preserve">4.32670402526855</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">4.27977657318115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.913743019104</t>
+    <t xml:space="preserve">3.91374325752258</t>
   </si>
   <si>
     <t xml:space="preserve">3.92312836647034</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">3.49139666557312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67910623550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38815641403198</t>
+    <t xml:space="preserve">3.67910599708557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3881561756134</t>
   </si>
   <si>
     <t xml:space="preserve">3.35999989509583</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">3.34122896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20044708251953</t>
+    <t xml:space="preserve">3.20044684410095</t>
   </si>
   <si>
     <t xml:space="preserve">3.24737429618835</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">3.47262573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57586574554443</t>
+    <t xml:space="preserve">3.57586598396301</t>
   </si>
   <si>
     <t xml:space="preserve">3.73541903495789</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">3.68849158287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72603368759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52893853187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63217878341675</t>
+    <t xml:space="preserve">3.72603344917297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52893877029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63217854499817</t>
   </si>
   <si>
     <t xml:space="preserve">3.51016759872437</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">3.58525133132935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53832411766052</t>
+    <t xml:space="preserve">3.53832387924194</t>
   </si>
   <si>
     <t xml:space="preserve">3.80111742019653</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">3.48201107978821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46324014663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4444694519043</t>
+    <t xml:space="preserve">3.46324038505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44446921348572</t>
   </si>
   <si>
     <t xml:space="preserve">3.42569851875305</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">3.41631293296814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754199981689</t>
+    <t xml:space="preserve">3.39754176139832</t>
   </si>
   <si>
     <t xml:space="preserve">3.21921801567078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1910617351532</t>
+    <t xml:space="preserve">3.19106149673462</t>
   </si>
   <si>
     <t xml:space="preserve">3.17229056358337</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">3.23798894882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14413404464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25675964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36938524246216</t>
+    <t xml:space="preserve">3.14413380622864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25675988197327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36938548088074</t>
   </si>
   <si>
     <t xml:space="preserve">3.15351939201355</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">3.18167614936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29430174827576</t>
+    <t xml:space="preserve">3.29430150985718</t>
   </si>
   <si>
     <t xml:space="preserve">3.2661452293396</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">3.12536311149597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04089379310608</t>
+    <t xml:space="preserve">3.04089403152466</t>
   </si>
   <si>
     <t xml:space="preserve">3.05027914047241</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">2.93765377998352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95642447471619</t>
+    <t xml:space="preserve">2.95642471313477</t>
   </si>
   <si>
     <t xml:space="preserve">3.03150844573975</t>
@@ -1805,19 +1805,19 @@
     <t xml:space="preserve">3.02212285995483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92826795578003</t>
+    <t xml:space="preserve">2.92826819419861</t>
   </si>
   <si>
     <t xml:space="preserve">2.94703912734985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90011167526245</t>
+    <t xml:space="preserve">2.90011143684387</t>
   </si>
   <si>
     <t xml:space="preserve">2.97519564628601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27553057670593</t>
+    <t xml:space="preserve">3.27553081512451</t>
   </si>
   <si>
     <t xml:space="preserve">3.33184361457825</t>
@@ -2358,6 +2358,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.5900000333786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52999997138977</t>
   </si>
 </sst>
 </file>
@@ -67358,7 +67361,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.5950925926</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>8705</v>
@@ -67379,6 +67382,32 @@
         <v>781</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6500115741</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>9792</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>782</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="786">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8582592010498</t>
+    <t xml:space="preserve">1.85825943946838</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9132376909256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109155654907</t>
+    <t xml:space="preserve">1.91323745250702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109167575836</t>
   </si>
   <si>
     <t xml:space="preserve">1.88496327400208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92423331737518</t>
+    <t xml:space="preserve">1.92423319816589</t>
   </si>
   <si>
     <t xml:space="preserve">1.80642282962799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82998478412628</t>
+    <t xml:space="preserve">1.82998490333557</t>
   </si>
   <si>
     <t xml:space="preserve">1.79856884479523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76715278625488</t>
+    <t xml:space="preserve">1.76715314388275</t>
   </si>
   <si>
     <t xml:space="preserve">1.85354709625244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86925506591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87710928916931</t>
+    <t xml:space="preserve">1.86925518512726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87710905075073</t>
   </si>
   <si>
     <t xml:space="preserve">1.89281725883484</t>
@@ -86,97 +86,97 @@
     <t xml:space="preserve">1.81584787368774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83783912658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8755384683609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684350013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84569275379181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898939609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83626842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85983049869537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80485212802887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82056021690369</t>
+    <t xml:space="preserve">1.83783876895905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553822994232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684338092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84569299221039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81898927688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8362683057785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85983037948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80485224723816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82056033611298</t>
   </si>
   <si>
     <t xml:space="preserve">1.81741857528687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85040545463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88025045394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81427705287933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85197651386261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84412217140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84098064899445</t>
+    <t xml:space="preserve">1.85040533542633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88025081157684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81427681446075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85197627544403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84412229061127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84098052978516</t>
   </si>
   <si>
     <t xml:space="preserve">1.82370173931122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8111355304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82213079929352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679964542389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622433185577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407843589783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96350312232971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96507394313812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9933488368988</t>
+    <t xml:space="preserve">1.81113541126251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8221310377121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9367995262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622421264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407819747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.963503241539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96507441997528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99334847927094</t>
   </si>
   <si>
     <t xml:space="preserve">2.00434422492981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.987065076828</t>
+    <t xml:space="preserve">1.98706519603729</t>
   </si>
   <si>
     <t xml:space="preserve">2.00905656814575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0247642993927</t>
+    <t xml:space="preserve">2.02476453781128</t>
   </si>
   <si>
     <t xml:space="preserve">1.93051624298096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9619323015213</t>
+    <t xml:space="preserve">1.96193242073059</t>
   </si>
   <si>
     <t xml:space="preserve">1.93994116783142</t>
@@ -188,88 +188,88 @@
     <t xml:space="preserve">1.91637921333313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8739675283432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378698825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017540454865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92231559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050932884216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95836925506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739904880524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542587757111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9419811964035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91248285770416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91084396839142</t>
+    <t xml:space="preserve">1.87396740913391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378722667694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017528533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92231547832489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050944805145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656346321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509159564972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95836913585663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739892959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9354259967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198107719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91248297691345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91084384918213</t>
   </si>
   <si>
     <t xml:space="preserve">1.83545899391174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80268287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84201407432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83218145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88298428058624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86823499202728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90756630897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281702041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592741966248</t>
+    <t xml:space="preserve">1.8026829957962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84201419353485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83218133449554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88298439979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86823511123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90756618976593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281690120697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90592753887177</t>
   </si>
   <si>
     <t xml:space="preserve">1.88462293148041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90920495986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87151265144348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89773368835449</t>
+    <t xml:space="preserve">1.90920507907867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87151253223419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89773344993591</t>
   </si>
   <si>
     <t xml:space="preserve">1.82398736476898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75843513011932</t>
+    <t xml:space="preserve">1.75843501091003</t>
   </si>
   <si>
     <t xml:space="preserve">1.76662921905518</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">1.78629505634308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77646207809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75188016891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75351881980896</t>
+    <t xml:space="preserve">1.77646195888519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75188004970551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75351905822754</t>
   </si>
   <si>
     <t xml:space="preserve">1.77973961830139</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">1.75024127960205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72074258327484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6699401140213</t>
+    <t xml:space="preserve">1.72074270248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66993999481201</t>
   </si>
   <si>
     <t xml:space="preserve">1.72893679141998</t>
@@ -305,19 +305,19 @@
     <t xml:space="preserve">1.69616067409515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76007401943207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70435464382172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73549211025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73385322093964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71254885196686</t>
+    <t xml:space="preserve">1.76007413864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70435476303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73549199104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73385310173035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71254873275757</t>
   </si>
   <si>
     <t xml:space="preserve">1.63060867786407</t>
@@ -326,22 +326,22 @@
     <t xml:space="preserve">1.67157876491547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66666233539581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61012363433838</t>
+    <t xml:space="preserve">1.66666221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61012351512909</t>
   </si>
   <si>
     <t xml:space="preserve">1.62241470813751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66338455677032</t>
+    <t xml:space="preserve">1.66338467597961</t>
   </si>
   <si>
     <t xml:space="preserve">1.67321753501892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64535796642303</t>
+    <t xml:space="preserve">1.64535784721375</t>
   </si>
   <si>
     <t xml:space="preserve">1.63880264759064</t>
@@ -353,34 +353,34 @@
     <t xml:space="preserve">1.66830122470856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65519070625305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64699673652649</t>
+    <t xml:space="preserve">1.65519082546234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6469966173172</t>
   </si>
   <si>
     <t xml:space="preserve">1.63798320293427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59865188598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62978911399841</t>
+    <t xml:space="preserve">1.59865212440491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6297892332077</t>
   </si>
   <si>
     <t xml:space="preserve">1.58308351039886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59537446498871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57898640632629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59127748012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54047453403473</t>
+    <t xml:space="preserve">1.595374584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.578986287117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59127736091614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54047465324402</t>
   </si>
   <si>
     <t xml:space="preserve">1.56751477718353</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">1.56669533252716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55850124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6027489900589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60356843471527</t>
+    <t xml:space="preserve">1.5585013628006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60274910926819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60356831550598</t>
   </si>
   <si>
     <t xml:space="preserve">1.6060266494751</t>
@@ -407,16 +407,16 @@
     <t xml:space="preserve">1.51917004585266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56177890300751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54539108276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37659418582916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41264796257019</t>
+    <t xml:space="preserve">1.5617790222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54539096355438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37659406661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4126478433609</t>
   </si>
   <si>
     <t xml:space="preserve">1.39462113380432</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">1.45771503448486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47082531452179</t>
+    <t xml:space="preserve">1.47082543373108</t>
   </si>
   <si>
     <t xml:space="preserve">1.53391933441162</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">1.61258184909821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61176240444183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59783256053925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54211330413818</t>
+    <t xml:space="preserve">1.61176252365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59783267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54211318492889</t>
   </si>
   <si>
     <t xml:space="preserve">1.51179552078247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55522382259369</t>
+    <t xml:space="preserve">1.5552237033844</t>
   </si>
   <si>
     <t xml:space="preserve">1.56505644321442</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">1.56423723697662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59291636943817</t>
+    <t xml:space="preserve">1.59291625022888</t>
   </si>
   <si>
     <t xml:space="preserve">1.55686259269714</t>
@@ -464,55 +464,55 @@
     <t xml:space="preserve">1.52162837982178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5412939786911</t>
+    <t xml:space="preserve">1.54129385948181</t>
   </si>
   <si>
     <t xml:space="preserve">1.50442087650299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51097619533539</t>
+    <t xml:space="preserve">1.5109760761261</t>
   </si>
   <si>
     <t xml:space="preserve">1.55112671852112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51589238643646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55194628238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50851774215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53228068351746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50933742523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5076984167099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50278210639954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49540734291077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51015675067902</t>
+    <t xml:space="preserve">1.51589250564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55194616317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50851786136627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53228056430817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50933730602264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50769853591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50278198719025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49540758132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51015663146973</t>
   </si>
   <si>
     <t xml:space="preserve">1.57325053215027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58554136753082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59455502033234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60684597492218</t>
+    <t xml:space="preserve">1.58554148674011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59455490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60684585571289</t>
   </si>
   <si>
     <t xml:space="preserve">1.62159538269043</t>
@@ -521,19 +521,19 @@
     <t xml:space="preserve">1.57161176204681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54375219345093</t>
+    <t xml:space="preserve">1.54375207424164</t>
   </si>
   <si>
     <t xml:space="preserve">1.57243120670319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58718025684357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54621016979218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55768203735352</t>
+    <t xml:space="preserve">1.58718049526215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54621040821075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55768191814423</t>
   </si>
   <si>
     <t xml:space="preserve">1.58799982070923</t>
@@ -542,22 +542,22 @@
     <t xml:space="preserve">1.5347386598587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58226406574249</t>
+    <t xml:space="preserve">1.5822639465332</t>
   </si>
   <si>
     <t xml:space="preserve">1.54702973365784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53883564472198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54784905910492</t>
+    <t xml:space="preserve">1.53883576393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54784917831421</t>
   </si>
   <si>
     <t xml:space="preserve">1.55276548862457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54948782920837</t>
+    <t xml:space="preserve">1.54948806762695</t>
   </si>
   <si>
     <t xml:space="preserve">1.53801620006561</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">1.54866850376129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53637742996216</t>
+    <t xml:space="preserve">1.53637754917145</t>
   </si>
   <si>
     <t xml:space="preserve">1.53965508937836</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191304683685</t>
+    <t xml:space="preserve">1.65191316604614</t>
   </si>
   <si>
     <t xml:space="preserve">1.69288313388824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65355169773102</t>
+    <t xml:space="preserve">1.65355181694031</t>
   </si>
   <si>
     <t xml:space="preserve">1.82070958614349</t>
@@ -590,40 +590,40 @@
     <t xml:space="preserve">1.82890391349792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81743216514587</t>
+    <t xml:space="preserve">1.81743204593658</t>
   </si>
   <si>
     <t xml:space="preserve">1.81579351425171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87970650196075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79448890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80104398727417</t>
+    <t xml:space="preserve">1.87970638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79448914527893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80104422569275</t>
   </si>
   <si>
     <t xml:space="preserve">1.73876953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729814052582</t>
+    <t xml:space="preserve">1.72729802131653</t>
   </si>
   <si>
     <t xml:space="preserve">1.74696373939514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76335155963898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84693038463593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81087708473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8092383146286</t>
+    <t xml:space="preserve">1.76335167884827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84693050384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81087684631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923807621002</t>
   </si>
   <si>
     <t xml:space="preserve">1.81251573562622</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">1.86495745182037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840213298798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87642908096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89937257766724</t>
+    <t xml:space="preserve">1.85840201377869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87642896175385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89937245845795</t>
   </si>
   <si>
     <t xml:space="preserve">1.84856951236725</t>
@@ -650,22 +650,22 @@
     <t xml:space="preserve">1.92479622364044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93679404258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850827217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97107374668121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822420597076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94193625450134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94365012645721</t>
+    <t xml:space="preserve">1.93679392337799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850815296173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107362747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822456359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94193637371063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94364988803864</t>
   </si>
   <si>
     <t xml:space="preserve">1.95907580852509</t>
@@ -674,49 +674,49 @@
     <t xml:space="preserve">1.96764576435089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92651033401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95393407344818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93336617946625</t>
+    <t xml:space="preserve">1.9265102148056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95393395423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93336629867554</t>
   </si>
   <si>
     <t xml:space="preserve">1.90594255924225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8939448595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8716629743576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92993855476379</t>
+    <t xml:space="preserve">1.89394462108612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87166309356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92993807792664</t>
   </si>
   <si>
     <t xml:space="preserve">1.90080046653748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91451239585876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88708889484406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87680494785309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91794049739838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8853747844696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86994898319244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88880276679993</t>
+    <t xml:space="preserve">1.91451263427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88708865642548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87680518627167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9179402589798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88537490367889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86994910240173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88880288600922</t>
   </si>
   <si>
     <t xml:space="preserve">1.90937054157257</t>
@@ -725,22 +725,22 @@
     <t xml:space="preserve">1.90251469612122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96421790122986</t>
+    <t xml:space="preserve">1.96421778202057</t>
   </si>
   <si>
     <t xml:space="preserve">1.96250379085541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821353912354</t>
+    <t xml:space="preserve">1.98821341991425</t>
   </si>
   <si>
     <t xml:space="preserve">1.98649966716766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97964370250702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12533164024353</t>
+    <t xml:space="preserve">1.97964346408844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12533140182495</t>
   </si>
   <si>
     <t xml:space="preserve">2.08591032028198</t>
@@ -749,31 +749,31 @@
     <t xml:space="preserve">2.05677270889282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07905435562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0807683467865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06534242630005</t>
+    <t xml:space="preserve">2.07905459403992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08076810836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06534266471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.06020045280457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07219839096069</t>
+    <t xml:space="preserve">2.07219862937927</t>
   </si>
   <si>
     <t xml:space="preserve">2.13390159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1081919670105</t>
+    <t xml:space="preserve">2.10819220542908</t>
   </si>
   <si>
     <t xml:space="preserve">2.09962201118469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10304999351501</t>
+    <t xml:space="preserve">2.10304975509644</t>
   </si>
   <si>
     <t xml:space="preserve">2.03963279724121</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">2.06877040863037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11504769325256</t>
+    <t xml:space="preserve">2.11504793167114</t>
   </si>
   <si>
     <t xml:space="preserve">2.07391238212585</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">2.09790802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1167619228363</t>
+    <t xml:space="preserve">2.11676168441772</t>
   </si>
   <si>
     <t xml:space="preserve">2.08248209953308</t>
@@ -800,19 +800,19 @@
     <t xml:space="preserve">2.06705641746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12190365791321</t>
+    <t xml:space="preserve">2.12190389633179</t>
   </si>
   <si>
     <t xml:space="preserve">2.10647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0893383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05163049697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17675089836121</t>
+    <t xml:space="preserve">2.08933806419373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05163073539734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17675113677979</t>
   </si>
   <si>
     <t xml:space="preserve">2.14247155189514</t>
@@ -821,19 +821,19 @@
     <t xml:space="preserve">2.1321873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13047385215759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15961122512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11847543716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09105181694031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12361764907837</t>
+    <t xml:space="preserve">2.13047361373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15961098670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11847567558289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09105229377747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12361741065979</t>
   </si>
   <si>
     <t xml:space="preserve">2.11161994934082</t>
@@ -854,40 +854,40 @@
     <t xml:space="preserve">2.1407573223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14932703971863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13904356956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17503690719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15104126930237</t>
+    <t xml:space="preserve">2.14932751655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13904333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17503714561462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15104150772095</t>
   </si>
   <si>
     <t xml:space="preserve">2.12018966674805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1047637462616</t>
+    <t xml:space="preserve">2.10476398468018</t>
   </si>
   <si>
     <t xml:space="preserve">2.06362843513489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03277707099915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0482029914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07048416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0499165058136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12875962257385</t>
+    <t xml:space="preserve">2.03277683258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04820275306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07048439979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04991674423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12875986099243</t>
   </si>
   <si>
     <t xml:space="preserve">2.08762431144714</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.0224928855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01392292976379</t>
+    <t xml:space="preserve">2.01392316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.00535321235657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16818118095398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18532085418701</t>
+    <t xml:space="preserve">2.1681809425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18532061576843</t>
   </si>
   <si>
     <t xml:space="preserve">2.29672932624817</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">2.32243895530701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35671830177307</t>
+    <t xml:space="preserve">2.35671854019165</t>
   </si>
   <si>
     <t xml:space="preserve">2.44241738319397</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">2.49383664131165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46812725067139</t>
+    <t xml:space="preserve">2.46812701225281</t>
   </si>
   <si>
     <t xml:space="preserve">2.47669696807861</t>
@@ -941,34 +941,37 @@
     <t xml:space="preserve">2.48526692390442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53668642044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57953572273254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.596675157547</t>
+    <t xml:space="preserve">2.53668594360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57953548431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59667539596558</t>
   </si>
   <si>
     <t xml:space="preserve">2.61381506919861</t>
   </si>
   <si>
+    <t xml:space="preserve">2.55382609367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63447308540344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59862995147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5896692276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61655163764954</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.55382585525513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63447332382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59862995147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5896692276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61655139923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52694344520569</t>
+    <t xml:space="preserve">2.52694368362427</t>
   </si>
   <si>
     <t xml:space="preserve">2.437335729599</t>
@@ -977,16 +980,16 @@
     <t xml:space="preserve">2.46421790122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50006127357483</t>
+    <t xml:space="preserve">2.50006103515625</t>
   </si>
   <si>
     <t xml:space="preserve">2.45525717735291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54486513137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57174754142761</t>
+    <t xml:space="preserve">2.54486489295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57174730300903</t>
   </si>
   <si>
     <t xml:space="preserve">2.51798272132874</t>
@@ -998,7 +1001,7 @@
     <t xml:space="preserve">2.53590416908264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49110054969788</t>
+    <t xml:space="preserve">2.4911003112793</t>
   </si>
   <si>
     <t xml:space="preserve">2.48213958740234</t>
@@ -1016,37 +1019,37 @@
     <t xml:space="preserve">2.7599241733551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77784585952759</t>
+    <t xml:space="preserve">2.77784562110901</t>
   </si>
   <si>
     <t xml:space="preserve">2.74200248718262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76888513565063</t>
+    <t xml:space="preserve">2.76888465881348</t>
   </si>
   <si>
     <t xml:space="preserve">2.71512031555176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75096321105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67031621932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72408103942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65239477157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68823790550232</t>
+    <t xml:space="preserve">2.75096344947815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67031645774841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72408080101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65239453315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68823766708374</t>
   </si>
   <si>
     <t xml:space="preserve">2.73304176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69719886779785</t>
+    <t xml:space="preserve">2.69719862937927</t>
   </si>
   <si>
     <t xml:space="preserve">2.67927694320679</t>
@@ -1055,25 +1058,25 @@
     <t xml:space="preserve">2.84953236579895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86745381355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83161067962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64343404769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62551259994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58070850372314</t>
+    <t xml:space="preserve">2.86745357513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83161044120789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6434338092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62551236152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58070826530457</t>
   </si>
   <si>
     <t xml:space="preserve">2.607590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41941404342651</t>
+    <t xml:space="preserve">2.41941428184509</t>
   </si>
   <si>
     <t xml:space="preserve">2.66135549545288</t>
@@ -1082,7 +1085,7 @@
     <t xml:space="preserve">2.81368899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.840571641922</t>
+    <t xml:space="preserve">2.84057140350342</t>
   </si>
   <si>
     <t xml:space="preserve">2.93914008140564</t>
@@ -1091,7 +1094,7 @@
     <t xml:space="preserve">2.87641453742981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82264971733093</t>
+    <t xml:space="preserve">2.82264995574951</t>
   </si>
   <si>
     <t xml:space="preserve">2.80472826957703</t>
@@ -1103,34 +1106,34 @@
     <t xml:space="preserve">3.12731671333313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16315960884094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13627743721008</t>
+    <t xml:space="preserve">3.16315984725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13627767562866</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004225730896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25276780128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26172852516174</t>
+    <t xml:space="preserve">3.25276803970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26172876358032</t>
   </si>
   <si>
     <t xml:space="preserve">3.28861093521118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29757165908813</t>
+    <t xml:space="preserve">3.29757189750671</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33341479301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34237575531006</t>
+    <t xml:space="preserve">3.33341503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34237551689148</t>
   </si>
   <si>
     <t xml:space="preserve">3.42302274703979</t>
@@ -1145,19 +1148,19 @@
     <t xml:space="preserve">3.41406202316284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36925792694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37821888923645</t>
+    <t xml:space="preserve">3.36925840377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37821865081787</t>
   </si>
   <si>
     <t xml:space="preserve">3.45886588096619</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4857485294342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47678756713867</t>
+    <t xml:space="preserve">3.48574829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47678780555725</t>
   </si>
   <si>
     <t xml:space="preserve">3.49470925331116</t>
@@ -1175,16 +1178,16 @@
     <t xml:space="preserve">3.59327816963196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55743479728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5215916633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51263093948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5395131111145</t>
+    <t xml:space="preserve">3.55743455886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52159142494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51263070106506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53951334953308</t>
   </si>
   <si>
     <t xml:space="preserve">3.60223865509033</t>
@@ -1193,13 +1196,13 @@
     <t xml:space="preserve">3.65600347518921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66496443748474</t>
+    <t xml:space="preserve">3.66496419906616</t>
   </si>
   <si>
     <t xml:space="preserve">3.72768974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71872925758362</t>
+    <t xml:space="preserve">3.71872901916504</t>
   </si>
   <si>
     <t xml:space="preserve">3.6918466091156</t>
@@ -1208,7 +1211,7 @@
     <t xml:space="preserve">3.70976805686951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68288588523865</t>
+    <t xml:space="preserve">3.68288612365723</t>
   </si>
   <si>
     <t xml:space="preserve">3.7635326385498</t>
@@ -1217,7 +1220,7 @@
     <t xml:space="preserve">3.78145432472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80833721160889</t>
+    <t xml:space="preserve">3.80833697319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.79041528701782</t>
@@ -1226,7 +1229,7 @@
     <t xml:space="preserve">3.95170950889587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96067070960999</t>
+    <t xml:space="preserve">3.96067023277283</t>
   </si>
   <si>
     <t xml:space="preserve">3.97005581855774</t>
@@ -1244,9 +1247,6 @@
     <t xml:space="preserve">3.87620115280151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96067023277283</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.02636861801147</t>
   </si>
   <si>
@@ -2367,6 +2367,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.54999995231628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50999999046326</t>
   </si>
 </sst>
 </file>
@@ -18609,7 +18612,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18635,7 +18638,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G613" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18661,7 +18664,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G614" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18687,7 +18690,7 @@
         <v>2.75</v>
       </c>
       <c r="G615" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18713,7 +18716,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G616" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18739,7 +18742,7 @@
         <v>2.75</v>
       </c>
       <c r="G617" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18765,7 +18768,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G618" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18791,7 +18794,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G619" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18817,7 +18820,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G620" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18843,7 +18846,7 @@
         <v>2.75</v>
       </c>
       <c r="G621" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18869,7 +18872,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G622" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18895,7 +18898,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18921,7 +18924,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18947,7 +18950,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -18973,7 +18976,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -18999,7 +19002,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G627" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19025,7 +19028,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G628" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19051,7 +19054,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G629" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19077,7 +19080,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G630" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19103,7 +19106,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19129,7 +19132,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G632" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19155,7 +19158,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19181,7 +19184,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G634" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19207,7 +19210,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G635" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19233,7 +19236,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G636" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19259,7 +19262,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19285,7 +19288,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19311,7 +19314,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19337,7 +19340,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19363,7 +19366,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19389,7 +19392,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19415,7 +19418,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19441,7 +19444,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19467,7 +19470,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19493,7 +19496,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19519,7 +19522,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G647" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19545,7 +19548,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G648" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19571,7 +19574,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G649" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19597,7 +19600,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G650" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19623,7 +19626,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G651" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19675,7 +19678,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G653" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19727,7 +19730,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19753,7 +19756,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G656" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19779,7 +19782,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -19805,7 +19808,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G658" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -19831,7 +19834,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19857,7 +19860,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G660" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19883,7 +19886,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G661" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19909,7 +19912,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G662" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19935,7 +19938,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G663" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19961,7 +19964,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G664" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19987,7 +19990,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20013,7 +20016,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20039,7 +20042,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20065,7 +20068,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20117,7 +20120,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G670" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20143,7 +20146,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20169,7 +20172,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G672" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20195,7 +20198,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G673" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20221,7 +20224,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20247,7 +20250,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20273,7 +20276,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G676" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20299,7 +20302,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20325,7 +20328,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20351,7 +20354,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G679" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20377,7 +20380,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20403,7 +20406,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G681" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20429,7 +20432,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20455,7 +20458,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20481,7 +20484,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20507,7 +20510,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20533,7 +20536,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20559,7 +20562,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20585,7 +20588,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20611,7 +20614,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20637,7 +20640,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20663,7 +20666,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20689,7 +20692,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G692" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20715,7 +20718,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20741,7 +20744,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20767,7 +20770,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20793,7 +20796,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20819,7 +20822,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20845,7 +20848,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -20871,7 +20874,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -20897,7 +20900,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -20923,7 +20926,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -20949,7 +20952,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20975,7 +20978,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21001,7 +21004,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21027,7 +21030,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21053,7 +21056,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21079,7 +21082,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21131,7 +21134,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G709" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21157,7 +21160,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G710" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21183,7 +21186,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G711" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21209,7 +21212,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21339,7 +21342,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G717" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21365,7 +21368,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21391,7 +21394,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G719" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21573,7 +21576,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G726" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21677,7 +21680,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21781,7 +21784,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G734" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21807,7 +21810,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G735" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21833,7 +21836,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G736" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21859,7 +21862,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G737" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21885,7 +21888,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21911,7 +21914,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G739" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21937,7 +21940,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21963,7 +21966,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G741" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -21989,7 +21992,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G742" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22015,7 +22018,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G743" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22041,7 +22044,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G744" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22067,7 +22070,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G745" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22093,7 +22096,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22119,7 +22122,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22145,7 +22148,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22171,7 +22174,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G749" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22197,7 +22200,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22223,7 +22226,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22249,7 +22252,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22275,7 +22278,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22301,7 +22304,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22327,7 +22330,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22353,7 +22356,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22379,7 +22382,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22405,7 +22408,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22431,7 +22434,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G759" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22457,7 +22460,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G760" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22483,7 +22486,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G761" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22509,7 +22512,7 @@
         <v>2.75</v>
       </c>
       <c r="G762" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22535,7 +22538,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22561,7 +22564,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22587,7 +22590,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22639,7 +22642,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22665,7 +22668,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G768" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22691,7 +22694,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22717,7 +22720,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22743,7 +22746,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22769,7 +22772,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22795,7 +22798,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22821,7 +22824,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22847,7 +22850,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22873,7 +22876,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22899,7 +22902,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22925,7 +22928,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22951,7 +22954,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G779" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22977,7 +22980,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23003,7 +23006,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23029,7 +23032,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G782" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23055,7 +23058,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23081,7 +23084,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G784" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23107,7 +23110,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G785" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23133,7 +23136,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23159,7 +23162,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G787" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23185,7 +23188,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G788" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23211,7 +23214,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G789" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23237,7 +23240,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23263,7 +23266,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G791" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23289,7 +23292,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G792" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23315,7 +23318,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G793" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23341,7 +23344,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23367,7 +23370,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23393,7 +23396,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23419,7 +23422,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G797" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23445,7 +23448,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G798" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23471,7 +23474,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23497,7 +23500,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G800" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23523,7 +23526,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23549,7 +23552,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G802" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23575,7 +23578,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23601,7 +23604,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G804" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23627,7 +23630,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23653,7 +23656,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23679,7 +23682,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G807" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23705,7 +23708,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G808" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23731,7 +23734,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G809" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23757,7 +23760,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G810" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23783,7 +23786,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G811" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23809,7 +23812,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23835,7 +23838,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G813" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23861,7 +23864,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G814" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23887,7 +23890,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23913,7 +23916,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G816" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23939,7 +23942,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23965,7 +23968,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G818" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23991,7 +23994,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24017,7 +24020,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G820" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24043,7 +24046,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G821" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24069,7 +24072,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24095,7 +24098,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G823" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24121,7 +24124,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G824" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24147,7 +24150,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G825" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24173,7 +24176,7 @@
         <v>4</v>
       </c>
       <c r="G826" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24199,7 +24202,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G827" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24225,7 +24228,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G828" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24251,7 +24254,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G829" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24277,7 +24280,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G830" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24303,7 +24306,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24329,7 +24332,7 @@
         <v>4</v>
       </c>
       <c r="G832" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24355,7 +24358,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24381,7 +24384,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24407,7 +24410,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24433,7 +24436,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G836" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24459,7 +24462,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24485,7 +24488,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24511,7 +24514,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G839" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24537,7 +24540,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24563,7 +24566,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G841" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24589,7 +24592,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G842" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24615,7 +24618,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24641,7 +24644,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G844" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24667,7 +24670,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G845" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24693,7 +24696,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24719,7 +24722,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24745,7 +24748,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24771,7 +24774,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24797,7 +24800,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G850" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24823,7 +24826,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24849,7 +24852,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24875,7 +24878,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G853" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24901,7 +24904,7 @@
         <v>4.25</v>
       </c>
       <c r="G854" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24927,7 +24930,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24953,7 +24956,7 @@
         <v>4.25</v>
       </c>
       <c r="G856" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24979,7 +24982,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G857" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25005,7 +25008,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G858" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25031,7 +25034,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G859" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25057,7 +25060,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25083,7 +25086,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G861" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25109,7 +25112,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G862" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25135,7 +25138,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G863" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25161,7 +25164,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G864" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25187,7 +25190,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G865" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25239,7 +25242,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G867" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25343,7 +25346,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25395,7 +25398,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G873" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25525,7 +25528,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G878" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25889,7 +25892,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G892" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25967,7 +25970,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G895" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26201,7 +26204,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G904" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -30387,7 +30390,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1065" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30673,7 +30676,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1076" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30699,7 +30702,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1077" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30933,7 +30936,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1086" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31297,7 +31300,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1100" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31401,7 +31404,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1104" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32909,7 +32912,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1162" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32935,7 +32938,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1163" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33377,7 +33380,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1180" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33507,7 +33510,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1185" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33715,7 +33718,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1193" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -67471,7 +67474,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6290856482</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>9676</v>
@@ -67492,6 +67495,32 @@
         <v>784</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6497337963</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>78315</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>785</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -38,100 +38,100 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825943946838</t>
+    <t xml:space="preserve">1.85825967788696</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91323745250702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109167575836</t>
+    <t xml:space="preserve">1.9132376909256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109155654907</t>
   </si>
   <si>
     <t xml:space="preserve">1.88496327400208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92423319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80642282962799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82998490333557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79856884479523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76715314388275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354709625244</t>
+    <t xml:space="preserve">1.92423343658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80642294883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82998502254486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79856896400452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76715278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354685783386</t>
   </si>
   <si>
     <t xml:space="preserve">1.86925518512726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87710905075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281725883484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86768412590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81584787368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83783876895905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87553822994232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684338092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84569299221039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898927688599</t>
+    <t xml:space="preserve">1.87710916996002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281702041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86768424510956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81584751605988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83783888816833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553811073303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8456928730011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81898951530457</t>
   </si>
   <si>
     <t xml:space="preserve">1.8362683057785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85983037948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80485224723816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82056033611298</t>
+    <t xml:space="preserve">1.85983002185822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80485212802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82056021690369</t>
   </si>
   <si>
     <t xml:space="preserve">1.81741857528687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85040533542633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88025081157684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81427681446075</t>
+    <t xml:space="preserve">1.85040545463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88025069236755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81427705287933</t>
   </si>
   <si>
     <t xml:space="preserve">1.85197627544403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84412229061127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84098052978516</t>
+    <t xml:space="preserve">1.84412217140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84098064899445</t>
   </si>
   <si>
     <t xml:space="preserve">1.82370173931122</t>
@@ -149,22 +149,22 @@
     <t xml:space="preserve">1.94622421264648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95407819747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.963503241539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96507441997528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99334847927094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00434422492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98706519603729</t>
+    <t xml:space="preserve">1.95407855510712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96350336074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9650741815567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99334836006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00434374809265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98706543445587</t>
   </si>
   <si>
     <t xml:space="preserve">2.00905656814575</t>
@@ -173,58 +173,58 @@
     <t xml:space="preserve">2.02476453781128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93051624298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96193242073059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994116783142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564925670624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637921333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87396740913391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378722667694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92231547832489</t>
+    <t xml:space="preserve">1.93051636219025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96193218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994128704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564901828766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637933254242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87396728992462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378710746765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017540454865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92231559753418</t>
   </si>
   <si>
     <t xml:space="preserve">1.93050944805145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96656346321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509159564972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95836913585663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739892959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9354259967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198107719421</t>
+    <t xml:space="preserve">1.96656334400177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509171485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9583694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739881038666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542611598969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9419811964035</t>
   </si>
   <si>
     <t xml:space="preserve">1.91248297691345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91084384918213</t>
+    <t xml:space="preserve">1.91084396839142</t>
   </si>
   <si>
     <t xml:space="preserve">1.83545899391174</t>
@@ -236,25 +236,22 @@
     <t xml:space="preserve">1.84201419353485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83218133449554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88298439979553</t>
+    <t xml:space="preserve">1.83218145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
     <t xml:space="preserve">1.86823511123657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90756618976593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281690120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592753887177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88462293148041</t>
+    <t xml:space="preserve">1.9075665473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90592730045319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8846230506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.90920507907867</t>
@@ -263,22 +260,22 @@
     <t xml:space="preserve">1.87151253223419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89773344993591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82398736476898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75843501091003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76662921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78629505634308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77646195888519</t>
+    <t xml:space="preserve">1.8977335691452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82398748397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75843524932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76662909984589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78629493713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77646219730377</t>
   </si>
   <si>
     <t xml:space="preserve">1.75188004970551</t>
@@ -287,10 +284,10 @@
     <t xml:space="preserve">1.75351905822754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77973961830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75024127960205</t>
+    <t xml:space="preserve">1.77973985671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75024116039276</t>
   </si>
   <si>
     <t xml:space="preserve">1.72074270248413</t>
@@ -302,19 +299,19 @@
     <t xml:space="preserve">1.72893679141998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69616067409515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76007413864136</t>
+    <t xml:space="preserve">1.69616079330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76007401943207</t>
   </si>
   <si>
     <t xml:space="preserve">1.70435476303101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73549199104309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73385310173035</t>
+    <t xml:space="preserve">1.73549211025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73385322093964</t>
   </si>
   <si>
     <t xml:space="preserve">1.71254873275757</t>
@@ -329,10 +326,10 @@
     <t xml:space="preserve">1.66666221618652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61012351512909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62241470813751</t>
+    <t xml:space="preserve">1.61012363433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62241458892822</t>
   </si>
   <si>
     <t xml:space="preserve">1.66338467597961</t>
@@ -353,34 +350,34 @@
     <t xml:space="preserve">1.66830122470856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65519082546234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6469966173172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63798320293427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59865212440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6297892332077</t>
+    <t xml:space="preserve">1.65519070625305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64699673652649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63798332214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59865200519562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62978911399841</t>
   </si>
   <si>
     <t xml:space="preserve">1.58308351039886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.595374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.578986287117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59127736091614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54047465324402</t>
+    <t xml:space="preserve">1.59537446498871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57898640632629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59127748012543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54047453403473</t>
   </si>
   <si>
     <t xml:space="preserve">1.56751477718353</t>
@@ -392,19 +389,19 @@
     <t xml:space="preserve">1.56669533252716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5585013628006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60274910926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60356831550598</t>
+    <t xml:space="preserve">1.55850124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6027489900589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60356855392456</t>
   </si>
   <si>
     <t xml:space="preserve">1.6060266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51917004585266</t>
+    <t xml:space="preserve">1.51917016506195</t>
   </si>
   <si>
     <t xml:space="preserve">1.5617790222168</t>
@@ -413,16 +410,16 @@
     <t xml:space="preserve">1.54539096355438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37659406661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4126478433609</t>
+    <t xml:space="preserve">1.37659418582916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41264796257019</t>
   </si>
   <si>
     <t xml:space="preserve">1.39462113380432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45771503448486</t>
+    <t xml:space="preserve">1.45771491527557</t>
   </si>
   <si>
     <t xml:space="preserve">1.47082543373108</t>
@@ -431,16 +428,16 @@
     <t xml:space="preserve">1.53391933441162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61258184909821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61176252365112</t>
+    <t xml:space="preserve">1.61258172988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61176240444183</t>
   </si>
   <si>
     <t xml:space="preserve">1.59783267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54211318492889</t>
+    <t xml:space="preserve">1.54211330413818</t>
   </si>
   <si>
     <t xml:space="preserve">1.51179552078247</t>
@@ -449,19 +446,19 @@
     <t xml:space="preserve">1.5552237033844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56505644321442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56423723697662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59291625022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55686259269714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52162837982178</t>
+    <t xml:space="preserve">1.565056681633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56423711776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59291613101959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55686247348785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52162826061249</t>
   </si>
   <si>
     <t xml:space="preserve">1.54129385948181</t>
@@ -473,7 +470,7 @@
     <t xml:space="preserve">1.5109760761261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55112671852112</t>
+    <t xml:space="preserve">1.55112683773041</t>
   </si>
   <si>
     <t xml:space="preserve">1.51589250564575</t>
@@ -482,10 +479,10 @@
     <t xml:space="preserve">1.55194616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50851786136627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53228056430817</t>
+    <t xml:space="preserve">1.50851774215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53228044509888</t>
   </si>
   <si>
     <t xml:space="preserve">1.50933730602264</t>
@@ -494,28 +491,28 @@
     <t xml:space="preserve">1.50769853591919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50278198719025</t>
+    <t xml:space="preserve">1.50278210639954</t>
   </si>
   <si>
     <t xml:space="preserve">1.49540758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51015663146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57325053215027</t>
+    <t xml:space="preserve">1.51015675067902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57325065135956</t>
   </si>
   <si>
     <t xml:space="preserve">1.58554148674011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59455490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60684585571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62159538269043</t>
+    <t xml:space="preserve">1.59455502033234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60684597492218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62159514427185</t>
   </si>
   <si>
     <t xml:space="preserve">1.57161176204681</t>
@@ -527,25 +524,25 @@
     <t xml:space="preserve">1.57243120670319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58718049526215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54621040821075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55768191814423</t>
+    <t xml:space="preserve">1.58718025684357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54621028900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55768203735352</t>
   </si>
   <si>
     <t xml:space="preserve">1.58799982070923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5347386598587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5822639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54702973365784</t>
+    <t xml:space="preserve">1.53473877906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58226406574249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54702961444855</t>
   </si>
   <si>
     <t xml:space="preserve">1.53883576393127</t>
@@ -560,58 +557,58 @@
     <t xml:space="preserve">1.54948806762695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53801620006561</t>
+    <t xml:space="preserve">1.5380163192749</t>
   </si>
   <si>
     <t xml:space="preserve">1.54866850376129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53637754917145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53965508937836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56915354728699</t>
+    <t xml:space="preserve">1.53637766838074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53965520858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5691534280777</t>
   </si>
   <si>
     <t xml:space="preserve">1.65191316604614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69288313388824</t>
+    <t xml:space="preserve">1.69288325309753</t>
   </si>
   <si>
     <t xml:space="preserve">1.65355181694031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82070958614349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82890391349792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81743204593658</t>
+    <t xml:space="preserve">1.82070982456207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82890379428864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81743216514587</t>
   </si>
   <si>
     <t xml:space="preserve">1.81579351425171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87970638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79448914527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80104422569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73876953125</t>
+    <t xml:space="preserve">1.87970650196075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79448890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80104398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73876965045929</t>
   </si>
   <si>
     <t xml:space="preserve">1.72729802131653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74696373939514</t>
+    <t xml:space="preserve">1.74696350097656</t>
   </si>
   <si>
     <t xml:space="preserve">1.76335167884827</t>
@@ -620,46 +617,46 @@
     <t xml:space="preserve">1.84693050384521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81087684631348</t>
+    <t xml:space="preserve">1.81087696552277</t>
   </si>
   <si>
     <t xml:space="preserve">1.80923807621002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81251573562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86167991161346</t>
+    <t xml:space="preserve">1.81251561641693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86168003082275</t>
   </si>
   <si>
     <t xml:space="preserve">1.86495745182037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840201377869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87642896175385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89937245845795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84856951236725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92479622364044</t>
+    <t xml:space="preserve">1.85840213298798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87642908096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89937233924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84856963157654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92479634284973</t>
   </si>
   <si>
     <t xml:space="preserve">1.93679392337799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93850815296173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97107362747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822456359863</t>
+    <t xml:space="preserve">1.93850827217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107374668121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822432518005</t>
   </si>
   <si>
     <t xml:space="preserve">1.94193637371063</t>
@@ -668,13 +665,13 @@
     <t xml:space="preserve">1.94364988803864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95907580852509</t>
+    <t xml:space="preserve">1.95907592773438</t>
   </si>
   <si>
     <t xml:space="preserve">1.96764576435089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9265102148056</t>
+    <t xml:space="preserve">1.92651009559631</t>
   </si>
   <si>
     <t xml:space="preserve">1.95393395423889</t>
@@ -686,28 +683,28 @@
     <t xml:space="preserve">1.90594255924225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89394462108612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87166309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92993807792664</t>
+    <t xml:space="preserve">1.8939448595047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8716629743576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9299384355545</t>
   </si>
   <si>
     <t xml:space="preserve">1.90080046653748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91451263427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88708865642548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87680518627167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9179402589798</t>
+    <t xml:space="preserve">1.91451239585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88708877563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87680494785309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91794049739838</t>
   </si>
   <si>
     <t xml:space="preserve">1.88537490367889</t>
@@ -716,13 +713,13 @@
     <t xml:space="preserve">1.86994910240173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88880288600922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90937054157257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90251469612122</t>
+    <t xml:space="preserve">1.88880264759064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90937042236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90251457691193</t>
   </si>
   <si>
     <t xml:space="preserve">1.96421778202057</t>
@@ -731,13 +728,13 @@
     <t xml:space="preserve">1.96250379085541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821341991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98649966716766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964346408844</t>
+    <t xml:space="preserve">1.98821365833282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98649954795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97964358329773</t>
   </si>
   <si>
     <t xml:space="preserve">2.12533140182495</t>
@@ -746,19 +743,19 @@
     <t xml:space="preserve">2.08591032028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05677270889282</t>
+    <t xml:space="preserve">2.05677247047424</t>
   </si>
   <si>
     <t xml:space="preserve">2.07905459403992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08076810836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06534266471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06020045280457</t>
+    <t xml:space="preserve">2.0807683467865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06534242630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06020069122314</t>
   </si>
   <si>
     <t xml:space="preserve">2.07219862937927</t>
@@ -767,28 +764,28 @@
     <t xml:space="preserve">2.13390159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10819220542908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09962201118469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10304975509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03963279724121</t>
+    <t xml:space="preserve">2.1081919670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09962224960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10304999351501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03963303565979</t>
   </si>
   <si>
     <t xml:space="preserve">2.06877040863037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11504793167114</t>
+    <t xml:space="preserve">2.11504769325256</t>
   </si>
   <si>
     <t xml:space="preserve">2.07391238212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09790802001953</t>
+    <t xml:space="preserve">2.09790778160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.11676168441772</t>
@@ -797,7 +794,7 @@
     <t xml:space="preserve">2.08248209953308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06705641746521</t>
+    <t xml:space="preserve">2.06705665588379</t>
   </si>
   <si>
     <t xml:space="preserve">2.12190389633179</t>
@@ -815,46 +812,46 @@
     <t xml:space="preserve">2.17675113677979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14247155189514</t>
+    <t xml:space="preserve">2.14247131347656</t>
   </si>
   <si>
     <t xml:space="preserve">2.1321873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13047361373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15961098670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11847567558289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09105229377747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12361741065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11161994934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10133600234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15789723396301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15618348121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1441855430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1407573223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14932751655579</t>
+    <t xml:space="preserve">2.13047337532043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15961122512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11847543716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09105205535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12361764907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11161971092224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10133576393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15789699554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15618324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14418530464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14075756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14932727813721</t>
   </si>
   <si>
     <t xml:space="preserve">2.13904333114624</t>
@@ -863,7 +860,7 @@
     <t xml:space="preserve">2.17503714561462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15104150772095</t>
+    <t xml:space="preserve">2.15104126930237</t>
   </si>
   <si>
     <t xml:space="preserve">2.12018966674805</t>
@@ -878,16 +875,16 @@
     <t xml:space="preserve">2.03277683258057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04820275306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07048439979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04991674423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12875986099243</t>
+    <t xml:space="preserve">2.0482029914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07048392295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0499165058136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12875962257385</t>
   </si>
   <si>
     <t xml:space="preserve">2.08762431144714</t>
@@ -902,19 +899,19 @@
     <t xml:space="preserve">2.0224928855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01392316818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00535321235657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1681809425354</t>
+    <t xml:space="preserve">2.01392292976379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00535297393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16818118095398</t>
   </si>
   <si>
     <t xml:space="preserve">2.18532061576843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29672932624817</t>
+    <t xml:space="preserve">2.29672956466675</t>
   </si>
   <si>
     <t xml:space="preserve">2.33100891113281</t>
@@ -932,31 +929,31 @@
     <t xml:space="preserve">2.49383664131165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46812701225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47669696807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48526692390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53668594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57953548431396</t>
+    <t xml:space="preserve">2.46812725067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47669720649719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48526668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53668642044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57953572273254</t>
   </si>
   <si>
     <t xml:space="preserve">2.59667539596558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61381506919861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55382609367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63447308540344</t>
+    <t xml:space="preserve">2.61381483078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55382561683655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63447332382202</t>
   </si>
   <si>
     <t xml:space="preserve">2.59862995147705</t>
@@ -965,16 +962,16 @@
     <t xml:space="preserve">2.5896692276001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61655163764954</t>
+    <t xml:space="preserve">2.61655139923096</t>
   </si>
   <si>
     <t xml:space="preserve">2.55382585525513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52694368362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.437335729599</t>
+    <t xml:space="preserve">2.52694344520569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43733549118042</t>
   </si>
   <si>
     <t xml:space="preserve">2.46421790122986</t>
@@ -986,16 +983,16 @@
     <t xml:space="preserve">2.45525717735291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54486489295959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57174730300903</t>
+    <t xml:space="preserve">2.54486513137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57174754142761</t>
   </si>
   <si>
     <t xml:space="preserve">2.51798272132874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56278681755066</t>
+    <t xml:space="preserve">2.56278657913208</t>
   </si>
   <si>
     <t xml:space="preserve">2.53590416908264</t>
@@ -1004,7 +1001,7 @@
     <t xml:space="preserve">2.4911003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48213958740234</t>
+    <t xml:space="preserve">2.48213982582092</t>
   </si>
   <si>
     <t xml:space="preserve">2.50902199745178</t>
@@ -1016,7 +1013,7 @@
     <t xml:space="preserve">2.78680658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7599241733551</t>
+    <t xml:space="preserve">2.75992441177368</t>
   </si>
   <si>
     <t xml:space="preserve">2.77784562110901</t>
@@ -1025,31 +1022,31 @@
     <t xml:space="preserve">2.74200248718262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76888465881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71512031555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75096344947815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67031645774841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72408080101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65239453315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68823766708374</t>
+    <t xml:space="preserve">2.76888489723206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71512007713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75096321105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67031621932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72408103942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65239477157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68823790550232</t>
   </si>
   <si>
     <t xml:space="preserve">2.73304176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69719862937927</t>
+    <t xml:space="preserve">2.69719886779785</t>
   </si>
   <si>
     <t xml:space="preserve">2.67927694320679</t>
@@ -1058,7 +1055,7 @@
     <t xml:space="preserve">2.84953236579895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86745357513428</t>
+    <t xml:space="preserve">2.86745381355286</t>
   </si>
   <si>
     <t xml:space="preserve">2.83161044120789</t>
@@ -1070,7 +1067,7 @@
     <t xml:space="preserve">2.62551236152649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58070826530457</t>
+    <t xml:space="preserve">2.58070850372314</t>
   </si>
   <si>
     <t xml:space="preserve">2.607590675354</t>
@@ -1094,13 +1091,13 @@
     <t xml:space="preserve">2.87641453742981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82264995574951</t>
+    <t xml:space="preserve">2.82264971733093</t>
   </si>
   <si>
     <t xml:space="preserve">2.80472826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90329694747925</t>
+    <t xml:space="preserve">2.90329670906067</t>
   </si>
   <si>
     <t xml:space="preserve">3.12731671333313</t>
@@ -1109,16 +1106,16 @@
     <t xml:space="preserve">3.16315984725952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13627767562866</t>
+    <t xml:space="preserve">3.13627743721008</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004225730896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25276803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26172876358032</t>
+    <t xml:space="preserve">3.25276780128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26172852516174</t>
   </si>
   <si>
     <t xml:space="preserve">3.28861093521118</t>
@@ -1133,10 +1130,10 @@
     <t xml:space="preserve">3.33341503143311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34237551689148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42302274703979</t>
+    <t xml:space="preserve">3.34237575531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42302298545837</t>
   </si>
   <si>
     <t xml:space="preserve">3.3871796131134</t>
@@ -1148,19 +1145,19 @@
     <t xml:space="preserve">3.41406202316284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36925840377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37821865081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45886588096619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48574829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47678780555725</t>
+    <t xml:space="preserve">3.36925792694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37821888923645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45886564254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48574876785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47678756713867</t>
   </si>
   <si>
     <t xml:space="preserve">3.49470925331116</t>
@@ -1169,7 +1166,7 @@
     <t xml:space="preserve">3.67392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58431720733643</t>
+    <t xml:space="preserve">3.58431696891785</t>
   </si>
   <si>
     <t xml:space="preserve">3.53055238723755</t>
@@ -1178,16 +1175,16 @@
     <t xml:space="preserve">3.59327816963196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55743455886841</t>
+    <t xml:space="preserve">3.55743479728699</t>
   </si>
   <si>
     <t xml:space="preserve">3.52159142494202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51263070106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53951334953308</t>
+    <t xml:space="preserve">3.51263093948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5395131111145</t>
   </si>
   <si>
     <t xml:space="preserve">3.60223865509033</t>
@@ -1196,13 +1193,13 @@
     <t xml:space="preserve">3.65600347518921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66496419906616</t>
+    <t xml:space="preserve">3.66496443748474</t>
   </si>
   <si>
     <t xml:space="preserve">3.72768974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71872901916504</t>
+    <t xml:space="preserve">3.71872925758362</t>
   </si>
   <si>
     <t xml:space="preserve">3.6918466091156</t>
@@ -1211,7 +1208,7 @@
     <t xml:space="preserve">3.70976805686951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68288612365723</t>
+    <t xml:space="preserve">3.68288588523865</t>
   </si>
   <si>
     <t xml:space="preserve">3.7635326385498</t>
@@ -1220,33 +1217,36 @@
     <t xml:space="preserve">3.78145432472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80833697319031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79041528701782</t>
+    <t xml:space="preserve">3.80833721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79041504859924</t>
   </si>
   <si>
     <t xml:space="preserve">3.95170950889587</t>
   </si>
   <si>
+    <t xml:space="preserve">3.96067070960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97005581855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00759792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0920672416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81988835334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87620115280151</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.96067023277283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97005581855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00759744644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0920672416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81988859176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87620115280151</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.02636861801147</t>
   </si>
   <si>
@@ -1262,40 +1262,40 @@
     <t xml:space="preserve">4.03575468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9982123374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97944116592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85743045806885</t>
+    <t xml:space="preserve">3.99821257591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97944092750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85743021965027</t>
   </si>
   <si>
     <t xml:space="preserve">3.84804463386536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81050276756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74480438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89497208595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.941899061203</t>
+    <t xml:space="preserve">3.81050252914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7448046207428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89497232437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94189953804016</t>
   </si>
   <si>
     <t xml:space="preserve">3.8668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93251419067383</t>
+    <t xml:space="preserve">3.93251395225525</t>
   </si>
   <si>
     <t xml:space="preserve">4.08268165588379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11083841323853</t>
+    <t xml:space="preserve">4.11083793640137</t>
   </si>
   <si>
     <t xml:space="preserve">4.12022304534912</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">4.18592166900635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1953067779541</t>
+    <t xml:space="preserve">4.19530725479126</t>
   </si>
   <si>
     <t xml:space="preserve">4.20469284057617</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">4.28916215896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26100540161133</t>
+    <t xml:space="preserve">4.26100587844849</t>
   </si>
   <si>
     <t xml:space="preserve">4.2703914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34547519683838</t>
+    <t xml:space="preserve">4.34547472000122</t>
   </si>
   <si>
     <t xml:space="preserve">4.36424589157104</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">4.50502824783325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49564218521118</t>
+    <t xml:space="preserve">4.49564266204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.43932962417603</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">4.5519552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54256963729858</t>
+    <t xml:space="preserve">4.54257011413574</t>
   </si>
   <si>
     <t xml:space="preserve">4.48625707626343</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">4.40178775787354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44871473312378</t>
+    <t xml:space="preserve">4.44871520996094</t>
   </si>
   <si>
     <t xml:space="preserve">4.42994403839111</t>
@@ -1373,13 +1373,13 @@
     <t xml:space="preserve">4.41117334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39240217208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2422342300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30793285369873</t>
+    <t xml:space="preserve">4.39240169525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24223470687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30793333053589</t>
   </si>
   <si>
     <t xml:space="preserve">4.17653608322144</t>
@@ -1397,28 +1397,28 @@
     <t xml:space="preserve">4.62703895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61765384674072</t>
+    <t xml:space="preserve">4.61765336990356</t>
   </si>
   <si>
     <t xml:space="preserve">4.51441335678101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57072639465332</t>
+    <t xml:space="preserve">4.57072591781616</t>
   </si>
   <si>
     <t xml:space="preserve">4.67396640777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80536317825317</t>
+    <t xml:space="preserve">4.80536270141602</t>
   </si>
   <si>
     <t xml:space="preserve">4.78659200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86167573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84290456771851</t>
+    <t xml:space="preserve">4.86167621612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84290504455566</t>
   </si>
   <si>
     <t xml:space="preserve">4.89921760559082</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">4.5988826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53318452835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58011198043823</t>
+    <t xml:space="preserve">4.53318405151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58011150360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.6927375793457</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">4.74905014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73027896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71150875091553</t>
+    <t xml:space="preserve">4.73027944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71150827407837</t>
   </si>
   <si>
     <t xml:space="preserve">4.76782131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95553064346313</t>
+    <t xml:space="preserve">4.95553112030029</t>
   </si>
   <si>
     <t xml:space="preserve">4.88044691085815</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">4.91798877716064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99307298660278</t>
+    <t xml:space="preserve">4.99307250976562</t>
   </si>
   <si>
     <t xml:space="preserve">4.93675994873047</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">6.60737419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28826761245728</t>
+    <t xml:space="preserve">6.28826808929443</t>
   </si>
   <si>
     <t xml:space="preserve">6.1568717956543</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">5.96916246414185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7063684463501</t>
+    <t xml:space="preserve">5.70636892318726</t>
   </si>
   <si>
     <t xml:space="preserve">5.53743028640747</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">5.87530755996704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66882705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68759775161743</t>
+    <t xml:space="preserve">5.66882658004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68759727478027</t>
   </si>
   <si>
     <t xml:space="preserve">5.83776521682739</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59374332427979</t>
+    <t xml:space="preserve">5.59374284744263</t>
   </si>
   <si>
     <t xml:space="preserve">5.38726234436035</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">5.10569858551025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68335151672363</t>
+    <t xml:space="preserve">4.68335199356079</t>
   </si>
   <si>
     <t xml:space="preserve">4.14837980270386</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">3.62279319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55709505081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37877106666565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50078201293945</t>
+    <t xml:space="preserve">3.55709481239319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37877082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50078225135803</t>
   </si>
   <si>
     <t xml:space="preserve">3.5664803981781</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">3.75418996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70726275444031</t>
+    <t xml:space="preserve">3.70726251602173</t>
   </si>
   <si>
     <t xml:space="preserve">3.71664810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83865928649902</t>
+    <t xml:space="preserve">3.8386595249176</t>
   </si>
   <si>
     <t xml:space="preserve">4.25162029266357</t>
@@ -1583,25 +1583,25 @@
     <t xml:space="preserve">4.12960910797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16715097427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05452489852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76357579231262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66972088813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65094971656799</t>
+    <t xml:space="preserve">4.16715049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05452537536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76357555389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66972064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65094995498657</t>
   </si>
   <si>
     <t xml:space="preserve">3.66033530235291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95128488540649</t>
+    <t xml:space="preserve">3.95128512382507</t>
   </si>
   <si>
     <t xml:space="preserve">4.29854726791382</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">4.31731843948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15776538848877</t>
+    <t xml:space="preserve">4.15776491165161</t>
   </si>
   <si>
     <t xml:space="preserve">4.10145235061646</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">4.13899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88558650016785</t>
+    <t xml:space="preserve">3.88558626174927</t>
   </si>
   <si>
     <t xml:space="preserve">4.32670402526855</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">4.27977657318115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91374325752258</t>
+    <t xml:space="preserve">3.913743019104</t>
   </si>
   <si>
     <t xml:space="preserve">3.92312836647034</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">3.49139666557312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67910599708557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3881561756134</t>
+    <t xml:space="preserve">3.67910623550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38815641403198</t>
   </si>
   <si>
     <t xml:space="preserve">3.35999989509583</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">3.34122896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20044684410095</t>
+    <t xml:space="preserve">3.20044708251953</t>
   </si>
   <si>
     <t xml:space="preserve">3.24737429618835</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">3.47262573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57586598396301</t>
+    <t xml:space="preserve">3.57586574554443</t>
   </si>
   <si>
     <t xml:space="preserve">3.73541903495789</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">3.68849158287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72603344917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52893877029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63217854499817</t>
+    <t xml:space="preserve">3.72603368759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52893853187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63217878341675</t>
   </si>
   <si>
     <t xml:space="preserve">3.51016759872437</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">3.58525133132935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53832387924194</t>
+    <t xml:space="preserve">3.53832411766052</t>
   </si>
   <si>
     <t xml:space="preserve">3.80111742019653</t>
@@ -1730,10 +1730,10 @@
     <t xml:space="preserve">3.48201107978821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46324038505554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44446921348572</t>
+    <t xml:space="preserve">3.46324014663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4444694519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.42569851875305</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">3.41631293296814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754176139832</t>
+    <t xml:space="preserve">3.39754199981689</t>
   </si>
   <si>
     <t xml:space="preserve">3.21921801567078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19106149673462</t>
+    <t xml:space="preserve">3.1910617351532</t>
   </si>
   <si>
     <t xml:space="preserve">3.17229056358337</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">3.23798894882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14413380622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25675988197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36938548088074</t>
+    <t xml:space="preserve">3.14413404464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25675964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36938524246216</t>
   </si>
   <si>
     <t xml:space="preserve">3.15351939201355</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">3.18167614936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29430150985718</t>
+    <t xml:space="preserve">3.29430174827576</t>
   </si>
   <si>
     <t xml:space="preserve">3.2661452293396</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">3.12536311149597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04089403152466</t>
+    <t xml:space="preserve">3.04089379310608</t>
   </si>
   <si>
     <t xml:space="preserve">3.05027914047241</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">2.93765377998352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95642471313477</t>
+    <t xml:space="preserve">2.95642447471619</t>
   </si>
   <si>
     <t xml:space="preserve">3.03150844573975</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">3.02212285995483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92826819419861</t>
+    <t xml:space="preserve">2.92826795578003</t>
   </si>
   <si>
     <t xml:space="preserve">2.94703912734985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90011143684387</t>
+    <t xml:space="preserve">2.90011167526245</t>
   </si>
   <si>
     <t xml:space="preserve">2.97519564628601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27553081512451</t>
+    <t xml:space="preserve">3.27553057670593</t>
   </si>
   <si>
     <t xml:space="preserve">3.33184361457825</t>
@@ -6236,7 +6236,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -6262,7 +6262,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -6288,7 +6288,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -6314,7 +6314,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G139" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -6340,7 +6340,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -6366,7 +6366,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -6418,7 +6418,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G143" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -6444,7 +6444,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G144" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -6470,7 +6470,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -6496,7 +6496,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -6522,7 +6522,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -6548,7 +6548,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G148" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -6574,7 +6574,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -6600,7 +6600,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G150" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -6626,7 +6626,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G151" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -6652,7 +6652,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -6678,7 +6678,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G153" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -6704,7 +6704,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G154" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -6730,7 +6730,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G155" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -6756,7 +6756,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -6782,7 +6782,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -6808,7 +6808,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -6834,7 +6834,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -6860,7 +6860,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G160" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -6886,7 +6886,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G161" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -6912,7 +6912,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G162" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -6938,7 +6938,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G163" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -6964,7 +6964,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G164" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -6990,7 +6990,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G165" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -7016,7 +7016,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G166" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7042,7 +7042,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G167" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7068,7 +7068,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G168" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7094,7 +7094,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G169" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7120,7 +7120,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7146,7 +7146,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G171" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7172,7 +7172,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7198,7 +7198,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7224,7 +7224,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G174" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7250,7 +7250,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7276,7 +7276,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G176" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7302,7 +7302,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G177" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7328,7 +7328,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G178" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7354,7 +7354,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G179" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7380,7 +7380,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G180" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7406,7 +7406,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G181" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7432,7 +7432,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G182" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7458,7 +7458,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G183" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7484,7 +7484,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G184" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -7510,7 +7510,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G185" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7536,7 +7536,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G186" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7562,7 +7562,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G187" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7588,7 +7588,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G188" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7614,7 +7614,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G189" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7640,7 +7640,7 @@
         <v>2</v>
       </c>
       <c r="G190" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7666,7 +7666,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G191" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7692,7 +7692,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G192" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7718,7 +7718,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G193" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7744,7 +7744,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G194" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -7770,7 +7770,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G195" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -7796,7 +7796,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G196" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -7822,7 +7822,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -7848,7 +7848,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -7874,7 +7874,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -7900,7 +7900,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -7926,7 +7926,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -7952,7 +7952,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -7978,7 +7978,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8004,7 +8004,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8030,7 +8030,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8056,7 +8056,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G206" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8082,7 +8082,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G207" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8108,7 +8108,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8134,7 +8134,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G209" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8160,7 +8160,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8186,7 +8186,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G211" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8212,7 +8212,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G212" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8238,7 +8238,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G213" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8264,7 +8264,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G214" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8290,7 +8290,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8316,7 +8316,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G216" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8342,7 +8342,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8368,7 +8368,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8394,7 +8394,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G219" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8420,7 +8420,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G220" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8446,7 +8446,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G221" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8472,7 +8472,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G222" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8498,7 +8498,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G223" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8524,7 +8524,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G224" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8550,7 +8550,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8576,7 +8576,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G226" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8602,7 +8602,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8628,7 +8628,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8654,7 +8654,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G229" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8680,7 +8680,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8706,7 +8706,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G231" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8732,7 +8732,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G232" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8758,7 +8758,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G233" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8784,7 +8784,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G234" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -8810,7 +8810,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G235" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -8836,7 +8836,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G236" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -8862,7 +8862,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G237" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -8888,7 +8888,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G238" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -8914,7 +8914,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G239" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -8940,7 +8940,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G240" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -8966,7 +8966,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -8992,7 +8992,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9018,7 +9018,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9044,7 +9044,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G244" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9070,7 +9070,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9096,7 +9096,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G246" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9122,7 +9122,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G247" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9148,7 +9148,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G248" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9174,7 +9174,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G249" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9200,7 +9200,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G250" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9226,7 +9226,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9252,7 +9252,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G252" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9278,7 +9278,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G253" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9304,7 +9304,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G254" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9330,7 +9330,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9356,7 +9356,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G256" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9382,7 +9382,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G257" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9408,7 +9408,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G258" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9434,7 +9434,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G259" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9460,7 +9460,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9486,7 +9486,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G261" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9512,7 +9512,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G262" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9538,7 +9538,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9564,7 +9564,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G264" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9590,7 +9590,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G265" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9616,7 +9616,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G266" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9642,7 +9642,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G267" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9668,7 +9668,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G268" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9694,7 +9694,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9720,7 +9720,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G270" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9746,7 +9746,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G271" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -9772,7 +9772,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -9798,7 +9798,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9824,7 +9824,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G274" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -9850,7 +9850,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G275" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -9876,7 +9876,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G276" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9902,7 +9902,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G277" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9928,7 +9928,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G278" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -9954,7 +9954,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G279" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -9980,7 +9980,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G280" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10006,7 +10006,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G281" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10032,7 +10032,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10058,7 +10058,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G283" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10084,7 +10084,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G284" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10110,7 +10110,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G285" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10136,7 +10136,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G286" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10162,7 +10162,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G287" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10188,7 +10188,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10214,7 +10214,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G289" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10240,7 +10240,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G290" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10266,7 +10266,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G291" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10292,7 +10292,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10318,7 +10318,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G293" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10344,7 +10344,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G294" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10370,7 +10370,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G295" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10396,7 +10396,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G296" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10422,7 +10422,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G297" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10448,7 +10448,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G298" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10474,7 +10474,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10500,7 +10500,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G300" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10526,7 +10526,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G301" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10552,7 +10552,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G302" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10578,7 +10578,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10604,7 +10604,7 @@
         <v>1.875</v>
       </c>
       <c r="G304" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10630,7 +10630,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G305" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10656,7 +10656,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G306" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10682,7 +10682,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G307" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10708,7 +10708,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G308" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10734,7 +10734,7 @@
         <v>2</v>
       </c>
       <c r="G309" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -10760,7 +10760,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10786,7 +10786,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -10812,7 +10812,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -10838,7 +10838,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G313" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10864,7 +10864,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G314" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -10890,7 +10890,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10916,7 +10916,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10942,7 +10942,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G317" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -10994,7 +10994,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11020,7 +11020,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11046,7 +11046,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11072,7 +11072,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11098,7 +11098,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11124,7 +11124,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11150,7 +11150,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11202,7 +11202,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G327" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11228,7 +11228,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11254,7 +11254,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11280,7 +11280,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11306,7 +11306,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11332,7 +11332,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G332" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11358,7 +11358,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11384,7 +11384,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11410,7 +11410,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G335" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11436,7 +11436,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11540,7 +11540,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11566,7 +11566,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G341" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11592,7 +11592,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11618,7 +11618,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11644,7 +11644,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G344" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11696,7 +11696,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G346" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11722,7 +11722,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G347" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11748,7 +11748,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -11774,7 +11774,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G349" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -11800,7 +11800,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -11852,7 +11852,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11878,7 +11878,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G353" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11930,7 +11930,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G355" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11956,7 +11956,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -11982,7 +11982,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G357" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12008,7 +12008,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12034,7 +12034,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12060,7 +12060,7 @@
         <v>2.25</v>
       </c>
       <c r="G360" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12086,7 +12086,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12112,7 +12112,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12138,7 +12138,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G363" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12164,7 +12164,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G364" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12190,7 +12190,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12216,7 +12216,7 @@
         <v>2.25</v>
       </c>
       <c r="G366" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12242,7 +12242,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12268,7 +12268,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12294,7 +12294,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12320,7 +12320,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12346,7 +12346,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12372,7 +12372,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12398,7 +12398,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G373" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12424,7 +12424,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G374" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12450,7 +12450,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G375" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12476,7 +12476,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G376" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12502,7 +12502,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G377" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12528,7 +12528,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12554,7 +12554,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12580,7 +12580,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G380" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12606,7 +12606,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G381" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12632,7 +12632,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G382" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12658,7 +12658,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12684,7 +12684,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G384" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12710,7 +12710,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G385" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12736,7 +12736,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12762,7 +12762,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G387" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12788,7 +12788,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G388" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -12814,7 +12814,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G389" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -12840,7 +12840,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -12866,7 +12866,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G391" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -12892,7 +12892,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -12918,7 +12918,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G393" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -12944,7 +12944,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -12970,7 +12970,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G395" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -12996,7 +12996,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13022,7 +13022,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13048,7 +13048,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13074,7 +13074,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G399" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13100,7 +13100,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G400" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13126,7 +13126,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G401" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13152,7 +13152,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13178,7 +13178,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G403" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13204,7 +13204,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13230,7 +13230,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G405" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13256,7 +13256,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13282,7 +13282,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13308,7 +13308,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13334,7 +13334,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G409" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13360,7 +13360,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G410" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13386,7 +13386,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G411" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13412,7 +13412,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13438,7 +13438,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G413" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13464,7 +13464,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G414" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13490,7 +13490,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G415" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13516,7 +13516,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G416" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13542,7 +13542,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G417" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13568,7 +13568,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G418" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13594,7 +13594,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G419" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13620,7 +13620,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G420" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13646,7 +13646,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G421" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13672,7 +13672,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G422" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13698,7 +13698,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13724,7 +13724,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G424" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13750,7 +13750,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G425" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13776,7 +13776,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G426" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -13802,7 +13802,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G427" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -13828,7 +13828,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G428" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -13854,7 +13854,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G429" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -13880,7 +13880,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G430" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -13906,7 +13906,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G431" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -13932,7 +13932,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -13958,7 +13958,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G433" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -13984,7 +13984,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14010,7 +14010,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G435" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14036,7 +14036,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G436" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14062,7 +14062,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G437" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14088,7 +14088,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G438" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14114,7 +14114,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G439" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14140,7 +14140,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G440" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14166,7 +14166,7 @@
         <v>2.5</v>
       </c>
       <c r="G441" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14192,7 +14192,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G442" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14218,7 +14218,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G443" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14244,7 +14244,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G444" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14270,7 +14270,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G445" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14296,7 +14296,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14322,7 +14322,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G447" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14348,7 +14348,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G448" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14374,7 +14374,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G449" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14400,7 +14400,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G450" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14426,7 +14426,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G451" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14452,7 +14452,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G452" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14478,7 +14478,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G453" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14504,7 +14504,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G454" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14530,7 +14530,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G455" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14556,7 +14556,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G456" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14582,7 +14582,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G457" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14608,7 +14608,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G458" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14634,7 +14634,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G459" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14660,7 +14660,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G460" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14686,7 +14686,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G461" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14712,7 +14712,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G462" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14738,7 +14738,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G463" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14764,7 +14764,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G464" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -14790,7 +14790,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -14816,7 +14816,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G466" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -14842,7 +14842,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G467" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -14868,7 +14868,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G468" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -14894,7 +14894,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G469" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -14920,7 +14920,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G470" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -14946,7 +14946,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G471" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -14972,7 +14972,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -14998,7 +14998,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G473" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15024,7 +15024,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15050,7 +15050,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G475" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15076,7 +15076,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G476" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15102,7 +15102,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G477" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15128,7 +15128,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G478" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15154,7 +15154,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G479" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15180,7 +15180,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G480" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15206,7 +15206,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15232,7 +15232,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G482" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15258,7 +15258,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G483" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15284,7 +15284,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G484" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15310,7 +15310,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G485" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15336,7 +15336,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G486" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15362,7 +15362,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15388,7 +15388,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G488" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15414,7 +15414,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G489" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15440,7 +15440,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G490" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15466,7 +15466,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G491" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15492,7 +15492,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15518,7 +15518,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G493" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15544,7 +15544,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G494" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15570,7 +15570,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15596,7 +15596,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G496" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15622,7 +15622,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G497" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15648,7 +15648,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G498" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15674,7 +15674,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G499" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15700,7 +15700,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G500" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15726,7 +15726,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G501" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15752,7 +15752,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G502" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15778,7 +15778,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G503" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -15804,7 +15804,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G504" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -15830,7 +15830,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G505" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -15856,7 +15856,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G506" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -15882,7 +15882,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G507" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -15908,7 +15908,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G508" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -15934,7 +15934,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G509" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -15960,7 +15960,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G510" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -15986,7 +15986,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G511" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16012,7 +16012,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G512" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16038,7 +16038,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G513" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16064,7 +16064,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G514" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16090,7 +16090,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G515" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16116,7 +16116,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G516" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16142,7 +16142,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G517" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16168,7 +16168,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G518" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16194,7 +16194,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G519" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16220,7 +16220,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G520" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16246,7 +16246,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G521" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16272,7 +16272,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16298,7 +16298,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G523" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16324,7 +16324,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G524" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16350,7 +16350,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G525" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16376,7 +16376,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G526" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16402,7 +16402,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G527" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16428,7 +16428,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G528" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16454,7 +16454,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G529" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16480,7 +16480,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16506,7 +16506,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G531" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16532,7 +16532,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G532" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16558,7 +16558,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G533" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16584,7 +16584,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G534" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16610,7 +16610,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G535" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16636,7 +16636,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G536" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16662,7 +16662,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G537" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16688,7 +16688,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G538" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16714,7 +16714,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G539" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16740,7 +16740,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G540" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16766,7 +16766,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G541" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -16792,7 +16792,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G542" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -16818,7 +16818,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G543" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -16844,7 +16844,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G544" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -16870,7 +16870,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G545" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16896,7 +16896,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G546" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16922,7 +16922,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G547" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16948,7 +16948,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G548" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -16974,7 +16974,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G549" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17000,7 +17000,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G550" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17026,7 +17026,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G551" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17052,7 +17052,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G552" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17078,7 +17078,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G553" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17104,7 +17104,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G554" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17130,7 +17130,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17156,7 +17156,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G556" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17182,7 +17182,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G557" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17208,7 +17208,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17234,7 +17234,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17260,7 +17260,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17286,7 +17286,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17312,7 +17312,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G562" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17338,7 +17338,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G563" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17364,7 +17364,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17390,7 +17390,7 @@
         <v>2.5</v>
       </c>
       <c r="G565" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17416,7 +17416,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17442,7 +17442,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G567" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17468,7 +17468,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G568" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17494,7 +17494,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G569" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17520,7 +17520,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G570" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17546,7 +17546,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G571" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17572,7 +17572,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G572" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17598,7 +17598,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G573" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17624,7 +17624,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G574" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17650,7 +17650,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G575" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17676,7 +17676,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17702,7 +17702,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G577" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17728,7 +17728,7 @@
         <v>2.5</v>
       </c>
       <c r="G578" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17754,7 +17754,7 @@
         <v>2.5</v>
       </c>
       <c r="G579" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17780,7 +17780,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G580" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -17806,7 +17806,7 @@
         <v>2.5</v>
       </c>
       <c r="G581" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -17832,7 +17832,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -17858,7 +17858,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -17884,7 +17884,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -17910,7 +17910,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -17936,7 +17936,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -17962,7 +17962,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G587" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -17988,7 +17988,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18014,7 +18014,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G589" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18040,7 +18040,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G590" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18066,7 +18066,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G591" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18092,7 +18092,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G592" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18118,7 +18118,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G593" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18144,7 +18144,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G594" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18170,7 +18170,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G595" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18196,7 +18196,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18222,7 +18222,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18248,7 +18248,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G598" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18274,7 +18274,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G599" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18300,7 +18300,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G600" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18326,7 +18326,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18352,7 +18352,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18378,7 +18378,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G603" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18404,7 +18404,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G604" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18430,7 +18430,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G605" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18456,7 +18456,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G606" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18482,7 +18482,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G607" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18508,7 +18508,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G608" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18534,7 +18534,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G609" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18560,7 +18560,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G610" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18586,7 +18586,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G611" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18612,7 +18612,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18638,7 +18638,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G613" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18664,7 +18664,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G614" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18690,7 +18690,7 @@
         <v>2.75</v>
       </c>
       <c r="G615" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18716,7 +18716,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G616" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18742,7 +18742,7 @@
         <v>2.75</v>
       </c>
       <c r="G617" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18768,7 +18768,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G618" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18794,7 +18794,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G619" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18820,7 +18820,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G620" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18846,7 +18846,7 @@
         <v>2.75</v>
       </c>
       <c r="G621" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18872,7 +18872,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G622" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18898,7 +18898,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18924,7 +18924,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18950,7 +18950,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -18976,7 +18976,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19002,7 +19002,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G627" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19028,7 +19028,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G628" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19054,7 +19054,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G629" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19080,7 +19080,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G630" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19106,7 +19106,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19132,7 +19132,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G632" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19158,7 +19158,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19184,7 +19184,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G634" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19210,7 +19210,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G635" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19236,7 +19236,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G636" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19262,7 +19262,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19288,7 +19288,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19314,7 +19314,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19340,7 +19340,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19366,7 +19366,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19392,7 +19392,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19418,7 +19418,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19444,7 +19444,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19470,7 +19470,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19496,7 +19496,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19522,7 +19522,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G647" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19548,7 +19548,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G648" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19574,7 +19574,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G649" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19600,7 +19600,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G650" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19626,7 +19626,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G651" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19652,7 +19652,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G652" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19678,7 +19678,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G653" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19704,7 +19704,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G654" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19730,7 +19730,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19756,7 +19756,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G656" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19782,7 +19782,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -19808,7 +19808,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G658" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -19834,7 +19834,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19860,7 +19860,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G660" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19886,7 +19886,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G661" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19912,7 +19912,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G662" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19938,7 +19938,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G663" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19964,7 +19964,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G664" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19990,7 +19990,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20016,7 +20016,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20042,7 +20042,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20068,7 +20068,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20094,7 +20094,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G669" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20120,7 +20120,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G670" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20146,7 +20146,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20172,7 +20172,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G672" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20198,7 +20198,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G673" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20224,7 +20224,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20250,7 +20250,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20276,7 +20276,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G676" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20302,7 +20302,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20328,7 +20328,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20354,7 +20354,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G679" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20380,7 +20380,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20406,7 +20406,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G681" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20432,7 +20432,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20458,7 +20458,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20484,7 +20484,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20510,7 +20510,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20536,7 +20536,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20562,7 +20562,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20588,7 +20588,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20614,7 +20614,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20640,7 +20640,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20666,7 +20666,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20692,7 +20692,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G692" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20718,7 +20718,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20744,7 +20744,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20770,7 +20770,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20796,7 +20796,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20822,7 +20822,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20848,7 +20848,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -20874,7 +20874,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -20900,7 +20900,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -20926,7 +20926,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -20952,7 +20952,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20978,7 +20978,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21004,7 +21004,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21030,7 +21030,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21056,7 +21056,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21082,7 +21082,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21108,7 +21108,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G708" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21134,7 +21134,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G709" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21160,7 +21160,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G710" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21186,7 +21186,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G711" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21212,7 +21212,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21238,7 +21238,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G713" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21264,7 +21264,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G714" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21290,7 +21290,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G715" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21316,7 +21316,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G716" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21342,7 +21342,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G717" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21368,7 +21368,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21394,7 +21394,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G719" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21420,7 +21420,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G720" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21446,7 +21446,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G721" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21472,7 +21472,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G722" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21498,7 +21498,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G723" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21524,7 +21524,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G724" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21550,7 +21550,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G725" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21576,7 +21576,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G726" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21602,7 +21602,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G727" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21628,7 +21628,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21654,7 +21654,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G729" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21680,7 +21680,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21706,7 +21706,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G731" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21732,7 +21732,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G732" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21758,7 +21758,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G733" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21784,7 +21784,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G734" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21810,7 +21810,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G735" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21836,7 +21836,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G736" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21862,7 +21862,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G737" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21888,7 +21888,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21914,7 +21914,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G739" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21940,7 +21940,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21966,7 +21966,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G741" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -21992,7 +21992,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G742" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22018,7 +22018,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G743" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22044,7 +22044,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G744" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22070,7 +22070,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G745" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22096,7 +22096,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22122,7 +22122,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22148,7 +22148,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22174,7 +22174,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G749" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22200,7 +22200,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22226,7 +22226,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22252,7 +22252,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22278,7 +22278,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22304,7 +22304,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22330,7 +22330,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22356,7 +22356,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22382,7 +22382,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22408,7 +22408,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22434,7 +22434,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G759" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22460,7 +22460,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G760" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22486,7 +22486,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G761" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22512,7 +22512,7 @@
         <v>2.75</v>
       </c>
       <c r="G762" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22538,7 +22538,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22564,7 +22564,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22590,7 +22590,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22616,7 +22616,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G766" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22642,7 +22642,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22668,7 +22668,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G768" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22694,7 +22694,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22720,7 +22720,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22746,7 +22746,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22772,7 +22772,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22798,7 +22798,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22824,7 +22824,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22850,7 +22850,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22876,7 +22876,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22902,7 +22902,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22928,7 +22928,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22954,7 +22954,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G779" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22980,7 +22980,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23006,7 +23006,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23032,7 +23032,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G782" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23058,7 +23058,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23084,7 +23084,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G784" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23110,7 +23110,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G785" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23136,7 +23136,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23162,7 +23162,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G787" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23188,7 +23188,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G788" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23214,7 +23214,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G789" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23240,7 +23240,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23266,7 +23266,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G791" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23292,7 +23292,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G792" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23318,7 +23318,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G793" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23344,7 +23344,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23370,7 +23370,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23396,7 +23396,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23422,7 +23422,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G797" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23448,7 +23448,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G798" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23474,7 +23474,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23500,7 +23500,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G800" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23526,7 +23526,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23552,7 +23552,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G802" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23578,7 +23578,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23604,7 +23604,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G804" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23630,7 +23630,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23656,7 +23656,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23682,7 +23682,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G807" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23708,7 +23708,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G808" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23734,7 +23734,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G809" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23760,7 +23760,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G810" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23786,7 +23786,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G811" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23812,7 +23812,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23838,7 +23838,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G813" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23864,7 +23864,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G814" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23890,7 +23890,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23916,7 +23916,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G816" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23942,7 +23942,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23968,7 +23968,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G818" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23994,7 +23994,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24020,7 +24020,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G820" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24046,7 +24046,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G821" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24072,7 +24072,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24098,7 +24098,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G823" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24124,7 +24124,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G824" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24150,7 +24150,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G825" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24176,7 +24176,7 @@
         <v>4</v>
       </c>
       <c r="G826" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24202,7 +24202,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G827" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24228,7 +24228,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G828" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24254,7 +24254,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G829" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24280,7 +24280,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G830" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24306,7 +24306,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24332,7 +24332,7 @@
         <v>4</v>
       </c>
       <c r="G832" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24358,7 +24358,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24384,7 +24384,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24410,7 +24410,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24436,7 +24436,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G836" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24462,7 +24462,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24488,7 +24488,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24514,7 +24514,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G839" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24540,7 +24540,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24566,7 +24566,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G841" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24592,7 +24592,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G842" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24618,7 +24618,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24644,7 +24644,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G844" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24670,7 +24670,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G845" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24696,7 +24696,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24722,7 +24722,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24748,7 +24748,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24774,7 +24774,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24800,7 +24800,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G850" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24826,7 +24826,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24852,7 +24852,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24878,7 +24878,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G853" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24904,7 +24904,7 @@
         <v>4.25</v>
       </c>
       <c r="G854" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24930,7 +24930,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24956,7 +24956,7 @@
         <v>4.25</v>
       </c>
       <c r="G856" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24982,7 +24982,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G857" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25008,7 +25008,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G858" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25034,7 +25034,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G859" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25060,7 +25060,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25086,7 +25086,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G861" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25112,7 +25112,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G862" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25138,7 +25138,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G863" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25164,7 +25164,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G864" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25190,7 +25190,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G865" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25242,7 +25242,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G867" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25346,7 +25346,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25398,7 +25398,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G873" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25528,7 +25528,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G878" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25892,7 +25892,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G892" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25970,7 +25970,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G895" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26204,7 +26204,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G904" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -30390,7 +30390,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1065" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30676,7 +30676,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1076" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30702,7 +30702,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1077" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30936,7 +30936,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1086" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31300,7 +31300,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1100" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31404,7 +31404,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1104" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32912,7 +32912,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1162" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32938,7 +32938,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1163" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33380,7 +33380,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1180" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33510,7 +33510,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1185" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33718,7 +33718,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1193" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -67500,7 +67500,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6497337963</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>78315</v>
@@ -67521,6 +67521,32 @@
         <v>785</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.3927662037</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>3780</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>783</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="790">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825955867767</t>
+    <t xml:space="preserve">1.85825932025909</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
@@ -50,70 +50,70 @@
     <t xml:space="preserve">1.92109167575836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8849630355835</t>
+    <t xml:space="preserve">1.88496327400208</t>
   </si>
   <si>
     <t xml:space="preserve">1.9242330789566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80642294883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82998502254486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79856884479523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76715314388275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354697704315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86925518512726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87710905075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281725883484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86768424510956</t>
+    <t xml:space="preserve">1.80642306804657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82998526096344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79856896400452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76715302467346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86925530433655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87710916996002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281737804413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86768448352814</t>
   </si>
   <si>
     <t xml:space="preserve">1.81584775447845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83783900737762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87553799152374</t>
+    <t xml:space="preserve">1.83783888816833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553834915161</t>
   </si>
   <si>
     <t xml:space="preserve">1.82684326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8456928730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898951530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8362683057785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85983037948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80485212802887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82056045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81741845607758</t>
+    <t xml:space="preserve">1.84569299221039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8189891576767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83626818656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8598301410675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80485224723816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8205600976944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81741857528687</t>
   </si>
   <si>
     <t xml:space="preserve">1.85040545463562</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">1.88025057315826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81427681446075</t>
+    <t xml:space="preserve">1.81427669525146</t>
   </si>
   <si>
     <t xml:space="preserve">1.85197639465332</t>
@@ -134,28 +134,28 @@
     <t xml:space="preserve">1.84098064899445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82370185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81113541126251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82213091850281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679988384247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622457027435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407819747925</t>
+    <t xml:space="preserve">1.8237019777298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8111355304718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8221310377121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679976463318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622421264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407831668854</t>
   </si>
   <si>
     <t xml:space="preserve">1.96350336074829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9650741815567</t>
+    <t xml:space="preserve">1.96507394313812</t>
   </si>
   <si>
     <t xml:space="preserve">1.99334859848022</t>
@@ -164,37 +164,37 @@
     <t xml:space="preserve">2.00434422492981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.987065076828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905632972717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02476453781128</t>
+    <t xml:space="preserve">1.98706519603729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905656814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0247642993927</t>
   </si>
   <si>
     <t xml:space="preserve">1.93051636219025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9619323015213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564925670624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637909412384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87396764755249</t>
+    <t xml:space="preserve">1.96193218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994128704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564949512482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637921333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8739675283432</t>
   </si>
   <si>
     <t xml:space="preserve">1.93378710746765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95017540454865</t>
+    <t xml:space="preserve">1.95017516613007</t>
   </si>
   <si>
     <t xml:space="preserve">1.9223153591156</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">1.93050968647003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96656322479248</t>
+    <t xml:space="preserve">1.96656334400177</t>
   </si>
   <si>
     <t xml:space="preserve">1.95509171485901</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">1.91739916801453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9354259967804</t>
+    <t xml:space="preserve">1.93542611598969</t>
   </si>
   <si>
     <t xml:space="preserve">1.9419811964035</t>
@@ -230,31 +230,31 @@
     <t xml:space="preserve">1.83545887470245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80268287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84201419353485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83218145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88298416137695</t>
+    <t xml:space="preserve">1.8026829957962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84201431274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83218133449554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
     <t xml:space="preserve">1.86823523044586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90756630897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281702041626</t>
+    <t xml:space="preserve">1.90756642818451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281713962555</t>
   </si>
   <si>
     <t xml:space="preserve">1.90592765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88462293148041</t>
+    <t xml:space="preserve">1.8846230506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.90920507907867</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">1.8977335691452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82398748397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75843524932861</t>
+    <t xml:space="preserve">1.82398736476898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75843513011932</t>
   </si>
   <si>
     <t xml:space="preserve">1.76662921905518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78629493713379</t>
+    <t xml:space="preserve">1.78629505634308</t>
   </si>
   <si>
     <t xml:space="preserve">1.77646219730377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75188016891479</t>
+    <t xml:space="preserve">1.75188004970551</t>
   </si>
   <si>
     <t xml:space="preserve">1.75351905822754</t>
@@ -293,28 +293,28 @@
     <t xml:space="preserve">1.75024116039276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72074294090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66993999481201</t>
+    <t xml:space="preserve">1.72074282169342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66993987560272</t>
   </si>
   <si>
     <t xml:space="preserve">1.72893679141998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69616067409515</t>
+    <t xml:space="preserve">1.69616091251373</t>
   </si>
   <si>
     <t xml:space="preserve">1.76007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70435464382172</t>
+    <t xml:space="preserve">1.70435476303101</t>
   </si>
   <si>
     <t xml:space="preserve">1.73549199104309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73385322093964</t>
+    <t xml:space="preserve">1.73385310173035</t>
   </si>
   <si>
     <t xml:space="preserve">1.71254873275757</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">1.63060867786407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67157864570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66666233539581</t>
+    <t xml:space="preserve">1.67157876491547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66666221618652</t>
   </si>
   <si>
     <t xml:space="preserve">1.61012375354767</t>
@@ -335,43 +335,43 @@
     <t xml:space="preserve">1.62241470813751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6633847951889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67321765422821</t>
+    <t xml:space="preserve">1.66338467597961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67321753501892</t>
   </si>
   <si>
     <t xml:space="preserve">1.64535772800446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63880264759064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62569224834442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66830122470856</t>
+    <t xml:space="preserve">1.63880276679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62569212913513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66830110549927</t>
   </si>
   <si>
     <t xml:space="preserve">1.65519070625305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64699673652649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63798308372498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59865188598633</t>
+    <t xml:space="preserve">1.64699685573578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63798320293427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59865200519562</t>
   </si>
   <si>
     <t xml:space="preserve">1.62978911399841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58308339118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59537434577942</t>
+    <t xml:space="preserve">1.58308351039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59537446498871</t>
   </si>
   <si>
     <t xml:space="preserve">1.57898640632629</t>
@@ -383,13 +383,13 @@
     <t xml:space="preserve">1.54047453403473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56751477718353</t>
+    <t xml:space="preserve">1.56751465797424</t>
   </si>
   <si>
     <t xml:space="preserve">1.56997299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56669521331787</t>
+    <t xml:space="preserve">1.56669533252716</t>
   </si>
   <si>
     <t xml:space="preserve">1.5585013628006</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">1.6060266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51917004585266</t>
+    <t xml:space="preserve">1.51917016506195</t>
   </si>
   <si>
     <t xml:space="preserve">1.56177890300751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54539108276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37659430503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41264796257019</t>
+    <t xml:space="preserve">1.54539096355438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37659418582916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4126478433609</t>
   </si>
   <si>
     <t xml:space="preserve">1.39462113380432</t>
@@ -425,13 +425,13 @@
     <t xml:space="preserve">1.45771503448486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47082543373108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53391921520233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61258184909821</t>
+    <t xml:space="preserve">1.47082531452179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53391933441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61258172988892</t>
   </si>
   <si>
     <t xml:space="preserve">1.61176240444183</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">1.54211330413818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51179563999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5552237033844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56505656242371</t>
+    <t xml:space="preserve">1.51179552078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55522358417511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.565056681633</t>
   </si>
   <si>
     <t xml:space="preserve">1.56423723697662</t>
@@ -458,19 +458,19 @@
     <t xml:space="preserve">1.59291613101959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55686259269714</t>
+    <t xml:space="preserve">1.55686247348785</t>
   </si>
   <si>
     <t xml:space="preserve">1.52162826061249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54129385948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50442087650299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51097619533539</t>
+    <t xml:space="preserve">1.5412939786911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5044207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5109760761261</t>
   </si>
   <si>
     <t xml:space="preserve">1.55112671852112</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">1.51589250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55194628238678</t>
+    <t xml:space="preserve">1.55194616317749</t>
   </si>
   <si>
     <t xml:space="preserve">1.50851774215698</t>
@@ -503,34 +503,34 @@
     <t xml:space="preserve">1.51015675067902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57325053215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58554148674011</t>
+    <t xml:space="preserve">1.57325065135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5855416059494</t>
   </si>
   <si>
     <t xml:space="preserve">1.59455502033234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60684597492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62159538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5716118812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54375207424164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57243132591248</t>
+    <t xml:space="preserve">1.60684609413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62159526348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57161176204681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54375219345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57243120670319</t>
   </si>
   <si>
     <t xml:space="preserve">1.58718037605286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54621028900146</t>
+    <t xml:space="preserve">1.54621040821075</t>
   </si>
   <si>
     <t xml:space="preserve">1.55768203735352</t>
@@ -539,16 +539,16 @@
     <t xml:space="preserve">1.58799982070923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5347386598587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58226382732391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54702973365784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53883576393127</t>
+    <t xml:space="preserve">1.53473877906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5822639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54702961444855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53883564472198</t>
   </si>
   <si>
     <t xml:space="preserve">1.54784917831421</t>
@@ -560,34 +560,34 @@
     <t xml:space="preserve">1.54948794841766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53801620006561</t>
+    <t xml:space="preserve">1.5380163192749</t>
   </si>
   <si>
     <t xml:space="preserve">1.54866850376129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53637742996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53965497016907</t>
+    <t xml:space="preserve">1.53637754917145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53965508937836</t>
   </si>
   <si>
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191304683685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69288313388824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65355169773102</t>
+    <t xml:space="preserve">1.65191316604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69288325309753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65355181694031</t>
   </si>
   <si>
     <t xml:space="preserve">1.82070970535278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82890379428864</t>
+    <t xml:space="preserve">1.82890391349792</t>
   </si>
   <si>
     <t xml:space="preserve">1.81743216514587</t>
@@ -599,16 +599,16 @@
     <t xml:space="preserve">1.87970662117004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79448890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80104398727417</t>
+    <t xml:space="preserve">1.79448902606964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80104410648346</t>
   </si>
   <si>
     <t xml:space="preserve">1.73876953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729814052582</t>
+    <t xml:space="preserve">1.72729802131653</t>
   </si>
   <si>
     <t xml:space="preserve">1.74696373939514</t>
@@ -617,16 +617,16 @@
     <t xml:space="preserve">1.76335167884827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8469306230545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81087708473206</t>
+    <t xml:space="preserve">1.84693050384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81087696552277</t>
   </si>
   <si>
     <t xml:space="preserve">1.80923819541931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81251585483551</t>
+    <t xml:space="preserve">1.81251561641693</t>
   </si>
   <si>
     <t xml:space="preserve">1.86167979240417</t>
@@ -638,70 +638,70 @@
     <t xml:space="preserve">1.85840201377869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87642896175385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89937245845795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84856963157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92479646205902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679428100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850803375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97107350826263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822444438934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94193601608276</t>
+    <t xml:space="preserve">1.87642884254456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89937257766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84856939315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92479658126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679416179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850827217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107362747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822420597076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94193613529205</t>
   </si>
   <si>
     <t xml:space="preserve">1.94364988803864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95907580852509</t>
+    <t xml:space="preserve">1.95907592773438</t>
   </si>
   <si>
     <t xml:space="preserve">1.96764576435089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92651033401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95393407344818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93336641788483</t>
+    <t xml:space="preserve">1.92651009559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95393395423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93336629867554</t>
   </si>
   <si>
     <t xml:space="preserve">1.90594255924225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8939448595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8716629743576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92993855476379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90080070495605</t>
+    <t xml:space="preserve">1.89394474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87166309356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92993831634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90080058574677</t>
   </si>
   <si>
     <t xml:space="preserve">1.91451239585876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88708865642548</t>
+    <t xml:space="preserve">1.88708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">1.87680494785309</t>
@@ -713,55 +713,55 @@
     <t xml:space="preserve">1.8853747844696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86994886398315</t>
+    <t xml:space="preserve">1.86994910240173</t>
   </si>
   <si>
     <t xml:space="preserve">1.88880300521851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90937054157257</t>
+    <t xml:space="preserve">1.90937030315399</t>
   </si>
   <si>
     <t xml:space="preserve">1.90251469612122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96421790122986</t>
+    <t xml:space="preserve">1.96421778202057</t>
   </si>
   <si>
     <t xml:space="preserve">1.96250379085541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821353912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98649966716766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964346408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12533164024353</t>
+    <t xml:space="preserve">1.98821365833282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98649954795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97964334487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12533140182495</t>
   </si>
   <si>
     <t xml:space="preserve">2.08591032028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05677270889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07905411720276</t>
+    <t xml:space="preserve">2.05677247047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07905435562134</t>
   </si>
   <si>
     <t xml:space="preserve">2.0807683467865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06534242630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06020045280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07219815254211</t>
+    <t xml:space="preserve">2.06534266471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06020069122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07219839096069</t>
   </si>
   <si>
     <t xml:space="preserve">2.13390159606934</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">2.10819172859192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09962201118469</t>
+    <t xml:space="preserve">2.09962224960327</t>
   </si>
   <si>
     <t xml:space="preserve">2.10304999351501</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">2.03963279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06877040863037</t>
+    <t xml:space="preserve">2.06877017021179</t>
   </si>
   <si>
     <t xml:space="preserve">2.11504793167114</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">2.07391238212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09790802001953</t>
+    <t xml:space="preserve">2.09790778160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.1167619228363</t>
@@ -797,31 +797,31 @@
     <t xml:space="preserve">2.08248233795166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06705617904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12190389633179</t>
+    <t xml:space="preserve">2.06705641746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12190365791321</t>
   </si>
   <si>
     <t xml:space="preserve">2.10647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0893383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05163049697876</t>
+    <t xml:space="preserve">2.08933806419373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05163073539734</t>
   </si>
   <si>
     <t xml:space="preserve">2.17675089836121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14247179031372</t>
+    <t xml:space="preserve">2.14247155189514</t>
   </si>
   <si>
     <t xml:space="preserve">2.1321873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13047385215759</t>
+    <t xml:space="preserve">2.13047361373901</t>
   </si>
   <si>
     <t xml:space="preserve">2.15961098670959</t>
@@ -833,19 +833,19 @@
     <t xml:space="preserve">2.09105205535889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12361764907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11161994934082</t>
+    <t xml:space="preserve">2.12361741065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11161971092224</t>
   </si>
   <si>
     <t xml:space="preserve">2.10133600234985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15789723396301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15618324279785</t>
+    <t xml:space="preserve">2.15789699554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15618348121643</t>
   </si>
   <si>
     <t xml:space="preserve">2.1441855430603</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">2.1407573223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14932703971863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13904356956482</t>
+    <t xml:space="preserve">2.14932727813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13904333114624</t>
   </si>
   <si>
     <t xml:space="preserve">2.17503714561462</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">2.15104126930237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12018966674805</t>
+    <t xml:space="preserve">2.12018990516663</t>
   </si>
   <si>
     <t xml:space="preserve">2.1047637462616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06362819671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03277707099915</t>
+    <t xml:space="preserve">2.06362843513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03277683258057</t>
   </si>
   <si>
     <t xml:space="preserve">2.0482029914856</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">2.07048416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0499165058136</t>
+    <t xml:space="preserve">2.04991674423218</t>
   </si>
   <si>
     <t xml:space="preserve">2.12875962257385</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">2.08762431144714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0207793712616</t>
+    <t xml:space="preserve">2.02077913284302</t>
   </si>
   <si>
     <t xml:space="preserve">2.08419609069824</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">2.00535321235657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1681809425354</t>
+    <t xml:space="preserve">2.16818118095398</t>
   </si>
   <si>
     <t xml:space="preserve">2.18532085418701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29672932624817</t>
+    <t xml:space="preserve">2.29672956466675</t>
   </si>
   <si>
     <t xml:space="preserve">2.33100891113281</t>
@@ -923,10 +923,10 @@
     <t xml:space="preserve">2.32243895530701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35671854019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44241738319397</t>
+    <t xml:space="preserve">2.35671830177307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44241714477539</t>
   </si>
   <si>
     <t xml:space="preserve">2.49383687973022</t>
@@ -938,22 +938,22 @@
     <t xml:space="preserve">2.47669696807861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48526692390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53668642044067</t>
+    <t xml:space="preserve">2.48526668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53668618202209</t>
   </si>
   <si>
     <t xml:space="preserve">2.57953548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.596675157547</t>
+    <t xml:space="preserve">2.59667539596558</t>
   </si>
   <si>
     <t xml:space="preserve">2.61381506919861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55382585525513</t>
+    <t xml:space="preserve">2.55382561683655</t>
   </si>
   <si>
     <t xml:space="preserve">2.63447332382202</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">2.50006127357483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45525717735291</t>
+    <t xml:space="preserve">2.45525741577148</t>
   </si>
   <si>
     <t xml:space="preserve">2.54486513137817</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">2.57174754142761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51798272132874</t>
+    <t xml:space="preserve">2.51798295974731</t>
   </si>
   <si>
     <t xml:space="preserve">2.56278681755066</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">2.53590416908264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49110054969788</t>
+    <t xml:space="preserve">2.4911003112793</t>
   </si>
   <si>
     <t xml:space="preserve">2.48213958740234</t>
@@ -1007,25 +1007,25 @@
     <t xml:space="preserve">2.50902199745178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47317886352539</t>
+    <t xml:space="preserve">2.47317862510681</t>
   </si>
   <si>
     <t xml:space="preserve">2.78680658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7599241733551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77784585952759</t>
+    <t xml:space="preserve">2.75992441177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77784562110901</t>
   </si>
   <si>
     <t xml:space="preserve">2.74200248718262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76888513565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71512031555176</t>
+    <t xml:space="preserve">2.76888489723206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71512007713318</t>
   </si>
   <si>
     <t xml:space="preserve">2.75096321105957</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">2.65239477157593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68823790550232</t>
+    <t xml:space="preserve">2.68823766708374</t>
   </si>
   <si>
     <t xml:space="preserve">2.73304176330566</t>
@@ -1055,22 +1055,22 @@
     <t xml:space="preserve">2.84953236579895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86745381355286</t>
+    <t xml:space="preserve">2.86745357513428</t>
   </si>
   <si>
     <t xml:space="preserve">2.83161067962646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64343404769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62551259994507</t>
+    <t xml:space="preserve">2.6434338092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62551236152649</t>
   </si>
   <si>
     <t xml:space="preserve">2.58070850372314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.607590675354</t>
+    <t xml:space="preserve">2.60759091377258</t>
   </si>
   <si>
     <t xml:space="preserve">2.41941404342651</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">2.81368899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.840571641922</t>
+    <t xml:space="preserve">2.84057140350342</t>
   </si>
   <si>
     <t xml:space="preserve">2.93914008140564</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">2.90329694747925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12731671333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16315960884094</t>
+    <t xml:space="preserve">3.12731647491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16315984725952</t>
   </si>
   <si>
     <t xml:space="preserve">3.13627743721008</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19004225730896</t>
+    <t xml:space="preserve">3.19004201889038</t>
   </si>
   <si>
     <t xml:space="preserve">3.25276780128479</t>
@@ -1118,22 +1118,22 @@
     <t xml:space="preserve">3.26172852516174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28861093521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29757165908813</t>
+    <t xml:space="preserve">3.28861117362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29757189750671</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33341479301453</t>
+    <t xml:space="preserve">3.33341503143311</t>
   </si>
   <si>
     <t xml:space="preserve">3.34237575531006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42302274703979</t>
+    <t xml:space="preserve">3.42302298545837</t>
   </si>
   <si>
     <t xml:space="preserve">3.3871796131134</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">3.37821888923645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45886588096619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4857485294342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47678756713867</t>
+    <t xml:space="preserve">3.45886564254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48574876785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47678780555725</t>
   </si>
   <si>
     <t xml:space="preserve">3.49470925331116</t>
@@ -1166,37 +1166,37 @@
     <t xml:space="preserve">3.67392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58431720733643</t>
+    <t xml:space="preserve">3.58431696891785</t>
   </si>
   <si>
     <t xml:space="preserve">3.53055238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59327816963196</t>
+    <t xml:space="preserve">3.59327793121338</t>
   </si>
   <si>
     <t xml:space="preserve">3.55743479728699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5215916633606</t>
+    <t xml:space="preserve">3.52159142494202</t>
   </si>
   <si>
     <t xml:space="preserve">3.51263093948364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5395131111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60223865509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65600347518921</t>
+    <t xml:space="preserve">3.53951334953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60223889350891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65600323677063</t>
   </si>
   <si>
     <t xml:space="preserve">3.66496443748474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72768974304199</t>
+    <t xml:space="preserve">3.72768998146057</t>
   </si>
   <si>
     <t xml:space="preserve">3.71872925758362</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">3.6918466091156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70976805686951</t>
+    <t xml:space="preserve">3.70976781845093</t>
   </si>
   <si>
     <t xml:space="preserve">3.68288588523865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7635326385498</t>
+    <t xml:space="preserve">3.76353287696838</t>
   </si>
   <si>
     <t xml:space="preserve">3.78145432472229</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">3.80833721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79041528701782</t>
+    <t xml:space="preserve">3.79041504859924</t>
   </si>
   <si>
     <t xml:space="preserve">3.95170950889587</t>
@@ -1232,13 +1232,13 @@
     <t xml:space="preserve">3.97005581855774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00759744644165</t>
+    <t xml:space="preserve">4.00759792327881</t>
   </si>
   <si>
     <t xml:space="preserve">4.0920672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81988859176636</t>
+    <t xml:space="preserve">3.81988835334778</t>
   </si>
   <si>
     <t xml:space="preserve">3.87620115280151</t>
@@ -1262,40 +1262,40 @@
     <t xml:space="preserve">4.03575468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9982123374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97944116592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85743045806885</t>
+    <t xml:space="preserve">3.99821257591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97944092750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85743021965027</t>
   </si>
   <si>
     <t xml:space="preserve">3.84804463386536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81050276756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74480438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89497208595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.941899061203</t>
+    <t xml:space="preserve">3.81050252914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7448046207428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89497232437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94189953804016</t>
   </si>
   <si>
     <t xml:space="preserve">3.8668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93251419067383</t>
+    <t xml:space="preserve">3.93251395225525</t>
   </si>
   <si>
     <t xml:space="preserve">4.08268165588379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11083841323853</t>
+    <t xml:space="preserve">4.11083793640137</t>
   </si>
   <si>
     <t xml:space="preserve">4.12022304534912</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">4.18592166900635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1953067779541</t>
+    <t xml:space="preserve">4.19530725479126</t>
   </si>
   <si>
     <t xml:space="preserve">4.20469284057617</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">4.28916215896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26100540161133</t>
+    <t xml:space="preserve">4.26100587844849</t>
   </si>
   <si>
     <t xml:space="preserve">4.2703914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34547519683838</t>
+    <t xml:space="preserve">4.34547472000122</t>
   </si>
   <si>
     <t xml:space="preserve">4.36424589157104</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">4.50502824783325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49564218521118</t>
+    <t xml:space="preserve">4.49564266204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.43932962417603</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">4.5519552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54256963729858</t>
+    <t xml:space="preserve">4.54257011413574</t>
   </si>
   <si>
     <t xml:space="preserve">4.48625707626343</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">4.40178775787354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44871473312378</t>
+    <t xml:space="preserve">4.44871520996094</t>
   </si>
   <si>
     <t xml:space="preserve">4.42994403839111</t>
@@ -1373,13 +1373,13 @@
     <t xml:space="preserve">4.41117334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39240217208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2422342300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30793285369873</t>
+    <t xml:space="preserve">4.39240169525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24223470687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30793333053589</t>
   </si>
   <si>
     <t xml:space="preserve">4.17653608322144</t>
@@ -1397,28 +1397,28 @@
     <t xml:space="preserve">4.62703895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61765384674072</t>
+    <t xml:space="preserve">4.61765336990356</t>
   </si>
   <si>
     <t xml:space="preserve">4.51441335678101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57072639465332</t>
+    <t xml:space="preserve">4.57072591781616</t>
   </si>
   <si>
     <t xml:space="preserve">4.67396640777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80536317825317</t>
+    <t xml:space="preserve">4.80536270141602</t>
   </si>
   <si>
     <t xml:space="preserve">4.78659200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86167573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84290456771851</t>
+    <t xml:space="preserve">4.86167621612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84290504455566</t>
   </si>
   <si>
     <t xml:space="preserve">4.89921760559082</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">4.5988826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53318452835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58011198043823</t>
+    <t xml:space="preserve">4.53318405151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58011150360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.6927375793457</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">4.74905014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73027896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71150875091553</t>
+    <t xml:space="preserve">4.73027944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71150827407837</t>
   </si>
   <si>
     <t xml:space="preserve">4.76782131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95553064346313</t>
+    <t xml:space="preserve">4.95553112030029</t>
   </si>
   <si>
     <t xml:space="preserve">4.88044691085815</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">4.91798877716064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99307298660278</t>
+    <t xml:space="preserve">4.99307250976562</t>
   </si>
   <si>
     <t xml:space="preserve">4.93675994873047</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">6.60737419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28826761245728</t>
+    <t xml:space="preserve">6.28826808929443</t>
   </si>
   <si>
     <t xml:space="preserve">6.1568717956543</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">5.96916246414185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7063684463501</t>
+    <t xml:space="preserve">5.70636892318726</t>
   </si>
   <si>
     <t xml:space="preserve">5.53743028640747</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">5.87530755996704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66882705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68759775161743</t>
+    <t xml:space="preserve">5.66882658004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68759727478027</t>
   </si>
   <si>
     <t xml:space="preserve">5.83776521682739</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59374332427979</t>
+    <t xml:space="preserve">5.59374284744263</t>
   </si>
   <si>
     <t xml:space="preserve">5.38726234436035</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">5.10569858551025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68335151672363</t>
+    <t xml:space="preserve">4.68335199356079</t>
   </si>
   <si>
     <t xml:space="preserve">4.14837980270386</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">3.62279319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55709505081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37877106666565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50078201293945</t>
+    <t xml:space="preserve">3.55709481239319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37877082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50078225135803</t>
   </si>
   <si>
     <t xml:space="preserve">3.5664803981781</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">3.75418996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70726275444031</t>
+    <t xml:space="preserve">3.70726251602173</t>
   </si>
   <si>
     <t xml:space="preserve">3.71664810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83865928649902</t>
+    <t xml:space="preserve">3.8386595249176</t>
   </si>
   <si>
     <t xml:space="preserve">4.25162029266357</t>
@@ -1583,25 +1583,25 @@
     <t xml:space="preserve">4.12960910797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16715097427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05452489852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76357579231262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66972088813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65094971656799</t>
+    <t xml:space="preserve">4.16715049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05452537536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76357555389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66972064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65094995498657</t>
   </si>
   <si>
     <t xml:space="preserve">3.66033530235291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95128488540649</t>
+    <t xml:space="preserve">3.95128512382507</t>
   </si>
   <si>
     <t xml:space="preserve">4.29854726791382</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">4.31731843948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15776538848877</t>
+    <t xml:space="preserve">4.15776491165161</t>
   </si>
   <si>
     <t xml:space="preserve">4.10145235061646</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">4.13899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88558650016785</t>
+    <t xml:space="preserve">3.88558626174927</t>
   </si>
   <si>
     <t xml:space="preserve">4.32670402526855</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">4.27977657318115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91374325752258</t>
+    <t xml:space="preserve">3.913743019104</t>
   </si>
   <si>
     <t xml:space="preserve">3.92312836647034</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">3.49139666557312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67910599708557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3881561756134</t>
+    <t xml:space="preserve">3.67910623550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38815641403198</t>
   </si>
   <si>
     <t xml:space="preserve">3.35999989509583</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">3.34122896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20044684410095</t>
+    <t xml:space="preserve">3.20044708251953</t>
   </si>
   <si>
     <t xml:space="preserve">3.24737429618835</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">3.47262573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57586598396301</t>
+    <t xml:space="preserve">3.57586574554443</t>
   </si>
   <si>
     <t xml:space="preserve">3.73541903495789</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">3.68849158287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72603344917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52893877029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63217854499817</t>
+    <t xml:space="preserve">3.72603368759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52893853187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63217878341675</t>
   </si>
   <si>
     <t xml:space="preserve">3.51016759872437</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">3.58525133132935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53832387924194</t>
+    <t xml:space="preserve">3.53832411766052</t>
   </si>
   <si>
     <t xml:space="preserve">3.80111742019653</t>
@@ -1730,10 +1730,10 @@
     <t xml:space="preserve">3.48201107978821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46324038505554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44446921348572</t>
+    <t xml:space="preserve">3.46324014663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4444694519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.42569851875305</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">3.41631293296814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754176139832</t>
+    <t xml:space="preserve">3.39754199981689</t>
   </si>
   <si>
     <t xml:space="preserve">3.21921801567078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19106149673462</t>
+    <t xml:space="preserve">3.1910617351532</t>
   </si>
   <si>
     <t xml:space="preserve">3.17229056358337</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">3.23798894882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14413380622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25675988197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36938548088074</t>
+    <t xml:space="preserve">3.14413404464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25675964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36938524246216</t>
   </si>
   <si>
     <t xml:space="preserve">3.15351939201355</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">3.18167614936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29430150985718</t>
+    <t xml:space="preserve">3.29430174827576</t>
   </si>
   <si>
     <t xml:space="preserve">3.2661452293396</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">3.12536311149597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04089403152466</t>
+    <t xml:space="preserve">3.04089379310608</t>
   </si>
   <si>
     <t xml:space="preserve">3.05027914047241</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">2.93765377998352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95642471313477</t>
+    <t xml:space="preserve">2.95642447471619</t>
   </si>
   <si>
     <t xml:space="preserve">3.03150844573975</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">3.02212285995483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92826819419861</t>
+    <t xml:space="preserve">2.92826795578003</t>
   </si>
   <si>
     <t xml:space="preserve">2.94703912734985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90011143684387</t>
+    <t xml:space="preserve">2.90011167526245</t>
   </si>
   <si>
     <t xml:space="preserve">2.97519564628601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27553081512451</t>
+    <t xml:space="preserve">3.27553057670593</t>
   </si>
   <si>
     <t xml:space="preserve">3.33184361457825</t>
@@ -2379,6 +2379,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.47000002861023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49000000953674</t>
   </si>
 </sst>
 </file>
@@ -67639,7 +67642,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6574074074</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>5890</v>
@@ -67660,6 +67663,32 @@
         <v>788</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6910648148</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>10887</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>789</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -38,73 +38,73 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825943946838</t>
+    <t xml:space="preserve">1.85825932025909</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9132376909256</t>
+    <t xml:space="preserve">1.91323781013489</t>
   </si>
   <si>
     <t xml:space="preserve">1.92109143733978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88496327400208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92423319816589</t>
+    <t xml:space="preserve">1.8849630355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92423331737518</t>
   </si>
   <si>
     <t xml:space="preserve">1.80642294883728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82998478412628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79856896400452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76715290546417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354697704315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86925530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87710928916931</t>
+    <t xml:space="preserve">1.82998502254486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79856884479523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76715302467346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86925506591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8771094083786</t>
   </si>
   <si>
     <t xml:space="preserve">1.89281713962555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86768436431885</t>
+    <t xml:space="preserve">1.86768412590027</t>
   </si>
   <si>
     <t xml:space="preserve">1.81584787368774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83783876895905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87553834915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684338092804</t>
+    <t xml:space="preserve">1.83783900737762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553822994232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684350013733</t>
   </si>
   <si>
     <t xml:space="preserve">1.8456928730011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81898951530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8362683057785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85983049869537</t>
+    <t xml:space="preserve">1.81898927688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83626818656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85983002185822</t>
   </si>
   <si>
     <t xml:space="preserve">1.80485212802887</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">1.8205600976944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81741869449615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85040533542633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88025069236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81427681446075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85197591781616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84412229061127</t>
+    <t xml:space="preserve">1.81741857528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85040557384491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88025081157684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81427705287933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85197615623474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84412205219269</t>
   </si>
   <si>
     <t xml:space="preserve">1.84098064899445</t>
@@ -137,109 +137,109 @@
     <t xml:space="preserve">1.82370173931122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81113541126251</t>
+    <t xml:space="preserve">1.81113517284393</t>
   </si>
   <si>
     <t xml:space="preserve">1.82213091850281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9367995262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622409343719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407843589783</t>
+    <t xml:space="preserve">1.93679976463318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622445106506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407807826996</t>
   </si>
   <si>
     <t xml:space="preserve">1.96350347995758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96507441997528</t>
+    <t xml:space="preserve">1.9650741815567</t>
   </si>
   <si>
     <t xml:space="preserve">1.99334859848022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00434422492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98706531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905632972717</t>
+    <t xml:space="preserve">2.00434398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98706519603729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905656814575</t>
   </si>
   <si>
     <t xml:space="preserve">2.02476453781128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93051648139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96193242073059</t>
+    <t xml:space="preserve">1.93051636219025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96193218231201</t>
   </si>
   <si>
     <t xml:space="preserve">1.93994128704071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95564937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637897491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87396740913391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378698825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017528533936</t>
+    <t xml:space="preserve">1.95564901828766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637945175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87396728992462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378710746765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017516613007</t>
   </si>
   <si>
     <t xml:space="preserve">1.9223153591156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93050956726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656334400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509135723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95836901664734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739881038666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9354259967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198131561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91248261928558</t>
+    <t xml:space="preserve">1.93050968647003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656310558319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9583694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739904880524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542587757111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9419811964035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91248285770416</t>
   </si>
   <si>
     <t xml:space="preserve">1.91084396839142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83545911312103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80268311500549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84201431274414</t>
+    <t xml:space="preserve">1.83545887470245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8026829957962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84201419353485</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88298439979553</t>
+    <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
     <t xml:space="preserve">1.86823511123657</t>
@@ -248,13 +248,10 @@
     <t xml:space="preserve">1.90756642818451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89281690120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592753887177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88462293148041</t>
+    <t xml:space="preserve">1.90592765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8846230506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.90920507907867</t>
@@ -263,13 +260,13 @@
     <t xml:space="preserve">1.87151265144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8977335691452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82398760318756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75843513011932</t>
+    <t xml:space="preserve">1.89773344993591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82398736476898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75843524932861</t>
   </si>
   <si>
     <t xml:space="preserve">1.76662921905518</t>
@@ -278,34 +275,34 @@
     <t xml:space="preserve">1.78629505634308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77646207809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75188016891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75351893901825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77973973751068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75024127960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72074282169342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66993999481201</t>
+    <t xml:space="preserve">1.77646219730377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75188004970551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75351905822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77973985671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75024116039276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72074270248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66993987560272</t>
   </si>
   <si>
     <t xml:space="preserve">1.72893667221069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69616067409515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76007401943207</t>
+    <t xml:space="preserve">1.69616079330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76007425785065</t>
   </si>
   <si>
     <t xml:space="preserve">1.70435464382172</t>
@@ -323,13 +320,13 @@
     <t xml:space="preserve">1.63060867786407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67157876491547</t>
+    <t xml:space="preserve">1.67157864570618</t>
   </si>
   <si>
     <t xml:space="preserve">1.66666233539581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61012351512909</t>
+    <t xml:space="preserve">1.61012363433838</t>
   </si>
   <si>
     <t xml:space="preserve">1.62241470813751</t>
@@ -341,13 +338,13 @@
     <t xml:space="preserve">1.67321753501892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64535760879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63880264759064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62569224834442</t>
+    <t xml:space="preserve">1.64535784721375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63880276679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62569212913513</t>
   </si>
   <si>
     <t xml:space="preserve">1.66830110549927</t>
@@ -362,10 +359,10 @@
     <t xml:space="preserve">1.63798320293427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59865212440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62978935241699</t>
+    <t xml:space="preserve">1.59865200519562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6297892332077</t>
   </si>
   <si>
     <t xml:space="preserve">1.58308339118958</t>
@@ -374,7 +371,7 @@
     <t xml:space="preserve">1.59537446498871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.578986287117</t>
+    <t xml:space="preserve">1.57898640632629</t>
   </si>
   <si>
     <t xml:space="preserve">1.59127736091614</t>
@@ -383,10 +380,10 @@
     <t xml:space="preserve">1.54047453403473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56751489639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56997311115265</t>
+    <t xml:space="preserve">1.56751465797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56997299194336</t>
   </si>
   <si>
     <t xml:space="preserve">1.56669533252716</t>
@@ -398,7 +395,7 @@
     <t xml:space="preserve">1.6027489900589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60356843471527</t>
+    <t xml:space="preserve">1.60356855392456</t>
   </si>
   <si>
     <t xml:space="preserve">1.6060266494751</t>
@@ -419,22 +416,22 @@
     <t xml:space="preserve">1.4126478433609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39462101459503</t>
+    <t xml:space="preserve">1.39462113380432</t>
   </si>
   <si>
     <t xml:space="preserve">1.45771503448486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4708251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53391921520233</t>
+    <t xml:space="preserve">1.47082543373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53391933441162</t>
   </si>
   <si>
     <t xml:space="preserve">1.61258184909821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61176252365112</t>
+    <t xml:space="preserve">1.61176240444183</t>
   </si>
   <si>
     <t xml:space="preserve">1.59783267974854</t>
@@ -449,28 +446,28 @@
     <t xml:space="preserve">1.5552237033844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56505644321442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56423723697662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59291625022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55686259269714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52162837982178</t>
+    <t xml:space="preserve">1.56505656242371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56423711776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59291613101959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55686247348785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5216281414032</t>
   </si>
   <si>
     <t xml:space="preserve">1.5412939786911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50442087650299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5109760761261</t>
+    <t xml:space="preserve">1.5044207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51097619533539</t>
   </si>
   <si>
     <t xml:space="preserve">1.55112671852112</t>
@@ -482,7 +479,7 @@
     <t xml:space="preserve">1.55194616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50851786136627</t>
+    <t xml:space="preserve">1.50851774215698</t>
   </si>
   <si>
     <t xml:space="preserve">1.53228056430817</t>
@@ -491,10 +488,10 @@
     <t xml:space="preserve">1.50933730602264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5076984167099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50278198719025</t>
+    <t xml:space="preserve">1.50769853591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50278210639954</t>
   </si>
   <si>
     <t xml:space="preserve">1.49540746212006</t>
@@ -506,22 +503,22 @@
     <t xml:space="preserve">1.57325053215027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5855416059494</t>
+    <t xml:space="preserve">1.58554148674011</t>
   </si>
   <si>
     <t xml:space="preserve">1.59455502033234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60684597492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62159538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57161176204681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54375207424164</t>
+    <t xml:space="preserve">1.60684621334076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62159526348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5716118812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54375219345093</t>
   </si>
   <si>
     <t xml:space="preserve">1.57243120670319</t>
@@ -533,25 +530,25 @@
     <t xml:space="preserve">1.54621040821075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55768191814423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58799982070923</t>
+    <t xml:space="preserve">1.55768203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58799993991852</t>
   </si>
   <si>
     <t xml:space="preserve">1.53473877906799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58226406574249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54702973365784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53883576393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54784905910492</t>
+    <t xml:space="preserve">1.5822639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54702961444855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53883564472198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54784917831421</t>
   </si>
   <si>
     <t xml:space="preserve">1.55276548862457</t>
@@ -563,7 +560,7 @@
     <t xml:space="preserve">1.5380163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54866862297058</t>
+    <t xml:space="preserve">1.548668384552</t>
   </si>
   <si>
     <t xml:space="preserve">1.53637754917145</t>
@@ -575,25 +572,25 @@
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191304683685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69288313388824</t>
+    <t xml:space="preserve">1.65191316604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69288325309753</t>
   </si>
   <si>
     <t xml:space="preserve">1.65355181694031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82070958614349</t>
+    <t xml:space="preserve">1.82070970535278</t>
   </si>
   <si>
     <t xml:space="preserve">1.82890391349792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81743228435516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579339504242</t>
+    <t xml:space="preserve">1.81743216514587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81579351425171</t>
   </si>
   <si>
     <t xml:space="preserve">1.87970674037933</t>
@@ -605,31 +602,31 @@
     <t xml:space="preserve">1.80104410648346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73876953125</t>
+    <t xml:space="preserve">1.73876941204071</t>
   </si>
   <si>
     <t xml:space="preserve">1.72729802131653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74696350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76335167884827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84693050384521</t>
+    <t xml:space="preserve">1.74696373939514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76335155963898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8469306230545</t>
   </si>
   <si>
     <t xml:space="preserve">1.81087696552277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80923795700073</t>
+    <t xml:space="preserve">1.80923807621002</t>
   </si>
   <si>
     <t xml:space="preserve">1.81251561641693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86167991161346</t>
+    <t xml:space="preserve">1.86167979240417</t>
   </si>
   <si>
     <t xml:space="preserve">1.86495745182037</t>
@@ -638,7 +635,7 @@
     <t xml:space="preserve">1.85840213298798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87642896175385</t>
+    <t xml:space="preserve">1.87642884254456</t>
   </si>
   <si>
     <t xml:space="preserve">1.89937233924866</t>
@@ -647,31 +644,31 @@
     <t xml:space="preserve">1.84856951236725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92479634284973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679428100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850827217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97107374668121</t>
+    <t xml:space="preserve">1.92479658126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679416179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850803375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107362747192</t>
   </si>
   <si>
     <t xml:space="preserve">1.92822444438934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94193601608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94365000724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95907580852509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9676456451416</t>
+    <t xml:space="preserve">1.94193589687347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94364976882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95907592773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96764576435089</t>
   </si>
   <si>
     <t xml:space="preserve">1.92651033401489</t>
@@ -686,13 +683,13 @@
     <t xml:space="preserve">1.90594255924225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89394474029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87166309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92993819713593</t>
+    <t xml:space="preserve">1.8939448595047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8716629743576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9299384355545</t>
   </si>
   <si>
     <t xml:space="preserve">1.90080070495605</t>
@@ -707,22 +704,22 @@
     <t xml:space="preserve">1.87680494785309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91794049739838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88537490367889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86994910240173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88880276679993</t>
+    <t xml:space="preserve">1.91794037818909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8853747844696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86994898319244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88880288600922</t>
   </si>
   <si>
     <t xml:space="preserve">1.90937042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90251445770264</t>
+    <t xml:space="preserve">1.90251469612122</t>
   </si>
   <si>
     <t xml:space="preserve">1.96421778202057</t>
@@ -731,10 +728,10 @@
     <t xml:space="preserve">1.96250379085541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821341991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98649966716766</t>
+    <t xml:space="preserve">1.98821365833282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98649954795837</t>
   </si>
   <si>
     <t xml:space="preserve">1.97964334487915</t>
@@ -743,31 +740,31 @@
     <t xml:space="preserve">2.12533164024353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0859100818634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05677270889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07905459403992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08076786994934</t>
+    <t xml:space="preserve">2.08591032028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05677247047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07905435562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0807683467865</t>
   </si>
   <si>
     <t xml:space="preserve">2.06534242630005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06020069122314</t>
+    <t xml:space="preserve">2.06020045280457</t>
   </si>
   <si>
     <t xml:space="preserve">2.07219839096069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13390135765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10819172859192</t>
+    <t xml:space="preserve">2.13390159606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1081919670105</t>
   </si>
   <si>
     <t xml:space="preserve">2.09962201118469</t>
@@ -776,19 +773,19 @@
     <t xml:space="preserve">2.10304975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03963279724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06877064704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11504769325256</t>
+    <t xml:space="preserve">2.03963303565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06877040863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11504793167114</t>
   </si>
   <si>
     <t xml:space="preserve">2.07391238212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09790802001953</t>
+    <t xml:space="preserve">2.09790778160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.1167619228363</t>
@@ -800,7 +797,7 @@
     <t xml:space="preserve">2.06705641746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12190365791321</t>
+    <t xml:space="preserve">2.12190389633179</t>
   </si>
   <si>
     <t xml:space="preserve">2.10647797584534</t>
@@ -809,25 +806,25 @@
     <t xml:space="preserve">2.08933806419373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05163049697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17675113677979</t>
+    <t xml:space="preserve">2.05163073539734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17675089836121</t>
   </si>
   <si>
     <t xml:space="preserve">2.14247155189514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13218760490417</t>
+    <t xml:space="preserve">2.1321873664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.13047361373901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15961122512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11847543716431</t>
+    <t xml:space="preserve">2.15961098670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11847567558289</t>
   </si>
   <si>
     <t xml:space="preserve">2.09105205535889</t>
@@ -839,16 +836,16 @@
     <t xml:space="preserve">2.11161994934082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10133600234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15789723396301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15618300437927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1441855430603</t>
+    <t xml:space="preserve">2.10133576393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15789699554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15618324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14418530464172</t>
   </si>
   <si>
     <t xml:space="preserve">2.1407573223114</t>
@@ -857,34 +854,34 @@
     <t xml:space="preserve">2.14932727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13904356956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17503690719604</t>
+    <t xml:space="preserve">2.13904333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17503714561462</t>
   </si>
   <si>
     <t xml:space="preserve">2.15104126930237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12018966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10476398468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06362843513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03277683258057</t>
+    <t xml:space="preserve">2.12018990516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1047637462616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06362819671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03277707099915</t>
   </si>
   <si>
     <t xml:space="preserve">2.04820275306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07048439979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04991674423218</t>
+    <t xml:space="preserve">2.07048416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0499165058136</t>
   </si>
   <si>
     <t xml:space="preserve">2.12875962257385</t>
@@ -893,7 +890,7 @@
     <t xml:space="preserve">2.08762431144714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02077889442444</t>
+    <t xml:space="preserve">2.02077913284302</t>
   </si>
   <si>
     <t xml:space="preserve">2.08419609069824</t>
@@ -902,7 +899,7 @@
     <t xml:space="preserve">2.0224928855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01392316818237</t>
+    <t xml:space="preserve">2.01392292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.00535321235657</t>
@@ -911,16 +908,16 @@
     <t xml:space="preserve">2.1681809425354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18532061576843</t>
+    <t xml:space="preserve">2.18532085418701</t>
   </si>
   <si>
     <t xml:space="preserve">2.29672932624817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33100914955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32243919372559</t>
+    <t xml:space="preserve">2.33100891113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32243895530701</t>
   </si>
   <si>
     <t xml:space="preserve">2.35671854019165</t>
@@ -932,25 +929,25 @@
     <t xml:space="preserve">2.49383687973022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46812701225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47669720649719</t>
+    <t xml:space="preserve">2.46812725067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47669696807861</t>
   </si>
   <si>
     <t xml:space="preserve">2.48526668548584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53668642044067</t>
+    <t xml:space="preserve">2.53668618202209</t>
   </si>
   <si>
     <t xml:space="preserve">2.57953548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.596675157547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61381506919861</t>
+    <t xml:space="preserve">2.59667539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61381483078003</t>
   </si>
   <si>
     <t xml:space="preserve">2.55382585525513</t>
@@ -968,10 +965,10 @@
     <t xml:space="preserve">2.61655139923096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52694368362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.437335729599</t>
+    <t xml:space="preserve">2.52694344520569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43733549118042</t>
   </si>
   <si>
     <t xml:space="preserve">2.46421790122986</t>
@@ -980,19 +977,19 @@
     <t xml:space="preserve">2.50006103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45525741577148</t>
+    <t xml:space="preserve">2.45525717735291</t>
   </si>
   <si>
     <t xml:space="preserve">2.54486513137817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57174730300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51798295974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56278681755066</t>
+    <t xml:space="preserve">2.57174754142761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51798272132874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56278657913208</t>
   </si>
   <si>
     <t xml:space="preserve">2.53590416908264</t>
@@ -1001,25 +998,25 @@
     <t xml:space="preserve">2.4911003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48213958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5090217590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47317862510681</t>
+    <t xml:space="preserve">2.48213982582092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50902199745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47317886352539</t>
   </si>
   <si>
     <t xml:space="preserve">2.78680658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7599241733551</t>
+    <t xml:space="preserve">2.75992441177368</t>
   </si>
   <si>
     <t xml:space="preserve">2.77784562110901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7420027256012</t>
+    <t xml:space="preserve">2.74200248718262</t>
   </si>
   <si>
     <t xml:space="preserve">2.76888489723206</t>
@@ -1028,7 +1025,7 @@
     <t xml:space="preserve">2.71512007713318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75096344947815</t>
+    <t xml:space="preserve">2.75096321105957</t>
   </si>
   <si>
     <t xml:space="preserve">2.67031621932983</t>
@@ -1040,13 +1037,13 @@
     <t xml:space="preserve">2.65239477157593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68823766708374</t>
+    <t xml:space="preserve">2.68823790550232</t>
   </si>
   <si>
     <t xml:space="preserve">2.73304176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69719862937927</t>
+    <t xml:space="preserve">2.69719886779785</t>
   </si>
   <si>
     <t xml:space="preserve">2.67927694320679</t>
@@ -1055,10 +1052,10 @@
     <t xml:space="preserve">2.84953236579895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86745357513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83161067962646</t>
+    <t xml:space="preserve">2.86745381355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83161044120789</t>
   </si>
   <si>
     <t xml:space="preserve">2.6434338092804</t>
@@ -1067,7 +1064,7 @@
     <t xml:space="preserve">2.62551236152649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58070826530457</t>
+    <t xml:space="preserve">2.58070850372314</t>
   </si>
   <si>
     <t xml:space="preserve">2.607590675354</t>
@@ -1100,25 +1097,25 @@
     <t xml:space="preserve">2.90329670906067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12731647491455</t>
+    <t xml:space="preserve">3.12731671333313</t>
   </si>
   <si>
     <t xml:space="preserve">3.16315984725952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13627767562866</t>
+    <t xml:space="preserve">3.13627743721008</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004225730896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25276803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26172876358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28861117362976</t>
+    <t xml:space="preserve">3.25276780128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26172852516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28861093521118</t>
   </si>
   <si>
     <t xml:space="preserve">3.29757189750671</t>
@@ -1133,7 +1130,7 @@
     <t xml:space="preserve">3.34237575531006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42302274703979</t>
+    <t xml:space="preserve">3.42302298545837</t>
   </si>
   <si>
     <t xml:space="preserve">3.3871796131134</t>
@@ -1142,22 +1139,22 @@
     <t xml:space="preserve">3.40510129928589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41406178474426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3692581653595</t>
+    <t xml:space="preserve">3.41406202316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36925792694092</t>
   </si>
   <si>
     <t xml:space="preserve">3.37821888923645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45886588096619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4857485294342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47678780555725</t>
+    <t xml:space="preserve">3.45886564254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48574876785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47678756713867</t>
   </si>
   <si>
     <t xml:space="preserve">3.49470925331116</t>
@@ -1166,13 +1163,13 @@
     <t xml:space="preserve">3.67392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58431720733643</t>
+    <t xml:space="preserve">3.58431696891785</t>
   </si>
   <si>
     <t xml:space="preserve">3.53055238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59327793121338</t>
+    <t xml:space="preserve">3.59327816963196</t>
   </si>
   <si>
     <t xml:space="preserve">3.55743479728699</t>
@@ -1205,43 +1202,46 @@
     <t xml:space="preserve">3.6918466091156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70976781845093</t>
+    <t xml:space="preserve">3.70976805686951</t>
   </si>
   <si>
     <t xml:space="preserve">3.68288588523865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76353311538696</t>
+    <t xml:space="preserve">3.7635326385498</t>
   </si>
   <si>
     <t xml:space="preserve">3.78145432472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80833697319031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79041528701782</t>
+    <t xml:space="preserve">3.80833721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79041504859924</t>
   </si>
   <si>
     <t xml:space="preserve">3.95170950889587</t>
   </si>
   <si>
+    <t xml:space="preserve">3.96067070960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97005581855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00759792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0920672416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81988835334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87620115280151</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.96067023277283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97005581855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00759792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0920672416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81988835334778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87620115280151</t>
   </si>
   <si>
     <t xml:space="preserve">4.02636861801147</t>
@@ -6245,7 +6245,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -6271,7 +6271,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -6297,7 +6297,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -6323,7 +6323,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G139" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -6349,7 +6349,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -6375,7 +6375,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -6427,7 +6427,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G143" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -6453,7 +6453,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G144" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -6479,7 +6479,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -6505,7 +6505,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -6531,7 +6531,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -6557,7 +6557,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G148" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -6583,7 +6583,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -6609,7 +6609,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G150" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -6635,7 +6635,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G151" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -6661,7 +6661,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -6687,7 +6687,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G153" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -6713,7 +6713,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G154" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -6739,7 +6739,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G155" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -6765,7 +6765,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -6791,7 +6791,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -6817,7 +6817,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -6843,7 +6843,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -6869,7 +6869,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G160" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -6895,7 +6895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G161" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -6921,7 +6921,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G162" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -6947,7 +6947,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G163" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -6973,7 +6973,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G164" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -6999,7 +6999,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G165" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -7025,7 +7025,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G166" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7051,7 +7051,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G167" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7077,7 +7077,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G168" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7103,7 +7103,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G169" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7129,7 +7129,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7155,7 +7155,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G171" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7181,7 +7181,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7207,7 +7207,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7233,7 +7233,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G174" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7259,7 +7259,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7285,7 +7285,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G176" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7311,7 +7311,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G177" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7337,7 +7337,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G178" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7363,7 +7363,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G179" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7389,7 +7389,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G180" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7415,7 +7415,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G181" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7441,7 +7441,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G182" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7467,7 +7467,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G183" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7493,7 +7493,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G184" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -7519,7 +7519,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G185" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7545,7 +7545,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G186" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7571,7 +7571,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G187" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7597,7 +7597,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G188" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7623,7 +7623,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G189" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7649,7 +7649,7 @@
         <v>2</v>
       </c>
       <c r="G190" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7675,7 +7675,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G191" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7701,7 +7701,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G192" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7727,7 +7727,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G193" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7753,7 +7753,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G194" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -7779,7 +7779,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G195" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -7805,7 +7805,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G196" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -7831,7 +7831,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -7857,7 +7857,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -7883,7 +7883,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -7909,7 +7909,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -7935,7 +7935,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -7961,7 +7961,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -7987,7 +7987,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8013,7 +8013,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8039,7 +8039,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8065,7 +8065,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G206" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8091,7 +8091,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G207" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8117,7 +8117,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8143,7 +8143,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G209" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8169,7 +8169,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8195,7 +8195,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G211" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8221,7 +8221,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G212" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8247,7 +8247,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G213" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8273,7 +8273,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G214" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8299,7 +8299,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8325,7 +8325,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G216" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8351,7 +8351,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8377,7 +8377,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8403,7 +8403,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G219" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8429,7 +8429,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G220" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8455,7 +8455,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G221" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8481,7 +8481,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G222" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8507,7 +8507,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G223" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8533,7 +8533,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G224" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8559,7 +8559,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8585,7 +8585,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G226" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8611,7 +8611,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8637,7 +8637,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8663,7 +8663,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G229" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8689,7 +8689,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8715,7 +8715,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G231" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8741,7 +8741,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G232" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8767,7 +8767,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G233" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8793,7 +8793,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G234" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -8819,7 +8819,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G235" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -8845,7 +8845,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G236" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -8871,7 +8871,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G237" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -8897,7 +8897,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G238" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -8923,7 +8923,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G239" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -8949,7 +8949,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G240" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -8975,7 +8975,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9001,7 +9001,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9027,7 +9027,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9053,7 +9053,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G244" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9079,7 +9079,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9105,7 +9105,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G246" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9131,7 +9131,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G247" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9157,7 +9157,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G248" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9183,7 +9183,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G249" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9209,7 +9209,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G250" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9235,7 +9235,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9261,7 +9261,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G252" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9287,7 +9287,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G253" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9313,7 +9313,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G254" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9339,7 +9339,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9365,7 +9365,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G256" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9391,7 +9391,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G257" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9417,7 +9417,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G258" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9443,7 +9443,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G259" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9469,7 +9469,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9495,7 +9495,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G261" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9521,7 +9521,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G262" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9547,7 +9547,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9573,7 +9573,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G264" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9599,7 +9599,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G265" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9625,7 +9625,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G266" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9651,7 +9651,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G267" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9677,7 +9677,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G268" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9703,7 +9703,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9729,7 +9729,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G270" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9755,7 +9755,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G271" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -9781,7 +9781,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -9807,7 +9807,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9833,7 +9833,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G274" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -9859,7 +9859,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G275" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -9885,7 +9885,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G276" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9911,7 +9911,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G277" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9937,7 +9937,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G278" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -9963,7 +9963,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G279" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -9989,7 +9989,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G280" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10015,7 +10015,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G281" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10041,7 +10041,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10067,7 +10067,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G283" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10093,7 +10093,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G284" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10119,7 +10119,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G285" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10145,7 +10145,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G286" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10171,7 +10171,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G287" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10197,7 +10197,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10223,7 +10223,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G289" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10249,7 +10249,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G290" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10275,7 +10275,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G291" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10301,7 +10301,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10327,7 +10327,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G293" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10353,7 +10353,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G294" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10379,7 +10379,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G295" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10405,7 +10405,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G296" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10431,7 +10431,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G297" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10457,7 +10457,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G298" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10483,7 +10483,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10509,7 +10509,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G300" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10535,7 +10535,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G301" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10561,7 +10561,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G302" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10587,7 +10587,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10613,7 +10613,7 @@
         <v>1.875</v>
       </c>
       <c r="G304" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10639,7 +10639,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G305" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10665,7 +10665,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G306" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10691,7 +10691,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G307" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10717,7 +10717,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G308" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10743,7 +10743,7 @@
         <v>2</v>
       </c>
       <c r="G309" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -10769,7 +10769,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10795,7 +10795,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -10821,7 +10821,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -10847,7 +10847,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G313" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10873,7 +10873,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G314" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -10899,7 +10899,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10925,7 +10925,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10951,7 +10951,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G317" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11003,7 +11003,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11029,7 +11029,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11055,7 +11055,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11081,7 +11081,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11107,7 +11107,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11133,7 +11133,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11159,7 +11159,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11211,7 +11211,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G327" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11237,7 +11237,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11263,7 +11263,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11289,7 +11289,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11315,7 +11315,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11341,7 +11341,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G332" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11367,7 +11367,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11393,7 +11393,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11419,7 +11419,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G335" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11445,7 +11445,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11549,7 +11549,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11575,7 +11575,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G341" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11601,7 +11601,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11627,7 +11627,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11653,7 +11653,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G344" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11705,7 +11705,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G346" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11731,7 +11731,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G347" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11757,7 +11757,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -11783,7 +11783,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G349" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -11809,7 +11809,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -11861,7 +11861,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11887,7 +11887,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G353" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11939,7 +11939,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G355" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11965,7 +11965,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -11991,7 +11991,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G357" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12017,7 +12017,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12043,7 +12043,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12069,7 +12069,7 @@
         <v>2.25</v>
       </c>
       <c r="G360" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12095,7 +12095,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12121,7 +12121,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12147,7 +12147,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G363" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12173,7 +12173,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G364" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12199,7 +12199,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12225,7 +12225,7 @@
         <v>2.25</v>
       </c>
       <c r="G366" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12251,7 +12251,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12277,7 +12277,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12303,7 +12303,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12329,7 +12329,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12355,7 +12355,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12381,7 +12381,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12407,7 +12407,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G373" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12433,7 +12433,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G374" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12459,7 +12459,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G375" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12485,7 +12485,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G376" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12511,7 +12511,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G377" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12537,7 +12537,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12563,7 +12563,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12589,7 +12589,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G380" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12615,7 +12615,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G381" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12641,7 +12641,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G382" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12667,7 +12667,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12693,7 +12693,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G384" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12719,7 +12719,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G385" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12745,7 +12745,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12771,7 +12771,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G387" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12797,7 +12797,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G388" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -12823,7 +12823,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G389" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -12849,7 +12849,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -12875,7 +12875,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G391" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -12901,7 +12901,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -12927,7 +12927,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G393" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -12953,7 +12953,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -12979,7 +12979,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G395" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13005,7 +13005,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13031,7 +13031,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13057,7 +13057,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13083,7 +13083,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G399" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13109,7 +13109,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G400" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13135,7 +13135,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G401" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13161,7 +13161,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13187,7 +13187,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G403" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13213,7 +13213,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13239,7 +13239,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G405" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13265,7 +13265,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13291,7 +13291,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13317,7 +13317,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13343,7 +13343,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G409" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13369,7 +13369,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G410" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13395,7 +13395,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G411" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13421,7 +13421,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13447,7 +13447,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G413" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13473,7 +13473,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G414" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13499,7 +13499,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G415" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13525,7 +13525,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G416" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13551,7 +13551,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G417" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13577,7 +13577,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G418" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13603,7 +13603,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G419" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13629,7 +13629,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G420" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13655,7 +13655,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G421" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13681,7 +13681,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G422" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13707,7 +13707,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13733,7 +13733,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G424" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13759,7 +13759,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G425" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13785,7 +13785,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G426" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -13811,7 +13811,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G427" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -13837,7 +13837,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G428" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -13863,7 +13863,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G429" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -13889,7 +13889,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G430" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -13915,7 +13915,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G431" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -13941,7 +13941,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -13967,7 +13967,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G433" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -13993,7 +13993,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14019,7 +14019,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G435" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14045,7 +14045,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G436" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14071,7 +14071,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G437" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14097,7 +14097,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G438" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14123,7 +14123,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G439" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14149,7 +14149,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G440" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14175,7 +14175,7 @@
         <v>2.5</v>
       </c>
       <c r="G441" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14201,7 +14201,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G442" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14227,7 +14227,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G443" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14253,7 +14253,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G444" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14279,7 +14279,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G445" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14305,7 +14305,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14331,7 +14331,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G447" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14357,7 +14357,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G448" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14383,7 +14383,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G449" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14409,7 +14409,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G450" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14435,7 +14435,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G451" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14461,7 +14461,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G452" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14487,7 +14487,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G453" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14513,7 +14513,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G454" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14539,7 +14539,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G455" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14565,7 +14565,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G456" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14591,7 +14591,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G457" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14617,7 +14617,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G458" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14643,7 +14643,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G459" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14669,7 +14669,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G460" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14695,7 +14695,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G461" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14721,7 +14721,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G462" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14747,7 +14747,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G463" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14773,7 +14773,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G464" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -14799,7 +14799,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -14825,7 +14825,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G466" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -14851,7 +14851,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G467" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -14877,7 +14877,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G468" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -14903,7 +14903,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G469" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -14929,7 +14929,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G470" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -14955,7 +14955,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G471" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -14981,7 +14981,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15007,7 +15007,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G473" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15033,7 +15033,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15059,7 +15059,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G475" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15085,7 +15085,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G476" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15111,7 +15111,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G477" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15137,7 +15137,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G478" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15163,7 +15163,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G479" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15189,7 +15189,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G480" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15215,7 +15215,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15241,7 +15241,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G482" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15267,7 +15267,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G483" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15293,7 +15293,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G484" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15319,7 +15319,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G485" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15345,7 +15345,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G486" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15371,7 +15371,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15397,7 +15397,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G488" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15423,7 +15423,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G489" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15449,7 +15449,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G490" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15475,7 +15475,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G491" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15501,7 +15501,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15527,7 +15527,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G493" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15553,7 +15553,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G494" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15579,7 +15579,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15605,7 +15605,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G496" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15631,7 +15631,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G497" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15657,7 +15657,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G498" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15683,7 +15683,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G499" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15709,7 +15709,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G500" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15735,7 +15735,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G501" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15761,7 +15761,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G502" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15787,7 +15787,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G503" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -15813,7 +15813,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G504" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -15839,7 +15839,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G505" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -15865,7 +15865,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G506" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -15891,7 +15891,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G507" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -15917,7 +15917,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G508" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -15943,7 +15943,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G509" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -15969,7 +15969,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G510" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -15995,7 +15995,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G511" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16021,7 +16021,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G512" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16047,7 +16047,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G513" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16073,7 +16073,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G514" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16099,7 +16099,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G515" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16125,7 +16125,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G516" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16151,7 +16151,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G517" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16177,7 +16177,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G518" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16203,7 +16203,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G519" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16229,7 +16229,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G520" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16255,7 +16255,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G521" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16281,7 +16281,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16307,7 +16307,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G523" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16333,7 +16333,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G524" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16359,7 +16359,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G525" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16385,7 +16385,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G526" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16411,7 +16411,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G527" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16437,7 +16437,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G528" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16463,7 +16463,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G529" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16489,7 +16489,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16515,7 +16515,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G531" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16541,7 +16541,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G532" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16567,7 +16567,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G533" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16593,7 +16593,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G534" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16619,7 +16619,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G535" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16645,7 +16645,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G536" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16671,7 +16671,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G537" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16697,7 +16697,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G538" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16723,7 +16723,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G539" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16749,7 +16749,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G540" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16775,7 +16775,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G541" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -16801,7 +16801,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G542" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -16827,7 +16827,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G543" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -16853,7 +16853,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G544" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -16879,7 +16879,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G545" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16905,7 +16905,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G546" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16931,7 +16931,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G547" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16957,7 +16957,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G548" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -16983,7 +16983,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G549" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17009,7 +17009,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G550" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17035,7 +17035,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G551" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17061,7 +17061,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G552" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17087,7 +17087,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G553" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17113,7 +17113,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G554" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17139,7 +17139,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17165,7 +17165,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G556" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17191,7 +17191,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G557" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17217,7 +17217,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17243,7 +17243,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17269,7 +17269,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17295,7 +17295,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17321,7 +17321,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G562" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17347,7 +17347,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G563" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17373,7 +17373,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17399,7 +17399,7 @@
         <v>2.5</v>
       </c>
       <c r="G565" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17425,7 +17425,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17451,7 +17451,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G567" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17477,7 +17477,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G568" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17503,7 +17503,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G569" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17529,7 +17529,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G570" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17555,7 +17555,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G571" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17581,7 +17581,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G572" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17607,7 +17607,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G573" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17633,7 +17633,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G574" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17659,7 +17659,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G575" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17685,7 +17685,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17711,7 +17711,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G577" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17737,7 +17737,7 @@
         <v>2.5</v>
       </c>
       <c r="G578" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17763,7 +17763,7 @@
         <v>2.5</v>
       </c>
       <c r="G579" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17789,7 +17789,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G580" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -17815,7 +17815,7 @@
         <v>2.5</v>
       </c>
       <c r="G581" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -17841,7 +17841,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -17867,7 +17867,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -17893,7 +17893,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -17919,7 +17919,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -17945,7 +17945,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -17971,7 +17971,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G587" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -17997,7 +17997,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18023,7 +18023,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G589" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18049,7 +18049,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G590" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18075,7 +18075,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G591" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18101,7 +18101,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G592" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18127,7 +18127,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G593" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18153,7 +18153,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G594" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18179,7 +18179,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G595" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18205,7 +18205,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18231,7 +18231,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18257,7 +18257,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G598" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18283,7 +18283,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G599" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18309,7 +18309,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G600" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18335,7 +18335,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18361,7 +18361,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18387,7 +18387,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G603" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18413,7 +18413,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G604" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18439,7 +18439,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G605" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18465,7 +18465,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G606" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18491,7 +18491,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G607" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18517,7 +18517,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G608" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18543,7 +18543,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G609" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18569,7 +18569,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G610" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18595,7 +18595,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G611" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18621,7 +18621,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18647,7 +18647,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G613" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18673,7 +18673,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G614" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18699,7 +18699,7 @@
         <v>2.75</v>
       </c>
       <c r="G615" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18725,7 +18725,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G616" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18751,7 +18751,7 @@
         <v>2.75</v>
       </c>
       <c r="G617" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18777,7 +18777,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G618" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18803,7 +18803,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G619" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18829,7 +18829,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G620" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18855,7 +18855,7 @@
         <v>2.75</v>
       </c>
       <c r="G621" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18881,7 +18881,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G622" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18907,7 +18907,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18933,7 +18933,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18959,7 +18959,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -18985,7 +18985,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19011,7 +19011,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G627" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19037,7 +19037,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G628" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19063,7 +19063,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G629" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19089,7 +19089,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G630" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19115,7 +19115,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19141,7 +19141,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G632" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19167,7 +19167,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19193,7 +19193,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G634" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19219,7 +19219,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G635" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19245,7 +19245,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G636" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19271,7 +19271,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19297,7 +19297,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19323,7 +19323,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19349,7 +19349,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19375,7 +19375,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19401,7 +19401,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19427,7 +19427,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19453,7 +19453,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19479,7 +19479,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19505,7 +19505,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19531,7 +19531,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G647" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19557,7 +19557,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G648" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19583,7 +19583,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G649" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19609,7 +19609,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G650" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19635,7 +19635,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G651" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19661,7 +19661,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G652" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19687,7 +19687,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G653" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19713,7 +19713,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G654" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19739,7 +19739,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19765,7 +19765,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G656" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19791,7 +19791,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -19817,7 +19817,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G658" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -19843,7 +19843,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19869,7 +19869,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G660" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19895,7 +19895,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G661" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19921,7 +19921,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G662" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19947,7 +19947,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G663" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19973,7 +19973,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G664" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19999,7 +19999,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20025,7 +20025,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20051,7 +20051,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20077,7 +20077,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20103,7 +20103,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G669" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20129,7 +20129,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G670" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20155,7 +20155,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20181,7 +20181,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G672" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20207,7 +20207,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G673" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20233,7 +20233,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20259,7 +20259,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20285,7 +20285,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G676" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20311,7 +20311,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20337,7 +20337,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20363,7 +20363,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G679" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20389,7 +20389,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20415,7 +20415,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G681" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20441,7 +20441,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20467,7 +20467,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20493,7 +20493,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20519,7 +20519,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20545,7 +20545,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20571,7 +20571,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20597,7 +20597,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20623,7 +20623,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20649,7 +20649,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20675,7 +20675,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20701,7 +20701,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G692" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20727,7 +20727,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20753,7 +20753,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20779,7 +20779,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20805,7 +20805,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20831,7 +20831,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20857,7 +20857,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -20883,7 +20883,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -20909,7 +20909,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -20935,7 +20935,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -20961,7 +20961,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20987,7 +20987,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21013,7 +21013,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21039,7 +21039,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21065,7 +21065,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21091,7 +21091,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21117,7 +21117,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G708" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21143,7 +21143,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G709" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21169,7 +21169,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G710" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21195,7 +21195,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G711" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21221,7 +21221,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21247,7 +21247,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G713" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21273,7 +21273,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G714" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21299,7 +21299,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G715" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21325,7 +21325,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G716" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21351,7 +21351,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G717" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21377,7 +21377,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21403,7 +21403,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G719" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21429,7 +21429,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G720" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21455,7 +21455,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G721" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21481,7 +21481,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G722" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21507,7 +21507,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G723" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21533,7 +21533,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G724" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21559,7 +21559,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G725" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21585,7 +21585,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G726" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21611,7 +21611,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G727" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21637,7 +21637,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21663,7 +21663,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G729" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21689,7 +21689,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21715,7 +21715,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G731" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21741,7 +21741,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G732" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21767,7 +21767,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G733" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21793,7 +21793,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G734" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21819,7 +21819,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G735" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21845,7 +21845,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G736" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21871,7 +21871,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G737" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21897,7 +21897,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21923,7 +21923,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G739" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21949,7 +21949,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21975,7 +21975,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G741" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22001,7 +22001,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G742" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22027,7 +22027,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G743" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22053,7 +22053,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G744" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22079,7 +22079,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G745" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22105,7 +22105,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22131,7 +22131,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22157,7 +22157,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22183,7 +22183,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G749" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22209,7 +22209,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22235,7 +22235,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22261,7 +22261,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22287,7 +22287,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22313,7 +22313,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22339,7 +22339,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22365,7 +22365,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22391,7 +22391,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22417,7 +22417,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22443,7 +22443,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G759" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22469,7 +22469,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G760" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22495,7 +22495,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G761" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22521,7 +22521,7 @@
         <v>2.75</v>
       </c>
       <c r="G762" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22547,7 +22547,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22573,7 +22573,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22599,7 +22599,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22625,7 +22625,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G766" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22651,7 +22651,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22677,7 +22677,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G768" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22703,7 +22703,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22729,7 +22729,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22755,7 +22755,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22781,7 +22781,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22807,7 +22807,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22833,7 +22833,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22859,7 +22859,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22885,7 +22885,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22911,7 +22911,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22937,7 +22937,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22963,7 +22963,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G779" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22989,7 +22989,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23015,7 +23015,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23041,7 +23041,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G782" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23067,7 +23067,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23093,7 +23093,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G784" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23119,7 +23119,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G785" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23145,7 +23145,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23171,7 +23171,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G787" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23197,7 +23197,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G788" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23223,7 +23223,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G789" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23249,7 +23249,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23275,7 +23275,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G791" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23301,7 +23301,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G792" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23327,7 +23327,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G793" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23353,7 +23353,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23379,7 +23379,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23405,7 +23405,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23431,7 +23431,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G797" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23457,7 +23457,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G798" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23483,7 +23483,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23509,7 +23509,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G800" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23535,7 +23535,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23561,7 +23561,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G802" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23587,7 +23587,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23613,7 +23613,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G804" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23639,7 +23639,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23665,7 +23665,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23691,7 +23691,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G807" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23717,7 +23717,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G808" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23743,7 +23743,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G809" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23769,7 +23769,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G810" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23795,7 +23795,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G811" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23821,7 +23821,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23847,7 +23847,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G813" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23873,7 +23873,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G814" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23899,7 +23899,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23925,7 +23925,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G816" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23951,7 +23951,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23977,7 +23977,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G818" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24003,7 +24003,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24029,7 +24029,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G820" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24055,7 +24055,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G821" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24081,7 +24081,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24107,7 +24107,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G823" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24133,7 +24133,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G824" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24159,7 +24159,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G825" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24185,7 +24185,7 @@
         <v>4</v>
       </c>
       <c r="G826" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24211,7 +24211,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G827" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24237,7 +24237,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G828" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24263,7 +24263,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G829" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24289,7 +24289,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G830" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24315,7 +24315,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24341,7 +24341,7 @@
         <v>4</v>
       </c>
       <c r="G832" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24367,7 +24367,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24393,7 +24393,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24419,7 +24419,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24445,7 +24445,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G836" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24471,7 +24471,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24497,7 +24497,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24523,7 +24523,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G839" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24549,7 +24549,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24575,7 +24575,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G841" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24601,7 +24601,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G842" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24627,7 +24627,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24653,7 +24653,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G844" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24679,7 +24679,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G845" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24705,7 +24705,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24731,7 +24731,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24757,7 +24757,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24783,7 +24783,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24809,7 +24809,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G850" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24835,7 +24835,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24861,7 +24861,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24887,7 +24887,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G853" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24913,7 +24913,7 @@
         <v>4.25</v>
       </c>
       <c r="G854" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24939,7 +24939,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24965,7 +24965,7 @@
         <v>4.25</v>
       </c>
       <c r="G856" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24991,7 +24991,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G857" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25017,7 +25017,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G858" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25043,7 +25043,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G859" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25069,7 +25069,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25095,7 +25095,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G861" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25121,7 +25121,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G862" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25147,7 +25147,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G863" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25173,7 +25173,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G864" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25199,7 +25199,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G865" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25251,7 +25251,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G867" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25355,7 +25355,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25407,7 +25407,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G873" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25537,7 +25537,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G878" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25901,7 +25901,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G892" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25979,7 +25979,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G895" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26213,7 +26213,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G904" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -30399,7 +30399,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1065" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30685,7 +30685,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1076" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30711,7 +30711,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1077" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30945,7 +30945,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1086" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31309,7 +31309,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1100" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31413,7 +31413,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1104" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32921,7 +32921,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1162" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32947,7 +32947,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1163" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33389,7 +33389,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1180" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33519,7 +33519,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1185" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33727,7 +33727,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1193" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -67691,7 +67691,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6602546296</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>3545</v>
@@ -67712,6 +67712,32 @@
         <v>786</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.5105439815</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>515</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>788</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825955867767</t>
+    <t xml:space="preserve">1.85825932025909</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91323792934418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109167575836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88496315479279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92423319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80642282962799</t>
+    <t xml:space="preserve">1.91323781013489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109191417694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88496327400208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92423331737518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80642294883728</t>
   </si>
   <si>
     <t xml:space="preserve">1.82998502254486</t>
@@ -65,250 +65,250 @@
     <t xml:space="preserve">1.79856884479523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76715302467346</t>
+    <t xml:space="preserve">1.76715290546417</t>
   </si>
   <si>
     <t xml:space="preserve">1.85354709625244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86925530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87710916996002</t>
+    <t xml:space="preserve">1.86925506591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8771094083786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281737804413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86768424510956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81584787368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83783912658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553811073303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84569299221039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81898939609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8362683057785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8598301410675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80485212802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82056021690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81741857528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85040545463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88025057315826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81427705287933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85197627544403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84412217140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84098064899445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82370173931122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81113529205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82213091850281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93680000305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622397422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407831668854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96350312232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9650741815567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99334836006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00434422492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98706519603729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905632972717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0247642993927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93051612377167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96193218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994128704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564949512482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637921333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8739675283432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378710746765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017516613007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9223153591156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050944805145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656334400177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509171485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9583694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739916801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542611598969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9419811964035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91248285770416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91084420681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545911312103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8026829957962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84201407432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83218157291412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88298428058624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86823499202728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90756618976593</t>
   </si>
   <si>
     <t xml:space="preserve">1.89281713962555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86768424510956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81584751605988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83783888816833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87553811073303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684350013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84569275379181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898951530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8362683057785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85983037948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80485212802887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82056045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81741845607758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85040557384491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88025069236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81427669525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85197639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84412217140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84098052978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8237019777298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81113529205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82213115692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9367995262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622445106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407843589783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.963503241539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9650741815567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99334847927094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00434398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98706519603729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905656814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02476453781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93051624298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96193242073059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994116783142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564925670624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637921333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87396740913391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378722667694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017540454865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9223153591156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050968647003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95836925506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739904880524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542611598969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9419811964035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91248285770416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91084396839142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545887470245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80268287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84201431274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83218133449554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88298428058624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86823511123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9075665473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281678199768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88462293148041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920519828796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87151265144348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89773368835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82398748397827</t>
+    <t xml:space="preserve">1.90592741966248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8846230506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920507907867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87151253223419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8977335691452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82398736476898</t>
   </si>
   <si>
     <t xml:space="preserve">1.75843513011932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76662921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78629493713379</t>
+    <t xml:space="preserve">1.76662933826447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78629505634308</t>
   </si>
   <si>
     <t xml:space="preserve">1.77646219730377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75188016891479</t>
+    <t xml:space="preserve">1.75188004970551</t>
   </si>
   <si>
     <t xml:space="preserve">1.75351893901825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77973973751068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75024127960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72074282169342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6699401140213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72893691062927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69616067409515</t>
+    <t xml:space="preserve">1.77973961830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75024116039276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72074270248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66993987560272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72893679141998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69616091251373</t>
   </si>
   <si>
     <t xml:space="preserve">1.76007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70435464382172</t>
+    <t xml:space="preserve">1.70435476303101</t>
   </si>
   <si>
     <t xml:space="preserve">1.73549199104309</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">1.73385310173035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71254885196686</t>
+    <t xml:space="preserve">1.71254873275757</t>
   </si>
   <si>
     <t xml:space="preserve">1.63060867786407</t>
@@ -326,37 +326,37 @@
     <t xml:space="preserve">1.67157876491547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66666233539581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61012363433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62241470813751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6633847951889</t>
+    <t xml:space="preserve">1.66666221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61012375354767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62241458892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66338467597961</t>
   </si>
   <si>
     <t xml:space="preserve">1.67321753501892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64535784721375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63880264759064</t>
+    <t xml:space="preserve">1.64535772800446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63880276679993</t>
   </si>
   <si>
     <t xml:space="preserve">1.62569224834442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66830122470856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65519058704376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64699673652649</t>
+    <t xml:space="preserve">1.66830110549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65519082546234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64699685573578</t>
   </si>
   <si>
     <t xml:space="preserve">1.63798320293427</t>
@@ -368,22 +368,22 @@
     <t xml:space="preserve">1.62978911399841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58308339118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59537434577942</t>
+    <t xml:space="preserve">1.58308351039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59537446498871</t>
   </si>
   <si>
     <t xml:space="preserve">1.57898640632629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59127748012543</t>
+    <t xml:space="preserve">1.59127736091614</t>
   </si>
   <si>
     <t xml:space="preserve">1.54047453403473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56751477718353</t>
+    <t xml:space="preserve">1.56751465797424</t>
   </si>
   <si>
     <t xml:space="preserve">1.56997299194336</t>
@@ -398,16 +398,16 @@
     <t xml:space="preserve">1.6027489900589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60356843471527</t>
+    <t xml:space="preserve">1.60356855392456</t>
   </si>
   <si>
     <t xml:space="preserve">1.6060266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51917004585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56177890300751</t>
+    <t xml:space="preserve">1.51917016506195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5617790222168</t>
   </si>
   <si>
     <t xml:space="preserve">1.54539096355438</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">1.37659418582916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41264796257019</t>
+    <t xml:space="preserve">1.4126478433609</t>
   </si>
   <si>
     <t xml:space="preserve">1.39462113380432</t>
@@ -425,13 +425,13 @@
     <t xml:space="preserve">1.45771503448486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47082543373108</t>
+    <t xml:space="preserve">1.47082531452179</t>
   </si>
   <si>
     <t xml:space="preserve">1.53391933441162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61258184909821</t>
+    <t xml:space="preserve">1.61258172988892</t>
   </si>
   <si>
     <t xml:space="preserve">1.61176240444183</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">1.54211330413818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51179552078247</t>
+    <t xml:space="preserve">1.51179540157318</t>
   </si>
   <si>
     <t xml:space="preserve">1.5552237033844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56505656242371</t>
+    <t xml:space="preserve">1.565056681633</t>
   </si>
   <si>
     <t xml:space="preserve">1.56423723697662</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">1.59291625022888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55686259269714</t>
+    <t xml:space="preserve">1.55686247348785</t>
   </si>
   <si>
     <t xml:space="preserve">1.52162837982178</t>
@@ -467,37 +467,37 @@
     <t xml:space="preserve">1.5412939786911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50442087650299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51097619533539</t>
+    <t xml:space="preserve">1.5044207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5109760761261</t>
   </si>
   <si>
     <t xml:space="preserve">1.55112671852112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51589238643646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55194628238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50851774215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53228056430817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50933730602264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50769853591919</t>
+    <t xml:space="preserve">1.51589250564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55194616317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50851786136627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53228044509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50933742523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5076984167099</t>
   </si>
   <si>
     <t xml:space="preserve">1.50278210639954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49540746212006</t>
+    <t xml:space="preserve">1.49540734291077</t>
   </si>
   <si>
     <t xml:space="preserve">1.51015675067902</t>
@@ -506,82 +506,82 @@
     <t xml:space="preserve">1.57325065135956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58554148674011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59455490112305</t>
+    <t xml:space="preserve">1.5855416059494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59455502033234</t>
   </si>
   <si>
     <t xml:space="preserve">1.60684597492218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62159538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5716118812561</t>
+    <t xml:space="preserve">1.62159514427185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57161176204681</t>
   </si>
   <si>
     <t xml:space="preserve">1.54375207424164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57243132591248</t>
+    <t xml:space="preserve">1.57243120670319</t>
   </si>
   <si>
     <t xml:space="preserve">1.58718037605286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54621016979218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55768203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58799982070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5347386598587</t>
+    <t xml:space="preserve">1.54621040821075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55768191814423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58799970149994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53473877906799</t>
   </si>
   <si>
     <t xml:space="preserve">1.5822639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54702973365784</t>
+    <t xml:space="preserve">1.54702961444855</t>
   </si>
   <si>
     <t xml:space="preserve">1.53883564472198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54784905910492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55276548862457</t>
+    <t xml:space="preserve">1.54784917831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55276560783386</t>
   </si>
   <si>
     <t xml:space="preserve">1.54948794841766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53801620006561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54866862297058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53637742996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53965497016907</t>
+    <t xml:space="preserve">1.5380163192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54866850376129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53637754917145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53965520858765</t>
   </si>
   <si>
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191316604614</t>
+    <t xml:space="preserve">1.65191304683685</t>
   </si>
   <si>
     <t xml:space="preserve">1.69288313388824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65355181694031</t>
+    <t xml:space="preserve">1.65355169773102</t>
   </si>
   <si>
     <t xml:space="preserve">1.82070970535278</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">1.81579351425171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87970650196075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79448890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80104398727417</t>
+    <t xml:space="preserve">1.87970662117004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79448902606964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80104410648346</t>
   </si>
   <si>
     <t xml:space="preserve">1.73876953125</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">1.72729814052582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74696373939514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76335167884827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84693074226379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81087708473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8092383146286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81251573562622</t>
+    <t xml:space="preserve">1.74696362018585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76335155963898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84693050384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81087696552277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923819541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81251561641693</t>
   </si>
   <si>
     <t xml:space="preserve">1.86167979240417</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">1.85840201377869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87642896175385</t>
+    <t xml:space="preserve">1.87642884254456</t>
   </si>
   <si>
     <t xml:space="preserve">1.89937257766724</t>
@@ -647,61 +647,61 @@
     <t xml:space="preserve">1.84856963157654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92479646205902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679428100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850803375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97107350826263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822444438934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94193601608276</t>
+    <t xml:space="preserve">1.92479658126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679416179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850827217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107362747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822420597076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94193613529205</t>
   </si>
   <si>
     <t xml:space="preserve">1.94364988803864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95907580852509</t>
+    <t xml:space="preserve">1.95907592773438</t>
   </si>
   <si>
     <t xml:space="preserve">1.96764576435089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92651033401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95393407344818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93336641788483</t>
+    <t xml:space="preserve">1.92651009559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95393395423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93336629867554</t>
   </si>
   <si>
     <t xml:space="preserve">1.90594255924225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8939448595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8716629743576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92993855476379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90080070495605</t>
+    <t xml:space="preserve">1.89394474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87166309356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92993831634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90080058574677</t>
   </si>
   <si>
     <t xml:space="preserve">1.91451239585876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88708865642548</t>
+    <t xml:space="preserve">1.88708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">1.87680494785309</t>
@@ -713,55 +713,55 @@
     <t xml:space="preserve">1.8853747844696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86994886398315</t>
+    <t xml:space="preserve">1.86994910240173</t>
   </si>
   <si>
     <t xml:space="preserve">1.88880300521851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90937054157257</t>
+    <t xml:space="preserve">1.90937030315399</t>
   </si>
   <si>
     <t xml:space="preserve">1.90251469612122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96421790122986</t>
+    <t xml:space="preserve">1.96421778202057</t>
   </si>
   <si>
     <t xml:space="preserve">1.96250379085541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821353912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98649966716766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964346408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12533164024353</t>
+    <t xml:space="preserve">1.98821365833282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98649954795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97964334487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12533140182495</t>
   </si>
   <si>
     <t xml:space="preserve">2.08591032028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05677270889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07905411720276</t>
+    <t xml:space="preserve">2.05677247047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07905435562134</t>
   </si>
   <si>
     <t xml:space="preserve">2.0807683467865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06534242630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06020045280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07219815254211</t>
+    <t xml:space="preserve">2.06534266471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06020069122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07219839096069</t>
   </si>
   <si>
     <t xml:space="preserve">2.13390159606934</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">2.10819172859192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09962201118469</t>
+    <t xml:space="preserve">2.09962224960327</t>
   </si>
   <si>
     <t xml:space="preserve">2.10304999351501</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">2.03963279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06877040863037</t>
+    <t xml:space="preserve">2.06877017021179</t>
   </si>
   <si>
     <t xml:space="preserve">2.11504793167114</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">2.07391238212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09790802001953</t>
+    <t xml:space="preserve">2.09790778160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.1167619228363</t>
@@ -797,31 +797,31 @@
     <t xml:space="preserve">2.08248233795166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06705617904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12190389633179</t>
+    <t xml:space="preserve">2.06705641746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12190365791321</t>
   </si>
   <si>
     <t xml:space="preserve">2.10647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0893383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05163049697876</t>
+    <t xml:space="preserve">2.08933806419373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05163073539734</t>
   </si>
   <si>
     <t xml:space="preserve">2.17675089836121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14247179031372</t>
+    <t xml:space="preserve">2.14247155189514</t>
   </si>
   <si>
     <t xml:space="preserve">2.1321873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13047385215759</t>
+    <t xml:space="preserve">2.13047361373901</t>
   </si>
   <si>
     <t xml:space="preserve">2.15961098670959</t>
@@ -833,19 +833,19 @@
     <t xml:space="preserve">2.09105205535889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12361764907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11161994934082</t>
+    <t xml:space="preserve">2.12361741065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11161971092224</t>
   </si>
   <si>
     <t xml:space="preserve">2.10133600234985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15789723396301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15618324279785</t>
+    <t xml:space="preserve">2.15789699554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15618348121643</t>
   </si>
   <si>
     <t xml:space="preserve">2.1441855430603</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">2.1407573223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14932703971863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13904356956482</t>
+    <t xml:space="preserve">2.14932727813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13904333114624</t>
   </si>
   <si>
     <t xml:space="preserve">2.17503714561462</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">2.15104126930237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12018966674805</t>
+    <t xml:space="preserve">2.12018990516663</t>
   </si>
   <si>
     <t xml:space="preserve">2.1047637462616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06362819671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03277707099915</t>
+    <t xml:space="preserve">2.06362843513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03277683258057</t>
   </si>
   <si>
     <t xml:space="preserve">2.0482029914856</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">2.07048416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0499165058136</t>
+    <t xml:space="preserve">2.04991674423218</t>
   </si>
   <si>
     <t xml:space="preserve">2.12875962257385</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">2.08762431144714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0207793712616</t>
+    <t xml:space="preserve">2.02077913284302</t>
   </si>
   <si>
     <t xml:space="preserve">2.08419609069824</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">2.00535321235657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1681809425354</t>
+    <t xml:space="preserve">2.16818118095398</t>
   </si>
   <si>
     <t xml:space="preserve">2.18532085418701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29672932624817</t>
+    <t xml:space="preserve">2.29672956466675</t>
   </si>
   <si>
     <t xml:space="preserve">2.33100891113281</t>
@@ -923,10 +923,10 @@
     <t xml:space="preserve">2.32243895530701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35671854019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44241738319397</t>
+    <t xml:space="preserve">2.35671830177307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44241714477539</t>
   </si>
   <si>
     <t xml:space="preserve">2.49383687973022</t>
@@ -938,22 +938,22 @@
     <t xml:space="preserve">2.47669696807861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48526692390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53668642044067</t>
+    <t xml:space="preserve">2.48526668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53668618202209</t>
   </si>
   <si>
     <t xml:space="preserve">2.57953548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.596675157547</t>
+    <t xml:space="preserve">2.59667539596558</t>
   </si>
   <si>
     <t xml:space="preserve">2.61381506919861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55382585525513</t>
+    <t xml:space="preserve">2.55382561683655</t>
   </si>
   <si>
     <t xml:space="preserve">2.63447332382202</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">2.50006127357483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45525717735291</t>
+    <t xml:space="preserve">2.45525741577148</t>
   </si>
   <si>
     <t xml:space="preserve">2.54486513137817</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">2.57174754142761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51798272132874</t>
+    <t xml:space="preserve">2.51798295974731</t>
   </si>
   <si>
     <t xml:space="preserve">2.56278681755066</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">2.53590416908264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49110054969788</t>
+    <t xml:space="preserve">2.4911003112793</t>
   </si>
   <si>
     <t xml:space="preserve">2.48213958740234</t>
@@ -1007,25 +1007,25 @@
     <t xml:space="preserve">2.50902199745178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47317886352539</t>
+    <t xml:space="preserve">2.47317862510681</t>
   </si>
   <si>
     <t xml:space="preserve">2.78680658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7599241733551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77784585952759</t>
+    <t xml:space="preserve">2.75992441177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77784562110901</t>
   </si>
   <si>
     <t xml:space="preserve">2.74200248718262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76888513565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71512031555176</t>
+    <t xml:space="preserve">2.76888489723206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71512007713318</t>
   </si>
   <si>
     <t xml:space="preserve">2.75096321105957</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">2.65239477157593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68823790550232</t>
+    <t xml:space="preserve">2.68823766708374</t>
   </si>
   <si>
     <t xml:space="preserve">2.73304176330566</t>
@@ -1055,22 +1055,22 @@
     <t xml:space="preserve">2.84953236579895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86745381355286</t>
+    <t xml:space="preserve">2.86745357513428</t>
   </si>
   <si>
     <t xml:space="preserve">2.83161067962646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64343404769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62551259994507</t>
+    <t xml:space="preserve">2.6434338092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62551236152649</t>
   </si>
   <si>
     <t xml:space="preserve">2.58070850372314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.607590675354</t>
+    <t xml:space="preserve">2.60759091377258</t>
   </si>
   <si>
     <t xml:space="preserve">2.41941404342651</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">2.81368899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.840571641922</t>
+    <t xml:space="preserve">2.84057140350342</t>
   </si>
   <si>
     <t xml:space="preserve">2.93914008140564</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">2.90329694747925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12731671333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16315960884094</t>
+    <t xml:space="preserve">3.12731647491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16315984725952</t>
   </si>
   <si>
     <t xml:space="preserve">3.13627743721008</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19004225730896</t>
+    <t xml:space="preserve">3.19004201889038</t>
   </si>
   <si>
     <t xml:space="preserve">3.25276780128479</t>
@@ -1118,22 +1118,22 @@
     <t xml:space="preserve">3.26172852516174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28861093521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29757165908813</t>
+    <t xml:space="preserve">3.28861117362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29757189750671</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33341479301453</t>
+    <t xml:space="preserve">3.33341503143311</t>
   </si>
   <si>
     <t xml:space="preserve">3.34237575531006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42302274703979</t>
+    <t xml:space="preserve">3.42302298545837</t>
   </si>
   <si>
     <t xml:space="preserve">3.3871796131134</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">3.37821888923645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45886588096619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4857485294342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47678756713867</t>
+    <t xml:space="preserve">3.45886564254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48574876785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47678780555725</t>
   </si>
   <si>
     <t xml:space="preserve">3.49470925331116</t>
@@ -1166,37 +1166,37 @@
     <t xml:space="preserve">3.67392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58431720733643</t>
+    <t xml:space="preserve">3.58431696891785</t>
   </si>
   <si>
     <t xml:space="preserve">3.53055238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59327816963196</t>
+    <t xml:space="preserve">3.59327793121338</t>
   </si>
   <si>
     <t xml:space="preserve">3.55743479728699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5215916633606</t>
+    <t xml:space="preserve">3.52159142494202</t>
   </si>
   <si>
     <t xml:space="preserve">3.51263093948364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5395131111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60223865509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65600347518921</t>
+    <t xml:space="preserve">3.53951334953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60223889350891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65600323677063</t>
   </si>
   <si>
     <t xml:space="preserve">3.66496443748474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72768974304199</t>
+    <t xml:space="preserve">3.72768998146057</t>
   </si>
   <si>
     <t xml:space="preserve">3.71872925758362</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">3.6918466091156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70976805686951</t>
+    <t xml:space="preserve">3.70976781845093</t>
   </si>
   <si>
     <t xml:space="preserve">3.68288588523865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7635326385498</t>
+    <t xml:space="preserve">3.76353287696838</t>
   </si>
   <si>
     <t xml:space="preserve">3.78145432472229</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">3.80833721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79041528701782</t>
+    <t xml:space="preserve">3.79041504859924</t>
   </si>
   <si>
     <t xml:space="preserve">3.95170950889587</t>
@@ -1232,13 +1232,13 @@
     <t xml:space="preserve">3.97005581855774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00759744644165</t>
+    <t xml:space="preserve">4.00759792327881</t>
   </si>
   <si>
     <t xml:space="preserve">4.0920672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81988859176636</t>
+    <t xml:space="preserve">3.81988835334778</t>
   </si>
   <si>
     <t xml:space="preserve">3.87620115280151</t>
@@ -1262,40 +1262,40 @@
     <t xml:space="preserve">4.03575468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9982123374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97944116592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85743045806885</t>
+    <t xml:space="preserve">3.99821257591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97944092750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85743021965027</t>
   </si>
   <si>
     <t xml:space="preserve">3.84804463386536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81050276756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74480438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89497208595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.941899061203</t>
+    <t xml:space="preserve">3.81050252914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7448046207428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89497232437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94189953804016</t>
   </si>
   <si>
     <t xml:space="preserve">3.8668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93251419067383</t>
+    <t xml:space="preserve">3.93251395225525</t>
   </si>
   <si>
     <t xml:space="preserve">4.08268165588379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11083841323853</t>
+    <t xml:space="preserve">4.11083793640137</t>
   </si>
   <si>
     <t xml:space="preserve">4.12022304534912</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">4.18592166900635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1953067779541</t>
+    <t xml:space="preserve">4.19530725479126</t>
   </si>
   <si>
     <t xml:space="preserve">4.20469284057617</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">4.28916215896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26100540161133</t>
+    <t xml:space="preserve">4.26100587844849</t>
   </si>
   <si>
     <t xml:space="preserve">4.2703914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34547519683838</t>
+    <t xml:space="preserve">4.34547472000122</t>
   </si>
   <si>
     <t xml:space="preserve">4.36424589157104</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">4.50502824783325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49564218521118</t>
+    <t xml:space="preserve">4.49564266204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.43932962417603</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">4.5519552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54256963729858</t>
+    <t xml:space="preserve">4.54257011413574</t>
   </si>
   <si>
     <t xml:space="preserve">4.48625707626343</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">4.40178775787354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44871473312378</t>
+    <t xml:space="preserve">4.44871520996094</t>
   </si>
   <si>
     <t xml:space="preserve">4.42994403839111</t>
@@ -1373,13 +1373,13 @@
     <t xml:space="preserve">4.41117334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39240217208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2422342300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30793285369873</t>
+    <t xml:space="preserve">4.39240169525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24223470687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30793333053589</t>
   </si>
   <si>
     <t xml:space="preserve">4.17653608322144</t>
@@ -1397,28 +1397,28 @@
     <t xml:space="preserve">4.62703895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61765384674072</t>
+    <t xml:space="preserve">4.61765336990356</t>
   </si>
   <si>
     <t xml:space="preserve">4.51441335678101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57072639465332</t>
+    <t xml:space="preserve">4.57072591781616</t>
   </si>
   <si>
     <t xml:space="preserve">4.67396640777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80536317825317</t>
+    <t xml:space="preserve">4.80536270141602</t>
   </si>
   <si>
     <t xml:space="preserve">4.78659200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86167573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84290456771851</t>
+    <t xml:space="preserve">4.86167621612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84290504455566</t>
   </si>
   <si>
     <t xml:space="preserve">4.89921760559082</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">4.5988826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53318452835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58011198043823</t>
+    <t xml:space="preserve">4.53318405151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58011150360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.6927375793457</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">4.74905014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73027896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71150875091553</t>
+    <t xml:space="preserve">4.73027944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71150827407837</t>
   </si>
   <si>
     <t xml:space="preserve">4.76782131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95553064346313</t>
+    <t xml:space="preserve">4.95553112030029</t>
   </si>
   <si>
     <t xml:space="preserve">4.88044691085815</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">4.91798877716064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99307298660278</t>
+    <t xml:space="preserve">4.99307250976562</t>
   </si>
   <si>
     <t xml:space="preserve">4.93675994873047</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">6.60737419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28826761245728</t>
+    <t xml:space="preserve">6.28826808929443</t>
   </si>
   <si>
     <t xml:space="preserve">6.1568717956543</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">5.96916246414185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7063684463501</t>
+    <t xml:space="preserve">5.70636892318726</t>
   </si>
   <si>
     <t xml:space="preserve">5.53743028640747</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">5.87530755996704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66882705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68759775161743</t>
+    <t xml:space="preserve">5.66882658004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68759727478027</t>
   </si>
   <si>
     <t xml:space="preserve">5.83776521682739</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59374332427979</t>
+    <t xml:space="preserve">5.59374284744263</t>
   </si>
   <si>
     <t xml:space="preserve">5.38726234436035</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">5.10569858551025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68335151672363</t>
+    <t xml:space="preserve">4.68335199356079</t>
   </si>
   <si>
     <t xml:space="preserve">4.14837980270386</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">3.62279319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55709505081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37877106666565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50078201293945</t>
+    <t xml:space="preserve">3.55709481239319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37877082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50078225135803</t>
   </si>
   <si>
     <t xml:space="preserve">3.5664803981781</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">3.75418996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70726275444031</t>
+    <t xml:space="preserve">3.70726251602173</t>
   </si>
   <si>
     <t xml:space="preserve">3.71664810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83865928649902</t>
+    <t xml:space="preserve">3.8386595249176</t>
   </si>
   <si>
     <t xml:space="preserve">4.25162029266357</t>
@@ -1583,25 +1583,25 @@
     <t xml:space="preserve">4.12960910797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16715097427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05452489852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76357579231262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66972088813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65094971656799</t>
+    <t xml:space="preserve">4.16715049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05452537536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76357555389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66972064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65094995498657</t>
   </si>
   <si>
     <t xml:space="preserve">3.66033530235291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95128488540649</t>
+    <t xml:space="preserve">3.95128512382507</t>
   </si>
   <si>
     <t xml:space="preserve">4.29854726791382</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">4.31731843948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15776538848877</t>
+    <t xml:space="preserve">4.15776491165161</t>
   </si>
   <si>
     <t xml:space="preserve">4.10145235061646</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">4.13899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88558650016785</t>
+    <t xml:space="preserve">3.88558626174927</t>
   </si>
   <si>
     <t xml:space="preserve">4.32670402526855</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">4.27977657318115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91374325752258</t>
+    <t xml:space="preserve">3.913743019104</t>
   </si>
   <si>
     <t xml:space="preserve">3.92312836647034</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">3.49139666557312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67910599708557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3881561756134</t>
+    <t xml:space="preserve">3.67910623550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38815641403198</t>
   </si>
   <si>
     <t xml:space="preserve">3.35999989509583</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">3.34122896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20044684410095</t>
+    <t xml:space="preserve">3.20044708251953</t>
   </si>
   <si>
     <t xml:space="preserve">3.24737429618835</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">3.47262573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57586598396301</t>
+    <t xml:space="preserve">3.57586574554443</t>
   </si>
   <si>
     <t xml:space="preserve">3.73541903495789</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">3.68849158287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72603344917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52893877029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63217854499817</t>
+    <t xml:space="preserve">3.72603368759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52893853187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63217878341675</t>
   </si>
   <si>
     <t xml:space="preserve">3.51016759872437</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">3.58525133132935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53832387924194</t>
+    <t xml:space="preserve">3.53832411766052</t>
   </si>
   <si>
     <t xml:space="preserve">3.80111742019653</t>
@@ -1730,10 +1730,10 @@
     <t xml:space="preserve">3.48201107978821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46324038505554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44446921348572</t>
+    <t xml:space="preserve">3.46324014663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4444694519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.42569851875305</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">3.41631293296814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754176139832</t>
+    <t xml:space="preserve">3.39754199981689</t>
   </si>
   <si>
     <t xml:space="preserve">3.21921801567078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19106149673462</t>
+    <t xml:space="preserve">3.1910617351532</t>
   </si>
   <si>
     <t xml:space="preserve">3.17229056358337</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">3.23798894882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14413380622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25675988197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36938548088074</t>
+    <t xml:space="preserve">3.14413404464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25675964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36938524246216</t>
   </si>
   <si>
     <t xml:space="preserve">3.15351939201355</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">3.18167614936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29430150985718</t>
+    <t xml:space="preserve">3.29430174827576</t>
   </si>
   <si>
     <t xml:space="preserve">3.2661452293396</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">3.12536311149597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04089403152466</t>
+    <t xml:space="preserve">3.04089379310608</t>
   </si>
   <si>
     <t xml:space="preserve">3.05027914047241</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">2.93765377998352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95642471313477</t>
+    <t xml:space="preserve">2.95642447471619</t>
   </si>
   <si>
     <t xml:space="preserve">3.03150844573975</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">3.02212285995483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92826819419861</t>
+    <t xml:space="preserve">2.92826795578003</t>
   </si>
   <si>
     <t xml:space="preserve">2.94703912734985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90011143684387</t>
+    <t xml:space="preserve">2.90011167526245</t>
   </si>
   <si>
     <t xml:space="preserve">2.97519564628601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27553081512451</t>
+    <t xml:space="preserve">3.27553057670593</t>
   </si>
   <si>
     <t xml:space="preserve">3.33184361457825</t>
@@ -67749,13 +67749,13 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6909722222</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>2292</v>
       </c>
       <c r="C2502" t="n">
-        <v>1.47000002861023</v>
+        <v>1.5</v>
       </c>
       <c r="D2502" t="n">
         <v>1.47000002861023</v>
@@ -67770,6 +67770,32 @@
         <v>790</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.5665625</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>3320</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>790</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825932025909</t>
+    <t xml:space="preserve">1.85825908184052</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">1.9132376909256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92109167575836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88496327400208</t>
+    <t xml:space="preserve">1.92109179496765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8849630355835</t>
   </si>
   <si>
     <t xml:space="preserve">1.92423319816589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80642282962799</t>
+    <t xml:space="preserve">1.80642306804657</t>
   </si>
   <si>
     <t xml:space="preserve">1.82998490333557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79856884479523</t>
+    <t xml:space="preserve">1.79856872558594</t>
   </si>
   <si>
     <t xml:space="preserve">1.76715302467346</t>
@@ -71,196 +71,196 @@
     <t xml:space="preserve">1.85354697704315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86925506591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8771094083786</t>
+    <t xml:space="preserve">1.86925530433655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87710916996002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281725883484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86768424510956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81584787368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83783900737762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553822994232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684338092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84569311141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81898939609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8362683057785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85983037948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80485212802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82056033611298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81741845607758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85040545463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88025057315826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81427705287933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85197627544403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84412240982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84098052978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82370185852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81113529205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82213091850281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679976463318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622457027435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407807826996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96350347995758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96507406234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99334859848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00434422492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.987065076828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905656814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02476453781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93051624298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9619323015213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994128704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564901828766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637921333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8739675283432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378698825836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017540454865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9223153591156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050968647003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656310558319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509159564972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95836925506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739904880524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542611598969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198107719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91248285770416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91084420681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545923233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80268287658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84201407432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83218145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88298428058624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86823511123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90756618976593</t>
   </si>
   <si>
     <t xml:space="preserve">1.89281713962555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86768424510956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81584775447845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83783900737762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87553811073303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684350013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8456928730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898939609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8362683057785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85983037948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80485200881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82056033611298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.817418217659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85040545463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88025057315826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81427693367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85197651386261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84412217140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84098052978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82370185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81113541126251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8221310377121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93680000305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622445106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407807826996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96350359916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96507406234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99334859848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00434422492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.987065076828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905656814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02476477622986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93051624298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9619323015213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994128704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564925670624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637921333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8739675283432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378698825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017516613007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9223153591156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050968647003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656334400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509159564972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9583694934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739904880524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542611598969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198107719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91248285770416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91084396839142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545899391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80268287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84201419353485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83218145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88298416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86823523044586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90756630897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281702041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88462293148041</t>
+    <t xml:space="preserve">1.90592753887177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88462316989899</t>
   </si>
   <si>
     <t xml:space="preserve">1.90920507907867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87151253223419</t>
+    <t xml:space="preserve">1.87151265144348</t>
   </si>
   <si>
     <t xml:space="preserve">1.8977335691452</t>
@@ -269,31 +269,31 @@
     <t xml:space="preserve">1.82398748397827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75843524932861</t>
+    <t xml:space="preserve">1.75843513011932</t>
   </si>
   <si>
     <t xml:space="preserve">1.76662921905518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78629505634308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77646219730377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75188016891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75351905822754</t>
+    <t xml:space="preserve">1.7862948179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77646195888519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75188004970551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75351893901825</t>
   </si>
   <si>
     <t xml:space="preserve">1.77973973751068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75024127960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72074282169342</t>
+    <t xml:space="preserve">1.75024139881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72074270248413</t>
   </si>
   <si>
     <t xml:space="preserve">1.66993999481201</t>
@@ -302,16 +302,16 @@
     <t xml:space="preserve">1.72893679141998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69616067409515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76007413864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70435464382172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7354918718338</t>
+    <t xml:space="preserve">1.69616079330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76007401943207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70435476303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73549199104309</t>
   </si>
   <si>
     <t xml:space="preserve">1.73385322093964</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">1.71254885196686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63060867786407</t>
+    <t xml:space="preserve">1.63060879707336</t>
   </si>
   <si>
     <t xml:space="preserve">1.67157876491547</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">1.61012375354767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62241470813751</t>
+    <t xml:space="preserve">1.62241458892822</t>
   </si>
   <si>
     <t xml:space="preserve">1.6633847951889</t>
@@ -341,10 +341,10 @@
     <t xml:space="preserve">1.67321753501892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64535772800446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63880264759064</t>
+    <t xml:space="preserve">1.64535784721375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63880276679993</t>
   </si>
   <si>
     <t xml:space="preserve">1.62569224834442</t>
@@ -356,25 +356,25 @@
     <t xml:space="preserve">1.65519070625305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64699673652649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63798308372498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59865188598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62978911399841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58308339118958</t>
+    <t xml:space="preserve">1.6469966173172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63798320293427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59865212440491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6297892332077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58308351039886</t>
   </si>
   <si>
     <t xml:space="preserve">1.59537434577942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.578986287117</t>
+    <t xml:space="preserve">1.57898640632629</t>
   </si>
   <si>
     <t xml:space="preserve">1.59127748012543</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">1.56997299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56669533252716</t>
+    <t xml:space="preserve">1.56669521331787</t>
   </si>
   <si>
     <t xml:space="preserve">1.5585013628006</t>
@@ -398,13 +398,13 @@
     <t xml:space="preserve">1.6027489900589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60356855392456</t>
+    <t xml:space="preserve">1.60356843471527</t>
   </si>
   <si>
     <t xml:space="preserve">1.6060266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51917004585266</t>
+    <t xml:space="preserve">1.51916992664337</t>
   </si>
   <si>
     <t xml:space="preserve">1.5617790222168</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">1.54539108276367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37659430503845</t>
+    <t xml:space="preserve">1.37659406661987</t>
   </si>
   <si>
     <t xml:space="preserve">1.4126478433609</t>
@@ -422,13 +422,13 @@
     <t xml:space="preserve">1.39462113380432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45771503448486</t>
+    <t xml:space="preserve">1.45771491527557</t>
   </si>
   <si>
     <t xml:space="preserve">1.47082531452179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53391921520233</t>
+    <t xml:space="preserve">1.53391933441162</t>
   </si>
   <si>
     <t xml:space="preserve">1.61258184909821</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">1.61176240444183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59783267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54211330413818</t>
+    <t xml:space="preserve">1.59783256053925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54211318492889</t>
   </si>
   <si>
     <t xml:space="preserve">1.51179552078247</t>
@@ -452,13 +452,13 @@
     <t xml:space="preserve">1.56505656242371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56423723697662</t>
+    <t xml:space="preserve">1.56423711776733</t>
   </si>
   <si>
     <t xml:space="preserve">1.59291613101959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55686259269714</t>
+    <t xml:space="preserve">1.55686247348785</t>
   </si>
   <si>
     <t xml:space="preserve">1.52162826061249</t>
@@ -467,22 +467,22 @@
     <t xml:space="preserve">1.5412939786911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50442087650299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5109760761261</t>
+    <t xml:space="preserve">1.5044207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51097595691681</t>
   </si>
   <si>
     <t xml:space="preserve">1.55112683773041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51589262485504</t>
+    <t xml:space="preserve">1.51589250564575</t>
   </si>
   <si>
     <t xml:space="preserve">1.55194616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50851774215698</t>
+    <t xml:space="preserve">1.50851786136627</t>
   </si>
   <si>
     <t xml:space="preserve">1.53228056430817</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">1.50933718681335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5076984167099</t>
+    <t xml:space="preserve">1.50769853591919</t>
   </si>
   <si>
     <t xml:space="preserve">1.50278210639954</t>
@@ -500,55 +500,55 @@
     <t xml:space="preserve">1.49540746212006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51015686988831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57325053215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58554148674011</t>
+    <t xml:space="preserve">1.51015675067902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57325041294098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5855416059494</t>
   </si>
   <si>
     <t xml:space="preserve">1.59455490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60684597492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62159526348114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5716118812561</t>
+    <t xml:space="preserve">1.60684585571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62159538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57161176204681</t>
   </si>
   <si>
     <t xml:space="preserve">1.54375207424164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57243132591248</t>
+    <t xml:space="preserve">1.57243120670319</t>
   </si>
   <si>
     <t xml:space="preserve">1.58718037605286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54621028900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55768203735352</t>
+    <t xml:space="preserve">1.54621040821075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55768191814423</t>
   </si>
   <si>
     <t xml:space="preserve">1.58799982070923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5347386598587</t>
+    <t xml:space="preserve">1.53473877906799</t>
   </si>
   <si>
     <t xml:space="preserve">1.5822639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54702973365784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53883564472198</t>
+    <t xml:space="preserve">1.54702961444855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53883576393127</t>
   </si>
   <si>
     <t xml:space="preserve">1.54784917831421</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">1.53801620006561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.548668384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53637742996216</t>
+    <t xml:space="preserve">1.54866850376129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53637754917145</t>
   </si>
   <si>
     <t xml:space="preserve">1.53965508937836</t>
@@ -578,49 +578,49 @@
     <t xml:space="preserve">1.65191304683685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69288325309753</t>
+    <t xml:space="preserve">1.69288313388824</t>
   </si>
   <si>
     <t xml:space="preserve">1.65355181694031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82070958614349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82890379428864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81743228435516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579351425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87970662117004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79448890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80104398727417</t>
+    <t xml:space="preserve">1.82070970535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82890391349792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81743216514587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81579327583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87970674037933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79448914527893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80104422569275</t>
   </si>
   <si>
     <t xml:space="preserve">1.73876953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729802131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74696373939514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76335167884827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84693074226379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81087708473206</t>
+    <t xml:space="preserve">1.72729790210724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74696362018585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76335179805756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84693050384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81087684631348</t>
   </si>
   <si>
     <t xml:space="preserve">1.80923819541931</t>
@@ -629,82 +629,82 @@
     <t xml:space="preserve">1.81251573562622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86167967319489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86495733261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85840201377869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87642908096313</t>
+    <t xml:space="preserve">1.86167991161346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86495745182037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8584018945694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87642884254456</t>
   </si>
   <si>
     <t xml:space="preserve">1.89937245845795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84856963157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92479646205902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679428100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850803375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97107350826263</t>
+    <t xml:space="preserve">1.84856951236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92479658126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679404258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850827217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107374668121</t>
   </si>
   <si>
     <t xml:space="preserve">1.92822444438934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94193601608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94364988803864</t>
+    <t xml:space="preserve">1.94193613529205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94364976882935</t>
   </si>
   <si>
     <t xml:space="preserve">1.95907580852509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96764576435089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92651033401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95393407344818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93336641788483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90594255924225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8939448595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8716629743576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92993855476379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90080070495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91451239585876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88708865642548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87680494785309</t>
+    <t xml:space="preserve">1.9676456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92651009559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95393395423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93336629867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90594244003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89394462108612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87166309356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92993819713593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90080058574677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91451263427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88708877563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87680518627167</t>
   </si>
   <si>
     <t xml:space="preserve">1.9179402589798</t>
@@ -713,61 +713,61 @@
     <t xml:space="preserve">1.8853747844696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86994886398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88880300521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90937054157257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90251469612122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96421790122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96250379085541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821353912354</t>
+    <t xml:space="preserve">1.86994910240173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88880276679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90937066078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90251481533051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96421778202057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96250355243683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821341991425</t>
   </si>
   <si>
     <t xml:space="preserve">1.98649966716766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97964346408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12533164024353</t>
+    <t xml:space="preserve">1.97964358329773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12533140182495</t>
   </si>
   <si>
     <t xml:space="preserve">2.08591032028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05677270889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07905411720276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0807683467865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06534242630005</t>
+    <t xml:space="preserve">2.05677247047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07905435562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08076810836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06534266471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.06020045280457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07219815254211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13390159606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10819172859192</t>
+    <t xml:space="preserve">2.07219839096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13390135765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1081919670105</t>
   </si>
   <si>
     <t xml:space="preserve">2.09962201118469</t>
@@ -776,16 +776,16 @@
     <t xml:space="preserve">2.10304999351501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03963279724121</t>
+    <t xml:space="preserve">2.03963303565979</t>
   </si>
   <si>
     <t xml:space="preserve">2.06877040863037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11504793167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07391238212585</t>
+    <t xml:space="preserve">2.11504769325256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07391214370728</t>
   </si>
   <si>
     <t xml:space="preserve">2.09790802001953</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">2.06705617904663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12190389633179</t>
+    <t xml:space="preserve">2.12190365791321</t>
   </si>
   <si>
     <t xml:space="preserve">2.10647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0893383026123</t>
+    <t xml:space="preserve">2.08933806419373</t>
   </si>
   <si>
     <t xml:space="preserve">2.05163049697876</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">2.17675089836121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14247179031372</t>
+    <t xml:space="preserve">2.14247155189514</t>
   </si>
   <si>
     <t xml:space="preserve">2.1321873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13047385215759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15961098670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11847567558289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09105205535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12361764907837</t>
+    <t xml:space="preserve">2.13047361373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15961122512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11847591400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09105229377747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12361788749695</t>
   </si>
   <si>
     <t xml:space="preserve">2.11161994934082</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">2.1407573223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14932703971863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13904356956482</t>
+    <t xml:space="preserve">2.14932727813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13904333114624</t>
   </si>
   <si>
     <t xml:space="preserve">2.17503714561462</t>
@@ -866,34 +866,34 @@
     <t xml:space="preserve">2.15104126930237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12018966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1047637462616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06362819671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03277707099915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0482029914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07048416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0499165058136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12875962257385</t>
+    <t xml:space="preserve">2.12018942832947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10476398468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06362843513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03277683258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04820275306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07048439979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04991674423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12875986099243</t>
   </si>
   <si>
     <t xml:space="preserve">2.08762431144714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0207793712616</t>
+    <t xml:space="preserve">2.02077913284302</t>
   </si>
   <si>
     <t xml:space="preserve">2.08419609069824</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">2.0224928855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01392292976379</t>
+    <t xml:space="preserve">2.01392316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.00535321235657</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">2.1681809425354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18532085418701</t>
+    <t xml:space="preserve">2.18532061576843</t>
   </si>
   <si>
     <t xml:space="preserve">2.29672932624817</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">2.33100891113281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32243895530701</t>
+    <t xml:space="preserve">2.32243919372559</t>
   </si>
   <si>
     <t xml:space="preserve">2.35671854019165</t>
@@ -935,16 +935,16 @@
     <t xml:space="preserve">2.46812725067139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47669696807861</t>
+    <t xml:space="preserve">2.47669720649719</t>
   </si>
   <si>
     <t xml:space="preserve">2.48526692390442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53668642044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57953548431396</t>
+    <t xml:space="preserve">2.53668618202209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57953572273254</t>
   </si>
   <si>
     <t xml:space="preserve">2.596675157547</t>
@@ -953,22 +953,25 @@
     <t xml:space="preserve">2.61381506919861</t>
   </si>
   <si>
+    <t xml:space="preserve">2.55382609367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63447308540344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59862995147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5896692276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61655163764954</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.55382585525513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63447332382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59862995147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5896692276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61655139923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52694344520569</t>
+    <t xml:space="preserve">2.52694368362427</t>
   </si>
   <si>
     <t xml:space="preserve">2.437335729599</t>
@@ -977,16 +980,16 @@
     <t xml:space="preserve">2.46421790122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50006127357483</t>
+    <t xml:space="preserve">2.50006103515625</t>
   </si>
   <si>
     <t xml:space="preserve">2.45525717735291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54486513137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57174754142761</t>
+    <t xml:space="preserve">2.54486489295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57174730300903</t>
   </si>
   <si>
     <t xml:space="preserve">2.51798272132874</t>
@@ -998,7 +1001,7 @@
     <t xml:space="preserve">2.53590416908264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49110054969788</t>
+    <t xml:space="preserve">2.4911003112793</t>
   </si>
   <si>
     <t xml:space="preserve">2.48213958740234</t>
@@ -1016,37 +1019,37 @@
     <t xml:space="preserve">2.7599241733551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77784585952759</t>
+    <t xml:space="preserve">2.77784562110901</t>
   </si>
   <si>
     <t xml:space="preserve">2.74200248718262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76888513565063</t>
+    <t xml:space="preserve">2.76888465881348</t>
   </si>
   <si>
     <t xml:space="preserve">2.71512031555176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75096321105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67031621932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72408103942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65239477157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68823790550232</t>
+    <t xml:space="preserve">2.75096344947815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67031645774841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72408080101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65239453315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68823766708374</t>
   </si>
   <si>
     <t xml:space="preserve">2.73304176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69719886779785</t>
+    <t xml:space="preserve">2.69719862937927</t>
   </si>
   <si>
     <t xml:space="preserve">2.67927694320679</t>
@@ -1055,25 +1058,25 @@
     <t xml:space="preserve">2.84953236579895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86745381355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83161067962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64343404769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62551259994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58070850372314</t>
+    <t xml:space="preserve">2.86745357513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83161044120789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6434338092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62551236152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58070826530457</t>
   </si>
   <si>
     <t xml:space="preserve">2.607590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41941404342651</t>
+    <t xml:space="preserve">2.41941428184509</t>
   </si>
   <si>
     <t xml:space="preserve">2.66135549545288</t>
@@ -1082,7 +1085,7 @@
     <t xml:space="preserve">2.81368899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.840571641922</t>
+    <t xml:space="preserve">2.84057140350342</t>
   </si>
   <si>
     <t xml:space="preserve">2.93914008140564</t>
@@ -1091,7 +1094,7 @@
     <t xml:space="preserve">2.87641453742981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82264971733093</t>
+    <t xml:space="preserve">2.82264995574951</t>
   </si>
   <si>
     <t xml:space="preserve">2.80472826957703</t>
@@ -1103,34 +1106,34 @@
     <t xml:space="preserve">3.12731671333313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16315960884094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13627743721008</t>
+    <t xml:space="preserve">3.16315984725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13627767562866</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004225730896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25276780128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26172852516174</t>
+    <t xml:space="preserve">3.25276803970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26172876358032</t>
   </si>
   <si>
     <t xml:space="preserve">3.28861093521118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29757165908813</t>
+    <t xml:space="preserve">3.29757189750671</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33341479301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34237575531006</t>
+    <t xml:space="preserve">3.33341503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34237551689148</t>
   </si>
   <si>
     <t xml:space="preserve">3.42302274703979</t>
@@ -1145,19 +1148,19 @@
     <t xml:space="preserve">3.41406202316284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36925792694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37821888923645</t>
+    <t xml:space="preserve">3.36925840377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37821865081787</t>
   </si>
   <si>
     <t xml:space="preserve">3.45886588096619</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4857485294342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47678756713867</t>
+    <t xml:space="preserve">3.48574829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47678780555725</t>
   </si>
   <si>
     <t xml:space="preserve">3.49470925331116</t>
@@ -1175,16 +1178,16 @@
     <t xml:space="preserve">3.59327816963196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55743479728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5215916633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51263093948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5395131111145</t>
+    <t xml:space="preserve">3.55743455886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52159142494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51263070106506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53951334953308</t>
   </si>
   <si>
     <t xml:space="preserve">3.60223865509033</t>
@@ -1193,13 +1196,13 @@
     <t xml:space="preserve">3.65600347518921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66496443748474</t>
+    <t xml:space="preserve">3.66496419906616</t>
   </si>
   <si>
     <t xml:space="preserve">3.72768974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71872925758362</t>
+    <t xml:space="preserve">3.71872901916504</t>
   </si>
   <si>
     <t xml:space="preserve">3.6918466091156</t>
@@ -1208,7 +1211,7 @@
     <t xml:space="preserve">3.70976805686951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68288588523865</t>
+    <t xml:space="preserve">3.68288612365723</t>
   </si>
   <si>
     <t xml:space="preserve">3.7635326385498</t>
@@ -1217,7 +1220,7 @@
     <t xml:space="preserve">3.78145432472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80833721160889</t>
+    <t xml:space="preserve">3.80833697319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.79041528701782</t>
@@ -1226,7 +1229,7 @@
     <t xml:space="preserve">3.95170950889587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96067070960999</t>
+    <t xml:space="preserve">3.96067023277283</t>
   </si>
   <si>
     <t xml:space="preserve">3.97005581855774</t>
@@ -1242,9 +1245,6 @@
   </si>
   <si>
     <t xml:space="preserve">3.87620115280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96067023277283</t>
   </si>
   <si>
     <t xml:space="preserve">4.02636861801147</t>
@@ -18630,7 +18630,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18656,7 +18656,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G613" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18682,7 +18682,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G614" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18708,7 +18708,7 @@
         <v>2.75</v>
       </c>
       <c r="G615" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18734,7 +18734,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G616" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18760,7 +18760,7 @@
         <v>2.75</v>
       </c>
       <c r="G617" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18786,7 +18786,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G618" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18812,7 +18812,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G619" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18838,7 +18838,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G620" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18864,7 +18864,7 @@
         <v>2.75</v>
       </c>
       <c r="G621" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18890,7 +18890,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G622" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18916,7 +18916,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18942,7 +18942,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18968,7 +18968,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -18994,7 +18994,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19020,7 +19020,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G627" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19046,7 +19046,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G628" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19072,7 +19072,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G629" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19098,7 +19098,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G630" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19124,7 +19124,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19150,7 +19150,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G632" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19176,7 +19176,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19202,7 +19202,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G634" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19228,7 +19228,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G635" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19254,7 +19254,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G636" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19280,7 +19280,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19306,7 +19306,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19332,7 +19332,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19358,7 +19358,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19384,7 +19384,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19410,7 +19410,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19436,7 +19436,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19462,7 +19462,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19488,7 +19488,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19514,7 +19514,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19540,7 +19540,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G647" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19566,7 +19566,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G648" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19592,7 +19592,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G649" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19618,7 +19618,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G650" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19644,7 +19644,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G651" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19696,7 +19696,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G653" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19748,7 +19748,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19774,7 +19774,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G656" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19800,7 +19800,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -19826,7 +19826,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G658" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -19852,7 +19852,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19878,7 +19878,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G660" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19904,7 +19904,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G661" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19930,7 +19930,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G662" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19956,7 +19956,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G663" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19982,7 +19982,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G664" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20008,7 +20008,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20034,7 +20034,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20060,7 +20060,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20086,7 +20086,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20138,7 +20138,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G670" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20164,7 +20164,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20190,7 +20190,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G672" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20216,7 +20216,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G673" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20242,7 +20242,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20268,7 +20268,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20294,7 +20294,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G676" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20320,7 +20320,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20346,7 +20346,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20372,7 +20372,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G679" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20398,7 +20398,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20424,7 +20424,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G681" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20450,7 +20450,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20476,7 +20476,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20502,7 +20502,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20528,7 +20528,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20554,7 +20554,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20580,7 +20580,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20606,7 +20606,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20632,7 +20632,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20658,7 +20658,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20684,7 +20684,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20710,7 +20710,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G692" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20736,7 +20736,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20762,7 +20762,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20788,7 +20788,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20814,7 +20814,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20840,7 +20840,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20866,7 +20866,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -20892,7 +20892,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -20918,7 +20918,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -20944,7 +20944,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -20970,7 +20970,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20996,7 +20996,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21022,7 +21022,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21048,7 +21048,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21074,7 +21074,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21100,7 +21100,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21152,7 +21152,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G709" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21178,7 +21178,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G710" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21204,7 +21204,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G711" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21230,7 +21230,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21360,7 +21360,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G717" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21386,7 +21386,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21412,7 +21412,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G719" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21594,7 +21594,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G726" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21698,7 +21698,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21802,7 +21802,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G734" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21828,7 +21828,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G735" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21854,7 +21854,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G736" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21880,7 +21880,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G737" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21906,7 +21906,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21932,7 +21932,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G739" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21958,7 +21958,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21984,7 +21984,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G741" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22010,7 +22010,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G742" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22036,7 +22036,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G743" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22062,7 +22062,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G744" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22088,7 +22088,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G745" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22114,7 +22114,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22140,7 +22140,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22166,7 +22166,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22192,7 +22192,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G749" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22218,7 +22218,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22244,7 +22244,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22270,7 +22270,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22296,7 +22296,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22322,7 +22322,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22348,7 +22348,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22374,7 +22374,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22400,7 +22400,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22426,7 +22426,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22452,7 +22452,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G759" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22478,7 +22478,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G760" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22504,7 +22504,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G761" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22530,7 +22530,7 @@
         <v>2.75</v>
       </c>
       <c r="G762" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22556,7 +22556,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22582,7 +22582,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22608,7 +22608,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22660,7 +22660,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22686,7 +22686,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G768" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22712,7 +22712,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22738,7 +22738,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22764,7 +22764,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22790,7 +22790,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22816,7 +22816,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22842,7 +22842,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22868,7 +22868,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22894,7 +22894,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22920,7 +22920,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22946,7 +22946,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22972,7 +22972,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G779" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22998,7 +22998,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23024,7 +23024,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23050,7 +23050,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G782" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23076,7 +23076,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23102,7 +23102,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G784" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23128,7 +23128,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G785" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23154,7 +23154,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23180,7 +23180,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G787" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23206,7 +23206,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G788" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23232,7 +23232,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G789" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23258,7 +23258,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23284,7 +23284,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G791" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23310,7 +23310,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G792" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23336,7 +23336,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G793" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23362,7 +23362,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23388,7 +23388,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23414,7 +23414,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23440,7 +23440,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G797" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23466,7 +23466,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G798" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23492,7 +23492,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23518,7 +23518,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G800" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23544,7 +23544,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23570,7 +23570,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G802" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23596,7 +23596,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23622,7 +23622,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G804" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23648,7 +23648,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23674,7 +23674,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23700,7 +23700,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G807" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23726,7 +23726,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G808" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23752,7 +23752,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G809" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23778,7 +23778,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G810" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23804,7 +23804,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G811" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23830,7 +23830,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23856,7 +23856,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G813" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23882,7 +23882,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G814" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23908,7 +23908,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23934,7 +23934,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G816" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23960,7 +23960,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23986,7 +23986,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G818" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24012,7 +24012,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24038,7 +24038,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G820" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24064,7 +24064,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G821" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24090,7 +24090,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24116,7 +24116,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G823" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24142,7 +24142,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G824" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24168,7 +24168,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G825" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24194,7 +24194,7 @@
         <v>4</v>
       </c>
       <c r="G826" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24220,7 +24220,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G827" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24246,7 +24246,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G828" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24272,7 +24272,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G829" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24298,7 +24298,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G830" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24324,7 +24324,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24350,7 +24350,7 @@
         <v>4</v>
       </c>
       <c r="G832" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24376,7 +24376,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24402,7 +24402,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24428,7 +24428,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24454,7 +24454,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G836" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24480,7 +24480,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24506,7 +24506,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24532,7 +24532,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G839" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24558,7 +24558,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24584,7 +24584,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G841" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24610,7 +24610,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G842" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24636,7 +24636,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24662,7 +24662,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G844" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24688,7 +24688,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G845" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24714,7 +24714,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24740,7 +24740,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24766,7 +24766,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24792,7 +24792,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24818,7 +24818,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G850" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24844,7 +24844,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24870,7 +24870,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24896,7 +24896,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G853" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24922,7 +24922,7 @@
         <v>4.25</v>
       </c>
       <c r="G854" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24948,7 +24948,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24974,7 +24974,7 @@
         <v>4.25</v>
       </c>
       <c r="G856" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25000,7 +25000,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G857" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25026,7 +25026,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G858" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25052,7 +25052,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G859" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25078,7 +25078,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25104,7 +25104,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G861" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25130,7 +25130,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G862" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25156,7 +25156,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G863" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25182,7 +25182,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G864" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25208,7 +25208,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G865" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25260,7 +25260,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G867" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25364,7 +25364,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25416,7 +25416,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G873" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25546,7 +25546,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G878" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25910,7 +25910,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G892" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25988,7 +25988,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G895" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26222,7 +26222,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G904" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -30408,7 +30408,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1065" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30694,7 +30694,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1076" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30720,7 +30720,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1077" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30954,7 +30954,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1086" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31318,7 +31318,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1100" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31422,7 +31422,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1104" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32930,7 +32930,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1162" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32956,7 +32956,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1163" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33398,7 +33398,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1180" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33528,7 +33528,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1185" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33736,7 +33736,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1193" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -67830,19 +67830,19 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6808333333</v>
+        <v>45967.6912268518</v>
       </c>
       <c r="B2505" t="n">
-        <v>6200</v>
+        <v>2815</v>
       </c>
       <c r="C2505" t="n">
-        <v>1.49000000953674</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="D2505" t="n">
-        <v>1.44000005722046</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="E2505" t="n">
-        <v>1.44000005722046</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="F2505" t="n">
         <v>1.46000003814697</v>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -50,49 +50,49 @@
     <t xml:space="preserve">1.92109167575836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88496315479279</t>
+    <t xml:space="preserve">1.8849630355835</t>
   </si>
   <si>
     <t xml:space="preserve">1.9242330789566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80642282962799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82998490333557</t>
+    <t xml:space="preserve">1.80642294883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82998502254486</t>
   </si>
   <si>
     <t xml:space="preserve">1.79856908321381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76715290546417</t>
+    <t xml:space="preserve">1.76715278625488</t>
   </si>
   <si>
     <t xml:space="preserve">1.85354709625244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86925506591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87710916996002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281725883484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86768436431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81584775447845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83783888816833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87553811073303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684350013733</t>
+    <t xml:space="preserve">1.86925530433655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8771094083786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281737804413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86768412590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81584787368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83783912658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553822994232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684326171875</t>
   </si>
   <si>
     <t xml:space="preserve">1.84569299221039</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">1.81898939609528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83626818656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85983026027679</t>
+    <t xml:space="preserve">1.8362683057785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85983002185822</t>
   </si>
   <si>
     <t xml:space="preserve">1.80485212802887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82056021690369</t>
+    <t xml:space="preserve">1.8205600976944</t>
   </si>
   <si>
     <t xml:space="preserve">1.81741857528687</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">1.88025057315826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81427693367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85197651386261</t>
+    <t xml:space="preserve">1.81427705287933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85197615623474</t>
   </si>
   <si>
     <t xml:space="preserve">1.84412217140198</t>
@@ -134,121 +134,121 @@
     <t xml:space="preserve">1.84098076820374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82370185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81113541126251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8221310377121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9367995262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622445106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407855510712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.963503241539</t>
+    <t xml:space="preserve">1.82370173931122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81113529205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82213091850281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679976463318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622421264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407831668854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96350312232971</t>
   </si>
   <si>
     <t xml:space="preserve">1.96507394313812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99334871768951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00434422492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98706519603729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905656814575</t>
+    <t xml:space="preserve">1.99334836006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00434398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98706543445587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905632972717</t>
   </si>
   <si>
     <t xml:space="preserve">2.02476453781128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93051636219025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96193242073059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994116783142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637921333313</t>
+    <t xml:space="preserve">1.93051612377167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96193218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994128704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564925670624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637945175171</t>
   </si>
   <si>
     <t xml:space="preserve">1.8739675283432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93378722667694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92231559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050920963287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509159564972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95836937427521</t>
+    <t xml:space="preserve">1.93378710746765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017540454865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9223153591156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050932884216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656310558319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509171485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9583694934845</t>
   </si>
   <si>
     <t xml:space="preserve">1.91739916801453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9354259967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198107719421</t>
+    <t xml:space="preserve">1.93542611598969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198095798492</t>
   </si>
   <si>
     <t xml:space="preserve">1.91248285770416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91084396839142</t>
+    <t xml:space="preserve">1.91084420681</t>
   </si>
   <si>
     <t xml:space="preserve">1.83545911312103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80268287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84201407432556</t>
+    <t xml:space="preserve">1.80268275737762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84201419353485</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218157291412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88298439979553</t>
+    <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
     <t xml:space="preserve">1.86823499202728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90756630897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281702041626</t>
+    <t xml:space="preserve">1.90756642818451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281713962555</t>
   </si>
   <si>
     <t xml:space="preserve">1.90592741966248</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">1.8846230506897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9092048406601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87151265144348</t>
+    <t xml:space="preserve">1.90920507907867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87151277065277</t>
   </si>
   <si>
     <t xml:space="preserve">1.8977335691452</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">1.75843513011932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76662933826447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78629505634308</t>
+    <t xml:space="preserve">1.76662921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78629517555237</t>
   </si>
   <si>
     <t xml:space="preserve">1.77646207809448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75188016891479</t>
+    <t xml:space="preserve">1.75188004970551</t>
   </si>
   <si>
     <t xml:space="preserve">1.75351893901825</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">1.77973961830139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75024127960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72074258327484</t>
+    <t xml:space="preserve">1.75024116039276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72074270248413</t>
   </si>
   <si>
     <t xml:space="preserve">1.66993999481201</t>
@@ -302,40 +302,40 @@
     <t xml:space="preserve">1.72893679141998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69616067409515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76007401943207</t>
+    <t xml:space="preserve">1.69616079330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76007413864136</t>
   </si>
   <si>
     <t xml:space="preserve">1.70435476303101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73549211025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73385322093964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71254873275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63060867786407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67157864570618</t>
+    <t xml:space="preserve">1.73549199104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73385310173035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71254885196686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63060879707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67157876491547</t>
   </si>
   <si>
     <t xml:space="preserve">1.66666233539581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61012363433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62241470813751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66338455677032</t>
+    <t xml:space="preserve">1.61012375354767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62241458892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66338467597961</t>
   </si>
   <si>
     <t xml:space="preserve">1.67321765422821</t>
@@ -344,19 +344,19 @@
     <t xml:space="preserve">1.64535784721375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63880252838135</t>
+    <t xml:space="preserve">1.63880276679993</t>
   </si>
   <si>
     <t xml:space="preserve">1.62569224834442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66830122470856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65519082546234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64699673652649</t>
+    <t xml:space="preserve">1.66830110549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65519070625305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64699685573578</t>
   </si>
   <si>
     <t xml:space="preserve">1.63798320293427</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">1.59865200519562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62978911399841</t>
+    <t xml:space="preserve">1.6297892332077</t>
   </si>
   <si>
     <t xml:space="preserve">1.58308351039886</t>
@@ -374,22 +374,22 @@
     <t xml:space="preserve">1.59537446498871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.578986287117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59127736091614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54047453403473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56751477718353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56997287273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56669533252716</t>
+    <t xml:space="preserve">1.57898640632629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59127748012543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54047441482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56751465797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56997299194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56669545173645</t>
   </si>
   <si>
     <t xml:space="preserve">1.55850124359131</t>
@@ -398,28 +398,28 @@
     <t xml:space="preserve">1.6027489900589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60356843471527</t>
+    <t xml:space="preserve">1.60356855392456</t>
   </si>
   <si>
     <t xml:space="preserve">1.60602676868439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51916992664337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5617790222168</t>
+    <t xml:space="preserve">1.51917016506195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56177890300751</t>
   </si>
   <si>
     <t xml:space="preserve">1.54539096355438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37659418582916</t>
+    <t xml:space="preserve">1.37659430503845</t>
   </si>
   <si>
     <t xml:space="preserve">1.4126478433609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39462113380432</t>
+    <t xml:space="preserve">1.39462125301361</t>
   </si>
   <si>
     <t xml:space="preserve">1.45771503448486</t>
@@ -431,37 +431,37 @@
     <t xml:space="preserve">1.53391933441162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61258172988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61176240444183</t>
+    <t xml:space="preserve">1.61258184909821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61176252365112</t>
   </si>
   <si>
     <t xml:space="preserve">1.59783267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54211318492889</t>
+    <t xml:space="preserve">1.54211330413818</t>
   </si>
   <si>
     <t xml:space="preserve">1.51179552078247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55522382259369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56505644321442</t>
+    <t xml:space="preserve">1.55522358417511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.565056681633</t>
   </si>
   <si>
     <t xml:space="preserve">1.56423723697662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59291625022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55686259269714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52162837982178</t>
+    <t xml:space="preserve">1.59291636943817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55686247348785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52162826061249</t>
   </si>
   <si>
     <t xml:space="preserve">1.5412939786911</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">1.50442087650299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5109760761261</t>
+    <t xml:space="preserve">1.51097619533539</t>
   </si>
   <si>
     <t xml:space="preserve">1.55112683773041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51589250564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55194616317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50851774215698</t>
+    <t xml:space="preserve">1.51589238643646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55194628238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50851786136627</t>
   </si>
   <si>
     <t xml:space="preserve">1.53228056430817</t>
@@ -497,28 +497,28 @@
     <t xml:space="preserve">1.50278210639954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49540746212006</t>
+    <t xml:space="preserve">1.49540734291077</t>
   </si>
   <si>
     <t xml:space="preserve">1.51015675067902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57325053215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58554148674011</t>
+    <t xml:space="preserve">1.57325065135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5855416059494</t>
   </si>
   <si>
     <t xml:space="preserve">1.59455490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60684597492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62159526348114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57161176204681</t>
+    <t xml:space="preserve">1.60684609413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62159514427185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5716118812561</t>
   </si>
   <si>
     <t xml:space="preserve">1.54375207424164</t>
@@ -536,25 +536,25 @@
     <t xml:space="preserve">1.55768191814423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58799982070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5347386598587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58226406574249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54702973365784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53883576393127</t>
+    <t xml:space="preserve">1.58799970149994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53473877906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5822639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54702961444855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53883564472198</t>
   </si>
   <si>
     <t xml:space="preserve">1.54784917831421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55276548862457</t>
+    <t xml:space="preserve">1.55276560783386</t>
   </si>
   <si>
     <t xml:space="preserve">1.54948794841766</t>
@@ -566,43 +566,43 @@
     <t xml:space="preserve">1.54866850376129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53637742996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53965508937836</t>
+    <t xml:space="preserve">1.53637754917145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53965520858765</t>
   </si>
   <si>
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191304683685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69288313388824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65355169773102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82070958614349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82890379428864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81743204593658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579339504242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87970650196075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79448902606964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80104410648346</t>
+    <t xml:space="preserve">1.65191316604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69288325309753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65355181694031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82070970535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82890403270721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81743216514587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81579327583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87970662117004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79448914527893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80104422569275</t>
   </si>
   <si>
     <t xml:space="preserve">1.73876953125</t>
@@ -614,67 +614,67 @@
     <t xml:space="preserve">1.74696373939514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76335144042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84693038463593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81087708473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80923819541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81251573562622</t>
+    <t xml:space="preserve">1.76335167884827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84693026542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81087696552277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923807621002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81251561641693</t>
   </si>
   <si>
     <t xml:space="preserve">1.86167979240417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86495745182037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85840213298798</t>
+    <t xml:space="preserve">1.86495733261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85840225219727</t>
   </si>
   <si>
     <t xml:space="preserve">1.87642908096313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89937257766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84856963157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92479622364044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679404258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850815296173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9710738658905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822432518005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94193637371063</t>
+    <t xml:space="preserve">1.89937233924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84856939315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92479634284973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679416179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850827217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107362747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822420597076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94193613529205</t>
   </si>
   <si>
     <t xml:space="preserve">1.94364988803864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95907604694366</t>
+    <t xml:space="preserve">1.9590756893158</t>
   </si>
   <si>
     <t xml:space="preserve">1.96764576435089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9265102148056</t>
+    <t xml:space="preserve">1.92651009559631</t>
   </si>
   <si>
     <t xml:space="preserve">1.95393395423889</t>
@@ -686,22 +686,22 @@
     <t xml:space="preserve">1.90594255924225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8939448595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8716629743576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92993855476379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90080046653748</t>
+    <t xml:space="preserve">1.89394474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87166285514832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92993831634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90080058574677</t>
   </si>
   <si>
     <t xml:space="preserve">1.91451239585876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88708889484406</t>
+    <t xml:space="preserve">1.88708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">1.87680494785309</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">1.91794049739838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8853747844696</t>
+    <t xml:space="preserve">1.88537502288818</t>
   </si>
   <si>
     <t xml:space="preserve">1.86994910240173</t>
@@ -719,34 +719,34 @@
     <t xml:space="preserve">1.88880276679993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90937054157257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90251457691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96421802043915</t>
+    <t xml:space="preserve">1.90937030315399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90251445770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96421778202057</t>
   </si>
   <si>
     <t xml:space="preserve">1.96250379085541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821341991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98649966716766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964346408844</t>
+    <t xml:space="preserve">1.98821365833282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98649954795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97964358329773</t>
   </si>
   <si>
     <t xml:space="preserve">2.12533140182495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0859100818634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05677270889282</t>
+    <t xml:space="preserve">2.08591032028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05677247047424</t>
   </si>
   <si>
     <t xml:space="preserve">2.07905459403992</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">2.08076810836792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06534218788147</t>
+    <t xml:space="preserve">2.06534266471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.06020069122314</t>
@@ -767,28 +767,28 @@
     <t xml:space="preserve">2.13390159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1081919670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09962201118469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10304975509644</t>
+    <t xml:space="preserve">2.10819172859192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09962224960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10304999351501</t>
   </si>
   <si>
     <t xml:space="preserve">2.03963279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06877064704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11504769325256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07391238212585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09790802001953</t>
+    <t xml:space="preserve">2.06877040863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11504793167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07391262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09790778160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.1167619228363</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">2.08248209953308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06705665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12190365791321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10647773742676</t>
+    <t xml:space="preserve">2.06705641746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12190389633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10647797584534</t>
   </si>
   <si>
     <t xml:space="preserve">2.08933806419373</t>
@@ -812,13 +812,13 @@
     <t xml:space="preserve">2.05163073539734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17675113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14247131347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13218760490417</t>
+    <t xml:space="preserve">2.17675089836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14247155189514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1321873664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.13047361373901</t>
@@ -830,40 +830,40 @@
     <t xml:space="preserve">2.11847543716431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09105229377747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12361764907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11161994934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10133576393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15789723396301</t>
+    <t xml:space="preserve">2.09105205535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12361741065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11161971092224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10133600234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15789699554443</t>
   </si>
   <si>
     <t xml:space="preserve">2.15618324279785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14418530464172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1407573223114</t>
+    <t xml:space="preserve">2.1441855430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14075756072998</t>
   </si>
   <si>
     <t xml:space="preserve">2.14932727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13904356956482</t>
+    <t xml:space="preserve">2.13904333114624</t>
   </si>
   <si>
     <t xml:space="preserve">2.17503714561462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15104150772095</t>
+    <t xml:space="preserve">2.15104103088379</t>
   </si>
   <si>
     <t xml:space="preserve">2.12018966674805</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">2.03277683258057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0482029914856</t>
+    <t xml:space="preserve">2.04820275306702</t>
   </si>
   <si>
     <t xml:space="preserve">2.07048416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04991674423218</t>
+    <t xml:space="preserve">2.0499165058136</t>
   </si>
   <si>
     <t xml:space="preserve">2.12875962257385</t>
@@ -908,52 +908,52 @@
     <t xml:space="preserve">2.00535321235657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1681809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18532061576843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29672932624817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33100867271423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32243919372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35671854019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44241738319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49383664131165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46812725067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47669696807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48526692390442</t>
+    <t xml:space="preserve">2.16818118095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18532085418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29672956466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33100891113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32243895530701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35671830177307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44241714477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49383687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46812701225281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47669720649719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48526668548584</t>
   </si>
   <si>
     <t xml:space="preserve">2.53668618202209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57953572273254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.596675157547</t>
+    <t xml:space="preserve">2.57953548431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59667539596558</t>
   </si>
   <si>
     <t xml:space="preserve">2.61381506919861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55382585525513</t>
+    <t xml:space="preserve">2.55382561683655</t>
   </si>
   <si>
     <t xml:space="preserve">2.63447332382202</t>
@@ -971,16 +971,16 @@
     <t xml:space="preserve">2.52694344520569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43733549118042</t>
+    <t xml:space="preserve">2.437335729599</t>
   </si>
   <si>
     <t xml:space="preserve">2.46421790122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50006103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45525717735291</t>
+    <t xml:space="preserve">2.50006127357483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45525741577148</t>
   </si>
   <si>
     <t xml:space="preserve">2.54486513137817</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">2.57174754142761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51798272132874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56278657913208</t>
+    <t xml:space="preserve">2.51798295974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56278681755066</t>
   </si>
   <si>
     <t xml:space="preserve">2.53590416908264</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">2.4911003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48213982582092</t>
+    <t xml:space="preserve">2.48213958740234</t>
   </si>
   <si>
     <t xml:space="preserve">2.50902199745178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47317886352539</t>
+    <t xml:space="preserve">2.47317862510681</t>
   </si>
   <si>
     <t xml:space="preserve">2.78680658340454</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">2.65239477157593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68823790550232</t>
+    <t xml:space="preserve">2.68823766708374</t>
   </si>
   <si>
     <t xml:space="preserve">2.73304176330566</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">2.84953236579895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86745381355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83161044120789</t>
+    <t xml:space="preserve">2.86745357513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83161067962646</t>
   </si>
   <si>
     <t xml:space="preserve">2.6434338092804</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">2.58070850372314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.607590675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41941428184509</t>
+    <t xml:space="preserve">2.60759091377258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41941404342651</t>
   </si>
   <si>
     <t xml:space="preserve">2.66135549545288</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">2.80472826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90329670906067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12731671333313</t>
+    <t xml:space="preserve">2.90329694747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12731647491455</t>
   </si>
   <si>
     <t xml:space="preserve">3.16315984725952</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">3.13627743721008</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19004225730896</t>
+    <t xml:space="preserve">3.19004201889038</t>
   </si>
   <si>
     <t xml:space="preserve">3.25276780128479</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">3.26172852516174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28861093521118</t>
+    <t xml:space="preserve">3.28861117362976</t>
   </si>
   <si>
     <t xml:space="preserve">3.29757189750671</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">3.48574876785278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47678756713867</t>
+    <t xml:space="preserve">3.47678780555725</t>
   </si>
   <si>
     <t xml:space="preserve">3.49470925331116</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">3.53055238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59327816963196</t>
+    <t xml:space="preserve">3.59327793121338</t>
   </si>
   <si>
     <t xml:space="preserve">3.55743479728699</t>
@@ -1184,19 +1184,19 @@
     <t xml:space="preserve">3.51263093948364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5395131111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60223865509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65600347518921</t>
+    <t xml:space="preserve">3.53951334953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60223889350891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65600323677063</t>
   </si>
   <si>
     <t xml:space="preserve">3.66496443748474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72768974304199</t>
+    <t xml:space="preserve">3.72768998146057</t>
   </si>
   <si>
     <t xml:space="preserve">3.71872925758362</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">3.6918466091156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70976805686951</t>
+    <t xml:space="preserve">3.70976781845093</t>
   </si>
   <si>
     <t xml:space="preserve">3.68288588523865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7635326385498</t>
+    <t xml:space="preserve">3.76353287696838</t>
   </si>
   <si>
     <t xml:space="preserve">3.78145432472229</t>
@@ -67908,7 +67908,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6910416667</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>4113</v>
@@ -67929,6 +67929,32 @@
         <v>791</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6061574074</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>4840</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>791</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8582592010498</t>
+    <t xml:space="preserve">1.85825943946838</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91323792934418</t>
+    <t xml:space="preserve">1.91323757171631</t>
   </si>
   <si>
     <t xml:space="preserve">1.92109143733978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88496315479279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92423319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80642282962799</t>
+    <t xml:space="preserve">1.88496327400208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92423331737518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80642294883728</t>
   </si>
   <si>
     <t xml:space="preserve">1.82998502254486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79856884479523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76715290546417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354697704315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86925506591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8771094083786</t>
+    <t xml:space="preserve">1.79856896400452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76715302467346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86925518512726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87710893154144</t>
   </si>
   <si>
     <t xml:space="preserve">1.89281690120697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86768400669098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81584763526917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83783900737762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87553834915161</t>
+    <t xml:space="preserve">1.86768424510956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81584787368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83783888816833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8755384683609</t>
   </si>
   <si>
     <t xml:space="preserve">1.82684350013733</t>
@@ -98,13 +98,13 @@
     <t xml:space="preserve">1.84569275379181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81898939609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83626842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8598301410675</t>
+    <t xml:space="preserve">1.81898927688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83626818656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85983037948608</t>
   </si>
   <si>
     <t xml:space="preserve">1.80485224723816</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">1.82056033611298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81741845607758</t>
+    <t xml:space="preserve">1.81741869449615</t>
   </si>
   <si>
     <t xml:space="preserve">1.85040557384491</t>
@@ -122,16 +122,16 @@
     <t xml:space="preserve">1.88025069236755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81427693367004</t>
+    <t xml:space="preserve">1.81427669525146</t>
   </si>
   <si>
     <t xml:space="preserve">1.85197615623474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84412217140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84098052978516</t>
+    <t xml:space="preserve">1.84412229061127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84098076820374</t>
   </si>
   <si>
     <t xml:space="preserve">1.82370185852051</t>
@@ -140,40 +140,40 @@
     <t xml:space="preserve">1.81113529205322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82213091850281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679976463318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622445106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407819747925</t>
+    <t xml:space="preserve">1.8221310377121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9367995262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622421264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407855510712</t>
   </si>
   <si>
     <t xml:space="preserve">1.963503241539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96507441997528</t>
+    <t xml:space="preserve">1.9650741815567</t>
   </si>
   <si>
     <t xml:space="preserve">1.99334847927094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00434398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98706543445587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905632972717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02476453781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93051600456238</t>
+    <t xml:space="preserve">2.00434446334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98706519603729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905656814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02476477622986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93051636219025</t>
   </si>
   <si>
     <t xml:space="preserve">1.96193242073059</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">1.93994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95564901828766</t>
+    <t xml:space="preserve">1.95564913749695</t>
   </si>
   <si>
     <t xml:space="preserve">1.91637921333313</t>
@@ -191,43 +191,43 @@
     <t xml:space="preserve">1.87396740913391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93378710746765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017516613007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92231547832489</t>
+    <t xml:space="preserve">1.93378722667694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017528533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92231523990631</t>
   </si>
   <si>
     <t xml:space="preserve">1.93050968647003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96656322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9583694934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739916801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542587757111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198107719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91248285770416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91084396839142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545875549316</t>
+    <t xml:space="preserve">1.96656346321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509159564972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95836913585663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739892959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9354259967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198131561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91248273849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91084384918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545899391174</t>
   </si>
   <si>
     <t xml:space="preserve">1.8026829957962</t>
@@ -245,34 +245,31 @@
     <t xml:space="preserve">1.86823511123657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90756642818451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281702041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88462293148041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920519828796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87151265144348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8977335691452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82398736476898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75843513011932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76662921905518</t>
+    <t xml:space="preserve">1.90756618976593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90592753887177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88462316989899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920507907867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87151253223419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89773344993591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82398760318756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75843501091003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76662933826447</t>
   </si>
   <si>
     <t xml:space="preserve">1.78629505634308</t>
@@ -281,16 +278,16 @@
     <t xml:space="preserve">1.77646219730377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75188004970551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75351905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77973985671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75024116039276</t>
+    <t xml:space="preserve">1.75188028812408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75351893901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77973961830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75024127960205</t>
   </si>
   <si>
     <t xml:space="preserve">1.72074282169342</t>
@@ -299,16 +296,16 @@
     <t xml:space="preserve">1.66993999481201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72893691062927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69616079330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76007413864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70435464382172</t>
+    <t xml:space="preserve">1.72893679141998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69616055488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76007401943207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7043548822403</t>
   </si>
   <si>
     <t xml:space="preserve">1.73549211025238</t>
@@ -329,10 +326,10 @@
     <t xml:space="preserve">1.66666221618652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61012375354767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62241470813751</t>
+    <t xml:space="preserve">1.61012351512909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62241458892822</t>
   </si>
   <si>
     <t xml:space="preserve">1.66338467597961</t>
@@ -344,16 +341,16 @@
     <t xml:space="preserve">1.64535784721375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63880276679993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62569212913513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66830110549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65519058704376</t>
+    <t xml:space="preserve">1.63880252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62569224834442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66830122470856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65519082546234</t>
   </si>
   <si>
     <t xml:space="preserve">1.64699673652649</t>
@@ -362,61 +359,61 @@
     <t xml:space="preserve">1.63798320293427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59865200519562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62978911399841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58308339118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59537446498871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57898640632629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59127748012543</t>
+    <t xml:space="preserve">1.59865212440491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6297892332077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58308351039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.595374584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.578986287117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59127736091614</t>
   </si>
   <si>
     <t xml:space="preserve">1.54047453403473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56751465797424</t>
+    <t xml:space="preserve">1.56751477718353</t>
   </si>
   <si>
     <t xml:space="preserve">1.56997299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56669521331787</t>
+    <t xml:space="preserve">1.56669533252716</t>
   </si>
   <si>
     <t xml:space="preserve">1.5585013628006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6027489900589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60356855392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60602653026581</t>
+    <t xml:space="preserve">1.60274910926819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60356843471527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60602676868439</t>
   </si>
   <si>
     <t xml:space="preserve">1.51917004585266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56177890300751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54539108276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37659418582916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4126478433609</t>
+    <t xml:space="preserve">1.5617790222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54539096355438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37659406661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41264796257019</t>
   </si>
   <si>
     <t xml:space="preserve">1.39462113380432</t>
@@ -434,19 +431,19 @@
     <t xml:space="preserve">1.61258172988892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61176252365112</t>
+    <t xml:space="preserve">1.61176240444183</t>
   </si>
   <si>
     <t xml:space="preserve">1.59783267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54211330413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51179563999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5552237033844</t>
+    <t xml:space="preserve">1.54211318492889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51179540157318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55522358417511</t>
   </si>
   <si>
     <t xml:space="preserve">1.56505656242371</t>
@@ -455,19 +452,19 @@
     <t xml:space="preserve">1.56423723697662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59291613101959</t>
+    <t xml:space="preserve">1.59291625022888</t>
   </si>
   <si>
     <t xml:space="preserve">1.55686259269714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52162826061249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54129385948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5044207572937</t>
+    <t xml:space="preserve">1.52162837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5412939786911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50442087650299</t>
   </si>
   <si>
     <t xml:space="preserve">1.5109760761261</t>
@@ -476,31 +473,31 @@
     <t xml:space="preserve">1.55112671852112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51589238643646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55194628238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50851774215698</t>
+    <t xml:space="preserve">1.51589250564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55194616317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50851786136627</t>
   </si>
   <si>
     <t xml:space="preserve">1.53228056430817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50933718681335</t>
+    <t xml:space="preserve">1.50933730602264</t>
   </si>
   <si>
     <t xml:space="preserve">1.50769853591919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50278198719025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49540746212006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51015675067902</t>
+    <t xml:space="preserve">1.50278210639954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49540758132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51015663146973</t>
   </si>
   <si>
     <t xml:space="preserve">1.57325041294098</t>
@@ -509,25 +506,25 @@
     <t xml:space="preserve">1.5855416059494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59455502033234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60684609413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62159526348114</t>
+    <t xml:space="preserve">1.59455490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60684585571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62159538269043</t>
   </si>
   <si>
     <t xml:space="preserve">1.57161176204681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54375219345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57243132591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58718037605286</t>
+    <t xml:space="preserve">1.54375207424164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57243120670319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58718049526215</t>
   </si>
   <si>
     <t xml:space="preserve">1.54621028900146</t>
@@ -539,7 +536,7 @@
     <t xml:space="preserve">1.58799982070923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5347386598587</t>
+    <t xml:space="preserve">1.53473877906799</t>
   </si>
   <si>
     <t xml:space="preserve">1.5822639465332</t>
@@ -551,31 +548,31 @@
     <t xml:space="preserve">1.53883576393127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54784905910492</t>
+    <t xml:space="preserve">1.54784917831421</t>
   </si>
   <si>
     <t xml:space="preserve">1.55276548862457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54948782920837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53801620006561</t>
+    <t xml:space="preserve">1.54948794841766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5380163192749</t>
   </si>
   <si>
     <t xml:space="preserve">1.54866850376129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53637731075287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53965497016907</t>
+    <t xml:space="preserve">1.53637754917145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53965508937836</t>
   </si>
   <si>
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191304683685</t>
+    <t xml:space="preserve">1.65191316604614</t>
   </si>
   <si>
     <t xml:space="preserve">1.69288313388824</t>
@@ -587,10 +584,10 @@
     <t xml:space="preserve">1.82070970535278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82890379428864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81743216514587</t>
+    <t xml:space="preserve">1.82890391349792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81743228435516</t>
   </si>
   <si>
     <t xml:space="preserve">1.81579351425171</t>
@@ -602,16 +599,16 @@
     <t xml:space="preserve">1.79448890686035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80104410648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72729814052582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74696373939514</t>
+    <t xml:space="preserve">1.80104398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73876965045929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72729802131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74696362018585</t>
   </si>
   <si>
     <t xml:space="preserve">1.76335155963898</t>
@@ -623,13 +620,13 @@
     <t xml:space="preserve">1.81087708473206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80923819541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81251573562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86167967319489</t>
+    <t xml:space="preserve">1.80923807621002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81251585483551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86167979240417</t>
   </si>
   <si>
     <t xml:space="preserve">1.86495745182037</t>
@@ -644,19 +641,19 @@
     <t xml:space="preserve">1.89937245845795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84856939315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92479634284973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679416179657</t>
+    <t xml:space="preserve">1.84856951236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92479622364044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679404258728</t>
   </si>
   <si>
     <t xml:space="preserve">1.93850815296173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97107374668121</t>
+    <t xml:space="preserve">1.9710738658905</t>
   </si>
   <si>
     <t xml:space="preserve">1.92822432518005</t>
@@ -668,22 +665,22 @@
     <t xml:space="preserve">1.94364988803864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95907580852509</t>
+    <t xml:space="preserve">1.95907604694366</t>
   </si>
   <si>
     <t xml:space="preserve">1.96764576435089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92651033401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95393407344818</t>
+    <t xml:space="preserve">1.9265102148056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95393395423889</t>
   </si>
   <si>
     <t xml:space="preserve">1.93336629867554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90594244003296</t>
+    <t xml:space="preserve">1.90594255924225</t>
   </si>
   <si>
     <t xml:space="preserve">1.8939448595047</t>
@@ -695,43 +692,43 @@
     <t xml:space="preserve">1.92993831634521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90080058574677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91451227664948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88708853721619</t>
+    <t xml:space="preserve">1.90080070495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91451239585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88708865642548</t>
   </si>
   <si>
     <t xml:space="preserve">1.87680494785309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9179402589798</t>
+    <t xml:space="preserve">1.91794049739838</t>
   </si>
   <si>
     <t xml:space="preserve">1.8853747844696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86994898319244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88880300521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90937042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90251469612122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96421790122986</t>
+    <t xml:space="preserve">1.86994910240173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88880276679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90937054157257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90251457691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96421802043915</t>
   </si>
   <si>
     <t xml:space="preserve">1.96250379085541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821353912354</t>
+    <t xml:space="preserve">1.98821341991425</t>
   </si>
   <si>
     <t xml:space="preserve">1.98649966716766</t>
@@ -740,34 +737,34 @@
     <t xml:space="preserve">1.97964346408844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12533164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08591032028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0567729473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07905411720276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08076858520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06534242630005</t>
+    <t xml:space="preserve">2.12533140182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0859100818634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05677270889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07905435562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08076810836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06534218788147</t>
   </si>
   <si>
     <t xml:space="preserve">2.06020045280457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07219815254211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13390159606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10819172859192</t>
+    <t xml:space="preserve">2.07219839096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13390135765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1081919670105</t>
   </si>
   <si>
     <t xml:space="preserve">2.09962201118469</t>
@@ -779,10 +776,10 @@
     <t xml:space="preserve">2.03963279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06877040863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11504793167114</t>
+    <t xml:space="preserve">2.06877064704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11504769325256</t>
   </si>
   <si>
     <t xml:space="preserve">2.07391238212585</t>
@@ -791,7 +788,7 @@
     <t xml:space="preserve">2.09790802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11676168441772</t>
+    <t xml:space="preserve">2.1167619228363</t>
   </si>
   <si>
     <t xml:space="preserve">2.08248233795166</t>
@@ -800,13 +797,13 @@
     <t xml:space="preserve">2.06705641746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12190389633179</t>
+    <t xml:space="preserve">2.12190365791321</t>
   </si>
   <si>
     <t xml:space="preserve">2.10647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08933806419373</t>
+    <t xml:space="preserve">2.0893383026123</t>
   </si>
   <si>
     <t xml:space="preserve">2.05163073539734</t>
@@ -818,7 +815,7 @@
     <t xml:space="preserve">2.14247155189514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1321873664856</t>
+    <t xml:space="preserve">2.13218760490417</t>
   </si>
   <si>
     <t xml:space="preserve">2.13047361373901</t>
@@ -827,13 +824,13 @@
     <t xml:space="preserve">2.15961122512817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11847567558289</t>
+    <t xml:space="preserve">2.11847543716431</t>
   </si>
   <si>
     <t xml:space="preserve">2.09105229377747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12361764907837</t>
+    <t xml:space="preserve">2.12361741065979</t>
   </si>
   <si>
     <t xml:space="preserve">2.11161994934082</t>
@@ -851,10 +848,10 @@
     <t xml:space="preserve">2.1441855430603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14075708389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14932727813721</t>
+    <t xml:space="preserve">2.1407573223114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14932751655579</t>
   </si>
   <si>
     <t xml:space="preserve">2.13904356956482</t>
@@ -863,7 +860,7 @@
     <t xml:space="preserve">2.17503714561462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15104126930237</t>
+    <t xml:space="preserve">2.15104150772095</t>
   </si>
   <si>
     <t xml:space="preserve">2.12018966674805</t>
@@ -875,10 +872,10 @@
     <t xml:space="preserve">2.06362843513489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03277707099915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0482029914856</t>
+    <t xml:space="preserve">2.03277683258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04820275306702</t>
   </si>
   <si>
     <t xml:space="preserve">2.07048416137695</t>
@@ -893,7 +890,7 @@
     <t xml:space="preserve">2.08762431144714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02077913284302</t>
+    <t xml:space="preserve">2.02077889442444</t>
   </si>
   <si>
     <t xml:space="preserve">2.08419609069824</t>
@@ -926,7 +923,7 @@
     <t xml:space="preserve">2.35671854019165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44241738319397</t>
+    <t xml:space="preserve">2.44241714477539</t>
   </si>
   <si>
     <t xml:space="preserve">2.49383687973022</t>
@@ -935,7 +932,7 @@
     <t xml:space="preserve">2.46812725067139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47669720649719</t>
+    <t xml:space="preserve">2.47669696807861</t>
   </si>
   <si>
     <t xml:space="preserve">2.48526692390442</t>
@@ -944,10 +941,10 @@
     <t xml:space="preserve">2.53668618202209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57953548431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59667539596558</t>
+    <t xml:space="preserve">2.57953572273254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.596675157547</t>
   </si>
   <si>
     <t xml:space="preserve">2.61381506919861</t>
@@ -956,7 +953,7 @@
     <t xml:space="preserve">2.55382585525513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63447308540344</t>
+    <t xml:space="preserve">2.63447332382202</t>
   </si>
   <si>
     <t xml:space="preserve">2.59862995147705</t>
@@ -965,7 +962,10 @@
     <t xml:space="preserve">2.5896692276001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61655163764954</t>
+    <t xml:space="preserve">2.61655139923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55382561683655</t>
   </si>
   <si>
     <t xml:space="preserve">2.52694344520569</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">2.50006127357483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45525717735291</t>
+    <t xml:space="preserve">2.45525741577148</t>
   </si>
   <si>
     <t xml:space="preserve">2.54486513137817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57174730300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51798272132874</t>
+    <t xml:space="preserve">2.57174754142761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51798295974731</t>
   </si>
   <si>
     <t xml:space="preserve">2.56278681755066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53590440750122</t>
+    <t xml:space="preserve">2.53590416908264</t>
   </si>
   <si>
     <t xml:space="preserve">2.4911003112793</t>
@@ -1007,13 +1007,13 @@
     <t xml:space="preserve">2.50902199745178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47317886352539</t>
+    <t xml:space="preserve">2.47317862510681</t>
   </si>
   <si>
     <t xml:space="preserve">2.78680658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7599241733551</t>
+    <t xml:space="preserve">2.75992441177368</t>
   </si>
   <si>
     <t xml:space="preserve">2.77784562110901</t>
@@ -1028,40 +1028,40 @@
     <t xml:space="preserve">2.71512007713318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75096344947815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67031645774841</t>
+    <t xml:space="preserve">2.75096321105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67031621932983</t>
   </si>
   <si>
     <t xml:space="preserve">2.72408103942871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65239453315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68823790550232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73304200172424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69719862937927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67927718162537</t>
+    <t xml:space="preserve">2.65239477157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68823766708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73304176330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69719886779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67927694320679</t>
   </si>
   <si>
     <t xml:space="preserve">2.84953236579895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86745381355286</t>
+    <t xml:space="preserve">2.86745357513428</t>
   </si>
   <si>
     <t xml:space="preserve">2.83161067962646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64343404769897</t>
+    <t xml:space="preserve">2.6434338092804</t>
   </si>
   <si>
     <t xml:space="preserve">2.62551236152649</t>
@@ -1073,25 +1073,25 @@
     <t xml:space="preserve">2.60759091377258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41941428184509</t>
+    <t xml:space="preserve">2.41941404342651</t>
   </si>
   <si>
     <t xml:space="preserve">2.66135549545288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81368923187256</t>
+    <t xml:space="preserve">2.81368899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.84057140350342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93914031982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87641477584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82264995574951</t>
+    <t xml:space="preserve">2.93914008140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87641453742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82264971733093</t>
   </si>
   <si>
     <t xml:space="preserve">2.80472826957703</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">2.90329694747925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12731671333313</t>
+    <t xml:space="preserve">3.12731647491455</t>
   </si>
   <si>
     <t xml:space="preserve">3.16315984725952</t>
@@ -1109,19 +1109,19 @@
     <t xml:space="preserve">3.13627743721008</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19004225730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25276803970337</t>
+    <t xml:space="preserve">3.19004201889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25276780128479</t>
   </si>
   <si>
     <t xml:space="preserve">3.26172852516174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28861093521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29757165908813</t>
+    <t xml:space="preserve">3.28861117362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29757189750671</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133647918701</t>
@@ -1130,31 +1130,31 @@
     <t xml:space="preserve">3.33341503143311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34237551689148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42302274703979</t>
+    <t xml:space="preserve">3.34237575531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42302298545837</t>
   </si>
   <si>
     <t xml:space="preserve">3.3871796131134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40510106086731</t>
+    <t xml:space="preserve">3.40510129928589</t>
   </si>
   <si>
     <t xml:space="preserve">3.41406202316284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3692581653595</t>
+    <t xml:space="preserve">3.36925792694092</t>
   </si>
   <si>
     <t xml:space="preserve">3.37821888923645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45886588096619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48574829101562</t>
+    <t xml:space="preserve">3.45886564254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48574876785278</t>
   </si>
   <si>
     <t xml:space="preserve">3.47678780555725</t>
@@ -1166,52 +1166,52 @@
     <t xml:space="preserve">3.67392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58431720733643</t>
+    <t xml:space="preserve">3.58431696891785</t>
   </si>
   <si>
     <t xml:space="preserve">3.53055238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59327816963196</t>
+    <t xml:space="preserve">3.59327793121338</t>
   </si>
   <si>
     <t xml:space="preserve">3.55743479728699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5215916633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51263070106506</t>
+    <t xml:space="preserve">3.52159142494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51263093948364</t>
   </si>
   <si>
     <t xml:space="preserve">3.53951334953308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60223865509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65600347518921</t>
+    <t xml:space="preserve">3.60223889350891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65600323677063</t>
   </si>
   <si>
     <t xml:space="preserve">3.66496443748474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72768974304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71872901916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69184637069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70976829528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68288612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7635326385498</t>
+    <t xml:space="preserve">3.72768998146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71872925758362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6918466091156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70976781845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68288588523865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76353287696838</t>
   </si>
   <si>
     <t xml:space="preserve">3.78145432472229</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">3.80833721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7904155254364</t>
+    <t xml:space="preserve">3.79041504859924</t>
   </si>
   <si>
     <t xml:space="preserve">3.95170950889587</t>
@@ -1232,13 +1232,13 @@
     <t xml:space="preserve">3.97005581855774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00759744644165</t>
+    <t xml:space="preserve">4.00759792327881</t>
   </si>
   <si>
     <t xml:space="preserve">4.0920672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81988859176636</t>
+    <t xml:space="preserve">3.81988835334778</t>
   </si>
   <si>
     <t xml:space="preserve">3.87620115280151</t>
@@ -1262,40 +1262,40 @@
     <t xml:space="preserve">4.03575468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9982123374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97944116592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85743045806885</t>
+    <t xml:space="preserve">3.99821257591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97944092750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85743021965027</t>
   </si>
   <si>
     <t xml:space="preserve">3.84804463386536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81050276756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74480438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89497208595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.941899061203</t>
+    <t xml:space="preserve">3.81050252914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7448046207428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89497232437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94189953804016</t>
   </si>
   <si>
     <t xml:space="preserve">3.8668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93251419067383</t>
+    <t xml:space="preserve">3.93251395225525</t>
   </si>
   <si>
     <t xml:space="preserve">4.08268165588379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11083841323853</t>
+    <t xml:space="preserve">4.11083793640137</t>
   </si>
   <si>
     <t xml:space="preserve">4.12022304534912</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">4.18592166900635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1953067779541</t>
+    <t xml:space="preserve">4.19530725479126</t>
   </si>
   <si>
     <t xml:space="preserve">4.20469284057617</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">4.28916215896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26100540161133</t>
+    <t xml:space="preserve">4.26100587844849</t>
   </si>
   <si>
     <t xml:space="preserve">4.2703914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34547519683838</t>
+    <t xml:space="preserve">4.34547472000122</t>
   </si>
   <si>
     <t xml:space="preserve">4.36424589157104</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">4.50502824783325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49564218521118</t>
+    <t xml:space="preserve">4.49564266204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.43932962417603</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">4.5519552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54256963729858</t>
+    <t xml:space="preserve">4.54257011413574</t>
   </si>
   <si>
     <t xml:space="preserve">4.48625707626343</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">4.40178775787354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44871473312378</t>
+    <t xml:space="preserve">4.44871520996094</t>
   </si>
   <si>
     <t xml:space="preserve">4.42994403839111</t>
@@ -1373,13 +1373,13 @@
     <t xml:space="preserve">4.41117334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39240217208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2422342300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30793285369873</t>
+    <t xml:space="preserve">4.39240169525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24223470687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30793333053589</t>
   </si>
   <si>
     <t xml:space="preserve">4.17653608322144</t>
@@ -1397,28 +1397,28 @@
     <t xml:space="preserve">4.62703895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61765384674072</t>
+    <t xml:space="preserve">4.61765336990356</t>
   </si>
   <si>
     <t xml:space="preserve">4.51441335678101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57072639465332</t>
+    <t xml:space="preserve">4.57072591781616</t>
   </si>
   <si>
     <t xml:space="preserve">4.67396640777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80536317825317</t>
+    <t xml:space="preserve">4.80536270141602</t>
   </si>
   <si>
     <t xml:space="preserve">4.78659200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86167573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84290456771851</t>
+    <t xml:space="preserve">4.86167621612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84290504455566</t>
   </si>
   <si>
     <t xml:space="preserve">4.89921760559082</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">4.5988826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53318452835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58011198043823</t>
+    <t xml:space="preserve">4.53318405151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58011150360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.6927375793457</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">4.74905014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73027896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71150875091553</t>
+    <t xml:space="preserve">4.73027944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71150827407837</t>
   </si>
   <si>
     <t xml:space="preserve">4.76782131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95553064346313</t>
+    <t xml:space="preserve">4.95553112030029</t>
   </si>
   <si>
     <t xml:space="preserve">4.88044691085815</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">4.91798877716064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99307298660278</t>
+    <t xml:space="preserve">4.99307250976562</t>
   </si>
   <si>
     <t xml:space="preserve">4.93675994873047</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">6.60737419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28826761245728</t>
+    <t xml:space="preserve">6.28826808929443</t>
   </si>
   <si>
     <t xml:space="preserve">6.1568717956543</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">5.96916246414185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7063684463501</t>
+    <t xml:space="preserve">5.70636892318726</t>
   </si>
   <si>
     <t xml:space="preserve">5.53743028640747</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">5.87530755996704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66882705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68759775161743</t>
+    <t xml:space="preserve">5.66882658004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68759727478027</t>
   </si>
   <si>
     <t xml:space="preserve">5.83776521682739</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59374332427979</t>
+    <t xml:space="preserve">5.59374284744263</t>
   </si>
   <si>
     <t xml:space="preserve">5.38726234436035</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">5.10569858551025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68335151672363</t>
+    <t xml:space="preserve">4.68335199356079</t>
   </si>
   <si>
     <t xml:space="preserve">4.14837980270386</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">3.62279319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55709505081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37877106666565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50078201293945</t>
+    <t xml:space="preserve">3.55709481239319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37877082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50078225135803</t>
   </si>
   <si>
     <t xml:space="preserve">3.5664803981781</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">3.75418996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70726275444031</t>
+    <t xml:space="preserve">3.70726251602173</t>
   </si>
   <si>
     <t xml:space="preserve">3.71664810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83865928649902</t>
+    <t xml:space="preserve">3.8386595249176</t>
   </si>
   <si>
     <t xml:space="preserve">4.25162029266357</t>
@@ -1583,25 +1583,25 @@
     <t xml:space="preserve">4.12960910797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16715097427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05452489852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76357579231262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66972088813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65094971656799</t>
+    <t xml:space="preserve">4.16715049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05452537536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76357555389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66972064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65094995498657</t>
   </si>
   <si>
     <t xml:space="preserve">3.66033530235291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95128488540649</t>
+    <t xml:space="preserve">3.95128512382507</t>
   </si>
   <si>
     <t xml:space="preserve">4.29854726791382</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">4.31731843948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15776538848877</t>
+    <t xml:space="preserve">4.15776491165161</t>
   </si>
   <si>
     <t xml:space="preserve">4.10145235061646</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">4.13899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88558650016785</t>
+    <t xml:space="preserve">3.88558626174927</t>
   </si>
   <si>
     <t xml:space="preserve">4.32670402526855</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">4.27977657318115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91374325752258</t>
+    <t xml:space="preserve">3.913743019104</t>
   </si>
   <si>
     <t xml:space="preserve">3.92312836647034</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">3.49139666557312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67910599708557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3881561756134</t>
+    <t xml:space="preserve">3.67910623550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38815641403198</t>
   </si>
   <si>
     <t xml:space="preserve">3.35999989509583</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">3.34122896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20044684410095</t>
+    <t xml:space="preserve">3.20044708251953</t>
   </si>
   <si>
     <t xml:space="preserve">3.24737429618835</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">3.47262573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57586598396301</t>
+    <t xml:space="preserve">3.57586574554443</t>
   </si>
   <si>
     <t xml:space="preserve">3.73541903495789</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">3.68849158287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72603344917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52893877029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63217854499817</t>
+    <t xml:space="preserve">3.72603368759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52893853187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63217878341675</t>
   </si>
   <si>
     <t xml:space="preserve">3.51016759872437</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">3.58525133132935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53832387924194</t>
+    <t xml:space="preserve">3.53832411766052</t>
   </si>
   <si>
     <t xml:space="preserve">3.80111742019653</t>
@@ -1730,10 +1730,10 @@
     <t xml:space="preserve">3.48201107978821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46324038505554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44446921348572</t>
+    <t xml:space="preserve">3.46324014663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4444694519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.42569851875305</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">3.41631293296814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754176139832</t>
+    <t xml:space="preserve">3.39754199981689</t>
   </si>
   <si>
     <t xml:space="preserve">3.21921801567078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19106149673462</t>
+    <t xml:space="preserve">3.1910617351532</t>
   </si>
   <si>
     <t xml:space="preserve">3.17229056358337</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">3.23798894882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14413380622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25675988197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36938548088074</t>
+    <t xml:space="preserve">3.14413404464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25675964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36938524246216</t>
   </si>
   <si>
     <t xml:space="preserve">3.15351939201355</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">3.18167614936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29430150985718</t>
+    <t xml:space="preserve">3.29430174827576</t>
   </si>
   <si>
     <t xml:space="preserve">3.2661452293396</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">3.12536311149597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04089403152466</t>
+    <t xml:space="preserve">3.04089379310608</t>
   </si>
   <si>
     <t xml:space="preserve">3.05027914047241</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">2.93765377998352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95642471313477</t>
+    <t xml:space="preserve">2.95642447471619</t>
   </si>
   <si>
     <t xml:space="preserve">3.03150844573975</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">3.02212285995483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92826819419861</t>
+    <t xml:space="preserve">2.92826795578003</t>
   </si>
   <si>
     <t xml:space="preserve">2.94703912734985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90011143684387</t>
+    <t xml:space="preserve">2.90011167526245</t>
   </si>
   <si>
     <t xml:space="preserve">2.97519564628601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27553081512451</t>
+    <t xml:space="preserve">3.27553057670593</t>
   </si>
   <si>
     <t xml:space="preserve">3.33184361457825</t>
@@ -6254,7 +6254,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -6280,7 +6280,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -6306,7 +6306,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -6332,7 +6332,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G139" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -6358,7 +6358,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -6384,7 +6384,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -6436,7 +6436,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G143" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -6462,7 +6462,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G144" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -6488,7 +6488,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -6514,7 +6514,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -6540,7 +6540,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -6566,7 +6566,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G148" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -6592,7 +6592,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -6618,7 +6618,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G150" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -6644,7 +6644,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G151" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -6670,7 +6670,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -6696,7 +6696,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G153" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -6722,7 +6722,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G154" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -6748,7 +6748,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G155" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -6774,7 +6774,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -6800,7 +6800,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -6826,7 +6826,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -6852,7 +6852,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -6878,7 +6878,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G160" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -6904,7 +6904,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G161" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -6930,7 +6930,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G162" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -6956,7 +6956,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G163" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -6982,7 +6982,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G164" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -7008,7 +7008,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G165" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -7034,7 +7034,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G166" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7060,7 +7060,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G167" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7086,7 +7086,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G168" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7112,7 +7112,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G169" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7138,7 +7138,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7164,7 +7164,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G171" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7190,7 +7190,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7216,7 +7216,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7242,7 +7242,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G174" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7268,7 +7268,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7294,7 +7294,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G176" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7320,7 +7320,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G177" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7346,7 +7346,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G178" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7372,7 +7372,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G179" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7398,7 +7398,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G180" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7424,7 +7424,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G181" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7450,7 +7450,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G182" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7476,7 +7476,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G183" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7502,7 +7502,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G184" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -7528,7 +7528,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G185" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7554,7 +7554,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G186" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7580,7 +7580,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G187" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7606,7 +7606,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G188" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7632,7 +7632,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G189" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7658,7 +7658,7 @@
         <v>2</v>
       </c>
       <c r="G190" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7684,7 +7684,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G191" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7710,7 +7710,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G192" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7736,7 +7736,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G193" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7762,7 +7762,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G194" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -7788,7 +7788,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G195" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -7814,7 +7814,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G196" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -7840,7 +7840,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -7866,7 +7866,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -7892,7 +7892,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -7918,7 +7918,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -7944,7 +7944,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -7970,7 +7970,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -7996,7 +7996,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8022,7 +8022,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8048,7 +8048,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8074,7 +8074,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G206" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8100,7 +8100,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G207" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8126,7 +8126,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8152,7 +8152,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G209" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8178,7 +8178,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8204,7 +8204,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G211" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8230,7 +8230,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G212" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8256,7 +8256,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G213" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8282,7 +8282,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G214" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8308,7 +8308,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8334,7 +8334,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G216" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8360,7 +8360,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8386,7 +8386,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8412,7 +8412,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G219" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8438,7 +8438,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G220" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8464,7 +8464,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G221" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8490,7 +8490,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G222" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8516,7 +8516,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G223" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8542,7 +8542,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G224" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8568,7 +8568,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8594,7 +8594,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G226" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8620,7 +8620,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8646,7 +8646,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8672,7 +8672,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G229" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8698,7 +8698,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8724,7 +8724,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G231" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8750,7 +8750,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G232" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8776,7 +8776,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G233" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8802,7 +8802,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G234" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -8828,7 +8828,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G235" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -8854,7 +8854,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G236" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -8880,7 +8880,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G237" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -8906,7 +8906,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G238" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -8932,7 +8932,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G239" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -8958,7 +8958,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G240" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -8984,7 +8984,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9010,7 +9010,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9036,7 +9036,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9062,7 +9062,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G244" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9088,7 +9088,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9114,7 +9114,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G246" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9140,7 +9140,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G247" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9166,7 +9166,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G248" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9192,7 +9192,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G249" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9218,7 +9218,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G250" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9244,7 +9244,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9270,7 +9270,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G252" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9296,7 +9296,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G253" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9322,7 +9322,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G254" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9348,7 +9348,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9374,7 +9374,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G256" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9400,7 +9400,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G257" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9426,7 +9426,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G258" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9452,7 +9452,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G259" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9478,7 +9478,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9504,7 +9504,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G261" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9530,7 +9530,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G262" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9556,7 +9556,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9582,7 +9582,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G264" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9608,7 +9608,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G265" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9634,7 +9634,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G266" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9660,7 +9660,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G267" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9686,7 +9686,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G268" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9712,7 +9712,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9738,7 +9738,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G270" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9764,7 +9764,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G271" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -9790,7 +9790,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -9816,7 +9816,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9842,7 +9842,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G274" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -9868,7 +9868,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G275" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -9894,7 +9894,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G276" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9920,7 +9920,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G277" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9946,7 +9946,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G278" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -9972,7 +9972,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G279" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -9998,7 +9998,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G280" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10024,7 +10024,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G281" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10050,7 +10050,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10076,7 +10076,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G283" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10102,7 +10102,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G284" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10128,7 +10128,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G285" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10154,7 +10154,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G286" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10180,7 +10180,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G287" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10206,7 +10206,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10232,7 +10232,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G289" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10258,7 +10258,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G290" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10284,7 +10284,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G291" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10310,7 +10310,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10336,7 +10336,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G293" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10362,7 +10362,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G294" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10388,7 +10388,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G295" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10414,7 +10414,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G296" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10440,7 +10440,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G297" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10466,7 +10466,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G298" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10492,7 +10492,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10518,7 +10518,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G300" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10544,7 +10544,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G301" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10570,7 +10570,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G302" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10596,7 +10596,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10622,7 +10622,7 @@
         <v>1.875</v>
       </c>
       <c r="G304" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10648,7 +10648,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G305" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10674,7 +10674,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G306" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10700,7 +10700,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G307" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10726,7 +10726,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G308" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10752,7 +10752,7 @@
         <v>2</v>
       </c>
       <c r="G309" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -10778,7 +10778,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10804,7 +10804,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -10830,7 +10830,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -10856,7 +10856,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G313" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10882,7 +10882,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G314" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -10908,7 +10908,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10934,7 +10934,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10960,7 +10960,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G317" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11012,7 +11012,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11038,7 +11038,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11064,7 +11064,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11090,7 +11090,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11116,7 +11116,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11142,7 +11142,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11168,7 +11168,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11220,7 +11220,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G327" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11246,7 +11246,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11272,7 +11272,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11298,7 +11298,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11324,7 +11324,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11350,7 +11350,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G332" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11376,7 +11376,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11402,7 +11402,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11428,7 +11428,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G335" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11454,7 +11454,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11558,7 +11558,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11584,7 +11584,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G341" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11610,7 +11610,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11636,7 +11636,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11662,7 +11662,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G344" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11714,7 +11714,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G346" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11740,7 +11740,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G347" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11766,7 +11766,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -11792,7 +11792,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G349" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -11818,7 +11818,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -11870,7 +11870,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11896,7 +11896,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G353" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11948,7 +11948,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G355" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11974,7 +11974,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12000,7 +12000,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G357" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12026,7 +12026,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12052,7 +12052,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12078,7 +12078,7 @@
         <v>2.25</v>
       </c>
       <c r="G360" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12104,7 +12104,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12130,7 +12130,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12156,7 +12156,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G363" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12182,7 +12182,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G364" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12208,7 +12208,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12234,7 +12234,7 @@
         <v>2.25</v>
       </c>
       <c r="G366" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12260,7 +12260,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12286,7 +12286,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12312,7 +12312,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12338,7 +12338,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12364,7 +12364,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12390,7 +12390,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12416,7 +12416,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G373" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12442,7 +12442,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G374" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12468,7 +12468,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G375" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12494,7 +12494,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G376" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12520,7 +12520,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G377" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12546,7 +12546,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12572,7 +12572,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12598,7 +12598,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G380" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12624,7 +12624,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G381" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12650,7 +12650,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G382" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12676,7 +12676,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12702,7 +12702,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G384" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12728,7 +12728,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G385" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12754,7 +12754,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12780,7 +12780,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G387" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12806,7 +12806,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G388" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -12832,7 +12832,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G389" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -12858,7 +12858,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -12884,7 +12884,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G391" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -12910,7 +12910,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -12936,7 +12936,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G393" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -12962,7 +12962,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -12988,7 +12988,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G395" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13014,7 +13014,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13040,7 +13040,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13066,7 +13066,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13092,7 +13092,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G399" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13118,7 +13118,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G400" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13144,7 +13144,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G401" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13170,7 +13170,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13196,7 +13196,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G403" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13222,7 +13222,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13248,7 +13248,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G405" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13274,7 +13274,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13300,7 +13300,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13326,7 +13326,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13352,7 +13352,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G409" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13378,7 +13378,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G410" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13404,7 +13404,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G411" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13430,7 +13430,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13456,7 +13456,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G413" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13482,7 +13482,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G414" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13508,7 +13508,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G415" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13534,7 +13534,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G416" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13560,7 +13560,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G417" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13586,7 +13586,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G418" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13612,7 +13612,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G419" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13638,7 +13638,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G420" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13664,7 +13664,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G421" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13690,7 +13690,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G422" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13716,7 +13716,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13742,7 +13742,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G424" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13768,7 +13768,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G425" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13794,7 +13794,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G426" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -13820,7 +13820,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G427" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -13846,7 +13846,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G428" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -13872,7 +13872,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G429" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -13898,7 +13898,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G430" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -13924,7 +13924,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G431" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -13950,7 +13950,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -13976,7 +13976,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G433" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14002,7 +14002,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14028,7 +14028,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G435" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14054,7 +14054,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G436" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14080,7 +14080,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G437" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14106,7 +14106,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G438" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14132,7 +14132,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G439" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14158,7 +14158,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G440" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14184,7 +14184,7 @@
         <v>2.5</v>
       </c>
       <c r="G441" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14210,7 +14210,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G442" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14236,7 +14236,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G443" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14262,7 +14262,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G444" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14288,7 +14288,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G445" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14314,7 +14314,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14340,7 +14340,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G447" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14366,7 +14366,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G448" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14392,7 +14392,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G449" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14418,7 +14418,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G450" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14444,7 +14444,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G451" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14470,7 +14470,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G452" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14496,7 +14496,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G453" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14522,7 +14522,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G454" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14548,7 +14548,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G455" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14574,7 +14574,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G456" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14600,7 +14600,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G457" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14626,7 +14626,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G458" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14652,7 +14652,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G459" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14678,7 +14678,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G460" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14704,7 +14704,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G461" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14730,7 +14730,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G462" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14756,7 +14756,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G463" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14782,7 +14782,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G464" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -14808,7 +14808,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -14834,7 +14834,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G466" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -14860,7 +14860,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G467" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -14886,7 +14886,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G468" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -14912,7 +14912,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G469" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -14938,7 +14938,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G470" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -14964,7 +14964,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G471" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -14990,7 +14990,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15016,7 +15016,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G473" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15042,7 +15042,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15068,7 +15068,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G475" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15094,7 +15094,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G476" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15120,7 +15120,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G477" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15146,7 +15146,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G478" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15172,7 +15172,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G479" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15198,7 +15198,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G480" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15224,7 +15224,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15250,7 +15250,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G482" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15276,7 +15276,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G483" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15302,7 +15302,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G484" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15328,7 +15328,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G485" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15354,7 +15354,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G486" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15380,7 +15380,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15406,7 +15406,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G488" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15432,7 +15432,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G489" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15458,7 +15458,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G490" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15484,7 +15484,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G491" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15510,7 +15510,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15536,7 +15536,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G493" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15562,7 +15562,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G494" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15588,7 +15588,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15614,7 +15614,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G496" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15640,7 +15640,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G497" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15666,7 +15666,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G498" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15692,7 +15692,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G499" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15718,7 +15718,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G500" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15744,7 +15744,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G501" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15770,7 +15770,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G502" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15796,7 +15796,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G503" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -15822,7 +15822,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G504" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -15848,7 +15848,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G505" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -15874,7 +15874,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G506" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -15900,7 +15900,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G507" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -15926,7 +15926,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G508" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -15952,7 +15952,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G509" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -15978,7 +15978,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G510" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16004,7 +16004,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G511" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16030,7 +16030,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G512" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16056,7 +16056,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G513" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16082,7 +16082,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G514" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16108,7 +16108,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G515" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16134,7 +16134,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G516" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16160,7 +16160,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G517" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16186,7 +16186,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G518" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16212,7 +16212,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G519" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16238,7 +16238,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G520" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16264,7 +16264,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G521" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16290,7 +16290,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16316,7 +16316,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G523" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16342,7 +16342,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G524" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16368,7 +16368,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G525" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16394,7 +16394,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G526" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16420,7 +16420,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G527" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16446,7 +16446,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G528" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16472,7 +16472,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G529" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16498,7 +16498,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16524,7 +16524,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G531" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16550,7 +16550,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G532" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16576,7 +16576,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G533" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16602,7 +16602,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G534" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16628,7 +16628,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G535" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16654,7 +16654,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G536" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16680,7 +16680,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G537" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16706,7 +16706,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G538" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16732,7 +16732,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G539" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16758,7 +16758,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G540" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16784,7 +16784,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G541" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -16810,7 +16810,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G542" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -16836,7 +16836,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G543" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -16862,7 +16862,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G544" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -16888,7 +16888,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G545" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16914,7 +16914,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G546" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16940,7 +16940,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G547" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16966,7 +16966,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G548" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -16992,7 +16992,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G549" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17018,7 +17018,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G550" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17044,7 +17044,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G551" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17070,7 +17070,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G552" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17096,7 +17096,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G553" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17122,7 +17122,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G554" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17148,7 +17148,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17174,7 +17174,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G556" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17200,7 +17200,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G557" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17226,7 +17226,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17252,7 +17252,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17278,7 +17278,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17304,7 +17304,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17330,7 +17330,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G562" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17356,7 +17356,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G563" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17382,7 +17382,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17408,7 +17408,7 @@
         <v>2.5</v>
       </c>
       <c r="G565" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17434,7 +17434,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17460,7 +17460,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G567" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17486,7 +17486,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G568" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17512,7 +17512,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G569" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17538,7 +17538,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G570" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17564,7 +17564,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G571" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17590,7 +17590,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G572" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17616,7 +17616,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G573" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17642,7 +17642,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G574" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17668,7 +17668,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G575" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17694,7 +17694,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17720,7 +17720,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G577" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17746,7 +17746,7 @@
         <v>2.5</v>
       </c>
       <c r="G578" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17772,7 +17772,7 @@
         <v>2.5</v>
       </c>
       <c r="G579" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17798,7 +17798,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G580" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -17824,7 +17824,7 @@
         <v>2.5</v>
       </c>
       <c r="G581" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -17850,7 +17850,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -17876,7 +17876,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -17902,7 +17902,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -17928,7 +17928,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -17954,7 +17954,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -17980,7 +17980,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G587" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18006,7 +18006,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18032,7 +18032,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G589" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18058,7 +18058,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G590" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18084,7 +18084,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G591" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18110,7 +18110,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G592" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18136,7 +18136,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G593" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18162,7 +18162,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G594" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18188,7 +18188,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G595" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18214,7 +18214,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18240,7 +18240,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18266,7 +18266,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G598" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18292,7 +18292,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G599" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18318,7 +18318,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G600" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18344,7 +18344,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18370,7 +18370,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18396,7 +18396,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G603" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18422,7 +18422,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G604" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18448,7 +18448,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G605" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18474,7 +18474,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G606" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18500,7 +18500,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G607" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18526,7 +18526,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G608" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18552,7 +18552,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G609" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18578,7 +18578,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G610" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18604,7 +18604,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G611" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18630,7 +18630,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18916,7 +18916,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18994,7 +18994,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19280,7 +19280,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19306,7 +19306,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19670,7 +19670,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G652" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19722,7 +19722,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G654" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19748,7 +19748,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20112,7 +20112,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G669" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21126,7 +21126,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G708" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21230,7 +21230,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21256,7 +21256,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G713" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21282,7 +21282,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G714" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21308,7 +21308,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G715" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21334,7 +21334,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G716" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21438,7 +21438,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G720" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21464,7 +21464,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G721" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21490,7 +21490,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G722" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21516,7 +21516,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G723" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21542,7 +21542,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G724" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21568,7 +21568,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G725" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21620,7 +21620,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G727" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21646,7 +21646,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21672,7 +21672,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G729" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21724,7 +21724,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G731" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21750,7 +21750,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G732" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21776,7 +21776,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G733" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22322,7 +22322,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22348,7 +22348,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22634,7 +22634,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G766" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -68012,7 +68012,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.4458912037</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>5500</v>
@@ -68033,6 +68033,32 @@
         <v>791</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6775231481</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>9826</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>791</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="793">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825943946838</t>
+    <t xml:space="preserve">1.85825932025909</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91323757171631</t>
+    <t xml:space="preserve">1.9132376909256</t>
   </si>
   <si>
     <t xml:space="preserve">1.92109143733978</t>
@@ -53,55 +53,55 @@
     <t xml:space="preserve">1.88496327400208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92423331737518</t>
+    <t xml:space="preserve">1.92423319816589</t>
   </si>
   <si>
     <t xml:space="preserve">1.80642294883728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82998502254486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79856896400452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76715302467346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354709625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86925518512726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87710893154144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281690120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86768424510956</t>
+    <t xml:space="preserve">1.82998478412628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79856884479523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76715278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354721546173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86925506591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87710916996002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281737804413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86768412590027</t>
   </si>
   <si>
     <t xml:space="preserve">1.81584787368774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83783888816833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8755384683609</t>
+    <t xml:space="preserve">1.83783876895905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553822994232</t>
   </si>
   <si>
     <t xml:space="preserve">1.82684350013733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84569275379181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898927688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83626818656921</t>
+    <t xml:space="preserve">1.84569311141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81898951530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83626842498779</t>
   </si>
   <si>
     <t xml:space="preserve">1.85983037948608</t>
@@ -110,37 +110,37 @@
     <t xml:space="preserve">1.80485224723816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82056033611298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81741869449615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85040557384491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88025069236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81427669525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85197615623474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84412229061127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84098076820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82370185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81113529205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8221310377121</t>
+    <t xml:space="preserve">1.82056021690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81741845607758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85040545463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88025057315826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81427681446075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85197603702545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84412217140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84098064899445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82370162010193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81113541126251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82213091850281</t>
   </si>
   <si>
     <t xml:space="preserve">1.9367995262146</t>
@@ -149,28 +149,28 @@
     <t xml:space="preserve">1.94622421264648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95407855510712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.963503241539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9650741815567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99334847927094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00434446334839</t>
+    <t xml:space="preserve">1.95407831668854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96350312232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96507394313812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99334859848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00434422492981</t>
   </si>
   <si>
     <t xml:space="preserve">1.98706519603729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00905656814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02476477622986</t>
+    <t xml:space="preserve">2.00905680656433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02476453781128</t>
   </si>
   <si>
     <t xml:space="preserve">1.93051636219025</t>
@@ -179,115 +179,118 @@
     <t xml:space="preserve">1.96193242073059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564913749695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637921333313</t>
+    <t xml:space="preserve">1.93994128704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564925670624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637909412384</t>
   </si>
   <si>
     <t xml:space="preserve">1.87396740913391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93378722667694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92231523990631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050968647003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656346321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509159564972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95836913585663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739892959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9354259967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198131561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91248273849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91084384918213</t>
+    <t xml:space="preserve">1.93378710746765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017516613007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92231547832489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656334400177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95836925506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739904880524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542587757111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9419811964035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91248261928558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91084396839142</t>
   </si>
   <si>
     <t xml:space="preserve">1.83545899391174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8026829957962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84201419353485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83218133449554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88298439979553</t>
+    <t xml:space="preserve">1.80268311500549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84201407432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83218145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
     <t xml:space="preserve">1.86823511123657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90756618976593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592753887177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88462316989899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920507907867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87151253223419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89773344993591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82398760318756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75843501091003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76662933826447</t>
+    <t xml:space="preserve">1.90756630897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281713962555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90592765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8846230506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920495986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8715124130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8977335691452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82398748397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75843524932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76662921905518</t>
   </si>
   <si>
     <t xml:space="preserve">1.78629505634308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77646219730377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75188028812408</t>
+    <t xml:space="preserve">1.77646207809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75188016891479</t>
   </si>
   <si>
     <t xml:space="preserve">1.75351893901825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77973961830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75024127960205</t>
+    <t xml:space="preserve">1.77973973751068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75024104118347</t>
   </si>
   <si>
     <t xml:space="preserve">1.72074282169342</t>
@@ -296,19 +299,19 @@
     <t xml:space="preserve">1.66993999481201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72893679141998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69616055488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76007401943207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7043548822403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73549211025238</t>
+    <t xml:space="preserve">1.72893667221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69616067409515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76007413864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70435476303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73549199104309</t>
   </si>
   <si>
     <t xml:space="preserve">1.73385322093964</t>
@@ -326,13 +329,13 @@
     <t xml:space="preserve">1.66666221618652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61012351512909</t>
+    <t xml:space="preserve">1.61012363433838</t>
   </si>
   <si>
     <t xml:space="preserve">1.62241458892822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66338467597961</t>
+    <t xml:space="preserve">1.66338455677032</t>
   </si>
   <si>
     <t xml:space="preserve">1.67321753501892</t>
@@ -341,25 +344,25 @@
     <t xml:space="preserve">1.64535784721375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63880252838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62569224834442</t>
+    <t xml:space="preserve">1.63880276679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62569212913513</t>
   </si>
   <si>
     <t xml:space="preserve">1.66830122470856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65519082546234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64699673652649</t>
+    <t xml:space="preserve">1.65519070625305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64699685573578</t>
   </si>
   <si>
     <t xml:space="preserve">1.63798320293427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59865212440491</t>
+    <t xml:space="preserve">1.59865200519562</t>
   </si>
   <si>
     <t xml:space="preserve">1.6297892332077</t>
@@ -368,7 +371,7 @@
     <t xml:space="preserve">1.58308351039886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.595374584198</t>
+    <t xml:space="preserve">1.59537446498871</t>
   </si>
   <si>
     <t xml:space="preserve">1.578986287117</t>
@@ -383,16 +386,16 @@
     <t xml:space="preserve">1.56751477718353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56997299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56669533252716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5585013628006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60274910926819</t>
+    <t xml:space="preserve">1.56997311115265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56669545173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55850124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6027489900589</t>
   </si>
   <si>
     <t xml:space="preserve">1.60356843471527</t>
@@ -401,22 +404,22 @@
     <t xml:space="preserve">1.60602676868439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51917004585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5617790222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54539096355438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37659406661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41264796257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39462113380432</t>
+    <t xml:space="preserve">1.51917016506195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56177890300751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54539084434509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37659430503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4126478433609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39462125301361</t>
   </si>
   <si>
     <t xml:space="preserve">1.45771491527557</t>
@@ -425,25 +428,25 @@
     <t xml:space="preserve">1.47082531452179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53391933441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61258172988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61176240444183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59783267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54211318492889</t>
+    <t xml:space="preserve">1.53391945362091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61258184909821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61176252365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59783256053925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54211330413818</t>
   </si>
   <si>
     <t xml:space="preserve">1.51179540157318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55522358417511</t>
+    <t xml:space="preserve">1.5552237033844</t>
   </si>
   <si>
     <t xml:space="preserve">1.56505656242371</t>
@@ -455,10 +458,10 @@
     <t xml:space="preserve">1.59291625022888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55686259269714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52162837982178</t>
+    <t xml:space="preserve">1.55686247348785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52162826061249</t>
   </si>
   <si>
     <t xml:space="preserve">1.5412939786911</t>
@@ -482,13 +485,13 @@
     <t xml:space="preserve">1.50851786136627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53228056430817</t>
+    <t xml:space="preserve">1.53228044509888</t>
   </si>
   <si>
     <t xml:space="preserve">1.50933730602264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50769853591919</t>
+    <t xml:space="preserve">1.50769865512848</t>
   </si>
   <si>
     <t xml:space="preserve">1.50278210639954</t>
@@ -497,22 +500,22 @@
     <t xml:space="preserve">1.49540758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51015663146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57325041294098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5855416059494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59455490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60684585571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62159538269043</t>
+    <t xml:space="preserve">1.51015675067902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57325053215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58554148674011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59455502033234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60684597492218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62159526348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.57161176204681</t>
@@ -527,7 +530,7 @@
     <t xml:space="preserve">1.58718049526215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54621028900146</t>
+    <t xml:space="preserve">1.54621040821075</t>
   </si>
   <si>
     <t xml:space="preserve">1.55768203735352</t>
@@ -545,16 +548,16 @@
     <t xml:space="preserve">1.54702973365784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53883576393127</t>
+    <t xml:space="preserve">1.53883564472198</t>
   </si>
   <si>
     <t xml:space="preserve">1.54784917831421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55276548862457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54948794841766</t>
+    <t xml:space="preserve">1.55276560783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54948806762695</t>
   </si>
   <si>
     <t xml:space="preserve">1.5380163192749</t>
@@ -566,34 +569,34 @@
     <t xml:space="preserve">1.53637754917145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53965508937836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56915354728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65191316604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69288313388824</t>
+    <t xml:space="preserve">1.53965532779694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5691534280777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65191304683685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69288325309753</t>
   </si>
   <si>
     <t xml:space="preserve">1.65355181694031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82070970535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82890391349792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81743228435516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579351425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87970662117004</t>
+    <t xml:space="preserve">1.82070982456207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82890403270721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81743216514587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81579339504242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87970674037933</t>
   </si>
   <si>
     <t xml:space="preserve">1.79448890686035</t>
@@ -608,7 +611,7 @@
     <t xml:space="preserve">1.72729802131653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74696362018585</t>
+    <t xml:space="preserve">1.74696350097656</t>
   </si>
   <si>
     <t xml:space="preserve">1.76335155963898</t>
@@ -617,46 +620,46 @@
     <t xml:space="preserve">1.84693050384521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81087708473206</t>
+    <t xml:space="preserve">1.81087684631348</t>
   </si>
   <si>
     <t xml:space="preserve">1.80923807621002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81251585483551</t>
+    <t xml:space="preserve">1.81251561641693</t>
   </si>
   <si>
     <t xml:space="preserve">1.86167979240417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86495745182037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85840201377869</t>
+    <t xml:space="preserve">1.86495757102966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85840213298798</t>
   </si>
   <si>
     <t xml:space="preserve">1.87642896175385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89937245845795</t>
+    <t xml:space="preserve">1.89937233924866</t>
   </si>
   <si>
     <t xml:space="preserve">1.84856951236725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92479622364044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679404258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850815296173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9710738658905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822432518005</t>
+    <t xml:space="preserve">1.92479634284973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679416179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850827217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107362747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822420597076</t>
   </si>
   <si>
     <t xml:space="preserve">1.94193613529205</t>
@@ -665,13 +668,13 @@
     <t xml:space="preserve">1.94364988803864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95907604694366</t>
+    <t xml:space="preserve">1.9590756893158</t>
   </si>
   <si>
     <t xml:space="preserve">1.96764576435089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9265102148056</t>
+    <t xml:space="preserve">1.92651009559631</t>
   </si>
   <si>
     <t xml:space="preserve">1.95393395423889</t>
@@ -683,22 +686,22 @@
     <t xml:space="preserve">1.90594255924225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8939448595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8716629743576</t>
+    <t xml:space="preserve">1.89394474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87166285514832</t>
   </si>
   <si>
     <t xml:space="preserve">1.92993831634521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90080070495605</t>
+    <t xml:space="preserve">1.90080058574677</t>
   </si>
   <si>
     <t xml:space="preserve">1.91451239585876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88708865642548</t>
+    <t xml:space="preserve">1.88708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">1.87680494785309</t>
@@ -707,7 +710,7 @@
     <t xml:space="preserve">1.91794049739838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8853747844696</t>
+    <t xml:space="preserve">1.88537502288818</t>
   </si>
   <si>
     <t xml:space="preserve">1.86994910240173</t>
@@ -716,106 +719,106 @@
     <t xml:space="preserve">1.88880276679993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90937054157257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90251457691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96421802043915</t>
+    <t xml:space="preserve">1.90937030315399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90251445770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96421778202057</t>
   </si>
   <si>
     <t xml:space="preserve">1.96250379085541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821341991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98649966716766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964346408844</t>
+    <t xml:space="preserve">1.98821365833282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98649954795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97964358329773</t>
   </si>
   <si>
     <t xml:space="preserve">2.12533140182495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0859100818634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05677270889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07905435562134</t>
+    <t xml:space="preserve">2.08591032028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05677247047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07905459403992</t>
   </si>
   <si>
     <t xml:space="preserve">2.08076810836792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06534218788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06020045280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07219839096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13390135765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1081919670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09962201118469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10304975509644</t>
+    <t xml:space="preserve">2.06534266471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06020069122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07219862937927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13390159606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10819172859192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09962224960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10304999351501</t>
   </si>
   <si>
     <t xml:space="preserve">2.03963279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06877064704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11504769325256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07391238212585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09790802001953</t>
+    <t xml:space="preserve">2.06877040863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11504793167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07391262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09790778160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.1167619228363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08248233795166</t>
+    <t xml:space="preserve">2.08248209953308</t>
   </si>
   <si>
     <t xml:space="preserve">2.06705641746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12190365791321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10647773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0893383026123</t>
+    <t xml:space="preserve">2.12190389633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10647797584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08933806419373</t>
   </si>
   <si>
     <t xml:space="preserve">2.05163073539734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17675113677979</t>
+    <t xml:space="preserve">2.17675089836121</t>
   </si>
   <si>
     <t xml:space="preserve">2.14247155189514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13218760490417</t>
+    <t xml:space="preserve">2.1321873664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.13047361373901</t>
@@ -827,19 +830,19 @@
     <t xml:space="preserve">2.11847543716431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09105229377747</t>
+    <t xml:space="preserve">2.09105205535889</t>
   </si>
   <si>
     <t xml:space="preserve">2.12361741065979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11161994934082</t>
+    <t xml:space="preserve">2.11161971092224</t>
   </si>
   <si>
     <t xml:space="preserve">2.10133600234985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15789723396301</t>
+    <t xml:space="preserve">2.15789699554443</t>
   </si>
   <si>
     <t xml:space="preserve">2.15618324279785</t>
@@ -848,19 +851,19 @@
     <t xml:space="preserve">2.1441855430603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1407573223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14932751655579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13904356956482</t>
+    <t xml:space="preserve">2.14075756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14932727813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13904333114624</t>
   </si>
   <si>
     <t xml:space="preserve">2.17503714561462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15104150772095</t>
+    <t xml:space="preserve">2.15104103088379</t>
   </si>
   <si>
     <t xml:space="preserve">2.12018966674805</t>
@@ -881,7 +884,7 @@
     <t xml:space="preserve">2.07048416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04991674423218</t>
+    <t xml:space="preserve">2.0499165058136</t>
   </si>
   <si>
     <t xml:space="preserve">2.12875962257385</t>
@@ -905,13 +908,13 @@
     <t xml:space="preserve">2.00535321235657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1681809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18532061576843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29672932624817</t>
+    <t xml:space="preserve">2.16818118095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18532085418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29672956466675</t>
   </si>
   <si>
     <t xml:space="preserve">2.33100891113281</t>
@@ -920,7 +923,7 @@
     <t xml:space="preserve">2.32243895530701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35671854019165</t>
+    <t xml:space="preserve">2.35671830177307</t>
   </si>
   <si>
     <t xml:space="preserve">2.44241714477539</t>
@@ -929,28 +932,28 @@
     <t xml:space="preserve">2.49383687973022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46812725067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47669696807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48526692390442</t>
+    <t xml:space="preserve">2.46812701225281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47669720649719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48526668548584</t>
   </si>
   <si>
     <t xml:space="preserve">2.53668618202209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57953572273254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.596675157547</t>
+    <t xml:space="preserve">2.57953548431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59667539596558</t>
   </si>
   <si>
     <t xml:space="preserve">2.61381506919861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55382585525513</t>
+    <t xml:space="preserve">2.55382561683655</t>
   </si>
   <si>
     <t xml:space="preserve">2.63447332382202</t>
@@ -965,9 +968,6 @@
     <t xml:space="preserve">2.61655139923096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55382561683655</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.52694344520569</t>
   </si>
   <si>
@@ -2388,6 +2388,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.46000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44000005722046</t>
   </si>
 </sst>
 </file>
@@ -6254,7 +6257,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -6280,7 +6283,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -6306,7 +6309,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -6332,7 +6335,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G139" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -6358,7 +6361,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -6384,7 +6387,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -6436,7 +6439,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G143" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -6462,7 +6465,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G144" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -6488,7 +6491,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -6514,7 +6517,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -6540,7 +6543,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -6566,7 +6569,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G148" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -6592,7 +6595,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -6618,7 +6621,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G150" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -6644,7 +6647,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G151" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -6670,7 +6673,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -6696,7 +6699,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G153" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -6722,7 +6725,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G154" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -6748,7 +6751,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G155" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -6774,7 +6777,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -6800,7 +6803,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -6826,7 +6829,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -6852,7 +6855,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -6878,7 +6881,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G160" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -6904,7 +6907,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G161" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -6930,7 +6933,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G162" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -6956,7 +6959,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G163" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -6982,7 +6985,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G164" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -7008,7 +7011,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G165" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -7034,7 +7037,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G166" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7060,7 +7063,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G167" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7086,7 +7089,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G168" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7112,7 +7115,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G169" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7138,7 +7141,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G170" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7164,7 +7167,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G171" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7190,7 +7193,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7216,7 +7219,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7242,7 +7245,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G174" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7268,7 +7271,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7294,7 +7297,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G176" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7320,7 +7323,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G177" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7346,7 +7349,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G178" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7372,7 +7375,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G179" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7398,7 +7401,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G180" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7424,7 +7427,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G181" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7450,7 +7453,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G182" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7476,7 +7479,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G183" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7502,7 +7505,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G184" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -7528,7 +7531,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G185" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7554,7 +7557,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G186" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7580,7 +7583,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G187" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7606,7 +7609,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G188" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7632,7 +7635,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G189" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7658,7 +7661,7 @@
         <v>2</v>
       </c>
       <c r="G190" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7684,7 +7687,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G191" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7710,7 +7713,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G192" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7736,7 +7739,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G193" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7762,7 +7765,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G194" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -7788,7 +7791,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G195" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -7814,7 +7817,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G196" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -7840,7 +7843,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -7866,7 +7869,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -7892,7 +7895,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -7918,7 +7921,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -7944,7 +7947,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -7970,7 +7973,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -7996,7 +7999,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8022,7 +8025,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8048,7 +8051,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8074,7 +8077,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G206" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8100,7 +8103,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G207" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8126,7 +8129,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8152,7 +8155,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G209" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8178,7 +8181,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8204,7 +8207,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G211" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8230,7 +8233,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G212" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8256,7 +8259,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G213" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8282,7 +8285,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G214" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8308,7 +8311,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8334,7 +8337,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G216" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8360,7 +8363,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8386,7 +8389,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8412,7 +8415,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G219" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8438,7 +8441,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G220" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8464,7 +8467,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G221" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8490,7 +8493,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G222" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8516,7 +8519,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G223" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8542,7 +8545,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G224" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8568,7 +8571,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8594,7 +8597,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G226" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8620,7 +8623,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8646,7 +8649,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8672,7 +8675,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G229" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8698,7 +8701,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8724,7 +8727,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G231" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8750,7 +8753,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G232" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8776,7 +8779,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G233" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8802,7 +8805,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G234" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -8828,7 +8831,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G235" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -8854,7 +8857,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G236" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -8880,7 +8883,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G237" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -8906,7 +8909,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G238" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -8932,7 +8935,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G239" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -8958,7 +8961,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G240" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -8984,7 +8987,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9010,7 +9013,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9036,7 +9039,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9062,7 +9065,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G244" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9088,7 +9091,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9114,7 +9117,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G246" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9140,7 +9143,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G247" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9166,7 +9169,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G248" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9192,7 +9195,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G249" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9218,7 +9221,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G250" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9244,7 +9247,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9270,7 +9273,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G252" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9296,7 +9299,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G253" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9322,7 +9325,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G254" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9348,7 +9351,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9374,7 +9377,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G256" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9400,7 +9403,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G257" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9426,7 +9429,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G258" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9452,7 +9455,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G259" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9478,7 +9481,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9504,7 +9507,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G261" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9530,7 +9533,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G262" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9556,7 +9559,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9582,7 +9585,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G264" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9608,7 +9611,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G265" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9634,7 +9637,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G266" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9660,7 +9663,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G267" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9686,7 +9689,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G268" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9712,7 +9715,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9738,7 +9741,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G270" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9764,7 +9767,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G271" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -9790,7 +9793,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -9816,7 +9819,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9842,7 +9845,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G274" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -9868,7 +9871,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G275" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -9894,7 +9897,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G276" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9920,7 +9923,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G277" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9946,7 +9949,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G278" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -9972,7 +9975,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G279" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -9998,7 +10001,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G280" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10024,7 +10027,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G281" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10050,7 +10053,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10076,7 +10079,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G283" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10102,7 +10105,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G284" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10128,7 +10131,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G285" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10154,7 +10157,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G286" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10180,7 +10183,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G287" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10206,7 +10209,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10232,7 +10235,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G289" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10258,7 +10261,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G290" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10284,7 +10287,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G291" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10310,7 +10313,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10336,7 +10339,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G293" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10362,7 +10365,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G294" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10388,7 +10391,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G295" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10414,7 +10417,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G296" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10440,7 +10443,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G297" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10466,7 +10469,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G298" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10492,7 +10495,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10518,7 +10521,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G300" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10544,7 +10547,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G301" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10570,7 +10573,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G302" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10596,7 +10599,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10622,7 +10625,7 @@
         <v>1.875</v>
       </c>
       <c r="G304" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10648,7 +10651,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G305" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10674,7 +10677,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G306" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10700,7 +10703,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G307" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10726,7 +10729,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G308" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10752,7 +10755,7 @@
         <v>2</v>
       </c>
       <c r="G309" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -10778,7 +10781,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10804,7 +10807,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -10830,7 +10833,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -10856,7 +10859,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G313" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10882,7 +10885,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G314" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -10908,7 +10911,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10934,7 +10937,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10960,7 +10963,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G317" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11012,7 +11015,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11038,7 +11041,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11064,7 +11067,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11090,7 +11093,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11116,7 +11119,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11142,7 +11145,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11168,7 +11171,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11220,7 +11223,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G327" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11246,7 +11249,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11272,7 +11275,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11298,7 +11301,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11324,7 +11327,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11350,7 +11353,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G332" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11376,7 +11379,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11402,7 +11405,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11428,7 +11431,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G335" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11454,7 +11457,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11558,7 +11561,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11584,7 +11587,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G341" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11610,7 +11613,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11636,7 +11639,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11662,7 +11665,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G344" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11714,7 +11717,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G346" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11740,7 +11743,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G347" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11766,7 +11769,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -11792,7 +11795,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G349" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -11818,7 +11821,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -11870,7 +11873,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11896,7 +11899,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G353" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11948,7 +11951,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G355" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11974,7 +11977,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12000,7 +12003,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G357" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12026,7 +12029,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12052,7 +12055,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12078,7 +12081,7 @@
         <v>2.25</v>
       </c>
       <c r="G360" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12104,7 +12107,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12130,7 +12133,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12156,7 +12159,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G363" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12182,7 +12185,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G364" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12208,7 +12211,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12234,7 +12237,7 @@
         <v>2.25</v>
       </c>
       <c r="G366" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12260,7 +12263,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12286,7 +12289,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12312,7 +12315,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12338,7 +12341,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12364,7 +12367,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12390,7 +12393,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12416,7 +12419,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G373" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12442,7 +12445,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G374" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12468,7 +12471,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G375" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12494,7 +12497,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G376" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12520,7 +12523,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G377" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12546,7 +12549,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12572,7 +12575,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12598,7 +12601,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G380" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12624,7 +12627,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G381" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12650,7 +12653,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G382" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12676,7 +12679,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12702,7 +12705,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G384" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12728,7 +12731,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G385" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12754,7 +12757,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12780,7 +12783,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G387" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12806,7 +12809,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G388" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -12832,7 +12835,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G389" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -12858,7 +12861,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -12884,7 +12887,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G391" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -12910,7 +12913,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -12936,7 +12939,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G393" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -12962,7 +12965,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -12988,7 +12991,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G395" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13014,7 +13017,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13040,7 +13043,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13066,7 +13069,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13092,7 +13095,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G399" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13118,7 +13121,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G400" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13144,7 +13147,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G401" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13170,7 +13173,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13196,7 +13199,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G403" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13222,7 +13225,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13248,7 +13251,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G405" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13274,7 +13277,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13300,7 +13303,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13326,7 +13329,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13352,7 +13355,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G409" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13378,7 +13381,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G410" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13404,7 +13407,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G411" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13430,7 +13433,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13456,7 +13459,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G413" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13482,7 +13485,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G414" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13508,7 +13511,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G415" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13534,7 +13537,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G416" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13560,7 +13563,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G417" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13586,7 +13589,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G418" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13612,7 +13615,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G419" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13638,7 +13641,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G420" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13664,7 +13667,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G421" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13690,7 +13693,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G422" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13716,7 +13719,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13742,7 +13745,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G424" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13768,7 +13771,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G425" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13794,7 +13797,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G426" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -13820,7 +13823,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G427" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -13846,7 +13849,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G428" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -13872,7 +13875,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G429" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -13898,7 +13901,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G430" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -13924,7 +13927,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G431" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -13950,7 +13953,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -13976,7 +13979,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G433" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14002,7 +14005,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14028,7 +14031,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G435" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14054,7 +14057,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G436" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14080,7 +14083,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G437" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14106,7 +14109,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G438" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14132,7 +14135,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G439" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14158,7 +14161,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G440" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14184,7 +14187,7 @@
         <v>2.5</v>
       </c>
       <c r="G441" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14210,7 +14213,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G442" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14236,7 +14239,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G443" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14262,7 +14265,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G444" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14288,7 +14291,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G445" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14314,7 +14317,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14340,7 +14343,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G447" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14366,7 +14369,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G448" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14392,7 +14395,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G449" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14418,7 +14421,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G450" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14444,7 +14447,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G451" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14470,7 +14473,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G452" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14496,7 +14499,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G453" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14522,7 +14525,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G454" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14548,7 +14551,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G455" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14574,7 +14577,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G456" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14600,7 +14603,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G457" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14626,7 +14629,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G458" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14652,7 +14655,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G459" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14678,7 +14681,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G460" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14704,7 +14707,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G461" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14730,7 +14733,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G462" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14756,7 +14759,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G463" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14782,7 +14785,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G464" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -14808,7 +14811,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -14834,7 +14837,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G466" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -14860,7 +14863,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G467" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -14886,7 +14889,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G468" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -14912,7 +14915,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G469" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -14938,7 +14941,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G470" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -14964,7 +14967,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G471" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -14990,7 +14993,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15016,7 +15019,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G473" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15042,7 +15045,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15068,7 +15071,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G475" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15094,7 +15097,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G476" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15120,7 +15123,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G477" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15146,7 +15149,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G478" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15172,7 +15175,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G479" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15198,7 +15201,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G480" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15224,7 +15227,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15250,7 +15253,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G482" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15276,7 +15279,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G483" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15302,7 +15305,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G484" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15328,7 +15331,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G485" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15354,7 +15357,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G486" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15380,7 +15383,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15406,7 +15409,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G488" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15432,7 +15435,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G489" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15458,7 +15461,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G490" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15484,7 +15487,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G491" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15510,7 +15513,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15536,7 +15539,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G493" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15562,7 +15565,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G494" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15588,7 +15591,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15614,7 +15617,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G496" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15640,7 +15643,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G497" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15666,7 +15669,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G498" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15692,7 +15695,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G499" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15718,7 +15721,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G500" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15744,7 +15747,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G501" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15770,7 +15773,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G502" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15796,7 +15799,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G503" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -15822,7 +15825,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G504" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -15848,7 +15851,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G505" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -15874,7 +15877,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G506" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -15900,7 +15903,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G507" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -15926,7 +15929,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G508" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -15952,7 +15955,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G509" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -15978,7 +15981,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G510" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16004,7 +16007,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G511" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16030,7 +16033,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G512" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16056,7 +16059,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G513" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16082,7 +16085,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G514" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16108,7 +16111,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G515" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16134,7 +16137,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G516" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16160,7 +16163,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G517" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16186,7 +16189,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G518" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16212,7 +16215,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G519" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16238,7 +16241,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G520" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16264,7 +16267,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G521" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16290,7 +16293,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16316,7 +16319,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G523" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16342,7 +16345,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G524" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16368,7 +16371,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G525" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16394,7 +16397,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G526" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16420,7 +16423,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G527" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16446,7 +16449,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G528" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16472,7 +16475,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G529" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16498,7 +16501,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16524,7 +16527,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G531" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16550,7 +16553,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G532" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16576,7 +16579,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G533" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16602,7 +16605,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G534" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16628,7 +16631,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G535" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16654,7 +16657,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G536" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16680,7 +16683,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G537" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16706,7 +16709,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G538" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16732,7 +16735,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G539" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16758,7 +16761,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G540" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16784,7 +16787,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G541" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -16810,7 +16813,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G542" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -16836,7 +16839,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G543" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -16862,7 +16865,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G544" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -16888,7 +16891,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G545" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16914,7 +16917,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G546" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16940,7 +16943,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G547" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16966,7 +16969,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G548" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -16992,7 +16995,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G549" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17018,7 +17021,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G550" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17044,7 +17047,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G551" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17070,7 +17073,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G552" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17096,7 +17099,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G553" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17122,7 +17125,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G554" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17148,7 +17151,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17174,7 +17177,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G556" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17200,7 +17203,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G557" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17226,7 +17229,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17252,7 +17255,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17278,7 +17281,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17304,7 +17307,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17330,7 +17333,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G562" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17356,7 +17359,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G563" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17382,7 +17385,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17408,7 +17411,7 @@
         <v>2.5</v>
       </c>
       <c r="G565" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17434,7 +17437,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17460,7 +17463,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G567" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17486,7 +17489,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G568" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17512,7 +17515,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G569" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17538,7 +17541,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G570" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17564,7 +17567,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G571" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17590,7 +17593,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G572" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17616,7 +17619,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G573" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17642,7 +17645,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G574" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17668,7 +17671,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G575" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17694,7 +17697,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17720,7 +17723,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G577" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17746,7 +17749,7 @@
         <v>2.5</v>
       </c>
       <c r="G578" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17772,7 +17775,7 @@
         <v>2.5</v>
       </c>
       <c r="G579" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17798,7 +17801,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G580" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -17824,7 +17827,7 @@
         <v>2.5</v>
       </c>
       <c r="G581" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -17850,7 +17853,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -17876,7 +17879,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -17902,7 +17905,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -17928,7 +17931,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -17954,7 +17957,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -17980,7 +17983,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G587" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18006,7 +18009,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18032,7 +18035,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G589" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18058,7 +18061,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G590" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18084,7 +18087,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G591" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18110,7 +18113,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G592" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18136,7 +18139,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G593" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18162,7 +18165,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G594" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18188,7 +18191,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G595" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18214,7 +18217,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18240,7 +18243,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18266,7 +18269,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G598" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18292,7 +18295,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G599" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18318,7 +18321,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G600" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18344,7 +18347,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18370,7 +18373,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18396,7 +18399,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G603" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18422,7 +18425,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G604" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18448,7 +18451,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G605" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18474,7 +18477,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G606" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18500,7 +18503,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G607" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18526,7 +18529,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G608" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18552,7 +18555,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G609" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18578,7 +18581,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G610" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18604,7 +18607,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G611" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18630,7 +18633,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18916,7 +18919,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18994,7 +18997,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19280,7 +19283,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19306,7 +19309,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19670,7 +19673,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G652" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19722,7 +19725,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G654" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19748,7 +19751,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20112,7 +20115,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G669" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21126,7 +21129,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G708" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21230,7 +21233,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21256,7 +21259,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G713" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21282,7 +21285,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G714" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21308,7 +21311,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G715" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21334,7 +21337,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G716" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21438,7 +21441,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G720" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21464,7 +21467,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G721" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21490,7 +21493,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G722" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21516,7 +21519,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G723" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21542,7 +21545,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G724" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21568,7 +21571,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G725" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21620,7 +21623,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G727" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21646,7 +21649,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21672,7 +21675,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G729" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21724,7 +21727,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G731" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21750,7 +21753,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G732" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21776,7 +21779,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G733" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22322,7 +22325,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22348,7 +22351,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22634,7 +22637,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G766" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -68038,7 +68041,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6775231481</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>9826</v>
@@ -68059,6 +68062,32 @@
         <v>791</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6783796296</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>2999</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>792</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -38,82 +38,82 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825943946838</t>
+    <t xml:space="preserve">1.85825967788696</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9132376909256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109155654907</t>
+    <t xml:space="preserve">1.91323757171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109191417694</t>
   </si>
   <si>
     <t xml:space="preserve">1.88496327400208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92423319816589</t>
+    <t xml:space="preserve">1.9242330789566</t>
   </si>
   <si>
     <t xml:space="preserve">1.80642282962799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82998478412628</t>
+    <t xml:space="preserve">1.82998502254486</t>
   </si>
   <si>
     <t xml:space="preserve">1.79856896400452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76715278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354721546173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86925506591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87710928916931</t>
+    <t xml:space="preserve">1.76715314388275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86925518512726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87710893154144</t>
   </si>
   <si>
     <t xml:space="preserve">1.89281713962555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86768412590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81584799289703</t>
+    <t xml:space="preserve">1.86768424510956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81584763526917</t>
   </si>
   <si>
     <t xml:space="preserve">1.83783900737762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87553834915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684338092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8456928730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898951530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8362683057785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85983049869537</t>
+    <t xml:space="preserve">1.87553822994232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84569275379181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81898939609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83626818656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8598301410675</t>
   </si>
   <si>
     <t xml:space="preserve">1.80485212802887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8205600976944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81741857528687</t>
+    <t xml:space="preserve">1.82056045532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81741845607758</t>
   </si>
   <si>
     <t xml:space="preserve">1.85040533542633</t>
@@ -122,94 +122,94 @@
     <t xml:space="preserve">1.88025069236755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81427681446075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85197639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84412229061127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84098064899445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82370173931122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8111355304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8221310377121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679976463318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622433185577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407819747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.963503241539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96507394313812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9933488368988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00434398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98706531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905632972717</t>
+    <t xml:space="preserve">1.81427693367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85197627544403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84412205219269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84098052978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82370185852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81113541126251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82213115692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9367995262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622445106506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407831668854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96350300312042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9650741815567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99334847927094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00434422492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98706519603729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905680656433</t>
   </si>
   <si>
     <t xml:space="preserve">2.02476477622986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93051624298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96193218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994104862213</t>
+    <t xml:space="preserve">1.93051636219025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96193242073059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994116783142</t>
   </si>
   <si>
     <t xml:space="preserve">1.95564937591553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91637945175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87396740913391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378698825836</t>
+    <t xml:space="preserve">1.91637897491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87396717071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378722667694</t>
   </si>
   <si>
     <t xml:space="preserve">1.95017528533936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9223153591156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050932884216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656310558319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509159564972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95836925506592</t>
+    <t xml:space="preserve">1.92231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050944805145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656346321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509135723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95836913585663</t>
   </si>
   <si>
     <t xml:space="preserve">1.91739916801453</t>
@@ -218,39 +218,36 @@
     <t xml:space="preserve">1.9354259967804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94198107719421</t>
+    <t xml:space="preserve">1.94198131561279</t>
   </si>
   <si>
     <t xml:space="preserve">1.91248285770416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91084420681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545911312103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80268287658691</t>
+    <t xml:space="preserve">1.91084396839142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545887470245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8026829957962</t>
   </si>
   <si>
     <t xml:space="preserve">1.84201431274414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83218157291412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88298416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86823487281799</t>
+    <t xml:space="preserve">1.83218145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88298428058624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86823523044586</t>
   </si>
   <si>
     <t xml:space="preserve">1.90756642818451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89281690120697</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.90592730045319</t>
   </si>
   <si>
@@ -260,31 +257,31 @@
     <t xml:space="preserve">1.90920507907867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87151265144348</t>
+    <t xml:space="preserve">1.87151277065277</t>
   </si>
   <si>
     <t xml:space="preserve">1.8977335691452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82398736476898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75843513011932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76662909984589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78629517555237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77646195888519</t>
+    <t xml:space="preserve">1.82398748397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75843501091003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76662921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78629493713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77646219730377</t>
   </si>
   <si>
     <t xml:space="preserve">1.75188016891479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75351881980896</t>
+    <t xml:space="preserve">1.75351905822754</t>
   </si>
   <si>
     <t xml:space="preserve">1.77973961830139</t>
@@ -293,13 +290,13 @@
     <t xml:space="preserve">1.75024127960205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72074258327484</t>
+    <t xml:space="preserve">1.72074270248413</t>
   </si>
   <si>
     <t xml:space="preserve">1.66993999481201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72893679141998</t>
+    <t xml:space="preserve">1.72893667221069</t>
   </si>
   <si>
     <t xml:space="preserve">1.69616079330444</t>
@@ -308,7 +305,7 @@
     <t xml:space="preserve">1.76007390022278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70435464382172</t>
+    <t xml:space="preserve">1.70435476303101</t>
   </si>
   <si>
     <t xml:space="preserve">1.73549199104309</t>
@@ -317,16 +314,16 @@
     <t xml:space="preserve">1.73385310173035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71254885196686</t>
+    <t xml:space="preserve">1.71254861354828</t>
   </si>
   <si>
     <t xml:space="preserve">1.63060867786407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67157876491547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66666233539581</t>
+    <t xml:space="preserve">1.67157864570618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66666221618652</t>
   </si>
   <si>
     <t xml:space="preserve">1.61012363433838</t>
@@ -335,7 +332,7 @@
     <t xml:space="preserve">1.62241458892822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6633847951889</t>
+    <t xml:space="preserve">1.66338467597961</t>
   </si>
   <si>
     <t xml:space="preserve">1.67321753501892</t>
@@ -347,19 +344,19 @@
     <t xml:space="preserve">1.63880264759064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62569236755371</t>
+    <t xml:space="preserve">1.62569212913513</t>
   </si>
   <si>
     <t xml:space="preserve">1.66830110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65519070625305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64699685573578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63798320293427</t>
+    <t xml:space="preserve">1.65519082546234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6469966173172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63798332214355</t>
   </si>
   <si>
     <t xml:space="preserve">1.59865200519562</t>
@@ -374,7 +371,7 @@
     <t xml:space="preserve">1.59537434577942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.578986287117</t>
+    <t xml:space="preserve">1.57898640632629</t>
   </si>
   <si>
     <t xml:space="preserve">1.59127736091614</t>
@@ -386,13 +383,13 @@
     <t xml:space="preserve">1.56751477718353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56997299194336</t>
+    <t xml:space="preserve">1.56997287273407</t>
   </si>
   <si>
     <t xml:space="preserve">1.56669533252716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55850124359131</t>
+    <t xml:space="preserve">1.5585013628006</t>
   </si>
   <si>
     <t xml:space="preserve">1.6027489900589</t>
@@ -401,19 +398,19 @@
     <t xml:space="preserve">1.60356843471527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6060266494751</t>
+    <t xml:space="preserve">1.60602676868439</t>
   </si>
   <si>
     <t xml:space="preserve">1.51917004585266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56177890300751</t>
+    <t xml:space="preserve">1.5617790222168</t>
   </si>
   <si>
     <t xml:space="preserve">1.54539096355438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37659418582916</t>
+    <t xml:space="preserve">1.37659406661987</t>
   </si>
   <si>
     <t xml:space="preserve">1.41264796257019</t>
@@ -422,16 +419,16 @@
     <t xml:space="preserve">1.39462113380432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45771503448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47082531452179</t>
+    <t xml:space="preserve">1.45771491527557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47082543373108</t>
   </si>
   <si>
     <t xml:space="preserve">1.53391933441162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61258184909821</t>
+    <t xml:space="preserve">1.61258172988892</t>
   </si>
   <si>
     <t xml:space="preserve">1.61176240444183</t>
@@ -449,22 +446,22 @@
     <t xml:space="preserve">1.5552237033844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56505656242371</t>
+    <t xml:space="preserve">1.56505644321442</t>
   </si>
   <si>
     <t xml:space="preserve">1.56423711776733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59291625022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55686247348785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52162837982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5412939786911</t>
+    <t xml:space="preserve">1.59291613101959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55686259269714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52162826061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54129385948181</t>
   </si>
   <si>
     <t xml:space="preserve">1.5044207572937</t>
@@ -479,28 +476,28 @@
     <t xml:space="preserve">1.51589250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55194628238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50851786136627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53228068351746</t>
+    <t xml:space="preserve">1.55194616317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50851762294769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53228056430817</t>
   </si>
   <si>
     <t xml:space="preserve">1.50933730602264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5076984167099</t>
+    <t xml:space="preserve">1.50769853591919</t>
   </si>
   <si>
     <t xml:space="preserve">1.50278198719025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49540734291077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51015675067902</t>
+    <t xml:space="preserve">1.49540758132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51015663146973</t>
   </si>
   <si>
     <t xml:space="preserve">1.57325065135956</t>
@@ -512,19 +509,19 @@
     <t xml:space="preserve">1.59455502033234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60684597492218</t>
+    <t xml:space="preserve">1.60684585571289</t>
   </si>
   <si>
     <t xml:space="preserve">1.62159526348114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5716118812561</t>
+    <t xml:space="preserve">1.57161176204681</t>
   </si>
   <si>
     <t xml:space="preserve">1.54375207424164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57243120670319</t>
+    <t xml:space="preserve">1.57243132591248</t>
   </si>
   <si>
     <t xml:space="preserve">1.58718049526215</t>
@@ -533,7 +530,7 @@
     <t xml:space="preserve">1.54621028900146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55768179893494</t>
+    <t xml:space="preserve">1.55768203735352</t>
   </si>
   <si>
     <t xml:space="preserve">1.58799982070923</t>
@@ -551,19 +548,19 @@
     <t xml:space="preserve">1.53883576393127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54784905910492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55276560783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54948794841766</t>
+    <t xml:space="preserve">1.5478492975235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55276548862457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54948806762695</t>
   </si>
   <si>
     <t xml:space="preserve">1.5380163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54866862297058</t>
+    <t xml:space="preserve">1.54866850376129</t>
   </si>
   <si>
     <t xml:space="preserve">1.53637742996216</t>
@@ -575,7 +572,7 @@
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191304683685</t>
+    <t xml:space="preserve">1.65191316604614</t>
   </si>
   <si>
     <t xml:space="preserve">1.69288313388824</t>
@@ -587,49 +584,49 @@
     <t xml:space="preserve">1.82070958614349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82890391349792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81743216514587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579327583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87970674037933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79448914527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80104422569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73876941204071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72729814052582</t>
+    <t xml:space="preserve">1.82890379428864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81743192672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81579351425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87970650196075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79448890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80104410648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72729802131653</t>
   </si>
   <si>
     <t xml:space="preserve">1.74696373939514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76335167884827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84693038463593</t>
+    <t xml:space="preserve">1.76335144042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84693050384521</t>
   </si>
   <si>
     <t xml:space="preserve">1.81087708473206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80923807621002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81251561641693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86167979240417</t>
+    <t xml:space="preserve">1.80923795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81251573562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86168015003204</t>
   </si>
   <si>
     <t xml:space="preserve">1.86495745182037</t>
@@ -638,91 +635,91 @@
     <t xml:space="preserve">1.85840213298798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87642920017242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89937233924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84856951236725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92479634284973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679428100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850827217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97107374668121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822444438934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94193601608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94365000724792</t>
+    <t xml:space="preserve">1.87642896175385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89937257766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84856939315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92479622364044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679404258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850839138031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107362747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822432518005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94193613529205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94364988803864</t>
   </si>
   <si>
     <t xml:space="preserve">1.95907580852509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9676456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92651033401489</t>
+    <t xml:space="preserve">1.96764576435089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9265102148056</t>
   </si>
   <si>
     <t xml:space="preserve">1.95393395423889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93336629867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90594255924225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89394474029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87166309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92993819713593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90080070495605</t>
+    <t xml:space="preserve">1.93336606025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90594267845154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8939448595047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8716629743576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92993831634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90080046653748</t>
   </si>
   <si>
     <t xml:space="preserve">1.91451239585876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88708865642548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87680494785309</t>
+    <t xml:space="preserve">1.88708889484406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87680506706238</t>
   </si>
   <si>
     <t xml:space="preserve">1.91794049739838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88537490367889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86994910240173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88880276679993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90937042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90251445770264</t>
+    <t xml:space="preserve">1.8853747844696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86994898319244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88880288600922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90937054157257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90251469612122</t>
   </si>
   <si>
     <t xml:space="preserve">1.96421778202057</t>
@@ -737,7 +734,7 @@
     <t xml:space="preserve">1.98649966716766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97964334487915</t>
+    <t xml:space="preserve">1.97964346408844</t>
   </si>
   <si>
     <t xml:space="preserve">2.12533164024353</t>
@@ -749,25 +746,25 @@
     <t xml:space="preserve">2.05677270889282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07905459403992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08076786994934</t>
+    <t xml:space="preserve">2.07905435562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08076810836792</t>
   </si>
   <si>
     <t xml:space="preserve">2.06534242630005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06020069122314</t>
+    <t xml:space="preserve">2.06020045280457</t>
   </si>
   <si>
     <t xml:space="preserve">2.07219839096069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13390135765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10819172859192</t>
+    <t xml:space="preserve">2.13390159606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1081919670105</t>
   </si>
   <si>
     <t xml:space="preserve">2.09962201118469</t>
@@ -779,7 +776,7 @@
     <t xml:space="preserve">2.03963279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06877064704895</t>
+    <t xml:space="preserve">2.06877040863037</t>
   </si>
   <si>
     <t xml:space="preserve">2.11504769325256</t>
@@ -788,34 +785,34 @@
     <t xml:space="preserve">2.07391238212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09790802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1167619228363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08248233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06705641746521</t>
+    <t xml:space="preserve">2.09790778160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11676168441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08248209953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06705665588379</t>
   </si>
   <si>
     <t xml:space="preserve">2.12190365791321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10647797584534</t>
+    <t xml:space="preserve">2.10647773742676</t>
   </si>
   <si>
     <t xml:space="preserve">2.08933806419373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05163049697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17675113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14247155189514</t>
+    <t xml:space="preserve">2.05163073539734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17675089836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14247131347656</t>
   </si>
   <si>
     <t xml:space="preserve">2.13218760490417</t>
@@ -839,13 +836,13 @@
     <t xml:space="preserve">2.11161994934082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10133600234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15789723396301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15618300437927</t>
+    <t xml:space="preserve">2.10133576393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15789699554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15618324279785</t>
   </si>
   <si>
     <t xml:space="preserve">2.1441855430603</t>
@@ -857,10 +854,10 @@
     <t xml:space="preserve">2.14932727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13904356956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17503690719604</t>
+    <t xml:space="preserve">2.13904333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17503714561462</t>
   </si>
   <si>
     <t xml:space="preserve">2.15104126930237</t>
@@ -881,10 +878,10 @@
     <t xml:space="preserve">2.04820275306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07048439979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04991674423218</t>
+    <t xml:space="preserve">2.07048416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0499165058136</t>
   </si>
   <si>
     <t xml:space="preserve">2.12875962257385</t>
@@ -902,7 +899,7 @@
     <t xml:space="preserve">2.0224928855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01392316818237</t>
+    <t xml:space="preserve">2.01392292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.00535321235657</t>
@@ -911,13 +908,13 @@
     <t xml:space="preserve">2.1681809425354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18532061576843</t>
+    <t xml:space="preserve">2.18532085418701</t>
   </si>
   <si>
     <t xml:space="preserve">2.29672932624817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33100914955139</t>
+    <t xml:space="preserve">2.33100891113281</t>
   </si>
   <si>
     <t xml:space="preserve">2.32243919372559</t>
@@ -929,25 +926,25 @@
     <t xml:space="preserve">2.44241738319397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49383687973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46812701225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47669720649719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48526668548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53668642044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57953548431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.596675157547</t>
+    <t xml:space="preserve">2.49383664131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46812725067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47669696807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48526692390442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53668618202209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57953572273254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59667539596558</t>
   </si>
   <si>
     <t xml:space="preserve">2.61381506919861</t>
@@ -968,7 +965,7 @@
     <t xml:space="preserve">2.61655139923096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52694368362427</t>
+    <t xml:space="preserve">2.52694344520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.437335729599</t>
@@ -977,19 +974,19 @@
     <t xml:space="preserve">2.46421790122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50006103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45525741577148</t>
+    <t xml:space="preserve">2.50006127357483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45525717735291</t>
   </si>
   <si>
     <t xml:space="preserve">2.54486513137817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57174730300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51798295974731</t>
+    <t xml:space="preserve">2.57174754142761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51798272132874</t>
   </si>
   <si>
     <t xml:space="preserve">2.56278681755066</t>
@@ -998,16 +995,16 @@
     <t xml:space="preserve">2.53590416908264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4911003112793</t>
+    <t xml:space="preserve">2.49110054969788</t>
   </si>
   <si>
     <t xml:space="preserve">2.48213958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5090217590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47317862510681</t>
+    <t xml:space="preserve">2.50902199745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47317886352539</t>
   </si>
   <si>
     <t xml:space="preserve">2.78680658340454</t>
@@ -1016,19 +1013,19 @@
     <t xml:space="preserve">2.7599241733551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77784562110901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7420027256012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76888489723206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71512007713318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75096344947815</t>
+    <t xml:space="preserve">2.77784585952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74200248718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76888513565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71512031555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75096321105957</t>
   </si>
   <si>
     <t xml:space="preserve">2.67031621932983</t>
@@ -1040,13 +1037,13 @@
     <t xml:space="preserve">2.65239477157593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68823766708374</t>
+    <t xml:space="preserve">2.68823790550232</t>
   </si>
   <si>
     <t xml:space="preserve">2.73304176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69719862937927</t>
+    <t xml:space="preserve">2.69719886779785</t>
   </si>
   <si>
     <t xml:space="preserve">2.67927694320679</t>
@@ -1055,25 +1052,25 @@
     <t xml:space="preserve">2.84953236579895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86745357513428</t>
+    <t xml:space="preserve">2.86745381355286</t>
   </si>
   <si>
     <t xml:space="preserve">2.83161067962646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6434338092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62551236152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58070826530457</t>
+    <t xml:space="preserve">2.64343404769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62551259994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58070850372314</t>
   </si>
   <si>
     <t xml:space="preserve">2.607590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41941428184509</t>
+    <t xml:space="preserve">2.41941404342651</t>
   </si>
   <si>
     <t xml:space="preserve">2.66135549545288</t>
@@ -1082,7 +1079,7 @@
     <t xml:space="preserve">2.81368899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84057140350342</t>
+    <t xml:space="preserve">2.840571641922</t>
   </si>
   <si>
     <t xml:space="preserve">2.93914008140564</t>
@@ -1097,37 +1094,37 @@
     <t xml:space="preserve">2.80472826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90329670906067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12731647491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16315984725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13627767562866</t>
+    <t xml:space="preserve">2.90329694747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12731671333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16315960884094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13627743721008</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004225730896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25276803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26172876358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28861117362976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29757189750671</t>
+    <t xml:space="preserve">3.25276780128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26172852516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28861093521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29757165908813</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33341503143311</t>
+    <t xml:space="preserve">3.33341479301453</t>
   </si>
   <si>
     <t xml:space="preserve">3.34237575531006</t>
@@ -1142,10 +1139,10 @@
     <t xml:space="preserve">3.40510129928589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41406178474426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3692581653595</t>
+    <t xml:space="preserve">3.41406202316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36925792694092</t>
   </si>
   <si>
     <t xml:space="preserve">3.37821888923645</t>
@@ -1157,7 +1154,7 @@
     <t xml:space="preserve">3.4857485294342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47678780555725</t>
+    <t xml:space="preserve">3.47678756713867</t>
   </si>
   <si>
     <t xml:space="preserve">3.49470925331116</t>
@@ -1172,13 +1169,13 @@
     <t xml:space="preserve">3.53055238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59327793121338</t>
+    <t xml:space="preserve">3.59327816963196</t>
   </si>
   <si>
     <t xml:space="preserve">3.55743479728699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52159142494202</t>
+    <t xml:space="preserve">3.5215916633606</t>
   </si>
   <si>
     <t xml:space="preserve">3.51263093948364</t>
@@ -1205,19 +1202,19 @@
     <t xml:space="preserve">3.6918466091156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70976781845093</t>
+    <t xml:space="preserve">3.70976805686951</t>
   </si>
   <si>
     <t xml:space="preserve">3.68288588523865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76353311538696</t>
+    <t xml:space="preserve">3.7635326385498</t>
   </si>
   <si>
     <t xml:space="preserve">3.78145432472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80833697319031</t>
+    <t xml:space="preserve">3.80833721160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.79041528701782</t>
@@ -1226,24 +1223,27 @@
     <t xml:space="preserve">3.95170950889587</t>
   </si>
   <si>
+    <t xml:space="preserve">3.96067070960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97005581855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00759744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0920672416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81988859176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87620115280151</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.96067023277283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97005581855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00759792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0920672416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81988835334778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87620115280151</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.02636861801147</t>
   </si>
   <si>
@@ -1259,40 +1259,40 @@
     <t xml:space="preserve">4.03575468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99821257591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97944092750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85743021965027</t>
+    <t xml:space="preserve">3.9982123374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97944116592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85743045806885</t>
   </si>
   <si>
     <t xml:space="preserve">3.84804463386536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81050252914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7448046207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89497232437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94189953804016</t>
+    <t xml:space="preserve">3.81050276756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74480438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89497208595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.941899061203</t>
   </si>
   <si>
     <t xml:space="preserve">3.8668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93251395225525</t>
+    <t xml:space="preserve">3.93251419067383</t>
   </si>
   <si>
     <t xml:space="preserve">4.08268165588379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11083793640137</t>
+    <t xml:space="preserve">4.11083841323853</t>
   </si>
   <si>
     <t xml:space="preserve">4.12022304534912</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">4.18592166900635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19530725479126</t>
+    <t xml:space="preserve">4.1953067779541</t>
   </si>
   <si>
     <t xml:space="preserve">4.20469284057617</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">4.28916215896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26100587844849</t>
+    <t xml:space="preserve">4.26100540161133</t>
   </si>
   <si>
     <t xml:space="preserve">4.2703914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34547472000122</t>
+    <t xml:space="preserve">4.34547519683838</t>
   </si>
   <si>
     <t xml:space="preserve">4.36424589157104</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">4.50502824783325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49564266204834</t>
+    <t xml:space="preserve">4.49564218521118</t>
   </si>
   <si>
     <t xml:space="preserve">4.43932962417603</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">4.5519552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54257011413574</t>
+    <t xml:space="preserve">4.54256963729858</t>
   </si>
   <si>
     <t xml:space="preserve">4.48625707626343</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">4.40178775787354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44871520996094</t>
+    <t xml:space="preserve">4.44871473312378</t>
   </si>
   <si>
     <t xml:space="preserve">4.42994403839111</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">4.41117334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39240169525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24223470687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30793333053589</t>
+    <t xml:space="preserve">4.39240217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2422342300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30793285369873</t>
   </si>
   <si>
     <t xml:space="preserve">4.17653608322144</t>
@@ -1394,28 +1394,28 @@
     <t xml:space="preserve">4.62703895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61765336990356</t>
+    <t xml:space="preserve">4.61765384674072</t>
   </si>
   <si>
     <t xml:space="preserve">4.51441335678101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57072591781616</t>
+    <t xml:space="preserve">4.57072639465332</t>
   </si>
   <si>
     <t xml:space="preserve">4.67396640777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80536270141602</t>
+    <t xml:space="preserve">4.80536317825317</t>
   </si>
   <si>
     <t xml:space="preserve">4.78659200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86167621612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84290504455566</t>
+    <t xml:space="preserve">4.86167573928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84290456771851</t>
   </si>
   <si>
     <t xml:space="preserve">4.89921760559082</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">4.5988826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53318405151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58011150360107</t>
+    <t xml:space="preserve">4.53318452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58011198043823</t>
   </si>
   <si>
     <t xml:space="preserve">4.6927375793457</t>
@@ -1439,16 +1439,16 @@
     <t xml:space="preserve">4.74905014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73027944564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71150827407837</t>
+    <t xml:space="preserve">4.73027896881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71150875091553</t>
   </si>
   <si>
     <t xml:space="preserve">4.76782131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95553112030029</t>
+    <t xml:space="preserve">4.95553064346313</t>
   </si>
   <si>
     <t xml:space="preserve">4.88044691085815</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">4.91798877716064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99307250976562</t>
+    <t xml:space="preserve">4.99307298660278</t>
   </si>
   <si>
     <t xml:space="preserve">4.93675994873047</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">6.60737419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28826808929443</t>
+    <t xml:space="preserve">6.28826761245728</t>
   </si>
   <si>
     <t xml:space="preserve">6.1568717956543</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">5.96916246414185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70636892318726</t>
+    <t xml:space="preserve">5.7063684463501</t>
   </si>
   <si>
     <t xml:space="preserve">5.53743028640747</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">5.87530755996704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66882658004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68759727478027</t>
+    <t xml:space="preserve">5.66882705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68759775161743</t>
   </si>
   <si>
     <t xml:space="preserve">5.83776521682739</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59374284744263</t>
+    <t xml:space="preserve">5.59374332427979</t>
   </si>
   <si>
     <t xml:space="preserve">5.38726234436035</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">5.10569858551025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68335199356079</t>
+    <t xml:space="preserve">4.68335151672363</t>
   </si>
   <si>
     <t xml:space="preserve">4.14837980270386</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">3.62279319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55709481239319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37877082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50078225135803</t>
+    <t xml:space="preserve">3.55709505081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37877106666565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50078201293945</t>
   </si>
   <si>
     <t xml:space="preserve">3.5664803981781</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">3.75418996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70726251602173</t>
+    <t xml:space="preserve">3.70726275444031</t>
   </si>
   <si>
     <t xml:space="preserve">3.71664810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8386595249176</t>
+    <t xml:space="preserve">3.83865928649902</t>
   </si>
   <si>
     <t xml:space="preserve">4.25162029266357</t>
@@ -1580,25 +1580,25 @@
     <t xml:space="preserve">4.12960910797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16715049743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05452537536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76357555389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66972064971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65094995498657</t>
+    <t xml:space="preserve">4.16715097427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05452489852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76357579231262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66972088813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65094971656799</t>
   </si>
   <si>
     <t xml:space="preserve">3.66033530235291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95128512382507</t>
+    <t xml:space="preserve">3.95128488540649</t>
   </si>
   <si>
     <t xml:space="preserve">4.29854726791382</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">4.31731843948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15776491165161</t>
+    <t xml:space="preserve">4.15776538848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.10145235061646</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">4.13899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88558626174927</t>
+    <t xml:space="preserve">3.88558650016785</t>
   </si>
   <si>
     <t xml:space="preserve">4.32670402526855</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">4.27977657318115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.913743019104</t>
+    <t xml:space="preserve">3.91374325752258</t>
   </si>
   <si>
     <t xml:space="preserve">3.92312836647034</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">3.49139666557312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67910623550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38815641403198</t>
+    <t xml:space="preserve">3.67910599708557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3881561756134</t>
   </si>
   <si>
     <t xml:space="preserve">3.35999989509583</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">3.34122896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20044708251953</t>
+    <t xml:space="preserve">3.20044684410095</t>
   </si>
   <si>
     <t xml:space="preserve">3.24737429618835</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">3.47262573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57586574554443</t>
+    <t xml:space="preserve">3.57586598396301</t>
   </si>
   <si>
     <t xml:space="preserve">3.73541903495789</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">3.68849158287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72603368759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52893853187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63217878341675</t>
+    <t xml:space="preserve">3.72603344917297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52893877029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63217854499817</t>
   </si>
   <si>
     <t xml:space="preserve">3.51016759872437</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">3.58525133132935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53832411766052</t>
+    <t xml:space="preserve">3.53832387924194</t>
   </si>
   <si>
     <t xml:space="preserve">3.80111742019653</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">3.48201107978821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46324014663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4444694519043</t>
+    <t xml:space="preserve">3.46324038505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44446921348572</t>
   </si>
   <si>
     <t xml:space="preserve">3.42569851875305</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">3.41631293296814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754199981689</t>
+    <t xml:space="preserve">3.39754176139832</t>
   </si>
   <si>
     <t xml:space="preserve">3.21921801567078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1910617351532</t>
+    <t xml:space="preserve">3.19106149673462</t>
   </si>
   <si>
     <t xml:space="preserve">3.17229056358337</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">3.23798894882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14413404464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25675964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36938524246216</t>
+    <t xml:space="preserve">3.14413380622864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25675988197327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36938548088074</t>
   </si>
   <si>
     <t xml:space="preserve">3.15351939201355</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">3.18167614936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29430174827576</t>
+    <t xml:space="preserve">3.29430150985718</t>
   </si>
   <si>
     <t xml:space="preserve">3.2661452293396</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">3.12536311149597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04089379310608</t>
+    <t xml:space="preserve">3.04089403152466</t>
   </si>
   <si>
     <t xml:space="preserve">3.05027914047241</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">2.93765377998352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95642447471619</t>
+    <t xml:space="preserve">2.95642471313477</t>
   </si>
   <si>
     <t xml:space="preserve">3.03150844573975</t>
@@ -1805,19 +1805,19 @@
     <t xml:space="preserve">3.02212285995483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92826795578003</t>
+    <t xml:space="preserve">2.92826819419861</t>
   </si>
   <si>
     <t xml:space="preserve">2.94703912734985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90011167526245</t>
+    <t xml:space="preserve">2.90011143684387</t>
   </si>
   <si>
     <t xml:space="preserve">2.97519564628601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27553057670593</t>
+    <t xml:space="preserve">3.27553081512451</t>
   </si>
   <si>
     <t xml:space="preserve">3.33184361457825</t>
@@ -6254,7 +6254,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -6280,7 +6280,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -6306,7 +6306,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -6332,7 +6332,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G139" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -6358,7 +6358,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -6384,7 +6384,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -6436,7 +6436,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G143" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -6462,7 +6462,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G144" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -6488,7 +6488,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -6514,7 +6514,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -6540,7 +6540,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -6566,7 +6566,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G148" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -6592,7 +6592,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -6618,7 +6618,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G150" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -6644,7 +6644,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G151" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -6670,7 +6670,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -6696,7 +6696,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G153" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -6722,7 +6722,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G154" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -6748,7 +6748,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G155" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -6774,7 +6774,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -6800,7 +6800,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -6826,7 +6826,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -6852,7 +6852,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -6878,7 +6878,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G160" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -6904,7 +6904,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G161" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -6930,7 +6930,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G162" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -6956,7 +6956,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G163" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -6982,7 +6982,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G164" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -7008,7 +7008,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G165" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -7034,7 +7034,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G166" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7060,7 +7060,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G167" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7086,7 +7086,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G168" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7112,7 +7112,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G169" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7138,7 +7138,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7164,7 +7164,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G171" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7190,7 +7190,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7216,7 +7216,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7242,7 +7242,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G174" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7268,7 +7268,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7294,7 +7294,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G176" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7320,7 +7320,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G177" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7346,7 +7346,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G178" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7372,7 +7372,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G179" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7398,7 +7398,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G180" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7424,7 +7424,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G181" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7450,7 +7450,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G182" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7476,7 +7476,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G183" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7502,7 +7502,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G184" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -7528,7 +7528,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G185" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7554,7 +7554,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G186" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7580,7 +7580,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G187" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7606,7 +7606,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G188" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7632,7 +7632,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G189" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7658,7 +7658,7 @@
         <v>2</v>
       </c>
       <c r="G190" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7684,7 +7684,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G191" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7710,7 +7710,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G192" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7736,7 +7736,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G193" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7762,7 +7762,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G194" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -7788,7 +7788,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G195" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -7814,7 +7814,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G196" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -7840,7 +7840,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -7866,7 +7866,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -7892,7 +7892,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -7918,7 +7918,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -7944,7 +7944,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -7970,7 +7970,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -7996,7 +7996,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8022,7 +8022,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8048,7 +8048,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8074,7 +8074,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G206" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8100,7 +8100,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G207" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8126,7 +8126,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8152,7 +8152,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G209" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8178,7 +8178,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8204,7 +8204,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G211" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8230,7 +8230,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G212" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8256,7 +8256,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G213" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8282,7 +8282,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G214" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8308,7 +8308,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8334,7 +8334,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G216" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8360,7 +8360,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8386,7 +8386,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8412,7 +8412,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G219" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8438,7 +8438,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G220" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8464,7 +8464,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G221" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8490,7 +8490,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G222" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8516,7 +8516,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G223" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8542,7 +8542,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G224" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8568,7 +8568,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8594,7 +8594,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G226" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8620,7 +8620,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8646,7 +8646,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8672,7 +8672,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G229" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8698,7 +8698,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8724,7 +8724,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G231" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8750,7 +8750,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G232" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8776,7 +8776,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G233" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8802,7 +8802,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G234" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -8828,7 +8828,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G235" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -8854,7 +8854,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G236" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -8880,7 +8880,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G237" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -8906,7 +8906,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G238" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -8932,7 +8932,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G239" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -8958,7 +8958,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G240" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -8984,7 +8984,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9010,7 +9010,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9036,7 +9036,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9062,7 +9062,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G244" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9088,7 +9088,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9114,7 +9114,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G246" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9140,7 +9140,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G247" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9166,7 +9166,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G248" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9192,7 +9192,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G249" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9218,7 +9218,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G250" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9244,7 +9244,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9270,7 +9270,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G252" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9296,7 +9296,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G253" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9322,7 +9322,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G254" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9348,7 +9348,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9374,7 +9374,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G256" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9400,7 +9400,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G257" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9426,7 +9426,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G258" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9452,7 +9452,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G259" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9478,7 +9478,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9504,7 +9504,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G261" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9530,7 +9530,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G262" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9556,7 +9556,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9582,7 +9582,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G264" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9608,7 +9608,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G265" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9634,7 +9634,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G266" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9660,7 +9660,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G267" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9686,7 +9686,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G268" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9712,7 +9712,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9738,7 +9738,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G270" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9764,7 +9764,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G271" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -9790,7 +9790,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -9816,7 +9816,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9842,7 +9842,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G274" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -9868,7 +9868,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G275" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -9894,7 +9894,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G276" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9920,7 +9920,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G277" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9946,7 +9946,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G278" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -9972,7 +9972,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G279" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -9998,7 +9998,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G280" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10024,7 +10024,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G281" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10050,7 +10050,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10076,7 +10076,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G283" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10102,7 +10102,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G284" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10128,7 +10128,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G285" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10154,7 +10154,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G286" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10180,7 +10180,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G287" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10206,7 +10206,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10232,7 +10232,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G289" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10258,7 +10258,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G290" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10284,7 +10284,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G291" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10310,7 +10310,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10336,7 +10336,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G293" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10362,7 +10362,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G294" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10388,7 +10388,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G295" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10414,7 +10414,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G296" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10440,7 +10440,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G297" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10466,7 +10466,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G298" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10492,7 +10492,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10518,7 +10518,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G300" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10544,7 +10544,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G301" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10570,7 +10570,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G302" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10596,7 +10596,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10622,7 +10622,7 @@
         <v>1.875</v>
       </c>
       <c r="G304" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10648,7 +10648,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G305" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10674,7 +10674,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G306" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10700,7 +10700,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G307" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10726,7 +10726,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G308" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10752,7 +10752,7 @@
         <v>2</v>
       </c>
       <c r="G309" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -10778,7 +10778,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10804,7 +10804,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -10830,7 +10830,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -10856,7 +10856,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G313" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10882,7 +10882,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G314" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -10908,7 +10908,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10934,7 +10934,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10960,7 +10960,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G317" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11012,7 +11012,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11038,7 +11038,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11064,7 +11064,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11090,7 +11090,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11116,7 +11116,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11142,7 +11142,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11168,7 +11168,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11220,7 +11220,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G327" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11246,7 +11246,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11272,7 +11272,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11298,7 +11298,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11324,7 +11324,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11350,7 +11350,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G332" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11376,7 +11376,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11402,7 +11402,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11428,7 +11428,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G335" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11454,7 +11454,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11558,7 +11558,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11584,7 +11584,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G341" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11610,7 +11610,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11636,7 +11636,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11662,7 +11662,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G344" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11714,7 +11714,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G346" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11740,7 +11740,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G347" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11766,7 +11766,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -11792,7 +11792,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G349" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -11818,7 +11818,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -11870,7 +11870,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11896,7 +11896,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G353" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11948,7 +11948,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G355" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11974,7 +11974,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12000,7 +12000,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G357" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12026,7 +12026,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12052,7 +12052,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12078,7 +12078,7 @@
         <v>2.25</v>
       </c>
       <c r="G360" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12104,7 +12104,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12130,7 +12130,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12156,7 +12156,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G363" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12182,7 +12182,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G364" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12208,7 +12208,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12234,7 +12234,7 @@
         <v>2.25</v>
       </c>
       <c r="G366" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12260,7 +12260,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12286,7 +12286,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12312,7 +12312,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12338,7 +12338,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12364,7 +12364,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12390,7 +12390,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12416,7 +12416,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G373" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12442,7 +12442,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G374" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12468,7 +12468,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G375" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12494,7 +12494,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G376" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12520,7 +12520,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G377" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12546,7 +12546,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12572,7 +12572,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12598,7 +12598,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G380" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12624,7 +12624,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G381" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12650,7 +12650,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G382" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12676,7 +12676,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12702,7 +12702,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G384" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12728,7 +12728,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G385" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12754,7 +12754,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12780,7 +12780,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G387" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12806,7 +12806,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G388" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -12832,7 +12832,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G389" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -12858,7 +12858,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -12884,7 +12884,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G391" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -12910,7 +12910,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -12936,7 +12936,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G393" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -12962,7 +12962,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -12988,7 +12988,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G395" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13014,7 +13014,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13040,7 +13040,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13066,7 +13066,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13092,7 +13092,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G399" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13118,7 +13118,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G400" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13144,7 +13144,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G401" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13170,7 +13170,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13196,7 +13196,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G403" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13222,7 +13222,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13248,7 +13248,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G405" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13274,7 +13274,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13300,7 +13300,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13326,7 +13326,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13352,7 +13352,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G409" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13378,7 +13378,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G410" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13404,7 +13404,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G411" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13430,7 +13430,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13456,7 +13456,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G413" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13482,7 +13482,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G414" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13508,7 +13508,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G415" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13534,7 +13534,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G416" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13560,7 +13560,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G417" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13586,7 +13586,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G418" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13612,7 +13612,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G419" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13638,7 +13638,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G420" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13664,7 +13664,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G421" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13690,7 +13690,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G422" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13716,7 +13716,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13742,7 +13742,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G424" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13768,7 +13768,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G425" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13794,7 +13794,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G426" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -13820,7 +13820,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G427" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -13846,7 +13846,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G428" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -13872,7 +13872,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G429" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -13898,7 +13898,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G430" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -13924,7 +13924,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G431" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -13950,7 +13950,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -13976,7 +13976,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G433" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14002,7 +14002,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14028,7 +14028,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G435" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14054,7 +14054,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G436" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14080,7 +14080,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G437" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14106,7 +14106,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G438" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14132,7 +14132,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G439" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14158,7 +14158,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G440" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14184,7 +14184,7 @@
         <v>2.5</v>
       </c>
       <c r="G441" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14210,7 +14210,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G442" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14236,7 +14236,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G443" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14262,7 +14262,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G444" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14288,7 +14288,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G445" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14314,7 +14314,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14340,7 +14340,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G447" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14366,7 +14366,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G448" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14392,7 +14392,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G449" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14418,7 +14418,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G450" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14444,7 +14444,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G451" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14470,7 +14470,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G452" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14496,7 +14496,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G453" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14522,7 +14522,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G454" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14548,7 +14548,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G455" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14574,7 +14574,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G456" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14600,7 +14600,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G457" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14626,7 +14626,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G458" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14652,7 +14652,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G459" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14678,7 +14678,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G460" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14704,7 +14704,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G461" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14730,7 +14730,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G462" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14756,7 +14756,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G463" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14782,7 +14782,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G464" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -14808,7 +14808,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -14834,7 +14834,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G466" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -14860,7 +14860,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G467" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -14886,7 +14886,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G468" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -14912,7 +14912,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G469" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -14938,7 +14938,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G470" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -14964,7 +14964,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G471" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -14990,7 +14990,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15016,7 +15016,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G473" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15042,7 +15042,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15068,7 +15068,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G475" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15094,7 +15094,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G476" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15120,7 +15120,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G477" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15146,7 +15146,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G478" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15172,7 +15172,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G479" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15198,7 +15198,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G480" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15224,7 +15224,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15250,7 +15250,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G482" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15276,7 +15276,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G483" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15302,7 +15302,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G484" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15328,7 +15328,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G485" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15354,7 +15354,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G486" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15380,7 +15380,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15406,7 +15406,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G488" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15432,7 +15432,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G489" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15458,7 +15458,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G490" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15484,7 +15484,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G491" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15510,7 +15510,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15536,7 +15536,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G493" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15562,7 +15562,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G494" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15588,7 +15588,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15614,7 +15614,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G496" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15640,7 +15640,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G497" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15666,7 +15666,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G498" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15692,7 +15692,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G499" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15718,7 +15718,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G500" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15744,7 +15744,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G501" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15770,7 +15770,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G502" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15796,7 +15796,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G503" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -15822,7 +15822,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G504" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -15848,7 +15848,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G505" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -15874,7 +15874,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G506" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -15900,7 +15900,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G507" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -15926,7 +15926,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G508" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -15952,7 +15952,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G509" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -15978,7 +15978,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G510" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16004,7 +16004,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G511" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16030,7 +16030,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G512" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16056,7 +16056,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G513" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16082,7 +16082,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G514" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16108,7 +16108,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G515" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16134,7 +16134,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G516" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16160,7 +16160,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G517" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16186,7 +16186,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G518" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16212,7 +16212,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G519" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16238,7 +16238,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G520" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16264,7 +16264,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G521" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16290,7 +16290,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16316,7 +16316,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G523" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16342,7 +16342,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G524" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16368,7 +16368,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G525" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16394,7 +16394,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G526" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16420,7 +16420,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G527" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16446,7 +16446,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G528" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16472,7 +16472,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G529" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16498,7 +16498,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16524,7 +16524,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G531" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16550,7 +16550,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G532" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16576,7 +16576,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G533" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16602,7 +16602,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G534" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16628,7 +16628,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G535" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16654,7 +16654,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G536" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16680,7 +16680,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G537" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16706,7 +16706,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G538" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16732,7 +16732,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G539" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16758,7 +16758,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G540" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16784,7 +16784,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G541" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -16810,7 +16810,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G542" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -16836,7 +16836,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G543" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -16862,7 +16862,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G544" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -16888,7 +16888,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G545" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16914,7 +16914,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G546" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16940,7 +16940,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G547" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16966,7 +16966,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G548" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -16992,7 +16992,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G549" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17018,7 +17018,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G550" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17044,7 +17044,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G551" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17070,7 +17070,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G552" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17096,7 +17096,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G553" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17122,7 +17122,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G554" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17148,7 +17148,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17174,7 +17174,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G556" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17200,7 +17200,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G557" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17226,7 +17226,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17252,7 +17252,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17278,7 +17278,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17304,7 +17304,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17330,7 +17330,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G562" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17356,7 +17356,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G563" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17382,7 +17382,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17408,7 +17408,7 @@
         <v>2.5</v>
       </c>
       <c r="G565" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17434,7 +17434,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17460,7 +17460,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G567" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17486,7 +17486,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G568" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17512,7 +17512,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G569" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17538,7 +17538,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G570" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17564,7 +17564,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G571" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17590,7 +17590,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G572" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17616,7 +17616,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G573" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17642,7 +17642,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G574" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17668,7 +17668,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G575" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17694,7 +17694,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17720,7 +17720,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G577" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17746,7 +17746,7 @@
         <v>2.5</v>
       </c>
       <c r="G578" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17772,7 +17772,7 @@
         <v>2.5</v>
       </c>
       <c r="G579" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17798,7 +17798,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G580" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -17824,7 +17824,7 @@
         <v>2.5</v>
       </c>
       <c r="G581" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -17850,7 +17850,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -17876,7 +17876,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -17902,7 +17902,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -17928,7 +17928,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -17954,7 +17954,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -17980,7 +17980,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G587" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18006,7 +18006,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18032,7 +18032,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G589" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18058,7 +18058,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G590" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18084,7 +18084,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G591" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18110,7 +18110,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G592" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18136,7 +18136,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G593" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18162,7 +18162,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G594" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18188,7 +18188,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G595" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18214,7 +18214,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18240,7 +18240,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18266,7 +18266,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G598" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18292,7 +18292,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G599" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18318,7 +18318,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G600" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18344,7 +18344,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18370,7 +18370,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18396,7 +18396,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G603" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18422,7 +18422,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G604" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18448,7 +18448,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G605" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18474,7 +18474,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G606" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18500,7 +18500,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G607" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18526,7 +18526,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G608" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18552,7 +18552,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G609" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18578,7 +18578,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G610" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18604,7 +18604,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G611" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18630,7 +18630,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18656,7 +18656,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G613" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18682,7 +18682,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G614" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18708,7 +18708,7 @@
         <v>2.75</v>
       </c>
       <c r="G615" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18734,7 +18734,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G616" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18760,7 +18760,7 @@
         <v>2.75</v>
       </c>
       <c r="G617" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18786,7 +18786,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G618" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18812,7 +18812,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G619" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18838,7 +18838,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G620" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18864,7 +18864,7 @@
         <v>2.75</v>
       </c>
       <c r="G621" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18890,7 +18890,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G622" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18916,7 +18916,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18942,7 +18942,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18968,7 +18968,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -18994,7 +18994,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19020,7 +19020,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G627" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19046,7 +19046,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G628" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19072,7 +19072,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G629" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19098,7 +19098,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G630" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19124,7 +19124,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19150,7 +19150,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G632" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19176,7 +19176,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19202,7 +19202,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G634" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19228,7 +19228,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G635" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19254,7 +19254,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G636" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19280,7 +19280,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19306,7 +19306,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19332,7 +19332,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19358,7 +19358,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19384,7 +19384,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19410,7 +19410,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19436,7 +19436,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19462,7 +19462,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19488,7 +19488,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19514,7 +19514,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19540,7 +19540,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G647" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19566,7 +19566,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G648" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19592,7 +19592,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G649" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19618,7 +19618,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G650" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19644,7 +19644,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G651" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19670,7 +19670,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G652" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19696,7 +19696,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G653" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19722,7 +19722,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G654" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19748,7 +19748,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19774,7 +19774,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G656" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19800,7 +19800,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -19826,7 +19826,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G658" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -19852,7 +19852,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19878,7 +19878,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G660" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19904,7 +19904,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G661" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19930,7 +19930,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G662" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19956,7 +19956,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G663" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19982,7 +19982,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G664" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20008,7 +20008,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20034,7 +20034,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20060,7 +20060,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20086,7 +20086,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20112,7 +20112,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G669" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20138,7 +20138,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G670" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20164,7 +20164,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20190,7 +20190,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G672" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20216,7 +20216,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G673" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20242,7 +20242,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20268,7 +20268,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20294,7 +20294,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G676" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20320,7 +20320,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20346,7 +20346,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20372,7 +20372,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G679" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20398,7 +20398,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20424,7 +20424,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G681" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20450,7 +20450,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20476,7 +20476,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20502,7 +20502,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20528,7 +20528,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20554,7 +20554,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20580,7 +20580,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20606,7 +20606,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20632,7 +20632,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20658,7 +20658,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20684,7 +20684,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20710,7 +20710,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G692" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20736,7 +20736,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20762,7 +20762,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20788,7 +20788,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20814,7 +20814,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20840,7 +20840,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20866,7 +20866,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -20892,7 +20892,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -20918,7 +20918,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -20944,7 +20944,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -20970,7 +20970,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20996,7 +20996,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21022,7 +21022,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21048,7 +21048,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21074,7 +21074,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21100,7 +21100,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21126,7 +21126,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G708" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21152,7 +21152,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G709" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21178,7 +21178,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G710" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21204,7 +21204,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G711" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21230,7 +21230,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21256,7 +21256,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G713" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21282,7 +21282,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G714" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21308,7 +21308,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G715" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21334,7 +21334,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G716" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21360,7 +21360,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G717" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21386,7 +21386,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21412,7 +21412,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G719" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21438,7 +21438,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G720" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21464,7 +21464,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G721" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21490,7 +21490,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G722" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21516,7 +21516,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G723" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21542,7 +21542,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G724" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21568,7 +21568,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G725" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21594,7 +21594,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G726" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21620,7 +21620,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G727" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21646,7 +21646,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21672,7 +21672,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G729" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21698,7 +21698,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21724,7 +21724,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G731" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21750,7 +21750,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G732" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21776,7 +21776,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G733" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21802,7 +21802,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G734" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21828,7 +21828,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G735" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21854,7 +21854,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G736" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21880,7 +21880,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G737" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21906,7 +21906,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21932,7 +21932,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G739" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21958,7 +21958,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21984,7 +21984,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G741" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22010,7 +22010,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G742" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22036,7 +22036,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G743" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22062,7 +22062,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G744" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22088,7 +22088,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G745" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22114,7 +22114,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22140,7 +22140,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22166,7 +22166,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22192,7 +22192,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G749" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22218,7 +22218,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22244,7 +22244,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22270,7 +22270,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22296,7 +22296,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22322,7 +22322,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22348,7 +22348,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22374,7 +22374,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22400,7 +22400,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22426,7 +22426,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22452,7 +22452,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G759" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22478,7 +22478,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G760" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22504,7 +22504,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G761" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22530,7 +22530,7 @@
         <v>2.75</v>
       </c>
       <c r="G762" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22556,7 +22556,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22582,7 +22582,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22608,7 +22608,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22634,7 +22634,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G766" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22660,7 +22660,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22686,7 +22686,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G768" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22712,7 +22712,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22738,7 +22738,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22764,7 +22764,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22790,7 +22790,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22816,7 +22816,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22842,7 +22842,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22868,7 +22868,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22894,7 +22894,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22920,7 +22920,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22946,7 +22946,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22972,7 +22972,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G779" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22998,7 +22998,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23024,7 +23024,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23050,7 +23050,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G782" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23076,7 +23076,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23102,7 +23102,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G784" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23128,7 +23128,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G785" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23154,7 +23154,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23180,7 +23180,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G787" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23206,7 +23206,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G788" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23232,7 +23232,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G789" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23258,7 +23258,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23284,7 +23284,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G791" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23310,7 +23310,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G792" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23336,7 +23336,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G793" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23362,7 +23362,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23388,7 +23388,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23414,7 +23414,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23440,7 +23440,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G797" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23466,7 +23466,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G798" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23492,7 +23492,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23518,7 +23518,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G800" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23544,7 +23544,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23570,7 +23570,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G802" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23596,7 +23596,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23622,7 +23622,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G804" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23648,7 +23648,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23674,7 +23674,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23700,7 +23700,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G807" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23726,7 +23726,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G808" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23752,7 +23752,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G809" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23778,7 +23778,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G810" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23804,7 +23804,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G811" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23830,7 +23830,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23856,7 +23856,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G813" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23882,7 +23882,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G814" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23908,7 +23908,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23934,7 +23934,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G816" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23960,7 +23960,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23986,7 +23986,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G818" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24012,7 +24012,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24038,7 +24038,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G820" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24064,7 +24064,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G821" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24090,7 +24090,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24116,7 +24116,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G823" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24142,7 +24142,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G824" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24168,7 +24168,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G825" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24194,7 +24194,7 @@
         <v>4</v>
       </c>
       <c r="G826" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24220,7 +24220,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G827" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24246,7 +24246,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G828" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24272,7 +24272,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G829" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24298,7 +24298,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G830" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24324,7 +24324,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24350,7 +24350,7 @@
         <v>4</v>
       </c>
       <c r="G832" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24376,7 +24376,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24402,7 +24402,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24428,7 +24428,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24454,7 +24454,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G836" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24480,7 +24480,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24506,7 +24506,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24532,7 +24532,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G839" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24558,7 +24558,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24584,7 +24584,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G841" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24610,7 +24610,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G842" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24636,7 +24636,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24662,7 +24662,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G844" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24688,7 +24688,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G845" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24714,7 +24714,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24740,7 +24740,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24766,7 +24766,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24792,7 +24792,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24818,7 +24818,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G850" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24844,7 +24844,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24870,7 +24870,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24896,7 +24896,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G853" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24922,7 +24922,7 @@
         <v>4.25</v>
       </c>
       <c r="G854" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24948,7 +24948,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24974,7 +24974,7 @@
         <v>4.25</v>
       </c>
       <c r="G856" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25000,7 +25000,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G857" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25026,7 +25026,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G858" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25052,7 +25052,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G859" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25078,7 +25078,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25104,7 +25104,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G861" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25130,7 +25130,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G862" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25156,7 +25156,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G863" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25182,7 +25182,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G864" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25208,7 +25208,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G865" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25260,7 +25260,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G867" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25364,7 +25364,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25416,7 +25416,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G873" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25546,7 +25546,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G878" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25910,7 +25910,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G892" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25988,7 +25988,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G895" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26222,7 +26222,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G904" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -30408,7 +30408,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1065" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30694,7 +30694,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1076" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30720,7 +30720,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1077" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30954,7 +30954,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1086" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31318,7 +31318,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1100" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31422,7 +31422,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1104" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32930,7 +32930,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1162" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32956,7 +32956,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1163" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33398,7 +33398,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1180" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33528,7 +33528,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1185" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33736,7 +33736,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1193" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -68090,7 +68090,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6912152778</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>1460</v>
@@ -68111,6 +68111,32 @@
         <v>789</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6911342593</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>279</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>790</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -38,121 +38,121 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825967788696</t>
+    <t xml:space="preserve">1.85825943946838</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91323757171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109191417694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88496327400208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9242330789566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80642282962799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82998502254486</t>
+    <t xml:space="preserve">1.9132376909256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109167575836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88496315479279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92423319816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80642306804657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82998490333557</t>
   </si>
   <si>
     <t xml:space="preserve">1.79856896400452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76715314388275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354709625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86925518512726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87710893154144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281713962555</t>
+    <t xml:space="preserve">1.76715302467346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354685783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86925506591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87710916996002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281702041626</t>
   </si>
   <si>
     <t xml:space="preserve">1.86768424510956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81584763526917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83783900737762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87553822994232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84569275379181</t>
+    <t xml:space="preserve">1.81584787368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83783888816833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553834915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684361934662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84569299221039</t>
   </si>
   <si>
     <t xml:space="preserve">1.81898939609528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83626818656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8598301410675</t>
+    <t xml:space="preserve">1.83626842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85983037948608</t>
   </si>
   <si>
     <t xml:space="preserve">1.80485212802887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82056045532227</t>
+    <t xml:space="preserve">1.82056033611298</t>
   </si>
   <si>
     <t xml:space="preserve">1.81741845607758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85040533542633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88025069236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81427693367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85197627544403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84412205219269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84098052978516</t>
+    <t xml:space="preserve">1.85040557384491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88025057315826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81427681446075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85197615623474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84412252902985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84098076820374</t>
   </si>
   <si>
     <t xml:space="preserve">1.82370185852051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81113541126251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82213115692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9367995262146</t>
+    <t xml:space="preserve">1.8111355304718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8221310377121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679976463318</t>
   </si>
   <si>
     <t xml:space="preserve">1.94622445106506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95407831668854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96350300312042</t>
+    <t xml:space="preserve">1.95407843589783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.963503241539</t>
   </si>
   <si>
     <t xml:space="preserve">1.9650741815567</t>
@@ -161,61 +161,61 @@
     <t xml:space="preserve">1.99334847927094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00434422492981</t>
+    <t xml:space="preserve">2.00434398651123</t>
   </si>
   <si>
     <t xml:space="preserve">1.98706519603729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00905680656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02476477622986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93051636219025</t>
+    <t xml:space="preserve">2.00905656814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0247642993927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93051648139954</t>
   </si>
   <si>
     <t xml:space="preserve">1.96193242073059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93994116783142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637897491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87396717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378722667694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92231559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050944805145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656346321106</t>
+    <t xml:space="preserve">1.93994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564901828766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637909412384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87396728992462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378698825836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017516613007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9223153591156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050968647003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656334400177</t>
   </si>
   <si>
     <t xml:space="preserve">1.95509135723114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95836913585663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739916801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9354259967804</t>
+    <t xml:space="preserve">1.95836925506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739904880524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542587757111</t>
   </si>
   <si>
     <t xml:space="preserve">1.94198131561279</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">1.91084396839142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83545887470245</t>
+    <t xml:space="preserve">1.83545899391174</t>
   </si>
   <si>
     <t xml:space="preserve">1.8026829957962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84201431274414</t>
+    <t xml:space="preserve">1.84201419353485</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218145370483</t>
@@ -242,31 +242,34 @@
     <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86823523044586</t>
+    <t xml:space="preserve">1.86823511123657</t>
   </si>
   <si>
     <t xml:space="preserve">1.90756642818451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90592730045319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88462293148041</t>
+    <t xml:space="preserve">1.89281690120697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90592777729034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88462316989899</t>
   </si>
   <si>
     <t xml:space="preserve">1.90920507907867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87151277065277</t>
+    <t xml:space="preserve">1.87151265144348</t>
   </si>
   <si>
     <t xml:space="preserve">1.8977335691452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82398748397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75843501091003</t>
+    <t xml:space="preserve">1.82398760318756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75843513011932</t>
   </si>
   <si>
     <t xml:space="preserve">1.76662921905518</t>
@@ -281,55 +284,55 @@
     <t xml:space="preserve">1.75188016891479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75351905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77973961830139</t>
+    <t xml:space="preserve">1.75351893901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77973973751068</t>
   </si>
   <si>
     <t xml:space="preserve">1.75024127960205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72074270248413</t>
+    <t xml:space="preserve">1.72074282169342</t>
   </si>
   <si>
     <t xml:space="preserve">1.66993999481201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72893667221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69616079330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76007390022278</t>
+    <t xml:space="preserve">1.72893679141998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69616067409515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76007413864136</t>
   </si>
   <si>
     <t xml:space="preserve">1.70435476303101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73549199104309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73385310173035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71254861354828</t>
+    <t xml:space="preserve">1.73549211025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73385334014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71254873275757</t>
   </si>
   <si>
     <t xml:space="preserve">1.63060867786407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67157864570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66666221618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61012363433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62241458892822</t>
+    <t xml:space="preserve">1.67157876491547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66666233539581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61012375354767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62241470813751</t>
   </si>
   <si>
     <t xml:space="preserve">1.66338467597961</t>
@@ -341,55 +344,55 @@
     <t xml:space="preserve">1.64535772800446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63880264759064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62569212913513</t>
+    <t xml:space="preserve">1.63880276679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62569224834442</t>
   </si>
   <si>
     <t xml:space="preserve">1.66830110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65519082546234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6469966173172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63798332214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59865200519562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6297892332077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58308339118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59537434577942</t>
+    <t xml:space="preserve">1.65519070625305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64699673652649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63798320293427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59865212440491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62978935241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58308351039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59537446498871</t>
   </si>
   <si>
     <t xml:space="preserve">1.57898640632629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59127736091614</t>
+    <t xml:space="preserve">1.59127748012543</t>
   </si>
   <si>
     <t xml:space="preserve">1.54047453403473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56751477718353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56997287273407</t>
+    <t xml:space="preserve">1.56751465797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56997299194336</t>
   </si>
   <si>
     <t xml:space="preserve">1.56669533252716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5585013628006</t>
+    <t xml:space="preserve">1.55850124359131</t>
   </si>
   <si>
     <t xml:space="preserve">1.6027489900589</t>
@@ -398,7 +401,7 @@
     <t xml:space="preserve">1.60356843471527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60602676868439</t>
+    <t xml:space="preserve">1.6060266494751</t>
   </si>
   <si>
     <t xml:space="preserve">1.51917004585266</t>
@@ -407,13 +410,13 @@
     <t xml:space="preserve">1.5617790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54539096355438</t>
+    <t xml:space="preserve">1.54539108276367</t>
   </si>
   <si>
     <t xml:space="preserve">1.37659406661987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41264796257019</t>
+    <t xml:space="preserve">1.4126478433609</t>
   </si>
   <si>
     <t xml:space="preserve">1.39462113380432</t>
@@ -422,19 +425,19 @@
     <t xml:space="preserve">1.45771491527557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47082543373108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53391933441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61258172988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61176240444183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59783267974854</t>
+    <t xml:space="preserve">1.4708251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53391921520233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61258184909821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61176252365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59783256053925</t>
   </si>
   <si>
     <t xml:space="preserve">1.54211330413818</t>
@@ -446,28 +449,28 @@
     <t xml:space="preserve">1.5552237033844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56505644321442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56423711776733</t>
+    <t xml:space="preserve">1.56505656242371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56423723697662</t>
   </si>
   <si>
     <t xml:space="preserve">1.59291613101959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55686259269714</t>
+    <t xml:space="preserve">1.55686247348785</t>
   </si>
   <si>
     <t xml:space="preserve">1.52162826061249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54129385948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5044207572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51097619533539</t>
+    <t xml:space="preserve">1.5412939786911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50442087650299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51097595691681</t>
   </si>
   <si>
     <t xml:space="preserve">1.55112683773041</t>
@@ -479,7 +482,7 @@
     <t xml:space="preserve">1.55194616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50851762294769</t>
+    <t xml:space="preserve">1.50851774215698</t>
   </si>
   <si>
     <t xml:space="preserve">1.53228056430817</t>
@@ -491,22 +494,22 @@
     <t xml:space="preserve">1.50769853591919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50278198719025</t>
+    <t xml:space="preserve">1.50278210639954</t>
   </si>
   <si>
     <t xml:space="preserve">1.49540758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51015663146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57325065135956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58554148674011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59455502033234</t>
+    <t xml:space="preserve">1.51015675067902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57325041294098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5855416059494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59455490112305</t>
   </si>
   <si>
     <t xml:space="preserve">1.60684585571289</t>
@@ -524,7 +527,7 @@
     <t xml:space="preserve">1.57243132591248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58718049526215</t>
+    <t xml:space="preserve">1.58718025684357</t>
   </si>
   <si>
     <t xml:space="preserve">1.54621028900146</t>
@@ -545,25 +548,25 @@
     <t xml:space="preserve">1.54702973365784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53883576393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5478492975235</t>
+    <t xml:space="preserve">1.53883564472198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54784905910492</t>
   </si>
   <si>
     <t xml:space="preserve">1.55276548862457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54948806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5380163192749</t>
+    <t xml:space="preserve">1.54948794841766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53801620006561</t>
   </si>
   <si>
     <t xml:space="preserve">1.54866850376129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53637742996216</t>
+    <t xml:space="preserve">1.53637754917145</t>
   </si>
   <si>
     <t xml:space="preserve">1.53965508937836</t>
@@ -572,7 +575,7 @@
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191316604614</t>
+    <t xml:space="preserve">1.65191304683685</t>
   </si>
   <si>
     <t xml:space="preserve">1.69288313388824</t>
@@ -584,16 +587,16 @@
     <t xml:space="preserve">1.82070958614349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82890379428864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81743192672729</t>
+    <t xml:space="preserve">1.82890391349792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81743228435516</t>
   </si>
   <si>
     <t xml:space="preserve">1.81579351425171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87970650196075</t>
+    <t xml:space="preserve">1.87970674037933</t>
   </si>
   <si>
     <t xml:space="preserve">1.79448890686035</t>
@@ -602,22 +605,22 @@
     <t xml:space="preserve">1.80104410648346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72729802131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74696373939514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76335144042969</t>
+    <t xml:space="preserve">1.73876965045929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72729790210724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74696338176727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76335167884827</t>
   </si>
   <si>
     <t xml:space="preserve">1.84693050384521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81087708473206</t>
+    <t xml:space="preserve">1.81087696552277</t>
   </si>
   <si>
     <t xml:space="preserve">1.80923795700073</t>
@@ -626,7 +629,7 @@
     <t xml:space="preserve">1.81251573562622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86168015003204</t>
+    <t xml:space="preserve">1.86167991161346</t>
   </si>
   <si>
     <t xml:space="preserve">1.86495745182037</t>
@@ -635,91 +638,91 @@
     <t xml:space="preserve">1.85840213298798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87642896175385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89937257766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84856939315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92479622364044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679404258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850839138031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97107362747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822432518005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94193613529205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94364988803864</t>
+    <t xml:space="preserve">1.87642908096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89937245845795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84856951236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92479634284973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679428100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850827217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107374668121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822444438934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94193601608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94365000724792</t>
   </si>
   <si>
     <t xml:space="preserve">1.95907580852509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96764576435089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9265102148056</t>
+    <t xml:space="preserve">1.9676456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92651033401489</t>
   </si>
   <si>
     <t xml:space="preserve">1.95393395423889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93336606025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90594267845154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8939448595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8716629743576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92993831634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90080046653748</t>
+    <t xml:space="preserve">1.93336629867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90594255924225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89394474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87166309356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92993819713593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90080070495605</t>
   </si>
   <si>
     <t xml:space="preserve">1.91451239585876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88708889484406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87680506706238</t>
+    <t xml:space="preserve">1.88708865642548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87680494785309</t>
   </si>
   <si>
     <t xml:space="preserve">1.91794049739838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8853747844696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86994898319244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88880288600922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90937054157257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90251469612122</t>
+    <t xml:space="preserve">1.88537490367889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86994910240173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88880276679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90937042236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90251445770264</t>
   </si>
   <si>
     <t xml:space="preserve">1.96421778202057</t>
@@ -734,7 +737,7 @@
     <t xml:space="preserve">1.98649966716766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97964346408844</t>
+    <t xml:space="preserve">1.97964334487915</t>
   </si>
   <si>
     <t xml:space="preserve">2.12533164024353</t>
@@ -746,25 +749,25 @@
     <t xml:space="preserve">2.05677270889282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07905435562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08076810836792</t>
+    <t xml:space="preserve">2.07905459403992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08076786994934</t>
   </si>
   <si>
     <t xml:space="preserve">2.06534242630005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06020045280457</t>
+    <t xml:space="preserve">2.06020069122314</t>
   </si>
   <si>
     <t xml:space="preserve">2.07219839096069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13390159606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1081919670105</t>
+    <t xml:space="preserve">2.13390135765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10819172859192</t>
   </si>
   <si>
     <t xml:space="preserve">2.09962201118469</t>
@@ -776,7 +779,7 @@
     <t xml:space="preserve">2.03963279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06877040863037</t>
+    <t xml:space="preserve">2.06877064704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.11504769325256</t>
@@ -785,34 +788,34 @@
     <t xml:space="preserve">2.07391238212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09790778160095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11676168441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08248209953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06705665588379</t>
+    <t xml:space="preserve">2.09790802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1167619228363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08248233795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06705641746521</t>
   </si>
   <si>
     <t xml:space="preserve">2.12190365791321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10647773742676</t>
+    <t xml:space="preserve">2.10647797584534</t>
   </si>
   <si>
     <t xml:space="preserve">2.08933806419373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05163073539734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17675089836121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14247131347656</t>
+    <t xml:space="preserve">2.05163049697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17675113677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14247155189514</t>
   </si>
   <si>
     <t xml:space="preserve">2.13218760490417</t>
@@ -836,13 +839,13 @@
     <t xml:space="preserve">2.11161994934082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10133576393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15789699554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15618324279785</t>
+    <t xml:space="preserve">2.10133600234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15789723396301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15618300437927</t>
   </si>
   <si>
     <t xml:space="preserve">2.1441855430603</t>
@@ -854,10 +857,10 @@
     <t xml:space="preserve">2.14932727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13904333114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17503714561462</t>
+    <t xml:space="preserve">2.13904356956482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17503690719604</t>
   </si>
   <si>
     <t xml:space="preserve">2.15104126930237</t>
@@ -878,10 +881,10 @@
     <t xml:space="preserve">2.04820275306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07048416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0499165058136</t>
+    <t xml:space="preserve">2.07048439979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04991674423218</t>
   </si>
   <si>
     <t xml:space="preserve">2.12875962257385</t>
@@ -899,7 +902,7 @@
     <t xml:space="preserve">2.0224928855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01392292976379</t>
+    <t xml:space="preserve">2.01392316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.00535321235657</t>
@@ -908,13 +911,13 @@
     <t xml:space="preserve">2.1681809425354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18532085418701</t>
+    <t xml:space="preserve">2.18532061576843</t>
   </si>
   <si>
     <t xml:space="preserve">2.29672932624817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33100891113281</t>
+    <t xml:space="preserve">2.33100914955139</t>
   </si>
   <si>
     <t xml:space="preserve">2.32243919372559</t>
@@ -926,25 +929,25 @@
     <t xml:space="preserve">2.44241738319397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49383664131165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46812725067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47669696807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48526692390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53668618202209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57953572273254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59667539596558</t>
+    <t xml:space="preserve">2.49383687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46812701225281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47669720649719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48526668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53668642044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57953548431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.596675157547</t>
   </si>
   <si>
     <t xml:space="preserve">2.61381506919861</t>
@@ -965,7 +968,7 @@
     <t xml:space="preserve">2.61655139923096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52694344520569</t>
+    <t xml:space="preserve">2.52694368362427</t>
   </si>
   <si>
     <t xml:space="preserve">2.437335729599</t>
@@ -974,19 +977,19 @@
     <t xml:space="preserve">2.46421790122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50006127357483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45525717735291</t>
+    <t xml:space="preserve">2.50006103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45525741577148</t>
   </si>
   <si>
     <t xml:space="preserve">2.54486513137817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57174754142761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51798272132874</t>
+    <t xml:space="preserve">2.57174730300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51798295974731</t>
   </si>
   <si>
     <t xml:space="preserve">2.56278681755066</t>
@@ -995,16 +998,16 @@
     <t xml:space="preserve">2.53590416908264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49110054969788</t>
+    <t xml:space="preserve">2.4911003112793</t>
   </si>
   <si>
     <t xml:space="preserve">2.48213958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50902199745178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47317886352539</t>
+    <t xml:space="preserve">2.5090217590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47317862510681</t>
   </si>
   <si>
     <t xml:space="preserve">2.78680658340454</t>
@@ -1013,19 +1016,19 @@
     <t xml:space="preserve">2.7599241733551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77784585952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74200248718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76888513565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71512031555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75096321105957</t>
+    <t xml:space="preserve">2.77784562110901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7420027256012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76888489723206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71512007713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75096344947815</t>
   </si>
   <si>
     <t xml:space="preserve">2.67031621932983</t>
@@ -1037,13 +1040,13 @@
     <t xml:space="preserve">2.65239477157593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68823790550232</t>
+    <t xml:space="preserve">2.68823766708374</t>
   </si>
   <si>
     <t xml:space="preserve">2.73304176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69719886779785</t>
+    <t xml:space="preserve">2.69719862937927</t>
   </si>
   <si>
     <t xml:space="preserve">2.67927694320679</t>
@@ -1052,25 +1055,25 @@
     <t xml:space="preserve">2.84953236579895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86745381355286</t>
+    <t xml:space="preserve">2.86745357513428</t>
   </si>
   <si>
     <t xml:space="preserve">2.83161067962646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64343404769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62551259994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58070850372314</t>
+    <t xml:space="preserve">2.6434338092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62551236152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58070826530457</t>
   </si>
   <si>
     <t xml:space="preserve">2.607590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41941404342651</t>
+    <t xml:space="preserve">2.41941428184509</t>
   </si>
   <si>
     <t xml:space="preserve">2.66135549545288</t>
@@ -1079,7 +1082,7 @@
     <t xml:space="preserve">2.81368899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.840571641922</t>
+    <t xml:space="preserve">2.84057140350342</t>
   </si>
   <si>
     <t xml:space="preserve">2.93914008140564</t>
@@ -1094,37 +1097,37 @@
     <t xml:space="preserve">2.80472826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90329694747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12731671333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16315960884094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13627743721008</t>
+    <t xml:space="preserve">2.90329670906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12731647491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16315984725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13627767562866</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004225730896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25276780128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26172852516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28861093521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29757165908813</t>
+    <t xml:space="preserve">3.25276803970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26172876358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28861117362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29757189750671</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33341479301453</t>
+    <t xml:space="preserve">3.33341503143311</t>
   </si>
   <si>
     <t xml:space="preserve">3.34237575531006</t>
@@ -1139,10 +1142,10 @@
     <t xml:space="preserve">3.40510129928589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41406202316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36925792694092</t>
+    <t xml:space="preserve">3.41406178474426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3692581653595</t>
   </si>
   <si>
     <t xml:space="preserve">3.37821888923645</t>
@@ -1154,7 +1157,7 @@
     <t xml:space="preserve">3.4857485294342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47678756713867</t>
+    <t xml:space="preserve">3.47678780555725</t>
   </si>
   <si>
     <t xml:space="preserve">3.49470925331116</t>
@@ -1169,13 +1172,13 @@
     <t xml:space="preserve">3.53055238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59327816963196</t>
+    <t xml:space="preserve">3.59327793121338</t>
   </si>
   <si>
     <t xml:space="preserve">3.55743479728699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5215916633606</t>
+    <t xml:space="preserve">3.52159142494202</t>
   </si>
   <si>
     <t xml:space="preserve">3.51263093948364</t>
@@ -1202,19 +1205,19 @@
     <t xml:space="preserve">3.6918466091156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70976805686951</t>
+    <t xml:space="preserve">3.70976781845093</t>
   </si>
   <si>
     <t xml:space="preserve">3.68288588523865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7635326385498</t>
+    <t xml:space="preserve">3.76353311538696</t>
   </si>
   <si>
     <t xml:space="preserve">3.78145432472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80833721160889</t>
+    <t xml:space="preserve">3.80833697319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.79041528701782</t>
@@ -1223,27 +1226,24 @@
     <t xml:space="preserve">3.95170950889587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96067070960999</t>
+    <t xml:space="preserve">3.96067023277283</t>
   </si>
   <si>
     <t xml:space="preserve">3.97005581855774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00759744644165</t>
+    <t xml:space="preserve">4.00759792327881</t>
   </si>
   <si>
     <t xml:space="preserve">4.0920672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81988859176636</t>
+    <t xml:space="preserve">3.81988835334778</t>
   </si>
   <si>
     <t xml:space="preserve">3.87620115280151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96067023277283</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.02636861801147</t>
   </si>
   <si>
@@ -1259,40 +1259,40 @@
     <t xml:space="preserve">4.03575468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9982123374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97944116592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85743045806885</t>
+    <t xml:space="preserve">3.99821257591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97944092750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85743021965027</t>
   </si>
   <si>
     <t xml:space="preserve">3.84804463386536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81050276756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74480438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89497208595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.941899061203</t>
+    <t xml:space="preserve">3.81050252914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7448046207428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89497232437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94189953804016</t>
   </si>
   <si>
     <t xml:space="preserve">3.8668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93251419067383</t>
+    <t xml:space="preserve">3.93251395225525</t>
   </si>
   <si>
     <t xml:space="preserve">4.08268165588379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11083841323853</t>
+    <t xml:space="preserve">4.11083793640137</t>
   </si>
   <si>
     <t xml:space="preserve">4.12022304534912</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">4.18592166900635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1953067779541</t>
+    <t xml:space="preserve">4.19530725479126</t>
   </si>
   <si>
     <t xml:space="preserve">4.20469284057617</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">4.28916215896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26100540161133</t>
+    <t xml:space="preserve">4.26100587844849</t>
   </si>
   <si>
     <t xml:space="preserve">4.2703914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34547519683838</t>
+    <t xml:space="preserve">4.34547472000122</t>
   </si>
   <si>
     <t xml:space="preserve">4.36424589157104</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">4.50502824783325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49564218521118</t>
+    <t xml:space="preserve">4.49564266204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.43932962417603</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">4.5519552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54256963729858</t>
+    <t xml:space="preserve">4.54257011413574</t>
   </si>
   <si>
     <t xml:space="preserve">4.48625707626343</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">4.40178775787354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44871473312378</t>
+    <t xml:space="preserve">4.44871520996094</t>
   </si>
   <si>
     <t xml:space="preserve">4.42994403839111</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">4.41117334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39240217208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2422342300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30793285369873</t>
+    <t xml:space="preserve">4.39240169525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24223470687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30793333053589</t>
   </si>
   <si>
     <t xml:space="preserve">4.17653608322144</t>
@@ -1394,28 +1394,28 @@
     <t xml:space="preserve">4.62703895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61765384674072</t>
+    <t xml:space="preserve">4.61765336990356</t>
   </si>
   <si>
     <t xml:space="preserve">4.51441335678101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57072639465332</t>
+    <t xml:space="preserve">4.57072591781616</t>
   </si>
   <si>
     <t xml:space="preserve">4.67396640777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80536317825317</t>
+    <t xml:space="preserve">4.80536270141602</t>
   </si>
   <si>
     <t xml:space="preserve">4.78659200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86167573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84290456771851</t>
+    <t xml:space="preserve">4.86167621612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84290504455566</t>
   </si>
   <si>
     <t xml:space="preserve">4.89921760559082</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">4.5988826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53318452835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58011198043823</t>
+    <t xml:space="preserve">4.53318405151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58011150360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.6927375793457</t>
@@ -1439,16 +1439,16 @@
     <t xml:space="preserve">4.74905014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73027896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71150875091553</t>
+    <t xml:space="preserve">4.73027944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71150827407837</t>
   </si>
   <si>
     <t xml:space="preserve">4.76782131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95553064346313</t>
+    <t xml:space="preserve">4.95553112030029</t>
   </si>
   <si>
     <t xml:space="preserve">4.88044691085815</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">4.91798877716064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99307298660278</t>
+    <t xml:space="preserve">4.99307250976562</t>
   </si>
   <si>
     <t xml:space="preserve">4.93675994873047</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">6.60737419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28826761245728</t>
+    <t xml:space="preserve">6.28826808929443</t>
   </si>
   <si>
     <t xml:space="preserve">6.1568717956543</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">5.96916246414185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7063684463501</t>
+    <t xml:space="preserve">5.70636892318726</t>
   </si>
   <si>
     <t xml:space="preserve">5.53743028640747</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">5.87530755996704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66882705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68759775161743</t>
+    <t xml:space="preserve">5.66882658004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68759727478027</t>
   </si>
   <si>
     <t xml:space="preserve">5.83776521682739</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59374332427979</t>
+    <t xml:space="preserve">5.59374284744263</t>
   </si>
   <si>
     <t xml:space="preserve">5.38726234436035</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">5.10569858551025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68335151672363</t>
+    <t xml:space="preserve">4.68335199356079</t>
   </si>
   <si>
     <t xml:space="preserve">4.14837980270386</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">3.62279319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55709505081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37877106666565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50078201293945</t>
+    <t xml:space="preserve">3.55709481239319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37877082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50078225135803</t>
   </si>
   <si>
     <t xml:space="preserve">3.5664803981781</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">3.75418996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70726275444031</t>
+    <t xml:space="preserve">3.70726251602173</t>
   </si>
   <si>
     <t xml:space="preserve">3.71664810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83865928649902</t>
+    <t xml:space="preserve">3.8386595249176</t>
   </si>
   <si>
     <t xml:space="preserve">4.25162029266357</t>
@@ -1580,25 +1580,25 @@
     <t xml:space="preserve">4.12960910797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16715097427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05452489852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76357579231262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66972088813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65094971656799</t>
+    <t xml:space="preserve">4.16715049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05452537536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76357555389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66972064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65094995498657</t>
   </si>
   <si>
     <t xml:space="preserve">3.66033530235291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95128488540649</t>
+    <t xml:space="preserve">3.95128512382507</t>
   </si>
   <si>
     <t xml:space="preserve">4.29854726791382</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">4.31731843948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15776538848877</t>
+    <t xml:space="preserve">4.15776491165161</t>
   </si>
   <si>
     <t xml:space="preserve">4.10145235061646</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">4.13899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88558650016785</t>
+    <t xml:space="preserve">3.88558626174927</t>
   </si>
   <si>
     <t xml:space="preserve">4.32670402526855</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">4.27977657318115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91374325752258</t>
+    <t xml:space="preserve">3.913743019104</t>
   </si>
   <si>
     <t xml:space="preserve">3.92312836647034</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">3.49139666557312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67910599708557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3881561756134</t>
+    <t xml:space="preserve">3.67910623550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38815641403198</t>
   </si>
   <si>
     <t xml:space="preserve">3.35999989509583</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">3.34122896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20044684410095</t>
+    <t xml:space="preserve">3.20044708251953</t>
   </si>
   <si>
     <t xml:space="preserve">3.24737429618835</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">3.47262573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57586598396301</t>
+    <t xml:space="preserve">3.57586574554443</t>
   </si>
   <si>
     <t xml:space="preserve">3.73541903495789</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">3.68849158287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72603344917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52893877029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63217854499817</t>
+    <t xml:space="preserve">3.72603368759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52893853187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63217878341675</t>
   </si>
   <si>
     <t xml:space="preserve">3.51016759872437</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">3.58525133132935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53832387924194</t>
+    <t xml:space="preserve">3.53832411766052</t>
   </si>
   <si>
     <t xml:space="preserve">3.80111742019653</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">3.48201107978821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46324038505554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44446921348572</t>
+    <t xml:space="preserve">3.46324014663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4444694519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.42569851875305</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">3.41631293296814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754176139832</t>
+    <t xml:space="preserve">3.39754199981689</t>
   </si>
   <si>
     <t xml:space="preserve">3.21921801567078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19106149673462</t>
+    <t xml:space="preserve">3.1910617351532</t>
   </si>
   <si>
     <t xml:space="preserve">3.17229056358337</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">3.23798894882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14413380622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25675988197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36938548088074</t>
+    <t xml:space="preserve">3.14413404464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25675964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36938524246216</t>
   </si>
   <si>
     <t xml:space="preserve">3.15351939201355</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">3.18167614936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29430150985718</t>
+    <t xml:space="preserve">3.29430174827576</t>
   </si>
   <si>
     <t xml:space="preserve">3.2661452293396</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">3.12536311149597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04089403152466</t>
+    <t xml:space="preserve">3.04089379310608</t>
   </si>
   <si>
     <t xml:space="preserve">3.05027914047241</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">2.93765377998352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95642471313477</t>
+    <t xml:space="preserve">2.95642447471619</t>
   </si>
   <si>
     <t xml:space="preserve">3.03150844573975</t>
@@ -1805,19 +1805,19 @@
     <t xml:space="preserve">3.02212285995483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92826819419861</t>
+    <t xml:space="preserve">2.92826795578003</t>
   </si>
   <si>
     <t xml:space="preserve">2.94703912734985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90011143684387</t>
+    <t xml:space="preserve">2.90011167526245</t>
   </si>
   <si>
     <t xml:space="preserve">2.97519564628601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27553081512451</t>
+    <t xml:space="preserve">3.27553057670593</t>
   </si>
   <si>
     <t xml:space="preserve">3.33184361457825</t>
@@ -6254,7 +6254,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -6280,7 +6280,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -6306,7 +6306,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -6332,7 +6332,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G139" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -6358,7 +6358,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -6384,7 +6384,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -6436,7 +6436,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G143" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -6462,7 +6462,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G144" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -6488,7 +6488,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -6514,7 +6514,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -6540,7 +6540,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -6566,7 +6566,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G148" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -6592,7 +6592,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -6618,7 +6618,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G150" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -6644,7 +6644,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G151" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -6670,7 +6670,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -6696,7 +6696,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G153" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -6722,7 +6722,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G154" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -6748,7 +6748,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G155" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -6774,7 +6774,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -6800,7 +6800,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -6826,7 +6826,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -6852,7 +6852,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -6878,7 +6878,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G160" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -6904,7 +6904,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G161" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -6930,7 +6930,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G162" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -6956,7 +6956,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G163" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -6982,7 +6982,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G164" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -7008,7 +7008,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G165" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -7034,7 +7034,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G166" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7060,7 +7060,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G167" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7086,7 +7086,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G168" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7112,7 +7112,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G169" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7138,7 +7138,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G170" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7164,7 +7164,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G171" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7190,7 +7190,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7216,7 +7216,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7242,7 +7242,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G174" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7268,7 +7268,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7294,7 +7294,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G176" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7320,7 +7320,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G177" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7346,7 +7346,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G178" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7372,7 +7372,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G179" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7398,7 +7398,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G180" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7424,7 +7424,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G181" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7450,7 +7450,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G182" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7476,7 +7476,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G183" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7502,7 +7502,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G184" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -7528,7 +7528,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G185" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7554,7 +7554,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G186" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7580,7 +7580,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G187" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7606,7 +7606,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G188" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7632,7 +7632,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G189" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7658,7 +7658,7 @@
         <v>2</v>
       </c>
       <c r="G190" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7684,7 +7684,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G191" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7710,7 +7710,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G192" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7736,7 +7736,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G193" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7762,7 +7762,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G194" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -7788,7 +7788,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G195" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -7814,7 +7814,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G196" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -7840,7 +7840,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -7866,7 +7866,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -7892,7 +7892,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -7918,7 +7918,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -7944,7 +7944,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -7970,7 +7970,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -7996,7 +7996,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8022,7 +8022,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8048,7 +8048,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8074,7 +8074,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G206" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8100,7 +8100,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G207" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8126,7 +8126,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8152,7 +8152,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G209" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8178,7 +8178,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8204,7 +8204,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G211" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8230,7 +8230,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G212" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8256,7 +8256,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G213" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8282,7 +8282,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G214" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8308,7 +8308,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8334,7 +8334,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G216" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8360,7 +8360,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8386,7 +8386,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8412,7 +8412,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G219" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8438,7 +8438,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G220" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8464,7 +8464,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G221" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8490,7 +8490,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G222" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8516,7 +8516,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G223" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8542,7 +8542,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G224" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8568,7 +8568,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8594,7 +8594,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G226" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8620,7 +8620,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8646,7 +8646,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8672,7 +8672,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G229" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8698,7 +8698,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8724,7 +8724,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G231" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8750,7 +8750,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G232" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8776,7 +8776,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G233" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8802,7 +8802,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G234" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -8828,7 +8828,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G235" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -8854,7 +8854,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G236" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -8880,7 +8880,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G237" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -8906,7 +8906,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G238" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -8932,7 +8932,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G239" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -8958,7 +8958,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G240" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -8984,7 +8984,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9010,7 +9010,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9036,7 +9036,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9062,7 +9062,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G244" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9088,7 +9088,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9114,7 +9114,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G246" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9140,7 +9140,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G247" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9166,7 +9166,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G248" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9192,7 +9192,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G249" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9218,7 +9218,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G250" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9244,7 +9244,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9270,7 +9270,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G252" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9296,7 +9296,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G253" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9322,7 +9322,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G254" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9348,7 +9348,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9374,7 +9374,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G256" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9400,7 +9400,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G257" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9426,7 +9426,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G258" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9452,7 +9452,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G259" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9478,7 +9478,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9504,7 +9504,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G261" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9530,7 +9530,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G262" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9556,7 +9556,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9582,7 +9582,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G264" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9608,7 +9608,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G265" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9634,7 +9634,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G266" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9660,7 +9660,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G267" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9686,7 +9686,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G268" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9712,7 +9712,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9738,7 +9738,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G270" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9764,7 +9764,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G271" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -9790,7 +9790,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -9816,7 +9816,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9842,7 +9842,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G274" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -9868,7 +9868,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G275" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -9894,7 +9894,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G276" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9920,7 +9920,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G277" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9946,7 +9946,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G278" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -9972,7 +9972,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G279" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -9998,7 +9998,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G280" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10024,7 +10024,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G281" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10050,7 +10050,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10076,7 +10076,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G283" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10102,7 +10102,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G284" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10128,7 +10128,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G285" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10154,7 +10154,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G286" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10180,7 +10180,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G287" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10206,7 +10206,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10232,7 +10232,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G289" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10258,7 +10258,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G290" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10284,7 +10284,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G291" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10310,7 +10310,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10336,7 +10336,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G293" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10362,7 +10362,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G294" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10388,7 +10388,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G295" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10414,7 +10414,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G296" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10440,7 +10440,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G297" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10466,7 +10466,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G298" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10492,7 +10492,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10518,7 +10518,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G300" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10544,7 +10544,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G301" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10570,7 +10570,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G302" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10596,7 +10596,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10622,7 +10622,7 @@
         <v>1.875</v>
       </c>
       <c r="G304" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10648,7 +10648,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G305" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10674,7 +10674,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G306" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10700,7 +10700,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G307" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10726,7 +10726,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G308" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10752,7 +10752,7 @@
         <v>2</v>
       </c>
       <c r="G309" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -10778,7 +10778,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10804,7 +10804,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -10830,7 +10830,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -10856,7 +10856,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G313" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10882,7 +10882,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G314" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -10908,7 +10908,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10934,7 +10934,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10960,7 +10960,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G317" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11012,7 +11012,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11038,7 +11038,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11064,7 +11064,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11090,7 +11090,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11116,7 +11116,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11142,7 +11142,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11168,7 +11168,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11220,7 +11220,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G327" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11246,7 +11246,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11272,7 +11272,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11298,7 +11298,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11324,7 +11324,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11350,7 +11350,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G332" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11376,7 +11376,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11402,7 +11402,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11428,7 +11428,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G335" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11454,7 +11454,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11558,7 +11558,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11584,7 +11584,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G341" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11610,7 +11610,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11636,7 +11636,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11662,7 +11662,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G344" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11714,7 +11714,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G346" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11740,7 +11740,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G347" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11766,7 +11766,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -11792,7 +11792,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G349" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -11818,7 +11818,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -11870,7 +11870,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11896,7 +11896,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G353" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11948,7 +11948,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G355" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11974,7 +11974,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12000,7 +12000,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G357" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12026,7 +12026,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12052,7 +12052,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12078,7 +12078,7 @@
         <v>2.25</v>
       </c>
       <c r="G360" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12104,7 +12104,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12130,7 +12130,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12156,7 +12156,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G363" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12182,7 +12182,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G364" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12208,7 +12208,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12234,7 +12234,7 @@
         <v>2.25</v>
       </c>
       <c r="G366" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12260,7 +12260,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12286,7 +12286,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12312,7 +12312,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12338,7 +12338,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12364,7 +12364,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12390,7 +12390,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12416,7 +12416,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G373" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12442,7 +12442,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G374" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12468,7 +12468,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G375" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12494,7 +12494,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G376" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12520,7 +12520,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G377" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12546,7 +12546,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12572,7 +12572,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12598,7 +12598,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G380" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12624,7 +12624,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G381" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12650,7 +12650,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G382" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12676,7 +12676,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12702,7 +12702,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G384" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12728,7 +12728,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G385" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12754,7 +12754,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12780,7 +12780,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G387" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12806,7 +12806,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G388" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -12832,7 +12832,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G389" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -12858,7 +12858,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -12884,7 +12884,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G391" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -12910,7 +12910,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -12936,7 +12936,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G393" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -12962,7 +12962,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -12988,7 +12988,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G395" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13014,7 +13014,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13040,7 +13040,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13066,7 +13066,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13092,7 +13092,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G399" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13118,7 +13118,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G400" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13144,7 +13144,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G401" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13170,7 +13170,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13196,7 +13196,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G403" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13222,7 +13222,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13248,7 +13248,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G405" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13274,7 +13274,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13300,7 +13300,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13326,7 +13326,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13352,7 +13352,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G409" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13378,7 +13378,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G410" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13404,7 +13404,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G411" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13430,7 +13430,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13456,7 +13456,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G413" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13482,7 +13482,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G414" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13508,7 +13508,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G415" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13534,7 +13534,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G416" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13560,7 +13560,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G417" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13586,7 +13586,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G418" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13612,7 +13612,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G419" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13638,7 +13638,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G420" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13664,7 +13664,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G421" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13690,7 +13690,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G422" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13716,7 +13716,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13742,7 +13742,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G424" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13768,7 +13768,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G425" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13794,7 +13794,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G426" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -13820,7 +13820,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G427" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -13846,7 +13846,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G428" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -13872,7 +13872,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G429" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -13898,7 +13898,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G430" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -13924,7 +13924,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G431" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -13950,7 +13950,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -13976,7 +13976,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G433" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14002,7 +14002,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14028,7 +14028,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G435" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14054,7 +14054,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G436" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14080,7 +14080,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G437" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14106,7 +14106,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G438" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14132,7 +14132,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G439" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14158,7 +14158,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G440" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14184,7 +14184,7 @@
         <v>2.5</v>
       </c>
       <c r="G441" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14210,7 +14210,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G442" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14236,7 +14236,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G443" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14262,7 +14262,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G444" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14288,7 +14288,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G445" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14314,7 +14314,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14340,7 +14340,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G447" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14366,7 +14366,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G448" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14392,7 +14392,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G449" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14418,7 +14418,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G450" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14444,7 +14444,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G451" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14470,7 +14470,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G452" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14496,7 +14496,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G453" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14522,7 +14522,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G454" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14548,7 +14548,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G455" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14574,7 +14574,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G456" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14600,7 +14600,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G457" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14626,7 +14626,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G458" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14652,7 +14652,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G459" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14678,7 +14678,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G460" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14704,7 +14704,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G461" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14730,7 +14730,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G462" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14756,7 +14756,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G463" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14782,7 +14782,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G464" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -14808,7 +14808,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -14834,7 +14834,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G466" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -14860,7 +14860,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G467" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -14886,7 +14886,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G468" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -14912,7 +14912,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G469" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -14938,7 +14938,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G470" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -14964,7 +14964,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G471" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -14990,7 +14990,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15016,7 +15016,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G473" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15042,7 +15042,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15068,7 +15068,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G475" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15094,7 +15094,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G476" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15120,7 +15120,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G477" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15146,7 +15146,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G478" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15172,7 +15172,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G479" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15198,7 +15198,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G480" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15224,7 +15224,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15250,7 +15250,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G482" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15276,7 +15276,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G483" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15302,7 +15302,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G484" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15328,7 +15328,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G485" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15354,7 +15354,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G486" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15380,7 +15380,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15406,7 +15406,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G488" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15432,7 +15432,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G489" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15458,7 +15458,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G490" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15484,7 +15484,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G491" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15510,7 +15510,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15536,7 +15536,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G493" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15562,7 +15562,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G494" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15588,7 +15588,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15614,7 +15614,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G496" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15640,7 +15640,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G497" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15666,7 +15666,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G498" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15692,7 +15692,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G499" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15718,7 +15718,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G500" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15744,7 +15744,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G501" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15770,7 +15770,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G502" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15796,7 +15796,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G503" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -15822,7 +15822,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G504" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -15848,7 +15848,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G505" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -15874,7 +15874,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G506" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -15900,7 +15900,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G507" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -15926,7 +15926,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G508" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -15952,7 +15952,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G509" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -15978,7 +15978,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G510" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16004,7 +16004,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G511" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16030,7 +16030,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G512" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16056,7 +16056,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G513" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16082,7 +16082,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G514" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16108,7 +16108,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G515" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16134,7 +16134,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G516" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16160,7 +16160,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G517" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16186,7 +16186,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G518" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16212,7 +16212,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G519" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16238,7 +16238,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G520" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16264,7 +16264,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G521" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16290,7 +16290,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16316,7 +16316,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G523" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16342,7 +16342,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G524" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16368,7 +16368,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G525" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16394,7 +16394,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G526" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16420,7 +16420,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G527" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16446,7 +16446,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G528" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16472,7 +16472,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G529" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16498,7 +16498,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16524,7 +16524,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G531" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16550,7 +16550,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G532" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16576,7 +16576,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G533" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16602,7 +16602,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G534" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16628,7 +16628,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G535" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16654,7 +16654,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G536" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16680,7 +16680,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G537" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16706,7 +16706,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G538" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16732,7 +16732,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G539" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16758,7 +16758,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G540" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16784,7 +16784,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G541" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -16810,7 +16810,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G542" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -16836,7 +16836,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G543" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -16862,7 +16862,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G544" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -16888,7 +16888,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G545" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16914,7 +16914,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G546" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16940,7 +16940,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G547" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16966,7 +16966,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G548" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -16992,7 +16992,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G549" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17018,7 +17018,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G550" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17044,7 +17044,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G551" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17070,7 +17070,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G552" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17096,7 +17096,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G553" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17122,7 +17122,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G554" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17148,7 +17148,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17174,7 +17174,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G556" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17200,7 +17200,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G557" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17226,7 +17226,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17252,7 +17252,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17278,7 +17278,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17304,7 +17304,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17330,7 +17330,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G562" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17356,7 +17356,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G563" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17382,7 +17382,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17408,7 +17408,7 @@
         <v>2.5</v>
       </c>
       <c r="G565" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17434,7 +17434,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17460,7 +17460,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G567" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17486,7 +17486,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G568" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17512,7 +17512,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G569" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17538,7 +17538,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G570" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17564,7 +17564,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G571" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17590,7 +17590,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G572" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17616,7 +17616,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G573" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17642,7 +17642,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G574" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17668,7 +17668,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G575" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17694,7 +17694,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17720,7 +17720,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G577" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17746,7 +17746,7 @@
         <v>2.5</v>
       </c>
       <c r="G578" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17772,7 +17772,7 @@
         <v>2.5</v>
       </c>
       <c r="G579" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17798,7 +17798,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G580" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -17824,7 +17824,7 @@
         <v>2.5</v>
       </c>
       <c r="G581" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -17850,7 +17850,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -17876,7 +17876,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -17902,7 +17902,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -17928,7 +17928,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -17954,7 +17954,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -17980,7 +17980,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G587" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18006,7 +18006,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18032,7 +18032,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G589" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18058,7 +18058,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G590" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18084,7 +18084,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G591" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18110,7 +18110,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G592" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18136,7 +18136,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G593" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18162,7 +18162,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G594" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18188,7 +18188,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G595" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18214,7 +18214,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18240,7 +18240,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18266,7 +18266,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G598" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18292,7 +18292,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G599" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18318,7 +18318,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G600" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18344,7 +18344,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18370,7 +18370,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18396,7 +18396,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G603" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18422,7 +18422,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G604" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18448,7 +18448,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G605" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18474,7 +18474,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G606" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18500,7 +18500,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G607" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18526,7 +18526,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G608" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18552,7 +18552,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G609" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18578,7 +18578,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G610" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18604,7 +18604,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G611" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18630,7 +18630,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18656,7 +18656,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G613" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18682,7 +18682,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G614" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18708,7 +18708,7 @@
         <v>2.75</v>
       </c>
       <c r="G615" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18734,7 +18734,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G616" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18760,7 +18760,7 @@
         <v>2.75</v>
       </c>
       <c r="G617" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18786,7 +18786,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G618" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18812,7 +18812,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G619" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18838,7 +18838,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G620" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18864,7 +18864,7 @@
         <v>2.75</v>
       </c>
       <c r="G621" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18890,7 +18890,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G622" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18916,7 +18916,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18942,7 +18942,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18968,7 +18968,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -18994,7 +18994,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19020,7 +19020,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G627" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19046,7 +19046,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G628" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19072,7 +19072,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G629" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19098,7 +19098,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G630" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19124,7 +19124,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19150,7 +19150,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G632" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19176,7 +19176,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19202,7 +19202,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G634" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19228,7 +19228,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G635" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19254,7 +19254,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G636" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19280,7 +19280,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19306,7 +19306,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19332,7 +19332,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19358,7 +19358,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19384,7 +19384,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19410,7 +19410,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19436,7 +19436,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19462,7 +19462,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19488,7 +19488,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19514,7 +19514,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19540,7 +19540,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G647" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19566,7 +19566,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G648" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19592,7 +19592,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G649" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19618,7 +19618,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G650" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19644,7 +19644,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G651" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19670,7 +19670,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G652" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19696,7 +19696,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G653" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19722,7 +19722,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G654" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19748,7 +19748,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19774,7 +19774,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G656" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19800,7 +19800,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -19826,7 +19826,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G658" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -19852,7 +19852,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19878,7 +19878,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G660" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19904,7 +19904,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G661" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19930,7 +19930,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G662" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19956,7 +19956,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G663" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19982,7 +19982,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G664" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20008,7 +20008,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20034,7 +20034,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20060,7 +20060,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20086,7 +20086,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20112,7 +20112,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G669" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20138,7 +20138,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G670" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20164,7 +20164,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20190,7 +20190,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G672" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20216,7 +20216,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G673" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20242,7 +20242,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20268,7 +20268,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20294,7 +20294,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G676" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20320,7 +20320,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20346,7 +20346,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20372,7 +20372,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G679" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20398,7 +20398,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20424,7 +20424,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G681" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20450,7 +20450,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20476,7 +20476,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20502,7 +20502,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20528,7 +20528,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20554,7 +20554,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20580,7 +20580,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20606,7 +20606,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20632,7 +20632,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20658,7 +20658,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20684,7 +20684,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20710,7 +20710,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G692" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20736,7 +20736,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20762,7 +20762,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20788,7 +20788,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20814,7 +20814,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20840,7 +20840,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20866,7 +20866,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -20892,7 +20892,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -20918,7 +20918,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -20944,7 +20944,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -20970,7 +20970,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20996,7 +20996,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21022,7 +21022,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21048,7 +21048,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21074,7 +21074,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21100,7 +21100,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21126,7 +21126,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G708" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21152,7 +21152,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G709" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21178,7 +21178,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G710" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21204,7 +21204,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G711" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21230,7 +21230,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21256,7 +21256,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G713" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21282,7 +21282,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G714" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21308,7 +21308,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G715" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21334,7 +21334,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G716" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21360,7 +21360,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G717" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21386,7 +21386,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21412,7 +21412,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G719" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21438,7 +21438,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G720" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21464,7 +21464,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G721" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21490,7 +21490,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G722" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21516,7 +21516,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G723" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21542,7 +21542,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G724" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21568,7 +21568,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G725" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21594,7 +21594,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G726" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21620,7 +21620,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G727" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21646,7 +21646,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21672,7 +21672,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G729" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21698,7 +21698,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21724,7 +21724,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G731" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21750,7 +21750,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G732" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21776,7 +21776,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G733" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21802,7 +21802,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G734" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21828,7 +21828,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G735" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21854,7 +21854,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G736" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21880,7 +21880,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G737" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21906,7 +21906,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21932,7 +21932,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G739" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21958,7 +21958,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21984,7 +21984,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G741" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22010,7 +22010,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G742" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22036,7 +22036,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G743" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22062,7 +22062,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G744" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22088,7 +22088,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G745" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22114,7 +22114,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22140,7 +22140,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22166,7 +22166,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22192,7 +22192,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G749" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22218,7 +22218,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22244,7 +22244,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22270,7 +22270,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22296,7 +22296,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22322,7 +22322,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22348,7 +22348,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22374,7 +22374,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22400,7 +22400,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22426,7 +22426,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22452,7 +22452,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G759" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22478,7 +22478,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G760" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22504,7 +22504,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G761" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22530,7 +22530,7 @@
         <v>2.75</v>
       </c>
       <c r="G762" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22556,7 +22556,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22582,7 +22582,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22608,7 +22608,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22634,7 +22634,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G766" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22660,7 +22660,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22686,7 +22686,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G768" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22712,7 +22712,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22738,7 +22738,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22764,7 +22764,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22790,7 +22790,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22816,7 +22816,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22842,7 +22842,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22868,7 +22868,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22894,7 +22894,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22920,7 +22920,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22946,7 +22946,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22972,7 +22972,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G779" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22998,7 +22998,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23024,7 +23024,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23050,7 +23050,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G782" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23076,7 +23076,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23102,7 +23102,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G784" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23128,7 +23128,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G785" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23154,7 +23154,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23180,7 +23180,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G787" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23206,7 +23206,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G788" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23232,7 +23232,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G789" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23258,7 +23258,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23284,7 +23284,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G791" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23310,7 +23310,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G792" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23336,7 +23336,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G793" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23362,7 +23362,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23388,7 +23388,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23414,7 +23414,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23440,7 +23440,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G797" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23466,7 +23466,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G798" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23492,7 +23492,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23518,7 +23518,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G800" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23544,7 +23544,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23570,7 +23570,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G802" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23596,7 +23596,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23622,7 +23622,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G804" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23648,7 +23648,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23674,7 +23674,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23700,7 +23700,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G807" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23726,7 +23726,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G808" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23752,7 +23752,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G809" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23778,7 +23778,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G810" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23804,7 +23804,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G811" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23830,7 +23830,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23856,7 +23856,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G813" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23882,7 +23882,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G814" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23908,7 +23908,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23934,7 +23934,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G816" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23960,7 +23960,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23986,7 +23986,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G818" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24012,7 +24012,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24038,7 +24038,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G820" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24064,7 +24064,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G821" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24090,7 +24090,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24116,7 +24116,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G823" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24142,7 +24142,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G824" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24168,7 +24168,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G825" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24194,7 +24194,7 @@
         <v>4</v>
       </c>
       <c r="G826" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24220,7 +24220,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G827" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24246,7 +24246,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G828" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24272,7 +24272,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G829" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24298,7 +24298,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G830" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24324,7 +24324,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24350,7 +24350,7 @@
         <v>4</v>
       </c>
       <c r="G832" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24376,7 +24376,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24402,7 +24402,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24428,7 +24428,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24454,7 +24454,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G836" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24480,7 +24480,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24506,7 +24506,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24532,7 +24532,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G839" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24558,7 +24558,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24584,7 +24584,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G841" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24610,7 +24610,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G842" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24636,7 +24636,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24662,7 +24662,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G844" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24688,7 +24688,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G845" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24714,7 +24714,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24740,7 +24740,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24766,7 +24766,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24792,7 +24792,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24818,7 +24818,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G850" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24844,7 +24844,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24870,7 +24870,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24896,7 +24896,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G853" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24922,7 +24922,7 @@
         <v>4.25</v>
       </c>
       <c r="G854" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24948,7 +24948,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24974,7 +24974,7 @@
         <v>4.25</v>
       </c>
       <c r="G856" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25000,7 +25000,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G857" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25026,7 +25026,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G858" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25052,7 +25052,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G859" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25078,7 +25078,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25104,7 +25104,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G861" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25130,7 +25130,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G862" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25156,7 +25156,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G863" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25182,7 +25182,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G864" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25208,7 +25208,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G865" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25260,7 +25260,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G867" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25364,7 +25364,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25416,7 +25416,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G873" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25546,7 +25546,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G878" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25910,7 +25910,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G892" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25988,7 +25988,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G895" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26222,7 +26222,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G904" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -30408,7 +30408,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1065" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30694,7 +30694,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1076" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30720,7 +30720,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1077" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30954,7 +30954,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1086" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31318,7 +31318,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1100" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31422,7 +31422,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1104" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32930,7 +32930,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1162" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32956,7 +32956,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1163" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33398,7 +33398,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1180" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33528,7 +33528,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1185" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33736,7 +33736,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1193" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -68116,7 +68116,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6911342593</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>279</v>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -44,79 +44,79 @@
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9132376909256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109167575836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88496315479279</t>
+    <t xml:space="preserve">1.91323745250702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109155654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88496339321136</t>
   </si>
   <si>
     <t xml:space="preserve">1.92423319816589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80642306804657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82998490333557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79856896400452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76715302467346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354685783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86925506591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87710916996002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281702041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86768424510956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81584787368774</t>
+    <t xml:space="preserve">1.80642282962799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82998502254486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79856884479523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76715278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86925518512726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87710928916931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281713962555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86768412590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81584775447845</t>
   </si>
   <si>
     <t xml:space="preserve">1.83783888816833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87553834915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684361934662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84569299221039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898939609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83626842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85983037948608</t>
+    <t xml:space="preserve">1.87553822994232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8456928730011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81898951530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83626818656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85983049869537</t>
   </si>
   <si>
     <t xml:space="preserve">1.80485212802887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82056033611298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81741845607758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85040557384491</t>
+    <t xml:space="preserve">1.82056021690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81741833686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85040545463562</t>
   </si>
   <si>
     <t xml:space="preserve">1.88025057315826</t>
@@ -125,31 +125,31 @@
     <t xml:space="preserve">1.81427681446075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85197615623474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84412252902985</t>
+    <t xml:space="preserve">1.85197639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84412217140198</t>
   </si>
   <si>
     <t xml:space="preserve">1.84098076820374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82370185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8111355304718</t>
+    <t xml:space="preserve">1.82370173931122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81113541126251</t>
   </si>
   <si>
     <t xml:space="preserve">1.8221310377121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93679976463318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622445106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407843589783</t>
+    <t xml:space="preserve">1.9367995262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622433185577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407819747925</t>
   </si>
   <si>
     <t xml:space="preserve">1.963503241539</t>
@@ -158,67 +158,67 @@
     <t xml:space="preserve">1.9650741815567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99334847927094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00434398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98706519603729</t>
+    <t xml:space="preserve">1.99334836006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00434422492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.987065076828</t>
   </si>
   <si>
     <t xml:space="preserve">2.00905656814575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0247642993927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93051648139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96193242073059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564901828766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637909412384</t>
+    <t xml:space="preserve">2.02476477622986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93051600456238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96193218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994128704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564913749695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637921333313</t>
   </si>
   <si>
     <t xml:space="preserve">1.87396728992462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93378698825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017516613007</t>
+    <t xml:space="preserve">1.93378722667694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017528533936</t>
   </si>
   <si>
     <t xml:space="preserve">1.9223153591156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93050968647003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656334400177</t>
+    <t xml:space="preserve">1.93050956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656346321106</t>
   </si>
   <si>
     <t xml:space="preserve">1.95509135723114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95836925506592</t>
+    <t xml:space="preserve">1.9583694934845</t>
   </si>
   <si>
     <t xml:space="preserve">1.91739904880524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93542587757111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198131561279</t>
+    <t xml:space="preserve">1.9354259967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198107719421</t>
   </si>
   <si>
     <t xml:space="preserve">1.91248285770416</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">1.8026829957962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84201419353485</t>
+    <t xml:space="preserve">1.84201407432556</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218145370483</t>
@@ -242,25 +242,25 @@
     <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86823511123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90756642818451</t>
+    <t xml:space="preserve">1.86823523044586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90756666660309</t>
   </si>
   <si>
     <t xml:space="preserve">1.89281690120697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90592777729034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88462316989899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920507907867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87151265144348</t>
+    <t xml:space="preserve">1.90592741966248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88462293148041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920519828796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87151277065277</t>
   </si>
   <si>
     <t xml:space="preserve">1.8977335691452</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">1.82398760318756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75843513011932</t>
+    <t xml:space="preserve">1.75843524932861</t>
   </si>
   <si>
     <t xml:space="preserve">1.76662921905518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78629493713379</t>
+    <t xml:space="preserve">1.78629517555237</t>
   </si>
   <si>
     <t xml:space="preserve">1.77646219730377</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">1.66993999481201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72893679141998</t>
+    <t xml:space="preserve">1.72893667221069</t>
   </si>
   <si>
     <t xml:space="preserve">1.69616067409515</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">1.76007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70435476303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73549211025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73385334014893</t>
+    <t xml:space="preserve">1.70435464382172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73549199104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73385322093964</t>
   </si>
   <si>
     <t xml:space="preserve">1.71254873275757</t>
@@ -323,58 +323,58 @@
     <t xml:space="preserve">1.63060867786407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67157876491547</t>
+    <t xml:space="preserve">1.67157864570618</t>
   </si>
   <si>
     <t xml:space="preserve">1.66666233539581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61012375354767</t>
+    <t xml:space="preserve">1.61012363433838</t>
   </si>
   <si>
     <t xml:space="preserve">1.62241470813751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66338467597961</t>
+    <t xml:space="preserve">1.6633847951889</t>
   </si>
   <si>
     <t xml:space="preserve">1.67321753501892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64535772800446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63880276679993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62569224834442</t>
+    <t xml:space="preserve">1.64535760879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63880264759064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62569212913513</t>
   </si>
   <si>
     <t xml:space="preserve">1.66830110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65519070625305</t>
+    <t xml:space="preserve">1.65519058704376</t>
   </si>
   <si>
     <t xml:space="preserve">1.64699673652649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63798320293427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59865212440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62978935241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58308351039886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59537446498871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57898640632629</t>
+    <t xml:space="preserve">1.63798332214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59865200519562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6297892332077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58308339118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59537434577942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.578986287117</t>
   </si>
   <si>
     <t xml:space="preserve">1.59127748012543</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">1.56997299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56669533252716</t>
+    <t xml:space="preserve">1.56669521331787</t>
   </si>
   <si>
     <t xml:space="preserve">1.55850124359131</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">1.6060266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51917004585266</t>
+    <t xml:space="preserve">1.51916992664337</t>
   </si>
   <si>
     <t xml:space="preserve">1.5617790222168</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">1.54539108276367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37659406661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4126478433609</t>
+    <t xml:space="preserve">1.37659430503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41264796257019</t>
   </si>
   <si>
     <t xml:space="preserve">1.39462113380432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45771491527557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4708251953125</t>
+    <t xml:space="preserve">1.45771503448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47082531452179</t>
   </si>
   <si>
     <t xml:space="preserve">1.53391921520233</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">1.61258184909821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61176252365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59783256053925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54211330413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51179552078247</t>
+    <t xml:space="preserve">1.61176240444183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59783267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54211342334747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51179563999176</t>
   </si>
   <si>
     <t xml:space="preserve">1.5552237033844</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">1.59291613101959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55686247348785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52162826061249</t>
+    <t xml:space="preserve">1.55686259269714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52162837982178</t>
   </si>
   <si>
     <t xml:space="preserve">1.5412939786911</t>
@@ -470,16 +470,16 @@
     <t xml:space="preserve">1.50442087650299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51097595691681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55112683773041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589250564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55194616317749</t>
+    <t xml:space="preserve">1.51097619533539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55112671852112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589238643646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55194628238678</t>
   </si>
   <si>
     <t xml:space="preserve">1.50851774215698</t>
@@ -488,13 +488,13 @@
     <t xml:space="preserve">1.53228056430817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50933730602264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50769853591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50278210639954</t>
+    <t xml:space="preserve">1.50933706760406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5076984167099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50278198719025</t>
   </si>
   <si>
     <t xml:space="preserve">1.49540758132935</t>
@@ -503,37 +503,37 @@
     <t xml:space="preserve">1.51015675067902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57325041294098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5855416059494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59455490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60684585571289</t>
+    <t xml:space="preserve">1.57325065135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58554148674011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59455502033234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60684597492218</t>
   </si>
   <si>
     <t xml:space="preserve">1.62159526348114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57161176204681</t>
+    <t xml:space="preserve">1.5716118812561</t>
   </si>
   <si>
     <t xml:space="preserve">1.54375207424164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57243132591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58718025684357</t>
+    <t xml:space="preserve">1.57243120670319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58718049526215</t>
   </si>
   <si>
     <t xml:space="preserve">1.54621028900146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55768203735352</t>
+    <t xml:space="preserve">1.55768191814423</t>
   </si>
   <si>
     <t xml:space="preserve">1.58799982070923</t>
@@ -542,34 +542,34 @@
     <t xml:space="preserve">1.53473877906799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58226406574249</t>
+    <t xml:space="preserve">1.5822639465332</t>
   </si>
   <si>
     <t xml:space="preserve">1.54702973365784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53883564472198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54784905910492</t>
+    <t xml:space="preserve">1.53883576393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54784917831421</t>
   </si>
   <si>
     <t xml:space="preserve">1.55276548862457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54948794841766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53801620006561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54866850376129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53637754917145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53965508937836</t>
+    <t xml:space="preserve">1.54948782920837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5380163192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54866862297058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53637742996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53965497016907</t>
   </si>
   <si>
     <t xml:space="preserve">1.56915354728699</t>
@@ -578,76 +578,76 @@
     <t xml:space="preserve">1.65191304683685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69288313388824</t>
+    <t xml:space="preserve">1.69288325309753</t>
   </si>
   <si>
     <t xml:space="preserve">1.65355181694031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82070958614349</t>
+    <t xml:space="preserve">1.82070970535278</t>
   </si>
   <si>
     <t xml:space="preserve">1.82890391349792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81743228435516</t>
+    <t xml:space="preserve">1.81743216514587</t>
   </si>
   <si>
     <t xml:space="preserve">1.81579351425171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87970674037933</t>
+    <t xml:space="preserve">1.87970650196075</t>
   </si>
   <si>
     <t xml:space="preserve">1.79448890686035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80104410648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73876965045929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72729790210724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74696338176727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76335167884827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84693050384521</t>
+    <t xml:space="preserve">1.80104398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72729802131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74696373939514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76335155963898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84693038463593</t>
   </si>
   <si>
     <t xml:space="preserve">1.81087696552277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80923795700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81251573562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86167991161346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86495745182037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85840213298798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87642908096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89937245845795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84856951236725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92479634284973</t>
+    <t xml:space="preserve">1.80923807621002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81251561641693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86167979240417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86495733261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85840225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87642896175385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89937233924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84856963157654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92479658126831</t>
   </si>
   <si>
     <t xml:space="preserve">1.93679428100586</t>
@@ -656,28 +656,28 @@
     <t xml:space="preserve">1.93850827217102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97107374668121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822444438934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94193601608276</t>
+    <t xml:space="preserve">1.97107350826263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822420597076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94193613529205</t>
   </si>
   <si>
     <t xml:space="preserve">1.94365000724792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95907580852509</t>
+    <t xml:space="preserve">1.95907604694366</t>
   </si>
   <si>
     <t xml:space="preserve">1.9676456451416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92651033401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95393395423889</t>
+    <t xml:space="preserve">1.92651009559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95393407344818</t>
   </si>
   <si>
     <t xml:space="preserve">1.93336629867554</t>
@@ -695,34 +695,34 @@
     <t xml:space="preserve">1.92993819713593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90080070495605</t>
+    <t xml:space="preserve">1.90080058574677</t>
   </si>
   <si>
     <t xml:space="preserve">1.91451239585876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88708865642548</t>
+    <t xml:space="preserve">1.88708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">1.87680494785309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91794049739838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88537490367889</t>
+    <t xml:space="preserve">1.9179402589798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8853747844696</t>
   </si>
   <si>
     <t xml:space="preserve">1.86994910240173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88880276679993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90937042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90251445770264</t>
+    <t xml:space="preserve">1.88880300521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90937030315399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90251469612122</t>
   </si>
   <si>
     <t xml:space="preserve">1.96421778202057</t>
@@ -749,19 +749,19 @@
     <t xml:space="preserve">2.05677270889282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07905459403992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08076786994934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06534242630005</t>
+    <t xml:space="preserve">2.07905435562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0807683467865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06534266471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.06020069122314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07219839096069</t>
+    <t xml:space="preserve">2.07219815254211</t>
   </si>
   <si>
     <t xml:space="preserve">2.13390135765076</t>
@@ -770,22 +770,22 @@
     <t xml:space="preserve">2.10819172859192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09962201118469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10304975509644</t>
+    <t xml:space="preserve">2.09962224960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10304999351501</t>
   </si>
   <si>
     <t xml:space="preserve">2.03963279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06877064704895</t>
+    <t xml:space="preserve">2.06877017021179</t>
   </si>
   <si>
     <t xml:space="preserve">2.11504769325256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07391238212585</t>
+    <t xml:space="preserve">2.07391214370728</t>
   </si>
   <si>
     <t xml:space="preserve">2.09790802001953</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">2.1167619228363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08248233795166</t>
+    <t xml:space="preserve">2.08248257637024</t>
   </si>
   <si>
     <t xml:space="preserve">2.06705641746521</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">2.12190365791321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10647797584534</t>
+    <t xml:space="preserve">2.10647773742676</t>
   </si>
   <si>
     <t xml:space="preserve">2.08933806419373</t>
@@ -812,13 +812,13 @@
     <t xml:space="preserve">2.05163049697876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17675113677979</t>
+    <t xml:space="preserve">2.17675089836121</t>
   </si>
   <si>
     <t xml:space="preserve">2.14247155189514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13218760490417</t>
+    <t xml:space="preserve">2.1321873664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.13047361373901</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">2.15961122512817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11847543716431</t>
+    <t xml:space="preserve">2.11847591400146</t>
   </si>
   <si>
     <t xml:space="preserve">2.09105205535889</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">2.15789723396301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15618300437927</t>
+    <t xml:space="preserve">2.15618324279785</t>
   </si>
   <si>
     <t xml:space="preserve">2.1441855430603</t>
@@ -866,22 +866,22 @@
     <t xml:space="preserve">2.15104126930237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12018966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10476398468018</t>
+    <t xml:space="preserve">2.12018990516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1047637462616</t>
   </si>
   <si>
     <t xml:space="preserve">2.06362843513489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03277683258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04820275306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07048439979553</t>
+    <t xml:space="preserve">2.03277659416199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0482029914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07048416137695</t>
   </si>
   <si>
     <t xml:space="preserve">2.04991674423218</t>
@@ -893,16 +893,16 @@
     <t xml:space="preserve">2.08762431144714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02077889442444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08419609069824</t>
+    <t xml:space="preserve">2.02077913284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08419632911682</t>
   </si>
   <si>
     <t xml:space="preserve">2.0224928855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01392316818237</t>
+    <t xml:space="preserve">2.01392292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.00535321235657</t>
@@ -911,43 +911,43 @@
     <t xml:space="preserve">2.1681809425354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18532061576843</t>
+    <t xml:space="preserve">2.18532085418701</t>
   </si>
   <si>
     <t xml:space="preserve">2.29672932624817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33100914955139</t>
+    <t xml:space="preserve">2.33100891113281</t>
   </si>
   <si>
     <t xml:space="preserve">2.32243919372559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35671854019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44241738319397</t>
+    <t xml:space="preserve">2.35671830177307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44241714477539</t>
   </si>
   <si>
     <t xml:space="preserve">2.49383687973022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46812701225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47669720649719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48526668548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53668642044067</t>
+    <t xml:space="preserve">2.46812725067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47669696807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48526692390442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53668618202209</t>
   </si>
   <si>
     <t xml:space="preserve">2.57953548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.596675157547</t>
+    <t xml:space="preserve">2.59667539596558</t>
   </si>
   <si>
     <t xml:space="preserve">2.61381506919861</t>
@@ -68140,6 +68140,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.3333333333</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>790</v>
+      </c>
+      <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.3644328704</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>789</v>
+      </c>
+      <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="793">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,163 +44,163 @@
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91323745250702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109155654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88496339321136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92423319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80642282962799</t>
+    <t xml:space="preserve">1.91323781013489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109143733978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88496327400208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92423331737518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80642294883728</t>
   </si>
   <si>
     <t xml:space="preserve">1.82998502254486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79856884479523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76715278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354709625244</t>
+    <t xml:space="preserve">1.79856896400452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76715314388275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354685783386</t>
   </si>
   <si>
     <t xml:space="preserve">1.86925518512726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87710928916931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281713962555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86768412590027</t>
+    <t xml:space="preserve">1.87710893154144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281737804413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86768424510956</t>
   </si>
   <si>
     <t xml:space="preserve">1.81584775447845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83783888816833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87553822994232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8456928730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898951530457</t>
+    <t xml:space="preserve">1.83783900737762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8755384683609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684350013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84569299221039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81898939609528</t>
   </si>
   <si>
     <t xml:space="preserve">1.83626818656921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85983049869537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80485212802887</t>
+    <t xml:space="preserve">1.85983037948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80485224723816</t>
   </si>
   <si>
     <t xml:space="preserve">1.82056021690369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81741833686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85040545463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88025057315826</t>
+    <t xml:space="preserve">1.81741857528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85040557384491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88025093078613</t>
   </si>
   <si>
     <t xml:space="preserve">1.81427681446075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85197639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84412217140198</t>
+    <t xml:space="preserve">1.85197615623474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84412229061127</t>
   </si>
   <si>
     <t xml:space="preserve">1.84098076820374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82370173931122</t>
+    <t xml:space="preserve">1.82370185852051</t>
   </si>
   <si>
     <t xml:space="preserve">1.81113541126251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8221310377121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9367995262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622433185577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407819747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.963503241539</t>
+    <t xml:space="preserve">1.82213115692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679928779602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622445106506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407855510712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96350336074829</t>
   </si>
   <si>
     <t xml:space="preserve">1.9650741815567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99334836006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00434422492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.987065076828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905656814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02476477622986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93051600456238</t>
+    <t xml:space="preserve">1.99334847927094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00434446334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98706519603729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905680656433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0247642993927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93051636219025</t>
   </si>
   <si>
     <t xml:space="preserve">1.96193218231201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93994128704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564913749695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637921333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87396728992462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378722667694</t>
+    <t xml:space="preserve">1.93994116783142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564937591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637897491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87396717071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378698825836</t>
   </si>
   <si>
     <t xml:space="preserve">1.95017528533936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9223153591156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050956726074</t>
+    <t xml:space="preserve">1.92231547832489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050968647003</t>
   </si>
   <si>
     <t xml:space="preserve">1.96656346321106</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">1.95509135723114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9583694934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739904880524</t>
+    <t xml:space="preserve">1.95836913585663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739916801453</t>
   </si>
   <si>
     <t xml:space="preserve">1.9354259967804</t>
@@ -221,46 +221,46 @@
     <t xml:space="preserve">1.94198107719421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91248285770416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91084396839142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545899391174</t>
+    <t xml:space="preserve">1.91248273849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91084408760071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545887470245</t>
   </si>
   <si>
     <t xml:space="preserve">1.8026829957962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84201407432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83218145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88298428058624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86823523044586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90756666660309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281690120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592741966248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88462293148041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920519828796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87151277065277</t>
+    <t xml:space="preserve">1.84201431274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83218157291412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88298439979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86823499202728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90756642818451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281702041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90592753887177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88462316989899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920507907867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8715124130249</t>
   </si>
   <si>
     <t xml:space="preserve">1.8977335691452</t>
@@ -269,16 +269,16 @@
     <t xml:space="preserve">1.82398760318756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75843524932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76662921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78629517555237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77646219730377</t>
+    <t xml:space="preserve">1.75843513011932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76662909984589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78629505634308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77646207809448</t>
   </si>
   <si>
     <t xml:space="preserve">1.75188016891479</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">1.75351893901825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77973973751068</t>
+    <t xml:space="preserve">1.77973961830139</t>
   </si>
   <si>
     <t xml:space="preserve">1.75024127960205</t>
@@ -296,100 +296,100 @@
     <t xml:space="preserve">1.72074282169342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66993999481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72893667221069</t>
+    <t xml:space="preserve">1.6699401140213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72893679141998</t>
   </si>
   <si>
     <t xml:space="preserve">1.69616067409515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76007413864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70435464382172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73549199104309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73385322093964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71254873275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63060867786407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67157864570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66666233539581</t>
+    <t xml:space="preserve">1.76007401943207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7043548822403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73549211025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73385310173035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71254861354828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63060879707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67157876491547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66666209697723</t>
   </si>
   <si>
     <t xml:space="preserve">1.61012363433838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62241470813751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6633847951889</t>
+    <t xml:space="preserve">1.62241458892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66338467597961</t>
   </si>
   <si>
     <t xml:space="preserve">1.67321753501892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64535760879517</t>
+    <t xml:space="preserve">1.64535772800446</t>
   </si>
   <si>
     <t xml:space="preserve">1.63880264759064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62569212913513</t>
+    <t xml:space="preserve">1.62569236755371</t>
   </si>
   <si>
     <t xml:space="preserve">1.66830110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65519058704376</t>
+    <t xml:space="preserve">1.65519070625305</t>
   </si>
   <si>
     <t xml:space="preserve">1.64699673652649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63798332214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59865200519562</t>
+    <t xml:space="preserve">1.63798320293427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59865212440491</t>
   </si>
   <si>
     <t xml:space="preserve">1.6297892332077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58308339118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59537434577942</t>
+    <t xml:space="preserve">1.58308351039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59537446498871</t>
   </si>
   <si>
     <t xml:space="preserve">1.578986287117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59127748012543</t>
+    <t xml:space="preserve">1.59127736091614</t>
   </si>
   <si>
     <t xml:space="preserve">1.54047453403473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56751465797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56997299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56669521331787</t>
+    <t xml:space="preserve">1.56751477718353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56997287273407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56669533252716</t>
   </si>
   <si>
     <t xml:space="preserve">1.55850124359131</t>
@@ -401,19 +401,19 @@
     <t xml:space="preserve">1.60356843471527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6060266494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51916992664337</t>
+    <t xml:space="preserve">1.60602676868439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51917004585266</t>
   </si>
   <si>
     <t xml:space="preserve">1.5617790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54539108276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37659430503845</t>
+    <t xml:space="preserve">1.54539096355438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37659406661987</t>
   </si>
   <si>
     <t xml:space="preserve">1.41264796257019</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">1.47082531452179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53391921520233</t>
+    <t xml:space="preserve">1.53391933441162</t>
   </si>
   <si>
     <t xml:space="preserve">1.61258184909821</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">1.59783267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54211342334747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51179563999176</t>
+    <t xml:space="preserve">1.54211318492889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51179540157318</t>
   </si>
   <si>
     <t xml:space="preserve">1.5552237033844</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">1.56505656242371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56423723697662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59291613101959</t>
+    <t xml:space="preserve">1.56423711776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59291625022888</t>
   </si>
   <si>
     <t xml:space="preserve">1.55686259269714</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">1.5412939786911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50442087650299</t>
+    <t xml:space="preserve">1.5044207572937</t>
   </si>
   <si>
     <t xml:space="preserve">1.51097619533539</t>
@@ -476,19 +476,19 @@
     <t xml:space="preserve">1.55112671852112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51589238643646</t>
+    <t xml:space="preserve">1.51589250564575</t>
   </si>
   <si>
     <t xml:space="preserve">1.55194628238678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50851774215698</t>
+    <t xml:space="preserve">1.50851786136627</t>
   </si>
   <si>
     <t xml:space="preserve">1.53228056430817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50933706760406</t>
+    <t xml:space="preserve">1.50933718681335</t>
   </si>
   <si>
     <t xml:space="preserve">1.5076984167099</t>
@@ -500,25 +500,25 @@
     <t xml:space="preserve">1.49540758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51015675067902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57325065135956</t>
+    <t xml:space="preserve">1.51015663146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57325053215027</t>
   </si>
   <si>
     <t xml:space="preserve">1.58554148674011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59455502033234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60684597492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62159526348114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5716118812561</t>
+    <t xml:space="preserve">1.59455490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60684585571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62159538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57161176204681</t>
   </si>
   <si>
     <t xml:space="preserve">1.54375207424164</t>
@@ -539,16 +539,16 @@
     <t xml:space="preserve">1.58799982070923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53473877906799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5822639465332</t>
+    <t xml:space="preserve">1.5347386598587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58226406574249</t>
   </si>
   <si>
     <t xml:space="preserve">1.54702973365784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53883576393127</t>
+    <t xml:space="preserve">1.53883588314056</t>
   </si>
   <si>
     <t xml:space="preserve">1.54784917831421</t>
@@ -557,34 +557,34 @@
     <t xml:space="preserve">1.55276548862457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54948782920837</t>
+    <t xml:space="preserve">1.54948806762695</t>
   </si>
   <si>
     <t xml:space="preserve">1.5380163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54866862297058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53637742996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53965497016907</t>
+    <t xml:space="preserve">1.54866850376129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53637754917145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53965508937836</t>
   </si>
   <si>
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191304683685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69288325309753</t>
+    <t xml:space="preserve">1.65191316604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69288313388824</t>
   </si>
   <si>
     <t xml:space="preserve">1.65355181694031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82070970535278</t>
+    <t xml:space="preserve">1.82070958614349</t>
   </si>
   <si>
     <t xml:space="preserve">1.82890391349792</t>
@@ -593,16 +593,16 @@
     <t xml:space="preserve">1.81743216514587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81579351425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87970650196075</t>
+    <t xml:space="preserve">1.81579339504242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87970662117004</t>
   </si>
   <si>
     <t xml:space="preserve">1.79448890686035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80104398727417</t>
+    <t xml:space="preserve">1.80104422569275</t>
   </si>
   <si>
     <t xml:space="preserve">1.73876953125</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">1.72729802131653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74696373939514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76335155963898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84693038463593</t>
+    <t xml:space="preserve">1.74696350097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76335167884827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8469306230545</t>
   </si>
   <si>
     <t xml:space="preserve">1.81087696552277</t>
@@ -632,10 +632,10 @@
     <t xml:space="preserve">1.86167979240417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86495733261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85840225219727</t>
+    <t xml:space="preserve">1.86495769023895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85840201377869</t>
   </si>
   <si>
     <t xml:space="preserve">1.87642896175385</t>
@@ -644,40 +644,40 @@
     <t xml:space="preserve">1.89937233924866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84856963157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92479658126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679428100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850827217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97107350826263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822420597076</t>
+    <t xml:space="preserve">1.84856951236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92479622364044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679404258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850839138031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107362747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822456359863</t>
   </si>
   <si>
     <t xml:space="preserve">1.94193613529205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94365000724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95907604694366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9676456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92651009559631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95393407344818</t>
+    <t xml:space="preserve">1.94364988803864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95907580852509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96764552593231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9265102148056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95393395423889</t>
   </si>
   <si>
     <t xml:space="preserve">1.93336629867554</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">1.90594255924225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89394474029541</t>
+    <t xml:space="preserve">1.89394462108612</t>
   </si>
   <si>
     <t xml:space="preserve">1.87166309356689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92993819713593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90080058574677</t>
+    <t xml:space="preserve">1.92993807792664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90080070495605</t>
   </si>
   <si>
     <t xml:space="preserve">1.91451239585876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88708877563477</t>
+    <t xml:space="preserve">1.88708865642548</t>
   </si>
   <si>
     <t xml:space="preserve">1.87680494785309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9179402589798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8853747844696</t>
+    <t xml:space="preserve">1.91794049739838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88537490367889</t>
   </si>
   <si>
     <t xml:space="preserve">1.86994910240173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88880300521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90937030315399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90251469612122</t>
+    <t xml:space="preserve">1.88880288600922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90937054157257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90251445770264</t>
   </si>
   <si>
     <t xml:space="preserve">1.96421778202057</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">1.98821341991425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98649966716766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964334487915</t>
+    <t xml:space="preserve">1.98649942874908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97964346408844</t>
   </si>
   <si>
     <t xml:space="preserve">2.12533164024353</t>
@@ -749,43 +749,43 @@
     <t xml:space="preserve">2.05677270889282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07905435562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0807683467865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06534266471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06020069122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07219815254211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13390135765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10819172859192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09962224960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10304999351501</t>
+    <t xml:space="preserve">2.07905459403992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08076810836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06534242630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06020045280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07219839096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13390159606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1081919670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09962201118469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10304975509644</t>
   </si>
   <si>
     <t xml:space="preserve">2.03963279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06877017021179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11504769325256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07391214370728</t>
+    <t xml:space="preserve">2.06877064704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11504793167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07391238212585</t>
   </si>
   <si>
     <t xml:space="preserve">2.09790802001953</t>
@@ -794,31 +794,31 @@
     <t xml:space="preserve">2.1167619228363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08248257637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06705641746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12190365791321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10647773742676</t>
+    <t xml:space="preserve">2.08248209953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06705665588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12190389633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10647797584534</t>
   </si>
   <si>
     <t xml:space="preserve">2.08933806419373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05163049697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17675089836121</t>
+    <t xml:space="preserve">2.05163073539734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17675113677979</t>
   </si>
   <si>
     <t xml:space="preserve">2.14247155189514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1321873664856</t>
+    <t xml:space="preserve">2.13218760490417</t>
   </si>
   <si>
     <t xml:space="preserve">2.13047361373901</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">2.15961122512817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11847591400146</t>
+    <t xml:space="preserve">2.11847543716431</t>
   </si>
   <si>
     <t xml:space="preserve">2.09105205535889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12361764907837</t>
+    <t xml:space="preserve">2.12361741065979</t>
   </si>
   <si>
     <t xml:space="preserve">2.11161994934082</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">2.10133600234985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15789723396301</t>
+    <t xml:space="preserve">2.15789699554443</t>
   </si>
   <si>
     <t xml:space="preserve">2.15618324279785</t>
@@ -854,34 +854,34 @@
     <t xml:space="preserve">2.1407573223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14932727813721</t>
+    <t xml:space="preserve">2.14932751655579</t>
   </si>
   <si>
     <t xml:space="preserve">2.13904356956482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17503690719604</t>
+    <t xml:space="preserve">2.17503714561462</t>
   </si>
   <si>
     <t xml:space="preserve">2.15104126930237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12018990516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1047637462616</t>
+    <t xml:space="preserve">2.12018966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10476398468018</t>
   </si>
   <si>
     <t xml:space="preserve">2.06362843513489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03277659416199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0482029914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07048416137695</t>
+    <t xml:space="preserve">2.03277683258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04820275306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07048439979553</t>
   </si>
   <si>
     <t xml:space="preserve">2.04991674423218</t>
@@ -893,16 +893,16 @@
     <t xml:space="preserve">2.08762431144714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02077913284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08419632911682</t>
+    <t xml:space="preserve">2.02077889442444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08419609069824</t>
   </si>
   <si>
     <t xml:space="preserve">2.0224928855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01392292976379</t>
+    <t xml:space="preserve">2.01392316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.00535321235657</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">2.1681809425354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18532085418701</t>
+    <t xml:space="preserve">2.18532061576843</t>
   </si>
   <si>
     <t xml:space="preserve">2.29672932624817</t>
@@ -920,19 +920,19 @@
     <t xml:space="preserve">2.33100891113281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32243919372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35671830177307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44241714477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49383687973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46812725067139</t>
+    <t xml:space="preserve">2.32243895530701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35671854019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44241738319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49383664131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46812701225281</t>
   </si>
   <si>
     <t xml:space="preserve">2.47669696807861</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">2.57953548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59667539596558</t>
+    <t xml:space="preserve">2.596675157547</t>
   </si>
   <si>
     <t xml:space="preserve">2.61381506919861</t>
@@ -2388,6 +2388,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.44000005722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45000004768372</t>
   </si>
 </sst>
 </file>
@@ -68168,7 +68171,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.3644328704</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>1000</v>
@@ -68189,6 +68192,32 @@
         <v>789</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6911689815</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>1812</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>792</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -38,88 +38,88 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825943946838</t>
+    <t xml:space="preserve">1.85825932025909</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91323781013489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109143733978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88496327400208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92423331737518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80642294883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82998502254486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79856896400452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76715314388275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354685783386</t>
+    <t xml:space="preserve">1.9132376909256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109155654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88496339321136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92423319816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80642306804657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82998490333557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79856884479523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76715302467346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354697704315</t>
   </si>
   <si>
     <t xml:space="preserve">1.86925518512726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87710893154144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281737804413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86768424510956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81584775447845</t>
+    <t xml:space="preserve">1.87710905075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281702041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86768412590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81584799289703</t>
   </si>
   <si>
     <t xml:space="preserve">1.83783900737762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8755384683609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684350013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84569299221039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898939609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83626818656921</t>
+    <t xml:space="preserve">1.87553811073303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684361934662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84569311141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81898951530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83626842498779</t>
   </si>
   <si>
     <t xml:space="preserve">1.85983037948608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80485224723816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82056021690369</t>
+    <t xml:space="preserve">1.80485212802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82056033611298</t>
   </si>
   <si>
     <t xml:space="preserve">1.81741857528687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85040557384491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88025093078613</t>
+    <t xml:space="preserve">1.85040545463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88025057315826</t>
   </si>
   <si>
     <t xml:space="preserve">1.81427681446075</t>
@@ -128,79 +128,79 @@
     <t xml:space="preserve">1.85197615623474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84412229061127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84098076820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82370185852051</t>
+    <t xml:space="preserve">1.84412240982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84098088741302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82370173931122</t>
   </si>
   <si>
     <t xml:space="preserve">1.81113541126251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82213115692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679928779602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622445106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407855510712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96350336074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9650741815567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99334847927094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00434446334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98706519603729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905680656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0247642993927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93051636219025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96193218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994116783142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637897491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87396717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378698825836</t>
+    <t xml:space="preserve">1.82213091850281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9367995262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622433185577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407843589783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.963503241539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96507441997528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99334859848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00434422492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98706531524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905632972717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02476453781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93051648139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96193242073059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564913749695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637921333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87396740913391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378722667694</t>
   </si>
   <si>
     <t xml:space="preserve">1.95017528533936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92231547832489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050968647003</t>
+    <t xml:space="preserve">1.9223153591156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050956726074</t>
   </si>
   <si>
     <t xml:space="preserve">1.96656346321106</t>
@@ -209,37 +209,37 @@
     <t xml:space="preserve">1.95509135723114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95836913585663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739916801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9354259967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198107719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91248273849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91084408760071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545887470245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8026829957962</t>
+    <t xml:space="preserve">1.95836925506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739904880524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542575836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198131561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91248285770416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91084396839142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545899391174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80268311500549</t>
   </si>
   <si>
     <t xml:space="preserve">1.84201431274414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83218157291412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88298439979553</t>
+    <t xml:space="preserve">1.83218145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
     <t xml:space="preserve">1.86823499202728</t>
@@ -248,10 +248,10 @@
     <t xml:space="preserve">1.90756642818451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89281702041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592753887177</t>
+    <t xml:space="preserve">1.89281690120697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90592765808105</t>
   </si>
   <si>
     <t xml:space="preserve">1.88462316989899</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">1.90920507907867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8715124130249</t>
+    <t xml:space="preserve">1.87151253223419</t>
   </si>
   <si>
     <t xml:space="preserve">1.8977335691452</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">1.75843513011932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76662909984589</t>
+    <t xml:space="preserve">1.76662921905518</t>
   </si>
   <si>
     <t xml:space="preserve">1.78629505634308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77646207809448</t>
+    <t xml:space="preserve">1.77646219730377</t>
   </si>
   <si>
     <t xml:space="preserve">1.75188016891479</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">1.75351893901825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77973961830139</t>
+    <t xml:space="preserve">1.77973973751068</t>
   </si>
   <si>
     <t xml:space="preserve">1.75024127960205</t>
@@ -296,43 +296,43 @@
     <t xml:space="preserve">1.72074282169342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6699401140213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72893679141998</t>
+    <t xml:space="preserve">1.66993999481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72893667221069</t>
   </si>
   <si>
     <t xml:space="preserve">1.69616067409515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76007401943207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7043548822403</t>
+    <t xml:space="preserve">1.76007413864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70435464382172</t>
   </si>
   <si>
     <t xml:space="preserve">1.73549211025238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73385310173035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71254861354828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63060879707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67157876491547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66666209697723</t>
+    <t xml:space="preserve">1.73385334014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71254873275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63060867786407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67157864570618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66666233539581</t>
   </si>
   <si>
     <t xml:space="preserve">1.61012363433838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62241458892822</t>
+    <t xml:space="preserve">1.62241470813751</t>
   </si>
   <si>
     <t xml:space="preserve">1.66338467597961</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">1.67321753501892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64535772800446</t>
+    <t xml:space="preserve">1.64535760879517</t>
   </si>
   <si>
     <t xml:space="preserve">1.63880264759064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62569236755371</t>
+    <t xml:space="preserve">1.62569224834442</t>
   </si>
   <si>
     <t xml:space="preserve">1.66830110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65519070625305</t>
+    <t xml:space="preserve">1.65519058704376</t>
   </si>
   <si>
     <t xml:space="preserve">1.64699673652649</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">1.63798320293427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59865212440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6297892332077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58308351039886</t>
+    <t xml:space="preserve">1.59865200519562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62978935241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58308339118958</t>
   </si>
   <si>
     <t xml:space="preserve">1.59537446498871</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">1.578986287117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59127736091614</t>
+    <t xml:space="preserve">1.59127748012543</t>
   </si>
   <si>
     <t xml:space="preserve">1.54047453403473</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">1.56751477718353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56997287273407</t>
+    <t xml:space="preserve">1.56997299194336</t>
   </si>
   <si>
     <t xml:space="preserve">1.56669533252716</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">1.60356843471527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60602676868439</t>
+    <t xml:space="preserve">1.6060266494751</t>
   </si>
   <si>
     <t xml:space="preserve">1.51917004585266</t>
@@ -410,40 +410,40 @@
     <t xml:space="preserve">1.5617790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54539096355438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37659406661987</t>
+    <t xml:space="preserve">1.54539108276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37659418582916</t>
   </si>
   <si>
     <t xml:space="preserve">1.41264796257019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39462113380432</t>
+    <t xml:space="preserve">1.39462101459503</t>
   </si>
   <si>
     <t xml:space="preserve">1.45771503448486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47082531452179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53391933441162</t>
+    <t xml:space="preserve">1.4708251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53391921520233</t>
   </si>
   <si>
     <t xml:space="preserve">1.61258184909821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61176240444183</t>
+    <t xml:space="preserve">1.61176252365112</t>
   </si>
   <si>
     <t xml:space="preserve">1.59783267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54211318492889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51179540157318</t>
+    <t xml:space="preserve">1.54211342334747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51179552078247</t>
   </si>
   <si>
     <t xml:space="preserve">1.5552237033844</t>
@@ -452,13 +452,13 @@
     <t xml:space="preserve">1.56505656242371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56423711776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59291625022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55686259269714</t>
+    <t xml:space="preserve">1.56423723697662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59291613101959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55686247348785</t>
   </si>
   <si>
     <t xml:space="preserve">1.52162837982178</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">1.5412939786911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5044207572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51097619533539</t>
+    <t xml:space="preserve">1.50442087650299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5109760761261</t>
   </si>
   <si>
     <t xml:space="preserve">1.55112671852112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51589250564575</t>
+    <t xml:space="preserve">1.51589238643646</t>
   </si>
   <si>
     <t xml:space="preserve">1.55194628238678</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">1.50933718681335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5076984167099</t>
+    <t xml:space="preserve">1.50769853591919</t>
   </si>
   <si>
     <t xml:space="preserve">1.50278198719025</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">1.49540758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51015663146973</t>
+    <t xml:space="preserve">1.51015675067902</t>
   </si>
   <si>
     <t xml:space="preserve">1.57325053215027</t>
@@ -509,13 +509,13 @@
     <t xml:space="preserve">1.58554148674011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59455490112305</t>
+    <t xml:space="preserve">1.59455502033234</t>
   </si>
   <si>
     <t xml:space="preserve">1.60684585571289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62159538269043</t>
+    <t xml:space="preserve">1.62159526348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.57161176204681</t>
@@ -527,43 +527,43 @@
     <t xml:space="preserve">1.57243120670319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58718049526215</t>
+    <t xml:space="preserve">1.58718037605286</t>
   </si>
   <si>
     <t xml:space="preserve">1.54621028900146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55768191814423</t>
+    <t xml:space="preserve">1.55768203735352</t>
   </si>
   <si>
     <t xml:space="preserve">1.58799982070923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5347386598587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58226406574249</t>
+    <t xml:space="preserve">1.53473877906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5822639465332</t>
   </si>
   <si>
     <t xml:space="preserve">1.54702973365784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53883588314056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54784917831421</t>
+    <t xml:space="preserve">1.53883576393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54784905910492</t>
   </si>
   <si>
     <t xml:space="preserve">1.55276548862457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54948806762695</t>
+    <t xml:space="preserve">1.54948794841766</t>
   </si>
   <si>
     <t xml:space="preserve">1.5380163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54866850376129</t>
+    <t xml:space="preserve">1.54866862297058</t>
   </si>
   <si>
     <t xml:space="preserve">1.53637754917145</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191316604614</t>
+    <t xml:space="preserve">1.65191304683685</t>
   </si>
   <si>
     <t xml:space="preserve">1.69288313388824</t>
@@ -590,22 +590,22 @@
     <t xml:space="preserve">1.82890391349792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81743216514587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579339504242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87970662117004</t>
+    <t xml:space="preserve">1.81743228435516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81579351425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87970674037933</t>
   </si>
   <si>
     <t xml:space="preserve">1.79448890686035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80104422569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73876953125</t>
+    <t xml:space="preserve">1.80104398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73876965045929</t>
   </si>
   <si>
     <t xml:space="preserve">1.72729802131653</t>
@@ -617,25 +617,25 @@
     <t xml:space="preserve">1.76335167884827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8469306230545</t>
+    <t xml:space="preserve">1.84693038463593</t>
   </si>
   <si>
     <t xml:space="preserve">1.81087696552277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80923807621002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81251561641693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86167979240417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86495769023895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85840201377869</t>
+    <t xml:space="preserve">1.80923795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81251573562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86167991161346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86495745182037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85840225219727</t>
   </si>
   <si>
     <t xml:space="preserve">1.87642896175385</t>
@@ -644,37 +644,37 @@
     <t xml:space="preserve">1.89937233924866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84856951236725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92479622364044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679404258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850839138031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97107362747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822456359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94193613529205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94364988803864</t>
+    <t xml:space="preserve">1.84856963157654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92479634284973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679428100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850827217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107374668121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822444438934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94193601608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94365000724792</t>
   </si>
   <si>
     <t xml:space="preserve">1.95907580852509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96764552593231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9265102148056</t>
+    <t xml:space="preserve">1.9676456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92651033401489</t>
   </si>
   <si>
     <t xml:space="preserve">1.95393395423889</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">1.90594255924225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89394462108612</t>
+    <t xml:space="preserve">1.89394474029541</t>
   </si>
   <si>
     <t xml:space="preserve">1.87166309356689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92993807792664</t>
+    <t xml:space="preserve">1.92993819713593</t>
   </si>
   <si>
     <t xml:space="preserve">1.90080070495605</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">1.86994910240173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88880288600922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90937054157257</t>
+    <t xml:space="preserve">1.88880276679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90937042236328</t>
   </si>
   <si>
     <t xml:space="preserve">1.90251445770264</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">1.98821341991425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98649942874908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964346408844</t>
+    <t xml:space="preserve">1.98649966716766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97964334487915</t>
   </si>
   <si>
     <t xml:space="preserve">2.12533164024353</t>
@@ -752,22 +752,22 @@
     <t xml:space="preserve">2.07905459403992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08076810836792</t>
+    <t xml:space="preserve">2.08076786994934</t>
   </si>
   <si>
     <t xml:space="preserve">2.06534242630005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06020045280457</t>
+    <t xml:space="preserve">2.06020069122314</t>
   </si>
   <si>
     <t xml:space="preserve">2.07219839096069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13390159606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1081919670105</t>
+    <t xml:space="preserve">2.13390135765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10819172859192</t>
   </si>
   <si>
     <t xml:space="preserve">2.09962201118469</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">2.06877064704895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11504793167114</t>
+    <t xml:space="preserve">2.11504769325256</t>
   </si>
   <si>
     <t xml:space="preserve">2.07391238212585</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">2.1167619228363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08248209953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06705665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12190389633179</t>
+    <t xml:space="preserve">2.08248233795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06705641746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12190365791321</t>
   </si>
   <si>
     <t xml:space="preserve">2.10647797584534</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">2.08933806419373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05163073539734</t>
+    <t xml:space="preserve">2.05163049697876</t>
   </si>
   <si>
     <t xml:space="preserve">2.17675113677979</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">2.09105205535889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12361741065979</t>
+    <t xml:space="preserve">2.12361764907837</t>
   </si>
   <si>
     <t xml:space="preserve">2.11161994934082</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">2.10133600234985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15789699554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15618324279785</t>
+    <t xml:space="preserve">2.15789723396301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15618300437927</t>
   </si>
   <si>
     <t xml:space="preserve">2.1441855430603</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">2.1407573223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14932751655579</t>
+    <t xml:space="preserve">2.14932727813721</t>
   </si>
   <si>
     <t xml:space="preserve">2.13904356956482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17503714561462</t>
+    <t xml:space="preserve">2.17503690719604</t>
   </si>
   <si>
     <t xml:space="preserve">2.15104126930237</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">2.29672932624817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33100891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32243895530701</t>
+    <t xml:space="preserve">2.33100914955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32243919372559</t>
   </si>
   <si>
     <t xml:space="preserve">2.35671854019165</t>
@@ -929,19 +929,19 @@
     <t xml:space="preserve">2.44241738319397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49383664131165</t>
+    <t xml:space="preserve">2.49383687973022</t>
   </si>
   <si>
     <t xml:space="preserve">2.46812701225281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47669696807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48526692390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53668618202209</t>
+    <t xml:space="preserve">2.47669720649719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48526668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53668642044067</t>
   </si>
   <si>
     <t xml:space="preserve">2.57953548431396</t>
@@ -68197,7 +68197,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6911689815</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>1812</v>
@@ -68218,6 +68218,32 @@
         <v>792</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6063425926</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>200</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>788</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -44,46 +44,46 @@
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9132376909256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109155654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88496339321136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92423319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80642306804657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82998490333557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79856884479523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76715302467346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354697704315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86925518512726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87710905075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281702041626</t>
+    <t xml:space="preserve">1.91323781013489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109167575836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88496327400208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92423331737518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80642318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82998478412628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79856908321381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76715290546417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86925554275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87710916996002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281713962555</t>
   </si>
   <si>
     <t xml:space="preserve">1.86768412590027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81584799289703</t>
+    <t xml:space="preserve">1.81584787368774</t>
   </si>
   <si>
     <t xml:space="preserve">1.83783900737762</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">1.87553811073303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82684361934662</t>
+    <t xml:space="preserve">1.82684326171875</t>
   </si>
   <si>
     <t xml:space="preserve">1.84569311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81898951530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83626842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85983037948608</t>
+    <t xml:space="preserve">1.81898927688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83626818656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85983002185822</t>
   </si>
   <si>
     <t xml:space="preserve">1.80485212802887</t>
@@ -113,25 +113,25 @@
     <t xml:space="preserve">1.82056033611298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81741857528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85040545463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88025057315826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81427681446075</t>
+    <t xml:space="preserve">1.81741869449615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85040533542633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88025081157684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81427705287933</t>
   </si>
   <si>
     <t xml:space="preserve">1.85197615623474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84412240982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84098088741302</t>
+    <t xml:space="preserve">1.84412229061127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84098064899445</t>
   </si>
   <si>
     <t xml:space="preserve">1.82370173931122</t>
@@ -140,73 +140,73 @@
     <t xml:space="preserve">1.81113541126251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82213091850281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9367995262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622433185577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407843589783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.963503241539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96507441997528</t>
+    <t xml:space="preserve">1.82213115692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679976463318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622445106506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407831668854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96350336074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9650741815567</t>
   </si>
   <si>
     <t xml:space="preserve">1.99334859848022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00434422492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98706531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905632972717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02476453781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93051648139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96193242073059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564913749695</t>
+    <t xml:space="preserve">2.00434398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98706543445587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905656814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0247642993927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93051636219025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96193218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994128704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564925670624</t>
   </si>
   <si>
     <t xml:space="preserve">1.91637921333313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87396740913391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378722667694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9223153591156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050956726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656346321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509135723114</t>
+    <t xml:space="preserve">1.87396728992462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378710746765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017552375793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050944805145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656334400177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509147644043</t>
   </si>
   <si>
     <t xml:space="preserve">1.95836925506592</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">1.91739904880524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93542575836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198131561279</t>
+    <t xml:space="preserve">1.93542587757111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9419811964035</t>
   </si>
   <si>
     <t xml:space="preserve">1.91248285770416</t>
@@ -227,61 +227,58 @@
     <t xml:space="preserve">1.91084396839142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83545899391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80268311500549</t>
+    <t xml:space="preserve">1.83545911312103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80268287658691</t>
   </si>
   <si>
     <t xml:space="preserve">1.84201431274414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83218145370483</t>
+    <t xml:space="preserve">1.83218133449554</t>
   </si>
   <si>
     <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86823499202728</t>
+    <t xml:space="preserve">1.86823511123657</t>
   </si>
   <si>
     <t xml:space="preserve">1.90756642818451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89281690120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592765808105</t>
+    <t xml:space="preserve">1.90592741966248</t>
   </si>
   <si>
     <t xml:space="preserve">1.88462316989899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90920507907867</t>
+    <t xml:space="preserve">1.9092048406601</t>
   </si>
   <si>
     <t xml:space="preserve">1.87151253223419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8977335691452</t>
+    <t xml:space="preserve">1.89773344993591</t>
   </si>
   <si>
     <t xml:space="preserve">1.82398760318756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75843513011932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76662921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78629505634308</t>
+    <t xml:space="preserve">1.75843524932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76662909984589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78629493713379</t>
   </si>
   <si>
     <t xml:space="preserve">1.77646219730377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75188016891479</t>
+    <t xml:space="preserve">1.75187993049622</t>
   </si>
   <si>
     <t xml:space="preserve">1.75351893901825</t>
@@ -290,19 +287,19 @@
     <t xml:space="preserve">1.77973973751068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75024127960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72074282169342</t>
+    <t xml:space="preserve">1.75024116039276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72074270248413</t>
   </si>
   <si>
     <t xml:space="preserve">1.66993999481201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72893667221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69616067409515</t>
+    <t xml:space="preserve">1.7289365530014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69616079330444</t>
   </si>
   <si>
     <t xml:space="preserve">1.76007413864136</t>
@@ -314,19 +311,19 @@
     <t xml:space="preserve">1.73549211025238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73385334014893</t>
+    <t xml:space="preserve">1.73385322093964</t>
   </si>
   <si>
     <t xml:space="preserve">1.71254873275757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63060867786407</t>
+    <t xml:space="preserve">1.63060879707336</t>
   </si>
   <si>
     <t xml:space="preserve">1.67157864570618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66666233539581</t>
+    <t xml:space="preserve">1.66666221618652</t>
   </si>
   <si>
     <t xml:space="preserve">1.61012363433838</t>
@@ -338,22 +335,22 @@
     <t xml:space="preserve">1.66338467597961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67321753501892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64535760879517</t>
+    <t xml:space="preserve">1.67321765422821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64535784721375</t>
   </si>
   <si>
     <t xml:space="preserve">1.63880264759064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62569224834442</t>
+    <t xml:space="preserve">1.62569212913513</t>
   </si>
   <si>
     <t xml:space="preserve">1.66830110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65519058704376</t>
+    <t xml:space="preserve">1.65519082546234</t>
   </si>
   <si>
     <t xml:space="preserve">1.64699673652649</t>
@@ -362,22 +359,22 @@
     <t xml:space="preserve">1.63798320293427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59865200519562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62978935241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58308339118958</t>
+    <t xml:space="preserve">1.59865188598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6297892332077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58308351039886</t>
   </si>
   <si>
     <t xml:space="preserve">1.59537446498871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.578986287117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59127748012543</t>
+    <t xml:space="preserve">1.57898640632629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59127736091614</t>
   </si>
   <si>
     <t xml:space="preserve">1.54047453403473</t>
@@ -389,70 +386,70 @@
     <t xml:space="preserve">1.56997299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56669533252716</t>
+    <t xml:space="preserve">1.56669545173645</t>
   </si>
   <si>
     <t xml:space="preserve">1.55850124359131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6027489900589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60356843471527</t>
+    <t xml:space="preserve">1.60274887084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60356855392456</t>
   </si>
   <si>
     <t xml:space="preserve">1.6060266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51917004585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5617790222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54539108276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37659418582916</t>
+    <t xml:space="preserve">1.51917016506195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56177890300751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54539096355438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37659430503845</t>
   </si>
   <si>
     <t xml:space="preserve">1.41264796257019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39462101459503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45771503448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4708251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53391921520233</t>
+    <t xml:space="preserve">1.39462113380432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45771491527557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47082543373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53391933441162</t>
   </si>
   <si>
     <t xml:space="preserve">1.61258184909821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61176252365112</t>
+    <t xml:space="preserve">1.61176240444183</t>
   </si>
   <si>
     <t xml:space="preserve">1.59783267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54211342334747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51179552078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5552237033844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56505656242371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56423723697662</t>
+    <t xml:space="preserve">1.54211330413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51179540157318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55522382259369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.565056681633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56423711776733</t>
   </si>
   <si>
     <t xml:space="preserve">1.59291613101959</t>
@@ -461,7 +458,7 @@
     <t xml:space="preserve">1.55686247348785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52162837982178</t>
+    <t xml:space="preserve">1.5216281414032</t>
   </si>
   <si>
     <t xml:space="preserve">1.5412939786911</t>
@@ -470,25 +467,25 @@
     <t xml:space="preserve">1.50442087650299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5109760761261</t>
+    <t xml:space="preserve">1.51097619533539</t>
   </si>
   <si>
     <t xml:space="preserve">1.55112671852112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51589238643646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55194628238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50851786136627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53228056430817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50933718681335</t>
+    <t xml:space="preserve">1.51589250564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55194616317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50851774215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53228068351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50933730602264</t>
   </si>
   <si>
     <t xml:space="preserve">1.50769853591919</t>
@@ -497,22 +494,22 @@
     <t xml:space="preserve">1.50278198719025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49540758132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51015675067902</t>
+    <t xml:space="preserve">1.49540746212006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51015663146973</t>
   </si>
   <si>
     <t xml:space="preserve">1.57325053215027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58554148674011</t>
+    <t xml:space="preserve">1.58554136753082</t>
   </si>
   <si>
     <t xml:space="preserve">1.59455502033234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60684585571289</t>
+    <t xml:space="preserve">1.60684609413147</t>
   </si>
   <si>
     <t xml:space="preserve">1.62159526348114</t>
@@ -521,13 +518,13 @@
     <t xml:space="preserve">1.57161176204681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54375207424164</t>
+    <t xml:space="preserve">1.54375219345093</t>
   </si>
   <si>
     <t xml:space="preserve">1.57243120670319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58718037605286</t>
+    <t xml:space="preserve">1.58718025684357</t>
   </si>
   <si>
     <t xml:space="preserve">1.54621028900146</t>
@@ -542,40 +539,40 @@
     <t xml:space="preserve">1.53473877906799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5822639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54702973365784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53883576393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54784905910492</t>
+    <t xml:space="preserve">1.58226406574249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54702961444855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53883564472198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54784917831421</t>
   </si>
   <si>
     <t xml:space="preserve">1.55276548862457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54948794841766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5380163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54866862297058</t>
+    <t xml:space="preserve">1.54948806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53801643848419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.548668384552</t>
   </si>
   <si>
     <t xml:space="preserve">1.53637754917145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53965508937836</t>
+    <t xml:space="preserve">1.53965520858765</t>
   </si>
   <si>
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191304683685</t>
+    <t xml:space="preserve">1.65191316604614</t>
   </si>
   <si>
     <t xml:space="preserve">1.69288313388824</t>
@@ -590,13 +587,13 @@
     <t xml:space="preserve">1.82890391349792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81743228435516</t>
+    <t xml:space="preserve">1.81743216514587</t>
   </si>
   <si>
     <t xml:space="preserve">1.81579351425171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87970674037933</t>
+    <t xml:space="preserve">1.87970638275146</t>
   </si>
   <si>
     <t xml:space="preserve">1.79448890686035</t>
@@ -611,16 +608,16 @@
     <t xml:space="preserve">1.72729802131653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74696350097656</t>
+    <t xml:space="preserve">1.74696362018585</t>
   </si>
   <si>
     <t xml:space="preserve">1.76335167884827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84693038463593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81087696552277</t>
+    <t xml:space="preserve">1.8469306230545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81087708473206</t>
   </si>
   <si>
     <t xml:space="preserve">1.80923795700073</t>
@@ -632,25 +629,25 @@
     <t xml:space="preserve">1.86167991161346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86495745182037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85840225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87642896175385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89937233924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84856963157654</t>
+    <t xml:space="preserve">1.86495757102966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85840213298798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87642908096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89937257766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84856951236725</t>
   </si>
   <si>
     <t xml:space="preserve">1.92479634284973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93679428100586</t>
+    <t xml:space="preserve">1.93679392337799</t>
   </si>
   <si>
     <t xml:space="preserve">1.93850827217102</t>
@@ -659,19 +656,19 @@
     <t xml:space="preserve">1.97107374668121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92822444438934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94193601608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94365000724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95907580852509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9676456451416</t>
+    <t xml:space="preserve">1.92822420597076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94193613529205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94364988803864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95907592773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96764576435089</t>
   </si>
   <si>
     <t xml:space="preserve">1.92651033401489</t>
@@ -680,28 +677,28 @@
     <t xml:space="preserve">1.95393395423889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93336629867554</t>
+    <t xml:space="preserve">1.93336606025696</t>
   </si>
   <si>
     <t xml:space="preserve">1.90594255924225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89394474029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87166309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92993819713593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90080070495605</t>
+    <t xml:space="preserve">1.8939448595047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8716629743576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9299384355545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90080046653748</t>
   </si>
   <si>
     <t xml:space="preserve">1.91451239585876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88708865642548</t>
+    <t xml:space="preserve">1.88708889484406</t>
   </si>
   <si>
     <t xml:space="preserve">1.87680494785309</t>
@@ -710,19 +707,19 @@
     <t xml:space="preserve">1.91794049739838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88537490367889</t>
+    <t xml:space="preserve">1.8853747844696</t>
   </si>
   <si>
     <t xml:space="preserve">1.86994910240173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88880276679993</t>
+    <t xml:space="preserve">1.88880264759064</t>
   </si>
   <si>
     <t xml:space="preserve">1.90937042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90251445770264</t>
+    <t xml:space="preserve">1.90251469612122</t>
   </si>
   <si>
     <t xml:space="preserve">1.96421778202057</t>
@@ -731,43 +728,43 @@
     <t xml:space="preserve">1.96250379085541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821341991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98649966716766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964334487915</t>
+    <t xml:space="preserve">1.98821365833282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98649954795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97964358329773</t>
   </si>
   <si>
     <t xml:space="preserve">2.12533164024353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0859100818634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05677270889282</t>
+    <t xml:space="preserve">2.08591032028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05677247047424</t>
   </si>
   <si>
     <t xml:space="preserve">2.07905459403992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08076786994934</t>
+    <t xml:space="preserve">2.0807683467865</t>
   </si>
   <si>
     <t xml:space="preserve">2.06534242630005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06020069122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07219839096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13390135765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10819172859192</t>
+    <t xml:space="preserve">2.06020045280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07219862937927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13390159606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10819220542908</t>
   </si>
   <si>
     <t xml:space="preserve">2.09962201118469</t>
@@ -776,10 +773,10 @@
     <t xml:space="preserve">2.10304975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03963279724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06877064704895</t>
+    <t xml:space="preserve">2.03963303565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06877040863037</t>
   </si>
   <si>
     <t xml:space="preserve">2.11504769325256</t>
@@ -788,16 +785,16 @@
     <t xml:space="preserve">2.07391238212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09790802001953</t>
+    <t xml:space="preserve">2.09790778160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.1167619228363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08248233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06705641746521</t>
+    <t xml:space="preserve">2.08248209953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06705665588379</t>
   </si>
   <si>
     <t xml:space="preserve">2.12190365791321</t>
@@ -809,16 +806,16 @@
     <t xml:space="preserve">2.08933806419373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05163049697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17675113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14247155189514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13218760490417</t>
+    <t xml:space="preserve">2.05163073539734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17675089836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14247131347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1321873664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.13047361373901</t>
@@ -830,7 +827,7 @@
     <t xml:space="preserve">2.11847543716431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09105205535889</t>
+    <t xml:space="preserve">2.09105181694031</t>
   </si>
   <si>
     <t xml:space="preserve">2.12361764907837</t>
@@ -839,16 +836,16 @@
     <t xml:space="preserve">2.11161994934082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10133600234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15789723396301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15618300437927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1441855430603</t>
+    <t xml:space="preserve">2.10133576393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15789699554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15618348121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14418530464172</t>
   </si>
   <si>
     <t xml:space="preserve">2.1407573223114</t>
@@ -857,7 +854,7 @@
     <t xml:space="preserve">2.14932727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13904356956482</t>
+    <t xml:space="preserve">2.13904333114624</t>
   </si>
   <si>
     <t xml:space="preserve">2.17503690719604</t>
@@ -866,25 +863,25 @@
     <t xml:space="preserve">2.15104126930237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12018966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10476398468018</t>
+    <t xml:space="preserve">2.12018990516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1047637462616</t>
   </si>
   <si>
     <t xml:space="preserve">2.06362843513489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03277683258057</t>
+    <t xml:space="preserve">2.03277707099915</t>
   </si>
   <si>
     <t xml:space="preserve">2.04820275306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07048439979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04991674423218</t>
+    <t xml:space="preserve">2.07048416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0499165058136</t>
   </si>
   <si>
     <t xml:space="preserve">2.12875962257385</t>
@@ -902,55 +899,55 @@
     <t xml:space="preserve">2.0224928855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01392316818237</t>
+    <t xml:space="preserve">2.01392292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.00535321235657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1681809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18532061576843</t>
+    <t xml:space="preserve">2.16818118095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18532085418701</t>
   </si>
   <si>
     <t xml:space="preserve">2.29672932624817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33100914955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32243919372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35671854019165</t>
+    <t xml:space="preserve">2.33100891113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32243895530701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35671830177307</t>
   </si>
   <si>
     <t xml:space="preserve">2.44241738319397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49383687973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46812701225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47669720649719</t>
+    <t xml:space="preserve">2.49383664131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46812725067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47669696807861</t>
   </si>
   <si>
     <t xml:space="preserve">2.48526668548584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53668642044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57953548431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.596675157547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61381506919861</t>
+    <t xml:space="preserve">2.53668618202209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57953572273254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59667539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61381483078003</t>
   </si>
   <si>
     <t xml:space="preserve">2.55382585525513</t>
@@ -968,10 +965,10 @@
     <t xml:space="preserve">2.61655139923096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52694368362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.437335729599</t>
+    <t xml:space="preserve">2.52694344520569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43733549118042</t>
   </si>
   <si>
     <t xml:space="preserve">2.46421790122986</t>
@@ -980,19 +977,19 @@
     <t xml:space="preserve">2.50006103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45525741577148</t>
+    <t xml:space="preserve">2.45525717735291</t>
   </si>
   <si>
     <t xml:space="preserve">2.54486513137817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57174730300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51798295974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56278681755066</t>
+    <t xml:space="preserve">2.57174754142761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51798272132874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56278657913208</t>
   </si>
   <si>
     <t xml:space="preserve">2.53590416908264</t>
@@ -1001,25 +998,25 @@
     <t xml:space="preserve">2.4911003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48213958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5090217590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47317862510681</t>
+    <t xml:space="preserve">2.48213982582092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50902199745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47317886352539</t>
   </si>
   <si>
     <t xml:space="preserve">2.78680658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7599241733551</t>
+    <t xml:space="preserve">2.75992441177368</t>
   </si>
   <si>
     <t xml:space="preserve">2.77784562110901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7420027256012</t>
+    <t xml:space="preserve">2.74200248718262</t>
   </si>
   <si>
     <t xml:space="preserve">2.76888489723206</t>
@@ -1028,7 +1025,7 @@
     <t xml:space="preserve">2.71512007713318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75096344947815</t>
+    <t xml:space="preserve">2.75096321105957</t>
   </si>
   <si>
     <t xml:space="preserve">2.67031621932983</t>
@@ -1040,13 +1037,13 @@
     <t xml:space="preserve">2.65239477157593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68823766708374</t>
+    <t xml:space="preserve">2.68823790550232</t>
   </si>
   <si>
     <t xml:space="preserve">2.73304176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69719862937927</t>
+    <t xml:space="preserve">2.69719886779785</t>
   </si>
   <si>
     <t xml:space="preserve">2.67927694320679</t>
@@ -1055,10 +1052,10 @@
     <t xml:space="preserve">2.84953236579895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86745357513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83161067962646</t>
+    <t xml:space="preserve">2.86745381355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83161044120789</t>
   </si>
   <si>
     <t xml:space="preserve">2.6434338092804</t>
@@ -1067,7 +1064,7 @@
     <t xml:space="preserve">2.62551236152649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58070826530457</t>
+    <t xml:space="preserve">2.58070850372314</t>
   </si>
   <si>
     <t xml:space="preserve">2.607590675354</t>
@@ -1100,25 +1097,25 @@
     <t xml:space="preserve">2.90329670906067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12731647491455</t>
+    <t xml:space="preserve">3.12731671333313</t>
   </si>
   <si>
     <t xml:space="preserve">3.16315984725952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13627767562866</t>
+    <t xml:space="preserve">3.13627743721008</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004225730896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25276803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26172876358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28861117362976</t>
+    <t xml:space="preserve">3.25276780128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26172852516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28861093521118</t>
   </si>
   <si>
     <t xml:space="preserve">3.29757189750671</t>
@@ -1133,7 +1130,7 @@
     <t xml:space="preserve">3.34237575531006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42302274703979</t>
+    <t xml:space="preserve">3.42302298545837</t>
   </si>
   <si>
     <t xml:space="preserve">3.3871796131134</t>
@@ -1142,22 +1139,22 @@
     <t xml:space="preserve">3.40510129928589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41406178474426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3692581653595</t>
+    <t xml:space="preserve">3.41406202316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36925792694092</t>
   </si>
   <si>
     <t xml:space="preserve">3.37821888923645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45886588096619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4857485294342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47678780555725</t>
+    <t xml:space="preserve">3.45886564254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48574876785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47678756713867</t>
   </si>
   <si>
     <t xml:space="preserve">3.49470925331116</t>
@@ -1166,13 +1163,13 @@
     <t xml:space="preserve">3.67392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58431720733643</t>
+    <t xml:space="preserve">3.58431696891785</t>
   </si>
   <si>
     <t xml:space="preserve">3.53055238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59327793121338</t>
+    <t xml:space="preserve">3.59327816963196</t>
   </si>
   <si>
     <t xml:space="preserve">3.55743479728699</t>
@@ -1205,43 +1202,46 @@
     <t xml:space="preserve">3.6918466091156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70976781845093</t>
+    <t xml:space="preserve">3.70976805686951</t>
   </si>
   <si>
     <t xml:space="preserve">3.68288588523865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76353311538696</t>
+    <t xml:space="preserve">3.7635326385498</t>
   </si>
   <si>
     <t xml:space="preserve">3.78145432472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80833697319031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79041528701782</t>
+    <t xml:space="preserve">3.80833721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79041504859924</t>
   </si>
   <si>
     <t xml:space="preserve">3.95170950889587</t>
   </si>
   <si>
+    <t xml:space="preserve">3.96067070960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97005581855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00759792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0920672416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81988835334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87620115280151</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.96067023277283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97005581855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00759792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0920672416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81988835334778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87620115280151</t>
   </si>
   <si>
     <t xml:space="preserve">4.02636861801147</t>
@@ -6257,7 +6257,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -6283,7 +6283,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -6309,7 +6309,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -6335,7 +6335,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G139" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -6361,7 +6361,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -6387,7 +6387,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -6439,7 +6439,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G143" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -6465,7 +6465,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G144" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -6491,7 +6491,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -6517,7 +6517,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -6543,7 +6543,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -6569,7 +6569,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G148" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -6595,7 +6595,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -6621,7 +6621,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G150" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -6647,7 +6647,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G151" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -6673,7 +6673,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -6699,7 +6699,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G153" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -6725,7 +6725,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G154" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -6751,7 +6751,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G155" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -6777,7 +6777,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -6803,7 +6803,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -6829,7 +6829,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -6855,7 +6855,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -6881,7 +6881,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G160" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -6907,7 +6907,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G161" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -6933,7 +6933,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G162" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -6959,7 +6959,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G163" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -6985,7 +6985,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G164" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -7011,7 +7011,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G165" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -7037,7 +7037,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G166" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7063,7 +7063,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G167" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7089,7 +7089,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G168" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7115,7 +7115,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G169" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7141,7 +7141,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7167,7 +7167,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G171" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7193,7 +7193,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -7219,7 +7219,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -7245,7 +7245,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G174" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -7271,7 +7271,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7297,7 +7297,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G176" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7323,7 +7323,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G177" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -7349,7 +7349,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G178" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7375,7 +7375,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G179" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7401,7 +7401,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G180" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7427,7 +7427,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G181" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7453,7 +7453,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G182" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7479,7 +7479,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G183" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7505,7 +7505,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G184" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -7531,7 +7531,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G185" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -7557,7 +7557,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G186" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7583,7 +7583,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G187" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7609,7 +7609,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G188" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7635,7 +7635,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G189" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7661,7 +7661,7 @@
         <v>2</v>
       </c>
       <c r="G190" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7687,7 +7687,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G191" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -7713,7 +7713,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G192" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7739,7 +7739,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G193" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -7765,7 +7765,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G194" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -7791,7 +7791,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G195" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -7817,7 +7817,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G196" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -7843,7 +7843,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -7869,7 +7869,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -7895,7 +7895,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -7921,7 +7921,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -7947,7 +7947,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -7973,7 +7973,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -7999,7 +7999,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8025,7 +8025,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -8051,7 +8051,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8077,7 +8077,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G206" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -8103,7 +8103,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G207" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8129,7 +8129,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8155,7 +8155,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G209" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8181,7 +8181,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8207,7 +8207,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G211" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -8233,7 +8233,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G212" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8259,7 +8259,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G213" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8285,7 +8285,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G214" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8311,7 +8311,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8337,7 +8337,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G216" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8363,7 +8363,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8389,7 +8389,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8415,7 +8415,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G219" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8441,7 +8441,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G220" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8467,7 +8467,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G221" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8493,7 +8493,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G222" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8519,7 +8519,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G223" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8545,7 +8545,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G224" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8571,7 +8571,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8597,7 +8597,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G226" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8623,7 +8623,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8649,7 +8649,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8675,7 +8675,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G229" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8701,7 +8701,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8727,7 +8727,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G231" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8753,7 +8753,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G232" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8779,7 +8779,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G233" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8805,7 +8805,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G234" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -8831,7 +8831,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G235" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -8857,7 +8857,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G236" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -8883,7 +8883,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G237" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -8909,7 +8909,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G238" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -8935,7 +8935,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G239" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -8961,7 +8961,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G240" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -8987,7 +8987,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9013,7 +9013,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9039,7 +9039,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9065,7 +9065,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G244" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9091,7 +9091,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9117,7 +9117,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G246" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9143,7 +9143,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G247" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9169,7 +9169,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G248" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9195,7 +9195,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G249" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9221,7 +9221,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G250" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9247,7 +9247,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9273,7 +9273,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G252" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9299,7 +9299,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G253" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9325,7 +9325,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G254" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9351,7 +9351,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9377,7 +9377,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G256" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9403,7 +9403,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G257" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9429,7 +9429,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G258" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9455,7 +9455,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G259" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9481,7 +9481,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9507,7 +9507,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G261" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9533,7 +9533,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G262" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9559,7 +9559,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9585,7 +9585,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G264" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9611,7 +9611,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G265" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9637,7 +9637,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G266" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9663,7 +9663,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G267" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9689,7 +9689,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G268" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9715,7 +9715,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9741,7 +9741,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G270" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9767,7 +9767,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G271" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -9793,7 +9793,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -9819,7 +9819,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9845,7 +9845,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G274" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -9871,7 +9871,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G275" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -9897,7 +9897,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G276" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9923,7 +9923,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G277" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9949,7 +9949,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G278" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -9975,7 +9975,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G279" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10001,7 +10001,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G280" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10027,7 +10027,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G281" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10053,7 +10053,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10079,7 +10079,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G283" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10105,7 +10105,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G284" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10131,7 +10131,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G285" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10157,7 +10157,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G286" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10183,7 +10183,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G287" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10209,7 +10209,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10235,7 +10235,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G289" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10261,7 +10261,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G290" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10287,7 +10287,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G291" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10313,7 +10313,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10339,7 +10339,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G293" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10365,7 +10365,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G294" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10391,7 +10391,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G295" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10417,7 +10417,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G296" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10443,7 +10443,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G297" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10469,7 +10469,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G298" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10495,7 +10495,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -10521,7 +10521,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G300" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10547,7 +10547,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G301" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -10573,7 +10573,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G302" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10599,7 +10599,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10625,7 +10625,7 @@
         <v>1.875</v>
       </c>
       <c r="G304" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10651,7 +10651,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G305" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10677,7 +10677,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G306" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -10703,7 +10703,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G307" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -10729,7 +10729,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G308" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10755,7 +10755,7 @@
         <v>2</v>
       </c>
       <c r="G309" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -10781,7 +10781,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10807,7 +10807,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -10833,7 +10833,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -10859,7 +10859,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G313" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10885,7 +10885,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G314" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -10911,7 +10911,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10937,7 +10937,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10963,7 +10963,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G317" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11015,7 +11015,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11041,7 +11041,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11067,7 +11067,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11093,7 +11093,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11119,7 +11119,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11145,7 +11145,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11171,7 +11171,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11223,7 +11223,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G327" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11249,7 +11249,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11275,7 +11275,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11301,7 +11301,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11327,7 +11327,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11353,7 +11353,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G332" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11379,7 +11379,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11405,7 +11405,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11431,7 +11431,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G335" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11457,7 +11457,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11561,7 +11561,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11587,7 +11587,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G341" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11613,7 +11613,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11639,7 +11639,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11665,7 +11665,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G344" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -11717,7 +11717,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G346" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -11743,7 +11743,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G347" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11769,7 +11769,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -11795,7 +11795,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G349" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -11821,7 +11821,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -11873,7 +11873,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11899,7 +11899,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G353" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11951,7 +11951,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G355" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11977,7 +11977,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12003,7 +12003,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G357" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12029,7 +12029,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12055,7 +12055,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12081,7 +12081,7 @@
         <v>2.25</v>
       </c>
       <c r="G360" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12107,7 +12107,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12133,7 +12133,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12159,7 +12159,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G363" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12185,7 +12185,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G364" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12211,7 +12211,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12237,7 +12237,7 @@
         <v>2.25</v>
       </c>
       <c r="G366" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12263,7 +12263,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12289,7 +12289,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12315,7 +12315,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12341,7 +12341,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12367,7 +12367,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12393,7 +12393,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12419,7 +12419,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G373" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12445,7 +12445,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G374" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12471,7 +12471,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G375" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12497,7 +12497,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G376" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12523,7 +12523,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G377" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12549,7 +12549,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12575,7 +12575,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12601,7 +12601,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G380" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12627,7 +12627,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G381" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12653,7 +12653,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G382" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12679,7 +12679,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12705,7 +12705,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G384" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12731,7 +12731,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G385" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12757,7 +12757,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12783,7 +12783,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G387" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12809,7 +12809,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G388" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -12835,7 +12835,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G389" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -12861,7 +12861,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -12887,7 +12887,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G391" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -12913,7 +12913,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -12939,7 +12939,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G393" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -12965,7 +12965,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -12991,7 +12991,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G395" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13017,7 +13017,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13043,7 +13043,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13069,7 +13069,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13095,7 +13095,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G399" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13121,7 +13121,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G400" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13147,7 +13147,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G401" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13173,7 +13173,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13199,7 +13199,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G403" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13225,7 +13225,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13251,7 +13251,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G405" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13277,7 +13277,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13303,7 +13303,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13329,7 +13329,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13355,7 +13355,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G409" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13381,7 +13381,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G410" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13407,7 +13407,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G411" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13433,7 +13433,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13459,7 +13459,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G413" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13485,7 +13485,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G414" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13511,7 +13511,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G415" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13537,7 +13537,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G416" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13563,7 +13563,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G417" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13589,7 +13589,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G418" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13615,7 +13615,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G419" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13641,7 +13641,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G420" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13667,7 +13667,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G421" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13693,7 +13693,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G422" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13719,7 +13719,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13745,7 +13745,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G424" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13771,7 +13771,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G425" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13797,7 +13797,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G426" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -13823,7 +13823,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G427" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -13849,7 +13849,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G428" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -13875,7 +13875,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G429" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -13901,7 +13901,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G430" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -13927,7 +13927,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G431" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -13953,7 +13953,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -13979,7 +13979,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G433" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14005,7 +14005,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G434" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14031,7 +14031,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G435" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14057,7 +14057,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G436" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14083,7 +14083,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G437" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14109,7 +14109,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G438" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14135,7 +14135,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G439" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14161,7 +14161,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G440" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14187,7 +14187,7 @@
         <v>2.5</v>
       </c>
       <c r="G441" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14213,7 +14213,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G442" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14239,7 +14239,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G443" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14265,7 +14265,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G444" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14291,7 +14291,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G445" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14317,7 +14317,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14343,7 +14343,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G447" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14369,7 +14369,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G448" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14395,7 +14395,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G449" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14421,7 +14421,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G450" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14447,7 +14447,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G451" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14473,7 +14473,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G452" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14499,7 +14499,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G453" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14525,7 +14525,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G454" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14551,7 +14551,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G455" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14577,7 +14577,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G456" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14603,7 +14603,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G457" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14629,7 +14629,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G458" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14655,7 +14655,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G459" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14681,7 +14681,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G460" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14707,7 +14707,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G461" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14733,7 +14733,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G462" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14759,7 +14759,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G463" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14785,7 +14785,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G464" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -14811,7 +14811,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -14837,7 +14837,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G466" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -14863,7 +14863,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G467" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -14889,7 +14889,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G468" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -14915,7 +14915,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G469" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -14941,7 +14941,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G470" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -14967,7 +14967,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G471" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -14993,7 +14993,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15019,7 +15019,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G473" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15045,7 +15045,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15071,7 +15071,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G475" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15097,7 +15097,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G476" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15123,7 +15123,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G477" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15149,7 +15149,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G478" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15175,7 +15175,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G479" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15201,7 +15201,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G480" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15227,7 +15227,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15253,7 +15253,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G482" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15279,7 +15279,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G483" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15305,7 +15305,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G484" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15331,7 +15331,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G485" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15357,7 +15357,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G486" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15383,7 +15383,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15409,7 +15409,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G488" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15435,7 +15435,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G489" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15461,7 +15461,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G490" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15487,7 +15487,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G491" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15513,7 +15513,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15539,7 +15539,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G493" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15565,7 +15565,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G494" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15591,7 +15591,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15617,7 +15617,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G496" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15643,7 +15643,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G497" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15669,7 +15669,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G498" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15695,7 +15695,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G499" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15721,7 +15721,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G500" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15747,7 +15747,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G501" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15773,7 +15773,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G502" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15799,7 +15799,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G503" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -15825,7 +15825,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G504" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -15851,7 +15851,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G505" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -15877,7 +15877,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G506" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -15903,7 +15903,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G507" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -15929,7 +15929,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G508" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -15955,7 +15955,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G509" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -15981,7 +15981,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G510" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16007,7 +16007,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G511" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16033,7 +16033,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G512" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16059,7 +16059,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G513" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16085,7 +16085,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G514" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16111,7 +16111,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G515" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16137,7 +16137,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G516" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16163,7 +16163,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G517" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16189,7 +16189,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G518" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16215,7 +16215,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G519" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16241,7 +16241,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G520" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16267,7 +16267,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G521" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16293,7 +16293,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16319,7 +16319,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G523" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16345,7 +16345,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G524" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16371,7 +16371,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G525" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16397,7 +16397,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G526" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16423,7 +16423,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G527" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16449,7 +16449,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G528" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16475,7 +16475,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G529" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16501,7 +16501,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16527,7 +16527,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G531" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16553,7 +16553,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G532" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16579,7 +16579,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G533" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16605,7 +16605,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G534" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16631,7 +16631,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G535" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16657,7 +16657,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G536" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16683,7 +16683,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G537" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16709,7 +16709,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G538" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16735,7 +16735,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G539" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16761,7 +16761,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G540" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16787,7 +16787,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G541" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -16813,7 +16813,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G542" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -16839,7 +16839,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G543" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -16865,7 +16865,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G544" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -16891,7 +16891,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G545" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16917,7 +16917,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G546" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16943,7 +16943,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G547" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16969,7 +16969,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G548" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -16995,7 +16995,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G549" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17021,7 +17021,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G550" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17047,7 +17047,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G551" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17073,7 +17073,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G552" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17099,7 +17099,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G553" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17125,7 +17125,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G554" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17151,7 +17151,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17177,7 +17177,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G556" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17203,7 +17203,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G557" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17229,7 +17229,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17255,7 +17255,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17281,7 +17281,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17307,7 +17307,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17333,7 +17333,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G562" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17359,7 +17359,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G563" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17385,7 +17385,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17411,7 +17411,7 @@
         <v>2.5</v>
       </c>
       <c r="G565" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17437,7 +17437,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17463,7 +17463,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G567" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17489,7 +17489,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G568" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17515,7 +17515,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G569" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17541,7 +17541,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G570" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17567,7 +17567,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G571" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17593,7 +17593,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G572" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17619,7 +17619,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G573" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17645,7 +17645,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G574" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17671,7 +17671,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G575" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17697,7 +17697,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17723,7 +17723,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G577" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17749,7 +17749,7 @@
         <v>2.5</v>
       </c>
       <c r="G578" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17775,7 +17775,7 @@
         <v>2.5</v>
       </c>
       <c r="G579" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17801,7 +17801,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G580" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -17827,7 +17827,7 @@
         <v>2.5</v>
       </c>
       <c r="G581" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -17853,7 +17853,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -17879,7 +17879,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -17905,7 +17905,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -17931,7 +17931,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -17957,7 +17957,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -17983,7 +17983,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G587" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18009,7 +18009,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18035,7 +18035,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G589" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18061,7 +18061,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G590" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18087,7 +18087,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G591" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18113,7 +18113,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G592" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18139,7 +18139,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G593" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18165,7 +18165,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G594" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18191,7 +18191,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G595" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18217,7 +18217,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18243,7 +18243,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18269,7 +18269,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G598" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18295,7 +18295,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G599" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18321,7 +18321,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G600" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18347,7 +18347,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18373,7 +18373,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18399,7 +18399,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G603" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18425,7 +18425,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G604" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18451,7 +18451,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G605" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18477,7 +18477,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G606" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18503,7 +18503,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G607" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18529,7 +18529,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G608" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18555,7 +18555,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G609" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18581,7 +18581,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G610" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18607,7 +18607,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G611" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18633,7 +18633,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18659,7 +18659,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G613" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18685,7 +18685,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G614" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18711,7 +18711,7 @@
         <v>2.75</v>
       </c>
       <c r="G615" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18737,7 +18737,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G616" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18763,7 +18763,7 @@
         <v>2.75</v>
       </c>
       <c r="G617" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18789,7 +18789,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G618" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18815,7 +18815,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G619" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18841,7 +18841,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G620" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18867,7 +18867,7 @@
         <v>2.75</v>
       </c>
       <c r="G621" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18893,7 +18893,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G622" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18919,7 +18919,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18945,7 +18945,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18971,7 +18971,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -18997,7 +18997,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19023,7 +19023,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G627" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19049,7 +19049,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G628" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19075,7 +19075,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G629" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19101,7 +19101,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G630" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19127,7 +19127,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19153,7 +19153,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G632" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19179,7 +19179,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19205,7 +19205,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G634" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19231,7 +19231,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G635" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19257,7 +19257,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G636" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19283,7 +19283,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19309,7 +19309,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19335,7 +19335,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19361,7 +19361,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19387,7 +19387,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19413,7 +19413,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19439,7 +19439,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19465,7 +19465,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19491,7 +19491,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19517,7 +19517,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19543,7 +19543,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G647" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19569,7 +19569,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G648" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19595,7 +19595,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G649" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19621,7 +19621,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G650" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19647,7 +19647,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G651" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19673,7 +19673,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G652" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19699,7 +19699,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G653" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19725,7 +19725,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G654" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19751,7 +19751,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19777,7 +19777,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G656" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19803,7 +19803,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -19829,7 +19829,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G658" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -19855,7 +19855,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19881,7 +19881,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G660" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19907,7 +19907,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G661" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19933,7 +19933,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G662" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19959,7 +19959,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G663" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19985,7 +19985,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G664" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20011,7 +20011,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20037,7 +20037,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20063,7 +20063,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20089,7 +20089,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20115,7 +20115,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G669" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20141,7 +20141,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G670" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20167,7 +20167,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20193,7 +20193,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G672" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20219,7 +20219,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G673" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20245,7 +20245,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20271,7 +20271,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20297,7 +20297,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G676" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20323,7 +20323,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20349,7 +20349,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20375,7 +20375,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G679" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20401,7 +20401,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20427,7 +20427,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G681" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20453,7 +20453,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20479,7 +20479,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20505,7 +20505,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20531,7 +20531,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20557,7 +20557,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20583,7 +20583,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20609,7 +20609,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20635,7 +20635,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20661,7 +20661,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20687,7 +20687,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20713,7 +20713,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G692" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20739,7 +20739,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20765,7 +20765,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20791,7 +20791,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20817,7 +20817,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20843,7 +20843,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20869,7 +20869,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -20895,7 +20895,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -20921,7 +20921,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -20947,7 +20947,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -20973,7 +20973,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20999,7 +20999,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21025,7 +21025,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21051,7 +21051,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21077,7 +21077,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21103,7 +21103,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21129,7 +21129,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G708" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21155,7 +21155,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G709" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21181,7 +21181,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G710" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21207,7 +21207,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G711" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21233,7 +21233,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21259,7 +21259,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G713" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21285,7 +21285,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G714" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21311,7 +21311,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G715" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21337,7 +21337,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G716" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21363,7 +21363,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G717" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21389,7 +21389,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21415,7 +21415,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G719" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21441,7 +21441,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G720" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21467,7 +21467,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G721" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21493,7 +21493,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G722" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21519,7 +21519,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G723" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21545,7 +21545,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G724" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21571,7 +21571,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G725" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21597,7 +21597,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G726" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21623,7 +21623,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G727" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21649,7 +21649,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21675,7 +21675,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G729" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21701,7 +21701,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21727,7 +21727,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G731" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21753,7 +21753,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G732" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21779,7 +21779,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G733" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21805,7 +21805,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G734" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21831,7 +21831,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G735" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21857,7 +21857,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G736" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21883,7 +21883,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G737" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21909,7 +21909,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21935,7 +21935,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G739" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21961,7 +21961,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21987,7 +21987,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G741" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22013,7 +22013,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G742" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22039,7 +22039,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G743" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22065,7 +22065,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G744" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22091,7 +22091,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G745" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22117,7 +22117,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22143,7 +22143,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22169,7 +22169,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22195,7 +22195,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G749" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22221,7 +22221,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22247,7 +22247,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22273,7 +22273,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22299,7 +22299,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22325,7 +22325,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22351,7 +22351,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22377,7 +22377,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22403,7 +22403,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22429,7 +22429,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22455,7 +22455,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G759" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22481,7 +22481,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G760" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22507,7 +22507,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G761" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22533,7 +22533,7 @@
         <v>2.75</v>
       </c>
       <c r="G762" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22559,7 +22559,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22585,7 +22585,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22611,7 +22611,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22637,7 +22637,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G766" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22663,7 +22663,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22689,7 +22689,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G768" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22715,7 +22715,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22741,7 +22741,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22767,7 +22767,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22793,7 +22793,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22819,7 +22819,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22845,7 +22845,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22871,7 +22871,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22897,7 +22897,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22923,7 +22923,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22949,7 +22949,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22975,7 +22975,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G779" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23001,7 +23001,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23027,7 +23027,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23053,7 +23053,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G782" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23079,7 +23079,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23105,7 +23105,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G784" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23131,7 +23131,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G785" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23157,7 +23157,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23183,7 +23183,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G787" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23209,7 +23209,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G788" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23235,7 +23235,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G789" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23261,7 +23261,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23287,7 +23287,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G791" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23313,7 +23313,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G792" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23339,7 +23339,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G793" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23365,7 +23365,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23391,7 +23391,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23417,7 +23417,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23443,7 +23443,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G797" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23469,7 +23469,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G798" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23495,7 +23495,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23521,7 +23521,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G800" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23547,7 +23547,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23573,7 +23573,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G802" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23599,7 +23599,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23625,7 +23625,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G804" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23651,7 +23651,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23677,7 +23677,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23703,7 +23703,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G807" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23729,7 +23729,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G808" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23755,7 +23755,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G809" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23781,7 +23781,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G810" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23807,7 +23807,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G811" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23833,7 +23833,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23859,7 +23859,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G813" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23885,7 +23885,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G814" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23911,7 +23911,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23937,7 +23937,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G816" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23963,7 +23963,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23989,7 +23989,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G818" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24015,7 +24015,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24041,7 +24041,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G820" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24067,7 +24067,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G821" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24093,7 +24093,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24119,7 +24119,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G823" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24145,7 +24145,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G824" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24171,7 +24171,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G825" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24197,7 +24197,7 @@
         <v>4</v>
       </c>
       <c r="G826" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24223,7 +24223,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G827" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24249,7 +24249,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G828" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24275,7 +24275,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G829" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24301,7 +24301,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G830" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24327,7 +24327,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24353,7 +24353,7 @@
         <v>4</v>
       </c>
       <c r="G832" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24379,7 +24379,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24405,7 +24405,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24431,7 +24431,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24457,7 +24457,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G836" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24483,7 +24483,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24509,7 +24509,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24535,7 +24535,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G839" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24561,7 +24561,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24587,7 +24587,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G841" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24613,7 +24613,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G842" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24639,7 +24639,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24665,7 +24665,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G844" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24691,7 +24691,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G845" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24717,7 +24717,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24743,7 +24743,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24769,7 +24769,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24795,7 +24795,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24821,7 +24821,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G850" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24847,7 +24847,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24873,7 +24873,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24899,7 +24899,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G853" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24925,7 +24925,7 @@
         <v>4.25</v>
       </c>
       <c r="G854" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24951,7 +24951,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24977,7 +24977,7 @@
         <v>4.25</v>
       </c>
       <c r="G856" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25003,7 +25003,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G857" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25029,7 +25029,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G858" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25055,7 +25055,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G859" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25081,7 +25081,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25107,7 +25107,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G861" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25133,7 +25133,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G862" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25159,7 +25159,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G863" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25185,7 +25185,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G864" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25211,7 +25211,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G865" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25263,7 +25263,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G867" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25367,7 +25367,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25419,7 +25419,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G873" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25549,7 +25549,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G878" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25913,7 +25913,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G892" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25991,7 +25991,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G895" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26225,7 +26225,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G904" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -30411,7 +30411,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1065" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30697,7 +30697,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1076" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30723,7 +30723,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1077" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30957,7 +30957,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1086" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31321,7 +31321,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1100" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31425,7 +31425,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1104" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32933,7 +32933,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1162" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32959,7 +32959,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1163" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33401,7 +33401,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1180" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33531,7 +33531,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1185" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33739,7 +33739,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1193" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -68223,7 +68223,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6063425926</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>200</v>
@@ -68244,6 +68244,32 @@
         <v>788</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6004976852</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>8250</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>786</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825955867767</t>
+    <t xml:space="preserve">1.85825932025909</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91323781013489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109167575836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88496315479279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9242330789566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80642282962799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82998490333557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79856908321381</t>
+    <t xml:space="preserve">1.9132376909256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109155654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8849630355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92423331737518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80642306804657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82998514175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79856896400452</t>
   </si>
   <si>
     <t xml:space="preserve">1.76715290546417</t>
@@ -74,97 +74,97 @@
     <t xml:space="preserve">1.86925506591797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87710916996002</t>
+    <t xml:space="preserve">1.87710905075073</t>
   </si>
   <si>
     <t xml:space="preserve">1.89281725883484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86768436431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81584775447845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83783888816833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87553811073303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684350013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84569299221039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898939609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83626818656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85983026027679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80485212802887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82056021690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81741857528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85040521621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88025057315826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81427693367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85197651386261</t>
+    <t xml:space="preserve">1.86768412590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81584787368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83783912658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553834915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684338092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8456928730011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8189891576767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83626806735992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8598301410675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80485224723816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82056033611298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81741845607758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85040545463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88025045394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81427669525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85197639465332</t>
   </si>
   <si>
     <t xml:space="preserve">1.84412217140198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84098076820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82370185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81113541126251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8221310377121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9367995262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622445106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407855510712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.963503241539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96507394313812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99334871768951</t>
+    <t xml:space="preserve">1.84098064899445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82370162010193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8111355304718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82213079929352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679964542389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622433185577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407843589783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96350312232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9650741815567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99334859848022</t>
   </si>
   <si>
     <t xml:space="preserve">2.00434422492981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98706519603729</t>
+    <t xml:space="preserve">1.987065076828</t>
   </si>
   <si>
     <t xml:space="preserve">2.00905656814575</t>
@@ -173,73 +173,73 @@
     <t xml:space="preserve">2.02476453781128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93051636219025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96193242073059</t>
+    <t xml:space="preserve">1.93051624298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9619323015213</t>
   </si>
   <si>
     <t xml:space="preserve">1.93994116783142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95564937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637921333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8739675283432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378722667694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92231559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050920963287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509159564972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95836937427521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739916801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9354259967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198107719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91248285770416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91084396839142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545911312103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80268287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84201407432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83218157291412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88298439979553</t>
+    <t xml:space="preserve">1.95564901828766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637909412384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87396764755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378698825836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017516613007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9223153591156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9665629863739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9583694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739904880524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542587757111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9419811964035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91248309612274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91084420681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545899391174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8026829957962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84201395511627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83218145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
     <t xml:space="preserve">1.86823499202728</t>
@@ -254,16 +254,16 @@
     <t xml:space="preserve">1.90592741966248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8846230506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9092048406601</t>
+    <t xml:space="preserve">1.88462293148041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920519828796</t>
   </si>
   <si>
     <t xml:space="preserve">1.87151265144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8977335691452</t>
+    <t xml:space="preserve">1.89773344993591</t>
   </si>
   <si>
     <t xml:space="preserve">1.82398736476898</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">1.75351893901825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77973961830139</t>
+    <t xml:space="preserve">1.77973973751068</t>
   </si>
   <si>
     <t xml:space="preserve">1.75024127960205</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">1.76007401943207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70435476303101</t>
+    <t xml:space="preserve">1.70435464382172</t>
   </si>
   <si>
     <t xml:space="preserve">1.73549211025238</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">1.63060867786407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67157864570618</t>
+    <t xml:space="preserve">1.67157876491547</t>
   </si>
   <si>
     <t xml:space="preserve">1.66666233539581</t>
@@ -332,28 +332,28 @@
     <t xml:space="preserve">1.61012363433838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62241470813751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66338455677032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67321765422821</t>
+    <t xml:space="preserve">1.62241458892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66338467597961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67321753501892</t>
   </si>
   <si>
     <t xml:space="preserve">1.64535784721375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63880252838135</t>
+    <t xml:space="preserve">1.63880276679993</t>
   </si>
   <si>
     <t xml:space="preserve">1.62569224834442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66830122470856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65519082546234</t>
+    <t xml:space="preserve">1.66830110549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65519070625305</t>
   </si>
   <si>
     <t xml:space="preserve">1.64699673652649</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">1.62978911399841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58308351039886</t>
+    <t xml:space="preserve">1.58308339118958</t>
   </si>
   <si>
     <t xml:space="preserve">1.59537446498871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.578986287117</t>
+    <t xml:space="preserve">1.57898640632629</t>
   </si>
   <si>
     <t xml:space="preserve">1.59127736091614</t>
@@ -383,13 +383,13 @@
     <t xml:space="preserve">1.54047453403473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56751477718353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56997287273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56669533252716</t>
+    <t xml:space="preserve">1.56751465797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56997299194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56669521331787</t>
   </si>
   <si>
     <t xml:space="preserve">1.55850124359131</t>
@@ -401,22 +401,22 @@
     <t xml:space="preserve">1.60356843471527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60602676868439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51916992664337</t>
+    <t xml:space="preserve">1.6060266494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51917004585266</t>
   </si>
   <si>
     <t xml:space="preserve">1.5617790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54539096355438</t>
+    <t xml:space="preserve">1.54539108276367</t>
   </si>
   <si>
     <t xml:space="preserve">1.37659418582916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4126478433609</t>
+    <t xml:space="preserve">1.41264796257019</t>
   </si>
   <si>
     <t xml:space="preserve">1.39462113380432</t>
@@ -425,13 +425,13 @@
     <t xml:space="preserve">1.45771503448486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47082543373108</t>
+    <t xml:space="preserve">1.47082531452179</t>
   </si>
   <si>
     <t xml:space="preserve">1.53391933441162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61258172988892</t>
+    <t xml:space="preserve">1.61258184909821</t>
   </si>
   <si>
     <t xml:space="preserve">1.61176240444183</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">1.59783267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54211318492889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51179552078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55522382259369</t>
+    <t xml:space="preserve">1.54211330413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51179540157318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5552237033844</t>
   </si>
   <si>
     <t xml:space="preserve">1.56505644321442</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">1.56423723697662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59291625022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55686259269714</t>
+    <t xml:space="preserve">1.59291636943817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55686247348785</t>
   </si>
   <si>
     <t xml:space="preserve">1.52162837982178</t>
@@ -467,22 +467,22 @@
     <t xml:space="preserve">1.5412939786911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50442087650299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5109760761261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55112683773041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589250564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55194616317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50851774215698</t>
+    <t xml:space="preserve">1.5044207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51097619533539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55112671852112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589238643646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55194628238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50851786136627</t>
   </si>
   <si>
     <t xml:space="preserve">1.53228056430817</t>
@@ -491,13 +491,13 @@
     <t xml:space="preserve">1.50933742523193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5076984167099</t>
+    <t xml:space="preserve">1.50769853591919</t>
   </si>
   <si>
     <t xml:space="preserve">1.50278210639954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49540746212006</t>
+    <t xml:space="preserve">1.49540734291077</t>
   </si>
   <si>
     <t xml:space="preserve">1.51015675067902</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">1.58554148674011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59455490112305</t>
+    <t xml:space="preserve">1.59455502033234</t>
   </si>
   <si>
     <t xml:space="preserve">1.60684597492218</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">1.62159526348114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57161176204681</t>
+    <t xml:space="preserve">1.5716118812561</t>
   </si>
   <si>
     <t xml:space="preserve">1.54375207424164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57243132591248</t>
+    <t xml:space="preserve">1.57243120670319</t>
   </si>
   <si>
     <t xml:space="preserve">1.58718037605286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54621040821075</t>
+    <t xml:space="preserve">1.54621028900146</t>
   </si>
   <si>
     <t xml:space="preserve">1.55768191814423</t>
@@ -542,31 +542,31 @@
     <t xml:space="preserve">1.5347386598587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58226406574249</t>
+    <t xml:space="preserve">1.5822639465332</t>
   </si>
   <si>
     <t xml:space="preserve">1.54702973365784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53883576393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54784917831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55276548862457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54948794841766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5380163192749</t>
+    <t xml:space="preserve">1.53883564472198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54784905910492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55276560783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54948782920837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53801620006561</t>
   </si>
   <si>
     <t xml:space="preserve">1.54866850376129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53637742996216</t>
+    <t xml:space="preserve">1.53637754917145</t>
   </si>
   <si>
     <t xml:space="preserve">1.53965508937836</t>
@@ -584,22 +584,22 @@
     <t xml:space="preserve">1.65355169773102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82070958614349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82890379428864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81743204593658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579339504242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87970650196075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79448902606964</t>
+    <t xml:space="preserve">1.82070970535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82890391349792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81743216514587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81579351425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87970674037933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79448890686035</t>
   </si>
   <si>
     <t xml:space="preserve">1.80104410648346</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">1.73876953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729814052582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74696373939514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76335144042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84693038463593</t>
+    <t xml:space="preserve">1.72729825973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74696362018585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76335155963898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8469306230545</t>
   </si>
   <si>
     <t xml:space="preserve">1.81087708473206</t>
@@ -626,61 +626,61 @@
     <t xml:space="preserve">1.80923819541931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81251573562622</t>
+    <t xml:space="preserve">1.81251561641693</t>
   </si>
   <si>
     <t xml:space="preserve">1.86167979240417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86495745182037</t>
+    <t xml:space="preserve">1.86495757102966</t>
   </si>
   <si>
     <t xml:space="preserve">1.85840213298798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87642908096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89937257766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84856963157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92479622364044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679404258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850815296173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9710738658905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822432518005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94193637371063</t>
+    <t xml:space="preserve">1.87642884254456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89937233924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84856975078583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92479646205902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679428100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850803375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107350826263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822444438934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94193601608276</t>
   </si>
   <si>
     <t xml:space="preserve">1.94364988803864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95907604694366</t>
+    <t xml:space="preserve">1.95907580852509</t>
   </si>
   <si>
     <t xml:space="preserve">1.96764576435089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9265102148056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95393395423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93336629867554</t>
+    <t xml:space="preserve">1.92651033401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95393407344818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93336641788483</t>
   </si>
   <si>
     <t xml:space="preserve">1.90594255924225</t>
@@ -695,43 +695,43 @@
     <t xml:space="preserve">1.92993855476379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90080046653748</t>
+    <t xml:space="preserve">1.90080070495605</t>
   </si>
   <si>
     <t xml:space="preserve">1.91451239585876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88708889484406</t>
+    <t xml:space="preserve">1.88708865642548</t>
   </si>
   <si>
     <t xml:space="preserve">1.87680494785309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91794049739838</t>
+    <t xml:space="preserve">1.9179402589798</t>
   </si>
   <si>
     <t xml:space="preserve">1.8853747844696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86994910240173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88880276679993</t>
+    <t xml:space="preserve">1.86994886398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88880300521851</t>
   </si>
   <si>
     <t xml:space="preserve">1.90937054157257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90251457691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96421802043915</t>
+    <t xml:space="preserve">1.90251469612122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96421790122986</t>
   </si>
   <si>
     <t xml:space="preserve">1.96250379085541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821341991425</t>
+    <t xml:space="preserve">1.98821353912354</t>
   </si>
   <si>
     <t xml:space="preserve">1.98649966716766</t>
@@ -740,49 +740,49 @@
     <t xml:space="preserve">1.97964346408844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12533140182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0859100818634</t>
+    <t xml:space="preserve">2.12533164024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08591032028198</t>
   </si>
   <si>
     <t xml:space="preserve">2.05677270889282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07905459403992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08076810836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06534218788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06020069122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07219862937927</t>
+    <t xml:space="preserve">2.07905411720276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0807683467865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06534242630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06020045280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07219815254211</t>
   </si>
   <si>
     <t xml:space="preserve">2.13390159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1081919670105</t>
+    <t xml:space="preserve">2.10819172859192</t>
   </si>
   <si>
     <t xml:space="preserve">2.09962201118469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10304975509644</t>
+    <t xml:space="preserve">2.10304999351501</t>
   </si>
   <si>
     <t xml:space="preserve">2.03963279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06877064704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11504769325256</t>
+    <t xml:space="preserve">2.06877040863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11504793167114</t>
   </si>
   <si>
     <t xml:space="preserve">2.07391238212585</t>
@@ -794,43 +794,43 @@
     <t xml:space="preserve">2.1167619228363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08248209953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06705665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12190365791321</t>
+    <t xml:space="preserve">2.08248233795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06705617904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12190389633179</t>
   </si>
   <si>
     <t xml:space="preserve">2.10647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08933806419373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05163073539734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17675113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14247131347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13218760490417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13047361373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15961122512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11847543716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09105229377747</t>
+    <t xml:space="preserve">2.0893383026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05163049697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17675089836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14247179031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1321873664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13047385215759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15961098670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11847567558289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09105205535889</t>
   </si>
   <si>
     <t xml:space="preserve">2.12361764907837</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">2.11161994934082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10133576393127</t>
+    <t xml:space="preserve">2.10133600234985</t>
   </si>
   <si>
     <t xml:space="preserve">2.15789723396301</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">2.15618324279785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14418530464172</t>
+    <t xml:space="preserve">2.1441855430603</t>
   </si>
   <si>
     <t xml:space="preserve">2.1407573223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14932727813721</t>
+    <t xml:space="preserve">2.14932703971863</t>
   </si>
   <si>
     <t xml:space="preserve">2.13904356956482</t>
@@ -863,19 +863,19 @@
     <t xml:space="preserve">2.17503714561462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15104150772095</t>
+    <t xml:space="preserve">2.15104126930237</t>
   </si>
   <si>
     <t xml:space="preserve">2.12018966674805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10476398468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06362843513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03277683258057</t>
+    <t xml:space="preserve">2.1047637462616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06362819671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03277707099915</t>
   </si>
   <si>
     <t xml:space="preserve">2.0482029914856</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">2.07048416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04991674423218</t>
+    <t xml:space="preserve">2.0499165058136</t>
   </si>
   <si>
     <t xml:space="preserve">2.12875962257385</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">2.08762431144714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02077889442444</t>
+    <t xml:space="preserve">2.0207793712616</t>
   </si>
   <si>
     <t xml:space="preserve">2.08419609069824</t>
@@ -911,16 +911,16 @@
     <t xml:space="preserve">2.1681809425354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18532061576843</t>
+    <t xml:space="preserve">2.18532085418701</t>
   </si>
   <si>
     <t xml:space="preserve">2.29672932624817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33100867271423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32243919372559</t>
+    <t xml:space="preserve">2.33100891113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32243895530701</t>
   </si>
   <si>
     <t xml:space="preserve">2.35671854019165</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">2.44241738319397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49383664131165</t>
+    <t xml:space="preserve">2.49383687973022</t>
   </si>
   <si>
     <t xml:space="preserve">2.46812725067139</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">2.48526692390442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53668618202209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57953572273254</t>
+    <t xml:space="preserve">2.53668642044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57953548431396</t>
   </si>
   <si>
     <t xml:space="preserve">2.596675157547</t>
@@ -971,13 +971,13 @@
     <t xml:space="preserve">2.52694344520569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43733549118042</t>
+    <t xml:space="preserve">2.437335729599</t>
   </si>
   <si>
     <t xml:space="preserve">2.46421790122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50006103515625</t>
+    <t xml:space="preserve">2.50006127357483</t>
   </si>
   <si>
     <t xml:space="preserve">2.45525717735291</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">2.51798272132874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56278657913208</t>
+    <t xml:space="preserve">2.56278681755066</t>
   </si>
   <si>
     <t xml:space="preserve">2.53590416908264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4911003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48213982582092</t>
+    <t xml:space="preserve">2.49110054969788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48213958740234</t>
   </si>
   <si>
     <t xml:space="preserve">2.50902199745178</t>
@@ -1013,19 +1013,19 @@
     <t xml:space="preserve">2.78680658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75992441177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77784562110901</t>
+    <t xml:space="preserve">2.7599241733551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77784585952759</t>
   </si>
   <si>
     <t xml:space="preserve">2.74200248718262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76888489723206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71512007713318</t>
+    <t xml:space="preserve">2.76888513565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71512031555176</t>
   </si>
   <si>
     <t xml:space="preserve">2.75096321105957</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">2.86745381355286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83161044120789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6434338092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62551236152649</t>
+    <t xml:space="preserve">2.83161067962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64343404769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62551259994507</t>
   </si>
   <si>
     <t xml:space="preserve">2.58070850372314</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">2.607590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41941428184509</t>
+    <t xml:space="preserve">2.41941404342651</t>
   </si>
   <si>
     <t xml:space="preserve">2.66135549545288</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">2.81368899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84057140350342</t>
+    <t xml:space="preserve">2.840571641922</t>
   </si>
   <si>
     <t xml:space="preserve">2.93914008140564</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">2.80472826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90329670906067</t>
+    <t xml:space="preserve">2.90329694747925</t>
   </si>
   <si>
     <t xml:space="preserve">3.12731671333313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16315984725952</t>
+    <t xml:space="preserve">3.16315960884094</t>
   </si>
   <si>
     <t xml:space="preserve">3.13627743721008</t>
@@ -1121,19 +1121,19 @@
     <t xml:space="preserve">3.28861093521118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29757189750671</t>
+    <t xml:space="preserve">3.29757165908813</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33341503143311</t>
+    <t xml:space="preserve">3.33341479301453</t>
   </si>
   <si>
     <t xml:space="preserve">3.34237575531006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42302298545837</t>
+    <t xml:space="preserve">3.42302274703979</t>
   </si>
   <si>
     <t xml:space="preserve">3.3871796131134</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">3.37821888923645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45886564254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48574876785278</t>
+    <t xml:space="preserve">3.45886588096619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4857485294342</t>
   </si>
   <si>
     <t xml:space="preserve">3.47678756713867</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">3.67392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58431696891785</t>
+    <t xml:space="preserve">3.58431720733643</t>
   </si>
   <si>
     <t xml:space="preserve">3.53055238723755</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">3.55743479728699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52159142494202</t>
+    <t xml:space="preserve">3.5215916633606</t>
   </si>
   <si>
     <t xml:space="preserve">3.51263093948364</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">3.80833721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79041504859924</t>
+    <t xml:space="preserve">3.79041528701782</t>
   </si>
   <si>
     <t xml:space="preserve">3.95170950889587</t>
@@ -1232,13 +1232,13 @@
     <t xml:space="preserve">3.97005581855774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00759792327881</t>
+    <t xml:space="preserve">4.00759744644165</t>
   </si>
   <si>
     <t xml:space="preserve">4.0920672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81988835334778</t>
+    <t xml:space="preserve">3.81988859176636</t>
   </si>
   <si>
     <t xml:space="preserve">3.87620115280151</t>
@@ -1262,40 +1262,40 @@
     <t xml:space="preserve">4.03575468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99821257591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97944092750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85743021965027</t>
+    <t xml:space="preserve">3.9982123374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97944116592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85743045806885</t>
   </si>
   <si>
     <t xml:space="preserve">3.84804463386536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81050252914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7448046207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89497232437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94189953804016</t>
+    <t xml:space="preserve">3.81050276756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74480438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89497208595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.941899061203</t>
   </si>
   <si>
     <t xml:space="preserve">3.8668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93251395225525</t>
+    <t xml:space="preserve">3.93251419067383</t>
   </si>
   <si>
     <t xml:space="preserve">4.08268165588379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11083793640137</t>
+    <t xml:space="preserve">4.11083841323853</t>
   </si>
   <si>
     <t xml:space="preserve">4.12022304534912</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">4.18592166900635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19530725479126</t>
+    <t xml:space="preserve">4.1953067779541</t>
   </si>
   <si>
     <t xml:space="preserve">4.20469284057617</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">4.28916215896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26100587844849</t>
+    <t xml:space="preserve">4.26100540161133</t>
   </si>
   <si>
     <t xml:space="preserve">4.2703914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34547472000122</t>
+    <t xml:space="preserve">4.34547519683838</t>
   </si>
   <si>
     <t xml:space="preserve">4.36424589157104</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">4.50502824783325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49564266204834</t>
+    <t xml:space="preserve">4.49564218521118</t>
   </si>
   <si>
     <t xml:space="preserve">4.43932962417603</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">4.5519552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54257011413574</t>
+    <t xml:space="preserve">4.54256963729858</t>
   </si>
   <si>
     <t xml:space="preserve">4.48625707626343</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">4.40178775787354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44871520996094</t>
+    <t xml:space="preserve">4.44871473312378</t>
   </si>
   <si>
     <t xml:space="preserve">4.42994403839111</t>
@@ -1373,13 +1373,13 @@
     <t xml:space="preserve">4.41117334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39240169525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24223470687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30793333053589</t>
+    <t xml:space="preserve">4.39240217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2422342300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30793285369873</t>
   </si>
   <si>
     <t xml:space="preserve">4.17653608322144</t>
@@ -1397,28 +1397,28 @@
     <t xml:space="preserve">4.62703895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61765336990356</t>
+    <t xml:space="preserve">4.61765384674072</t>
   </si>
   <si>
     <t xml:space="preserve">4.51441335678101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57072591781616</t>
+    <t xml:space="preserve">4.57072639465332</t>
   </si>
   <si>
     <t xml:space="preserve">4.67396640777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80536270141602</t>
+    <t xml:space="preserve">4.80536317825317</t>
   </si>
   <si>
     <t xml:space="preserve">4.78659200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86167621612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84290504455566</t>
+    <t xml:space="preserve">4.86167573928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84290456771851</t>
   </si>
   <si>
     <t xml:space="preserve">4.89921760559082</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">4.5988826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53318405151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58011150360107</t>
+    <t xml:space="preserve">4.53318452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58011198043823</t>
   </si>
   <si>
     <t xml:space="preserve">4.6927375793457</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">4.74905014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73027944564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71150827407837</t>
+    <t xml:space="preserve">4.73027896881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71150875091553</t>
   </si>
   <si>
     <t xml:space="preserve">4.76782131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95553112030029</t>
+    <t xml:space="preserve">4.95553064346313</t>
   </si>
   <si>
     <t xml:space="preserve">4.88044691085815</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">4.91798877716064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99307250976562</t>
+    <t xml:space="preserve">4.99307298660278</t>
   </si>
   <si>
     <t xml:space="preserve">4.93675994873047</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">6.60737419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28826808929443</t>
+    <t xml:space="preserve">6.28826761245728</t>
   </si>
   <si>
     <t xml:space="preserve">6.1568717956543</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">5.96916246414185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70636892318726</t>
+    <t xml:space="preserve">5.7063684463501</t>
   </si>
   <si>
     <t xml:space="preserve">5.53743028640747</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">5.87530755996704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66882658004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68759727478027</t>
+    <t xml:space="preserve">5.66882705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68759775161743</t>
   </si>
   <si>
     <t xml:space="preserve">5.83776521682739</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59374284744263</t>
+    <t xml:space="preserve">5.59374332427979</t>
   </si>
   <si>
     <t xml:space="preserve">5.38726234436035</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">5.10569858551025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68335199356079</t>
+    <t xml:space="preserve">4.68335151672363</t>
   </si>
   <si>
     <t xml:space="preserve">4.14837980270386</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">3.62279319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55709481239319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37877082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50078225135803</t>
+    <t xml:space="preserve">3.55709505081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37877106666565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50078201293945</t>
   </si>
   <si>
     <t xml:space="preserve">3.5664803981781</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">3.75418996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70726251602173</t>
+    <t xml:space="preserve">3.70726275444031</t>
   </si>
   <si>
     <t xml:space="preserve">3.71664810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8386595249176</t>
+    <t xml:space="preserve">3.83865928649902</t>
   </si>
   <si>
     <t xml:space="preserve">4.25162029266357</t>
@@ -1583,25 +1583,25 @@
     <t xml:space="preserve">4.12960910797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16715049743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05452537536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76357555389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66972064971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65094995498657</t>
+    <t xml:space="preserve">4.16715097427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05452489852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76357579231262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66972088813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65094971656799</t>
   </si>
   <si>
     <t xml:space="preserve">3.66033530235291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95128512382507</t>
+    <t xml:space="preserve">3.95128488540649</t>
   </si>
   <si>
     <t xml:space="preserve">4.29854726791382</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">4.31731843948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15776491165161</t>
+    <t xml:space="preserve">4.15776538848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.10145235061646</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">4.13899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88558626174927</t>
+    <t xml:space="preserve">3.88558650016785</t>
   </si>
   <si>
     <t xml:space="preserve">4.32670402526855</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">4.27977657318115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.913743019104</t>
+    <t xml:space="preserve">3.91374325752258</t>
   </si>
   <si>
     <t xml:space="preserve">3.92312836647034</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">3.49139666557312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67910623550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38815641403198</t>
+    <t xml:space="preserve">3.67910599708557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3881561756134</t>
   </si>
   <si>
     <t xml:space="preserve">3.35999989509583</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">3.34122896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20044708251953</t>
+    <t xml:space="preserve">3.20044684410095</t>
   </si>
   <si>
     <t xml:space="preserve">3.24737429618835</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">3.47262573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57586574554443</t>
+    <t xml:space="preserve">3.57586598396301</t>
   </si>
   <si>
     <t xml:space="preserve">3.73541903495789</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">3.68849158287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72603368759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52893853187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63217878341675</t>
+    <t xml:space="preserve">3.72603344917297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52893877029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63217854499817</t>
   </si>
   <si>
     <t xml:space="preserve">3.51016759872437</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">3.58525133132935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53832411766052</t>
+    <t xml:space="preserve">3.53832387924194</t>
   </si>
   <si>
     <t xml:space="preserve">3.80111742019653</t>
@@ -1730,10 +1730,10 @@
     <t xml:space="preserve">3.48201107978821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46324014663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4444694519043</t>
+    <t xml:space="preserve">3.46324038505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44446921348572</t>
   </si>
   <si>
     <t xml:space="preserve">3.42569851875305</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">3.41631293296814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754199981689</t>
+    <t xml:space="preserve">3.39754176139832</t>
   </si>
   <si>
     <t xml:space="preserve">3.21921801567078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1910617351532</t>
+    <t xml:space="preserve">3.19106149673462</t>
   </si>
   <si>
     <t xml:space="preserve">3.17229056358337</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">3.23798894882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14413404464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25675964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36938524246216</t>
+    <t xml:space="preserve">3.14413380622864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25675988197327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36938548088074</t>
   </si>
   <si>
     <t xml:space="preserve">3.15351939201355</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">3.18167614936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29430174827576</t>
+    <t xml:space="preserve">3.29430150985718</t>
   </si>
   <si>
     <t xml:space="preserve">3.2661452293396</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">3.12536311149597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04089379310608</t>
+    <t xml:space="preserve">3.04089403152466</t>
   </si>
   <si>
     <t xml:space="preserve">3.05027914047241</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">2.93765377998352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95642447471619</t>
+    <t xml:space="preserve">2.95642471313477</t>
   </si>
   <si>
     <t xml:space="preserve">3.03150844573975</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">3.02212285995483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92826795578003</t>
+    <t xml:space="preserve">2.92826819419861</t>
   </si>
   <si>
     <t xml:space="preserve">2.94703912734985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90011167526245</t>
+    <t xml:space="preserve">2.90011143684387</t>
   </si>
   <si>
     <t xml:space="preserve">2.97519564628601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27553057670593</t>
+    <t xml:space="preserve">3.27553081512451</t>
   </si>
   <si>
     <t xml:space="preserve">3.33184361457825</t>
@@ -68328,6 +68328,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.3333333333</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>787</v>
+      </c>
+      <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825943946838</t>
+    <t xml:space="preserve">1.85825908184052</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
@@ -47,226 +47,226 @@
     <t xml:space="preserve">1.9132376909256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92109155654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88496315479279</t>
+    <t xml:space="preserve">1.92109179496765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8849630355835</t>
   </si>
   <si>
     <t xml:space="preserve">1.92423319816589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80642282962799</t>
+    <t xml:space="preserve">1.80642306804657</t>
   </si>
   <si>
     <t xml:space="preserve">1.82998490333557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79856896400452</t>
+    <t xml:space="preserve">1.79856872558594</t>
   </si>
   <si>
     <t xml:space="preserve">1.76715302467346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85354709625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86925518512726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87710905075073</t>
+    <t xml:space="preserve">1.85354697704315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86925530433655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87710916996002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281725883484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86768424510956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81584787368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83783900737762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553822994232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684338092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84569311141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81898939609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8362683057785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85983037948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80485212802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82056033611298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81741845607758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85040545463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88025057315826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81427705287933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85197627544403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84412240982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84098052978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82370185852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81113529205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82213091850281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679976463318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622457027435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407807826996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96350347995758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96507406234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99334859848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00434422492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.987065076828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905656814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02476453781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93051624298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9619323015213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994128704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564901828766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637921333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8739675283432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378698825836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017540454865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9223153591156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050968647003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656310558319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509159564972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95836925506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739904880524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542611598969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198107719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91248285770416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91084420681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545923233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80268287658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84201407432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83218145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88298428058624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86823511123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90756618976593</t>
   </si>
   <si>
     <t xml:space="preserve">1.89281713962555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86768436431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81584787368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83783888816833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8755384683609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8456928730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898951530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83626818656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85983049869537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80485236644745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82056033611298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81741845607758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85040521621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88025081157684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81427693367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85197615623474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84412217140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84098076820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82370173931122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8111355304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82213091850281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9367995262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622433185577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407819747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.963503241539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96507394313812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99334859848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00434398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98706531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905632972717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02476477622986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93051624298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96193242073059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994128704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564913749695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637921333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87396728992462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378722667694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92231559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050932884216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656334400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509135723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95836925506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739904880524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9354259967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198107719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91248285770416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91084420681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545899391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8026829957962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84201407432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83218157291412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88298451900482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8682347536087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90756618976593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281702041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592741966248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88462293148041</t>
+    <t xml:space="preserve">1.90592753887177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88462316989899</t>
   </si>
   <si>
     <t xml:space="preserve">1.90920507907867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87151277065277</t>
+    <t xml:space="preserve">1.87151265144348</t>
   </si>
   <si>
     <t xml:space="preserve">1.8977335691452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82398736476898</t>
+    <t xml:space="preserve">1.82398748397827</t>
   </si>
   <si>
     <t xml:space="preserve">1.75843513011932</t>
@@ -275,25 +275,25 @@
     <t xml:space="preserve">1.76662921905518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78629517555237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77646207809448</t>
+    <t xml:space="preserve">1.7862948179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77646195888519</t>
   </si>
   <si>
     <t xml:space="preserve">1.75188004970551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75351881980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77973961830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75024127960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72074258327484</t>
+    <t xml:space="preserve">1.75351893901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77973973751068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75024139881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72074270248413</t>
   </si>
   <si>
     <t xml:space="preserve">1.66993999481201</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">1.69616079330444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76007390022278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70435464382172</t>
+    <t xml:space="preserve">1.76007401943207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70435476303101</t>
   </si>
   <si>
     <t xml:space="preserve">1.73549199104309</t>
@@ -317,25 +317,25 @@
     <t xml:space="preserve">1.73385322093964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71254873275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63060867786407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67157864570618</t>
+    <t xml:space="preserve">1.71254885196686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63060879707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67157876491547</t>
   </si>
   <si>
     <t xml:space="preserve">1.66666233539581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61012351512909</t>
+    <t xml:space="preserve">1.61012375354767</t>
   </si>
   <si>
     <t xml:space="preserve">1.62241458892822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66338467597961</t>
+    <t xml:space="preserve">1.6633847951889</t>
   </si>
   <si>
     <t xml:space="preserve">1.67321753501892</t>
@@ -344,31 +344,31 @@
     <t xml:space="preserve">1.64535784721375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63880264759064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62569236755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66830110549927</t>
+    <t xml:space="preserve">1.63880276679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62569224834442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66830122470856</t>
   </si>
   <si>
     <t xml:space="preserve">1.65519070625305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64699673652649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63798308372498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59865200519562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62978911399841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58308339118958</t>
+    <t xml:space="preserve">1.6469966173172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63798320293427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59865212440491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6297892332077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58308351039886</t>
   </si>
   <si>
     <t xml:space="preserve">1.59537434577942</t>
@@ -377,22 +377,22 @@
     <t xml:space="preserve">1.57898640632629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59127736091614</t>
+    <t xml:space="preserve">1.59127748012543</t>
   </si>
   <si>
     <t xml:space="preserve">1.54047453403473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56751477718353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56997287273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56669533252716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55850124359131</t>
+    <t xml:space="preserve">1.56751465797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56997299194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56669521331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5585013628006</t>
   </si>
   <si>
     <t xml:space="preserve">1.6027489900589</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">1.6060266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51917016506195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56177890300751</t>
+    <t xml:space="preserve">1.51916992664337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5617790222168</t>
   </si>
   <si>
     <t xml:space="preserve">1.54539108276367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37659418582916</t>
+    <t xml:space="preserve">1.37659406661987</t>
   </si>
   <si>
     <t xml:space="preserve">1.4126478433609</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">1.39462113380432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45771503448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47082543373108</t>
+    <t xml:space="preserve">1.45771491527557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47082531452179</t>
   </si>
   <si>
     <t xml:space="preserve">1.53391933441162</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">1.61258184909821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61176252365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59783279895782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54211330413818</t>
+    <t xml:space="preserve">1.61176240444183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59783256053925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54211318492889</t>
   </si>
   <si>
     <t xml:space="preserve">1.51179552078247</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">1.56505656242371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56423723697662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59291625022888</t>
+    <t xml:space="preserve">1.56423711776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59291613101959</t>
   </si>
   <si>
     <t xml:space="preserve">1.55686247348785</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">1.5044207572937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51097619533539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55112671852112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589238643646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55194628238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50851774215698</t>
+    <t xml:space="preserve">1.51097595691681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55112683773041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589250564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55194616317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50851786136627</t>
   </si>
   <si>
     <t xml:space="preserve">1.53228056430817</t>
@@ -491,46 +491,46 @@
     <t xml:space="preserve">1.50933718681335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5076984167099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50278198719025</t>
+    <t xml:space="preserve">1.50769853591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50278210639954</t>
   </si>
   <si>
     <t xml:space="preserve">1.49540746212006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51015686988831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57325065135956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58554148674011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59455502033234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60684597492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62159526348114</t>
+    <t xml:space="preserve">1.51015675067902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57325041294098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5855416059494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59455490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60684585571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62159538269043</t>
   </si>
   <si>
     <t xml:space="preserve">1.57161176204681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54375219345093</t>
+    <t xml:space="preserve">1.54375207424164</t>
   </si>
   <si>
     <t xml:space="preserve">1.57243120670319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58718049526215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54621028900146</t>
+    <t xml:space="preserve">1.58718037605286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54621040821075</t>
   </si>
   <si>
     <t xml:space="preserve">1.55768191814423</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">1.53473877906799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58226406574249</t>
+    <t xml:space="preserve">1.5822639465332</t>
   </si>
   <si>
     <t xml:space="preserve">1.54702961444855</t>
@@ -551,31 +551,31 @@
     <t xml:space="preserve">1.53883576393127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54784905910492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55276548862457</t>
+    <t xml:space="preserve">1.54784917831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55276560783386</t>
   </si>
   <si>
     <t xml:space="preserve">1.54948794841766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5380163192749</t>
+    <t xml:space="preserve">1.53801620006561</t>
   </si>
   <si>
     <t xml:space="preserve">1.54866850376129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53637742996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53965520858765</t>
+    <t xml:space="preserve">1.53637754917145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53965508937836</t>
   </si>
   <si>
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191316604614</t>
+    <t xml:space="preserve">1.65191304683685</t>
   </si>
   <si>
     <t xml:space="preserve">1.69288313388824</t>
@@ -587,64 +587,64 @@
     <t xml:space="preserve">1.82070970535278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8289041519165</t>
+    <t xml:space="preserve">1.82890391349792</t>
   </si>
   <si>
     <t xml:space="preserve">1.81743216514587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81579339504242</t>
+    <t xml:space="preserve">1.81579327583313</t>
   </si>
   <si>
     <t xml:space="preserve">1.87970674037933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79448902606964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80104398727417</t>
+    <t xml:space="preserve">1.79448914527893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80104422569275</t>
   </si>
   <si>
     <t xml:space="preserve">1.73876953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729825973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74696373939514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76335144042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84693026542664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81087708473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8092383146286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81251549720764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86167979240417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86495733261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85840201377869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87642908096313</t>
+    <t xml:space="preserve">1.72729790210724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74696362018585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76335179805756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84693050384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81087684631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923819541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81251573562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86167991161346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86495745182037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8584018945694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87642884254456</t>
   </si>
   <si>
     <t xml:space="preserve">1.89937245845795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84856963157654</t>
+    <t xml:space="preserve">1.84856951236725</t>
   </si>
   <si>
     <t xml:space="preserve">1.92479658126831</t>
@@ -68408,7 +68408,7 @@
     </row>
     <row r="2527">
       <c r="A2527" s="1" t="n">
-        <v>45996.5101041667</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2527" t="n">
         <v>1200</v>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825908184052</t>
+    <t xml:space="preserve">1.85825932025909</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9132376909256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109179496765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8849630355835</t>
+    <t xml:space="preserve">1.91323792934418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109167575836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88496315479279</t>
   </si>
   <si>
     <t xml:space="preserve">1.92423319816589</t>
@@ -59,22 +59,22 @@
     <t xml:space="preserve">1.80642306804657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82998490333557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79856872558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76715302467346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354697704315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86925530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87710916996002</t>
+    <t xml:space="preserve">1.82998478412628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79856908321381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76715290546417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354685783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86925554275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87710905075073</t>
   </si>
   <si>
     <t xml:space="preserve">1.89281725883484</t>
@@ -86,43 +86,43 @@
     <t xml:space="preserve">1.81584787368774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83783900737762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87553822994232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82684338092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84569311141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898939609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8362683057785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85983037948608</t>
+    <t xml:space="preserve">1.83783888816833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553811073303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82684326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84569299221039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81898927688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83626818656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85983026027679</t>
   </si>
   <si>
     <t xml:space="preserve">1.80485212802887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82056033611298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81741845607758</t>
+    <t xml:space="preserve">1.82056045532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81741869449615</t>
   </si>
   <si>
     <t xml:space="preserve">1.85040545463562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88025057315826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81427705287933</t>
+    <t xml:space="preserve">1.88025081157684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81427681446075</t>
   </si>
   <si>
     <t xml:space="preserve">1.85197627544403</t>
@@ -131,82 +131,82 @@
     <t xml:space="preserve">1.84412240982056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84098052978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82370185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81113529205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82213091850281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679976463318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622457027435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407807826996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96350347995758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96507406234741</t>
+    <t xml:space="preserve">1.84098064899445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82370173931122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8111355304718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8221310377121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679964542389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622433185577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407843589783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96350312232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9650741815567</t>
   </si>
   <si>
     <t xml:space="preserve">1.99334859848022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00434422492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.987065076828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905656814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02476453781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93051624298096</t>
+    <t xml:space="preserve">2.00434398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98706531524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905680656433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0247642993927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93051636219025</t>
   </si>
   <si>
     <t xml:space="preserve">1.9619323015213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93994128704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564901828766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91637921333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8739675283432</t>
+    <t xml:space="preserve">1.93994116783142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564925670624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91637909412384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87396728992462</t>
   </si>
   <si>
     <t xml:space="preserve">1.93378698825836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95017540454865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9223153591156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050968647003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656310558319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509159564972</t>
+    <t xml:space="preserve">1.95017564296722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656322479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509147644043</t>
   </si>
   <si>
     <t xml:space="preserve">1.95836925506592</t>
@@ -215,70 +215,70 @@
     <t xml:space="preserve">1.91739904880524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93542611598969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198107719421</t>
+    <t xml:space="preserve">1.93542587757111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9419811964035</t>
   </si>
   <si>
     <t xml:space="preserve">1.91248285770416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91084420681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545923233032</t>
+    <t xml:space="preserve">1.91084396839142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545899391174</t>
   </si>
   <si>
     <t xml:space="preserve">1.80268287658691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84201407432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83218145370483</t>
+    <t xml:space="preserve">1.84201431274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83218121528625</t>
   </si>
   <si>
     <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86823511123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90756618976593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281713962555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592753887177</t>
+    <t xml:space="preserve">1.86823523044586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9075665473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281702041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90592741966248</t>
   </si>
   <si>
     <t xml:space="preserve">1.88462316989899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90920507907867</t>
+    <t xml:space="preserve">1.90920495986938</t>
   </si>
   <si>
     <t xml:space="preserve">1.87151265144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8977335691452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82398748397827</t>
+    <t xml:space="preserve">1.89773344993591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82398760318756</t>
   </si>
   <si>
     <t xml:space="preserve">1.75843513011932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76662921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7862948179245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77646195888519</t>
+    <t xml:space="preserve">1.76662909984589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78629493713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77646219730377</t>
   </si>
   <si>
     <t xml:space="preserve">1.75188004970551</t>
@@ -290,34 +290,34 @@
     <t xml:space="preserve">1.77973973751068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75024139881134</t>
+    <t xml:space="preserve">1.75024127960205</t>
   </si>
   <si>
     <t xml:space="preserve">1.72074270248413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66993999481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72893679141998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69616079330444</t>
+    <t xml:space="preserve">1.6699401140213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72893667221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69616067409515</t>
   </si>
   <si>
     <t xml:space="preserve">1.76007401943207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70435476303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73549199104309</t>
+    <t xml:space="preserve">1.70435464382172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73549211025238</t>
   </si>
   <si>
     <t xml:space="preserve">1.73385322093964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71254885196686</t>
+    <t xml:space="preserve">1.71254873275757</t>
   </si>
   <si>
     <t xml:space="preserve">1.63060879707336</t>
@@ -326,52 +326,52 @@
     <t xml:space="preserve">1.67157876491547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66666233539581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61012375354767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62241458892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6633847951889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67321753501892</t>
+    <t xml:space="preserve">1.66666221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61012363433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62241470813751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66338467597961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67321765422821</t>
   </si>
   <si>
     <t xml:space="preserve">1.64535784721375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63880276679993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62569224834442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66830122470856</t>
+    <t xml:space="preserve">1.63880264759064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62569212913513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66830110549927</t>
   </si>
   <si>
     <t xml:space="preserve">1.65519070625305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6469966173172</t>
+    <t xml:space="preserve">1.64699673652649</t>
   </si>
   <si>
     <t xml:space="preserve">1.63798320293427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59865212440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6297892332077</t>
+    <t xml:space="preserve">1.59865188598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62978911399841</t>
   </si>
   <si>
     <t xml:space="preserve">1.58308351039886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59537434577942</t>
+    <t xml:space="preserve">1.59537446498871</t>
   </si>
   <si>
     <t xml:space="preserve">1.57898640632629</t>
@@ -383,16 +383,16 @@
     <t xml:space="preserve">1.54047453403473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56751465797424</t>
+    <t xml:space="preserve">1.56751477718353</t>
   </si>
   <si>
     <t xml:space="preserve">1.56997299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56669521331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5585013628006</t>
+    <t xml:space="preserve">1.56669533252716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55850124359131</t>
   </si>
   <si>
     <t xml:space="preserve">1.6027489900589</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">1.6060266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51916992664337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5617790222168</t>
+    <t xml:space="preserve">1.51917004585266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56177890300751</t>
   </si>
   <si>
     <t xml:space="preserve">1.54539108276367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37659406661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4126478433609</t>
+    <t xml:space="preserve">1.37659418582916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41264808177948</t>
   </si>
   <si>
     <t xml:space="preserve">1.39462113380432</t>
@@ -437,28 +437,28 @@
     <t xml:space="preserve">1.61176240444183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59783256053925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54211318492889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51179552078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5552237033844</t>
+    <t xml:space="preserve">1.59783267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54211330413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51179540157318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55522382259369</t>
   </si>
   <si>
     <t xml:space="preserve">1.56505656242371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56423711776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59291613101959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55686247348785</t>
+    <t xml:space="preserve">1.56423723697662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59291625022888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55686259269714</t>
   </si>
   <si>
     <t xml:space="preserve">1.52162826061249</t>
@@ -467,52 +467,52 @@
     <t xml:space="preserve">1.5412939786911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5044207572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51097595691681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55112683773041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589250564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55194616317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50851786136627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53228056430817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50933718681335</t>
+    <t xml:space="preserve">1.50442087650299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51097619533539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55112671852112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589238643646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55194628238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50851774215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53228068351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50933730602264</t>
   </si>
   <si>
     <t xml:space="preserve">1.50769853591919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50278210639954</t>
+    <t xml:space="preserve">1.50278198719025</t>
   </si>
   <si>
     <t xml:space="preserve">1.49540746212006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51015675067902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57325041294098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5855416059494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59455490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60684585571289</t>
+    <t xml:space="preserve">1.51015663146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57325053215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58554136753082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59455502033234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60684597492218</t>
   </si>
   <si>
     <t xml:space="preserve">1.62159538269043</t>
@@ -521,52 +521,52 @@
     <t xml:space="preserve">1.57161176204681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54375207424164</t>
+    <t xml:space="preserve">1.54375219345093</t>
   </si>
   <si>
     <t xml:space="preserve">1.57243120670319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58718037605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54621040821075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55768191814423</t>
+    <t xml:space="preserve">1.58718025684357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54621016979218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55768203735352</t>
   </si>
   <si>
     <t xml:space="preserve">1.58799982070923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53473877906799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5822639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54702961444855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53883576393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54784917831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55276560783386</t>
+    <t xml:space="preserve">1.5347386598587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58226406574249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54702973365784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53883564472198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54784905910492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55276548862457</t>
   </si>
   <si>
     <t xml:space="preserve">1.54948794841766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53801620006561</t>
+    <t xml:space="preserve">1.5380163192749</t>
   </si>
   <si>
     <t xml:space="preserve">1.54866850376129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53637754917145</t>
+    <t xml:space="preserve">1.53637742996216</t>
   </si>
   <si>
     <t xml:space="preserve">1.53965508937836</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191304683685</t>
+    <t xml:space="preserve">1.65191316604614</t>
   </si>
   <si>
     <t xml:space="preserve">1.69288313388824</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">1.65355181694031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82070970535278</t>
+    <t xml:space="preserve">1.82070958614349</t>
   </si>
   <si>
     <t xml:space="preserve">1.82890391349792</t>
@@ -593,37 +593,37 @@
     <t xml:space="preserve">1.81743216514587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81579327583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87970674037933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79448914527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80104422569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72729790210724</t>
+    <t xml:space="preserve">1.81579351425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87970626354218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79448878765106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80104398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73876965045929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72729814052582</t>
   </si>
   <si>
     <t xml:space="preserve">1.74696362018585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76335179805756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84693050384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81087684631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80923819541931</t>
+    <t xml:space="preserve">1.76335167884827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8469306230545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81087708473206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923807621002</t>
   </si>
   <si>
     <t xml:space="preserve">1.81251573562622</t>
@@ -632,22 +632,22 @@
     <t xml:space="preserve">1.86167991161346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86495745182037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8584018945694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87642884254456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89937245845795</t>
+    <t xml:space="preserve">1.86495769023895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85840213298798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87642908096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89937257766724</t>
   </si>
   <si>
     <t xml:space="preserve">1.84856951236725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92479658126831</t>
+    <t xml:space="preserve">1.92479622364044</t>
   </si>
   <si>
     <t xml:space="preserve">1.93679404258728</t>
@@ -659,103 +659,103 @@
     <t xml:space="preserve">1.97107374668121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92822444438934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94193613529205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94364976882935</t>
+    <t xml:space="preserve">1.92822420597076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94193625450134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94365012645721</t>
   </si>
   <si>
     <t xml:space="preserve">1.95907580852509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9676456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92651009559631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95393395423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93336629867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90594244003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89394462108612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87166309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92993819713593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90080058574677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91451263427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88708877563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87680518627167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9179402589798</t>
+    <t xml:space="preserve">1.96764576435089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92651033401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95393407344818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93336617946625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90594255924225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8939448595047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8716629743576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92993855476379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90080046653748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91451239585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88708889484406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87680494785309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91794049739838</t>
   </si>
   <si>
     <t xml:space="preserve">1.8853747844696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86994910240173</t>
+    <t xml:space="preserve">1.86994898319244</t>
   </si>
   <si>
     <t xml:space="preserve">1.88880276679993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90937066078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90251481533051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96421778202057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96250355243683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821341991425</t>
+    <t xml:space="preserve">1.90937054157257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90251469612122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96421790122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96250379085541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821353912354</t>
   </si>
   <si>
     <t xml:space="preserve">1.98649966716766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97964358329773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12533140182495</t>
+    <t xml:space="preserve">1.97964370250702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12533164024353</t>
   </si>
   <si>
     <t xml:space="preserve">2.08591032028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05677247047424</t>
+    <t xml:space="preserve">2.05677270889282</t>
   </si>
   <si>
     <t xml:space="preserve">2.07905435562134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08076810836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06534266471863</t>
+    <t xml:space="preserve">2.0807683467865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06534242630005</t>
   </si>
   <si>
     <t xml:space="preserve">2.06020045280457</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">2.07219839096069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13390135765076</t>
+    <t xml:space="preserve">2.13390159606934</t>
   </si>
   <si>
     <t xml:space="preserve">2.1081919670105</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">2.10304999351501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03963303565979</t>
+    <t xml:space="preserve">2.03963279724121</t>
   </si>
   <si>
     <t xml:space="preserve">2.06877040863037</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">2.11504769325256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07391214370728</t>
+    <t xml:space="preserve">2.07391238212585</t>
   </si>
   <si>
     <t xml:space="preserve">2.09790802001953</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">2.1167619228363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08248233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06705617904663</t>
+    <t xml:space="preserve">2.08248209953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06705641746521</t>
   </si>
   <si>
     <t xml:space="preserve">2.12190365791321</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">2.10647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08933806419373</t>
+    <t xml:space="preserve">2.0893383026123</t>
   </si>
   <si>
     <t xml:space="preserve">2.05163049697876</t>
@@ -821,19 +821,19 @@
     <t xml:space="preserve">2.1321873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13047361373901</t>
+    <t xml:space="preserve">2.13047385215759</t>
   </si>
   <si>
     <t xml:space="preserve">2.15961122512817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11847591400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09105229377747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12361788749695</t>
+    <t xml:space="preserve">2.11847543716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09105181694031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12361764907837</t>
   </si>
   <si>
     <t xml:space="preserve">2.11161994934082</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">2.15789723396301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15618324279785</t>
+    <t xml:space="preserve">2.15618348121643</t>
   </si>
   <si>
     <t xml:space="preserve">2.1441855430603</t>
@@ -854,40 +854,40 @@
     <t xml:space="preserve">2.1407573223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14932727813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13904333114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17503714561462</t>
+    <t xml:space="preserve">2.14932703971863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13904356956482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17503690719604</t>
   </si>
   <si>
     <t xml:space="preserve">2.15104126930237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12018942832947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10476398468018</t>
+    <t xml:space="preserve">2.12018966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1047637462616</t>
   </si>
   <si>
     <t xml:space="preserve">2.06362843513489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03277683258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04820275306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07048439979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04991674423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12875986099243</t>
+    <t xml:space="preserve">2.03277707099915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0482029914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07048416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0499165058136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12875962257385</t>
   </si>
   <si>
     <t xml:space="preserve">2.08762431144714</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.0224928855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01392316818237</t>
+    <t xml:space="preserve">2.01392292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.00535321235657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1681809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18532061576843</t>
+    <t xml:space="preserve">2.16818118095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18532085418701</t>
   </si>
   <si>
     <t xml:space="preserve">2.29672932624817</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">2.33100891113281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32243919372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35671854019165</t>
+    <t xml:space="preserve">2.32243895530701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35671830177307</t>
   </si>
   <si>
     <t xml:space="preserve">2.44241738319397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49383687973022</t>
+    <t xml:space="preserve">2.49383664131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.46812725067139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47669720649719</t>
+    <t xml:space="preserve">2.47669696807861</t>
   </si>
   <si>
     <t xml:space="preserve">2.48526692390442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53668618202209</t>
+    <t xml:space="preserve">2.53668642044067</t>
   </si>
   <si>
     <t xml:space="preserve">2.57953572273254</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">2.61381506919861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55382609367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63447308540344</t>
+    <t xml:space="preserve">2.55382585525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63447332382202</t>
   </si>
   <si>
     <t xml:space="preserve">2.59862995147705</t>
@@ -965,13 +965,10 @@
     <t xml:space="preserve">2.5896692276001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61655163764954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55382585525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52694368362427</t>
+    <t xml:space="preserve">2.61655139923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52694344520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.437335729599</t>
@@ -980,16 +977,16 @@
     <t xml:space="preserve">2.46421790122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50006103515625</t>
+    <t xml:space="preserve">2.50006127357483</t>
   </si>
   <si>
     <t xml:space="preserve">2.45525717735291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54486489295959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57174730300903</t>
+    <t xml:space="preserve">2.54486513137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57174754142761</t>
   </si>
   <si>
     <t xml:space="preserve">2.51798272132874</t>
@@ -1001,7 +998,7 @@
     <t xml:space="preserve">2.53590416908264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4911003112793</t>
+    <t xml:space="preserve">2.49110054969788</t>
   </si>
   <si>
     <t xml:space="preserve">2.48213958740234</t>
@@ -1019,37 +1016,37 @@
     <t xml:space="preserve">2.7599241733551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77784562110901</t>
+    <t xml:space="preserve">2.77784585952759</t>
   </si>
   <si>
     <t xml:space="preserve">2.74200248718262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76888465881348</t>
+    <t xml:space="preserve">2.76888513565063</t>
   </si>
   <si>
     <t xml:space="preserve">2.71512031555176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75096344947815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67031645774841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72408080101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65239453315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68823766708374</t>
+    <t xml:space="preserve">2.75096321105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67031621932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72408103942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65239477157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68823790550232</t>
   </si>
   <si>
     <t xml:space="preserve">2.73304176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69719862937927</t>
+    <t xml:space="preserve">2.69719886779785</t>
   </si>
   <si>
     <t xml:space="preserve">2.67927694320679</t>
@@ -1058,25 +1055,25 @@
     <t xml:space="preserve">2.84953236579895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86745357513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83161044120789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6434338092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62551236152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58070826530457</t>
+    <t xml:space="preserve">2.86745381355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83161067962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64343404769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62551259994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58070850372314</t>
   </si>
   <si>
     <t xml:space="preserve">2.607590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41941428184509</t>
+    <t xml:space="preserve">2.41941404342651</t>
   </si>
   <si>
     <t xml:space="preserve">2.66135549545288</t>
@@ -1085,7 +1082,7 @@
     <t xml:space="preserve">2.81368899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84057140350342</t>
+    <t xml:space="preserve">2.840571641922</t>
   </si>
   <si>
     <t xml:space="preserve">2.93914008140564</t>
@@ -1094,7 +1091,7 @@
     <t xml:space="preserve">2.87641453742981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82264995574951</t>
+    <t xml:space="preserve">2.82264971733093</t>
   </si>
   <si>
     <t xml:space="preserve">2.80472826957703</t>
@@ -1106,34 +1103,34 @@
     <t xml:space="preserve">3.12731671333313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16315984725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13627767562866</t>
+    <t xml:space="preserve">3.16315960884094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13627743721008</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004225730896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25276803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26172876358032</t>
+    <t xml:space="preserve">3.25276780128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26172852516174</t>
   </si>
   <si>
     <t xml:space="preserve">3.28861093521118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29757189750671</t>
+    <t xml:space="preserve">3.29757165908813</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33341503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34237551689148</t>
+    <t xml:space="preserve">3.33341479301453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34237575531006</t>
   </si>
   <si>
     <t xml:space="preserve">3.42302274703979</t>
@@ -1148,19 +1145,19 @@
     <t xml:space="preserve">3.41406202316284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36925840377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37821865081787</t>
+    <t xml:space="preserve">3.36925792694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37821888923645</t>
   </si>
   <si>
     <t xml:space="preserve">3.45886588096619</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48574829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47678780555725</t>
+    <t xml:space="preserve">3.4857485294342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47678756713867</t>
   </si>
   <si>
     <t xml:space="preserve">3.49470925331116</t>
@@ -1178,16 +1175,16 @@
     <t xml:space="preserve">3.59327816963196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55743455886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52159142494202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51263070106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53951334953308</t>
+    <t xml:space="preserve">3.55743479728699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5215916633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51263093948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5395131111145</t>
   </si>
   <si>
     <t xml:space="preserve">3.60223865509033</t>
@@ -1196,13 +1193,13 @@
     <t xml:space="preserve">3.65600347518921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66496419906616</t>
+    <t xml:space="preserve">3.66496443748474</t>
   </si>
   <si>
     <t xml:space="preserve">3.72768974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71872901916504</t>
+    <t xml:space="preserve">3.71872925758362</t>
   </si>
   <si>
     <t xml:space="preserve">3.6918466091156</t>
@@ -1211,7 +1208,7 @@
     <t xml:space="preserve">3.70976805686951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68288612365723</t>
+    <t xml:space="preserve">3.68288588523865</t>
   </si>
   <si>
     <t xml:space="preserve">3.7635326385498</t>
@@ -1220,7 +1217,7 @@
     <t xml:space="preserve">3.78145432472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80833697319031</t>
+    <t xml:space="preserve">3.80833721160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.79041528701782</t>
@@ -1229,22 +1226,25 @@
     <t xml:space="preserve">3.95170950889587</t>
   </si>
   <si>
+    <t xml:space="preserve">3.96067070960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97005581855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00759744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0920672416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81988859176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87620115280151</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.96067023277283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97005581855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00759744644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0920672416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81988859176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87620115280151</t>
   </si>
   <si>
     <t xml:space="preserve">4.02636861801147</t>
@@ -18636,7 +18636,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18662,7 +18662,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G613" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18688,7 +18688,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G614" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18714,7 +18714,7 @@
         <v>2.75</v>
       </c>
       <c r="G615" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18740,7 +18740,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G616" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18766,7 +18766,7 @@
         <v>2.75</v>
       </c>
       <c r="G617" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18792,7 +18792,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G618" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18818,7 +18818,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G619" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18844,7 +18844,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G620" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18870,7 +18870,7 @@
         <v>2.75</v>
       </c>
       <c r="G621" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18896,7 +18896,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G622" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18922,7 +18922,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18948,7 +18948,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18974,7 +18974,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19000,7 +19000,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19026,7 +19026,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G627" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19052,7 +19052,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G628" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19078,7 +19078,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G629" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19104,7 +19104,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G630" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19130,7 +19130,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19156,7 +19156,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G632" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19182,7 +19182,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19208,7 +19208,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G634" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19234,7 +19234,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G635" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19260,7 +19260,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G636" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19286,7 +19286,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19312,7 +19312,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19338,7 +19338,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19364,7 +19364,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19390,7 +19390,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19416,7 +19416,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19442,7 +19442,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19468,7 +19468,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19494,7 +19494,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19520,7 +19520,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19546,7 +19546,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G647" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19572,7 +19572,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G648" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19598,7 +19598,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G649" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19624,7 +19624,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G650" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19650,7 +19650,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G651" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19702,7 +19702,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G653" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19754,7 +19754,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19780,7 +19780,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G656" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19806,7 +19806,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -19832,7 +19832,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G658" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -19858,7 +19858,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19884,7 +19884,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G660" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19910,7 +19910,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G661" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19936,7 +19936,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G662" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19962,7 +19962,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G663" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19988,7 +19988,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G664" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20014,7 +20014,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20040,7 +20040,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20066,7 +20066,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20092,7 +20092,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20144,7 +20144,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G670" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20170,7 +20170,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20196,7 +20196,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G672" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20222,7 +20222,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G673" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20248,7 +20248,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20274,7 +20274,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20300,7 +20300,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G676" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20326,7 +20326,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20352,7 +20352,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20378,7 +20378,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G679" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20404,7 +20404,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20430,7 +20430,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G681" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20456,7 +20456,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20482,7 +20482,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20508,7 +20508,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20534,7 +20534,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20560,7 +20560,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20586,7 +20586,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20612,7 +20612,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20638,7 +20638,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20664,7 +20664,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20690,7 +20690,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20716,7 +20716,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G692" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20742,7 +20742,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20768,7 +20768,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20794,7 +20794,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20820,7 +20820,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20846,7 +20846,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20872,7 +20872,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -20898,7 +20898,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -20924,7 +20924,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -20950,7 +20950,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -20976,7 +20976,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21002,7 +21002,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21028,7 +21028,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21054,7 +21054,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21080,7 +21080,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21106,7 +21106,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21158,7 +21158,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G709" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21184,7 +21184,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G710" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21210,7 +21210,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G711" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21236,7 +21236,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21366,7 +21366,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G717" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21392,7 +21392,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21418,7 +21418,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G719" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21600,7 +21600,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G726" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21704,7 +21704,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21808,7 +21808,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G734" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21834,7 +21834,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G735" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21860,7 +21860,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G736" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21886,7 +21886,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G737" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21912,7 +21912,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21938,7 +21938,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G739" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21964,7 +21964,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21990,7 +21990,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G741" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22016,7 +22016,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G742" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22042,7 +22042,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G743" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22068,7 +22068,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G744" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22094,7 +22094,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G745" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22120,7 +22120,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22146,7 +22146,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22172,7 +22172,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22198,7 +22198,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G749" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22224,7 +22224,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22250,7 +22250,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22276,7 +22276,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22302,7 +22302,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22328,7 +22328,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22354,7 +22354,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22380,7 +22380,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22406,7 +22406,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22432,7 +22432,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22458,7 +22458,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G759" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22484,7 +22484,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G760" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22510,7 +22510,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G761" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22536,7 +22536,7 @@
         <v>2.75</v>
       </c>
       <c r="G762" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22562,7 +22562,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22588,7 +22588,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22614,7 +22614,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22666,7 +22666,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22692,7 +22692,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G768" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22718,7 +22718,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22744,7 +22744,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22770,7 +22770,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22796,7 +22796,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22822,7 +22822,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22848,7 +22848,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22874,7 +22874,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22900,7 +22900,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22926,7 +22926,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22952,7 +22952,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22978,7 +22978,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G779" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23004,7 +23004,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23030,7 +23030,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23056,7 +23056,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G782" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23082,7 +23082,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23108,7 +23108,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G784" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23134,7 +23134,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G785" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23160,7 +23160,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23186,7 +23186,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G787" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23212,7 +23212,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G788" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23238,7 +23238,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G789" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23264,7 +23264,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23290,7 +23290,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G791" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23316,7 +23316,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G792" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23342,7 +23342,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G793" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23368,7 +23368,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23394,7 +23394,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23420,7 +23420,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23446,7 +23446,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G797" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23472,7 +23472,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G798" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23498,7 +23498,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23524,7 +23524,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G800" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23550,7 +23550,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23576,7 +23576,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G802" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23602,7 +23602,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23628,7 +23628,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G804" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23654,7 +23654,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23680,7 +23680,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23706,7 +23706,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G807" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23732,7 +23732,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G808" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23758,7 +23758,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G809" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23784,7 +23784,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G810" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23810,7 +23810,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G811" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23836,7 +23836,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23862,7 +23862,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G813" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23888,7 +23888,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G814" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23914,7 +23914,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23940,7 +23940,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G816" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23966,7 +23966,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23992,7 +23992,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G818" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24018,7 +24018,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24044,7 +24044,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G820" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24070,7 +24070,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G821" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24096,7 +24096,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24122,7 +24122,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G823" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24148,7 +24148,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G824" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24174,7 +24174,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G825" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24200,7 +24200,7 @@
         <v>4</v>
       </c>
       <c r="G826" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24226,7 +24226,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G827" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24252,7 +24252,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G828" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24278,7 +24278,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G829" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24304,7 +24304,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G830" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24330,7 +24330,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24356,7 +24356,7 @@
         <v>4</v>
       </c>
       <c r="G832" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24382,7 +24382,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24408,7 +24408,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24434,7 +24434,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24460,7 +24460,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G836" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24486,7 +24486,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24512,7 +24512,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24538,7 +24538,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G839" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24564,7 +24564,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24590,7 +24590,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G841" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24616,7 +24616,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G842" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24642,7 +24642,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24668,7 +24668,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G844" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24694,7 +24694,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G845" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24720,7 +24720,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24746,7 +24746,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24772,7 +24772,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24798,7 +24798,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24824,7 +24824,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G850" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24850,7 +24850,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24876,7 +24876,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24902,7 +24902,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G853" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24928,7 +24928,7 @@
         <v>4.25</v>
       </c>
       <c r="G854" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24954,7 +24954,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24980,7 +24980,7 @@
         <v>4.25</v>
       </c>
       <c r="G856" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25006,7 +25006,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G857" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25032,7 +25032,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G858" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25058,7 +25058,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G859" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25084,7 +25084,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25110,7 +25110,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G861" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25136,7 +25136,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G862" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25162,7 +25162,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G863" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25188,7 +25188,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G864" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25214,7 +25214,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G865" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25266,7 +25266,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G867" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25370,7 +25370,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25422,7 +25422,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G873" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25552,7 +25552,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G878" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25916,7 +25916,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G892" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25994,7 +25994,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G895" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26228,7 +26228,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G904" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -30414,7 +30414,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1065" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30700,7 +30700,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1076" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30726,7 +30726,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1077" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30960,7 +30960,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1086" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31324,7 +31324,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1100" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31428,7 +31428,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1104" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32936,7 +32936,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1162" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32962,7 +32962,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1163" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33404,7 +33404,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1180" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33534,7 +33534,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1185" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33742,7 +33742,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1193" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -68429,6 +68429,58 @@
         <v>789</v>
       </c>
       <c r="H2527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>45999.3333333333</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>789</v>
+      </c>
+      <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6816203704</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>31010</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>790</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825932025909</t>
+    <t xml:space="preserve">1.85825955867767</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91323792934418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109167575836</t>
+    <t xml:space="preserve">1.9132376909256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109191417694</t>
   </si>
   <si>
     <t xml:space="preserve">1.88496315479279</t>
@@ -56,22 +56,22 @@
     <t xml:space="preserve">1.92423319816589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80642306804657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82998478412628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79856908321381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76715290546417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354685783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86925554275513</t>
+    <t xml:space="preserve">1.80642294883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82998502254486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79856896400452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76715302467346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86925530433655</t>
   </si>
   <si>
     <t xml:space="preserve">1.87710905075073</t>
@@ -80,22 +80,22 @@
     <t xml:space="preserve">1.89281725883484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86768424510956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81584787368774</t>
+    <t xml:space="preserve">1.86768400669098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81584775447845</t>
   </si>
   <si>
     <t xml:space="preserve">1.83783888816833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87553811073303</t>
+    <t xml:space="preserve">1.87553834915161</t>
   </si>
   <si>
     <t xml:space="preserve">1.82684326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84569299221039</t>
+    <t xml:space="preserve">1.84569275379181</t>
   </si>
   <si>
     <t xml:space="preserve">1.81898927688599</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">1.82056045532227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81741869449615</t>
+    <t xml:space="preserve">1.81741845607758</t>
   </si>
   <si>
     <t xml:space="preserve">1.85040545463562</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">1.88025081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81427681446075</t>
+    <t xml:space="preserve">1.81427693367004</t>
   </si>
   <si>
     <t xml:space="preserve">1.85197627544403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84412240982056</t>
+    <t xml:space="preserve">1.84412217140198</t>
   </si>
   <si>
     <t xml:space="preserve">1.84098064899445</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">1.94622433185577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95407843589783</t>
+    <t xml:space="preserve">1.95407819747925</t>
   </si>
   <si>
     <t xml:space="preserve">1.96350312232971</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">2.00905680656433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0247642993927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93051636219025</t>
+    <t xml:space="preserve">2.02476453781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93051660060883</t>
   </si>
   <si>
     <t xml:space="preserve">1.9619323015213</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">1.95564925670624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91637909412384</t>
+    <t xml:space="preserve">1.91637885570526</t>
   </si>
   <si>
     <t xml:space="preserve">1.87396728992462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93378698825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017564296722</t>
+    <t xml:space="preserve">1.93378722667694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017540454865</t>
   </si>
   <si>
     <t xml:space="preserve">1.92231559753418</t>
@@ -224,19 +224,19 @@
     <t xml:space="preserve">1.91248285770416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91084396839142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545899391174</t>
+    <t xml:space="preserve">1.91084408760071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545887470245</t>
   </si>
   <si>
     <t xml:space="preserve">1.80268287658691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84201431274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83218121528625</t>
+    <t xml:space="preserve">1.84201419353485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83218145370483</t>
   </si>
   <si>
     <t xml:space="preserve">1.88298428058624</t>
@@ -248,31 +248,31 @@
     <t xml:space="preserve">1.9075665473938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89281702041626</t>
+    <t xml:space="preserve">1.89281713962555</t>
   </si>
   <si>
     <t xml:space="preserve">1.90592741966248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88462316989899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920495986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87151265144348</t>
+    <t xml:space="preserve">1.88462293148041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920519828796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87151277065277</t>
   </si>
   <si>
     <t xml:space="preserve">1.89773344993591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82398760318756</t>
+    <t xml:space="preserve">1.82398748397827</t>
   </si>
   <si>
     <t xml:space="preserve">1.75843513011932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76662909984589</t>
+    <t xml:space="preserve">1.76662921905518</t>
   </si>
   <si>
     <t xml:space="preserve">1.78629493713379</t>
@@ -290,13 +290,13 @@
     <t xml:space="preserve">1.77973973751068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75024127960205</t>
+    <t xml:space="preserve">1.75024116039276</t>
   </si>
   <si>
     <t xml:space="preserve">1.72074270248413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6699401140213</t>
+    <t xml:space="preserve">1.66993999481201</t>
   </si>
   <si>
     <t xml:space="preserve">1.72893667221069</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">1.76007401943207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70435464382172</t>
+    <t xml:space="preserve">1.70435476303101</t>
   </si>
   <si>
     <t xml:space="preserve">1.73549211025238</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">1.73385322093964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71254873275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63060879707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67157876491547</t>
+    <t xml:space="preserve">1.71254861354828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63060867786407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67157864570618</t>
   </si>
   <si>
     <t xml:space="preserve">1.66666221618652</t>
@@ -332,19 +332,19 @@
     <t xml:space="preserve">1.61012363433838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62241470813751</t>
+    <t xml:space="preserve">1.62241458892822</t>
   </si>
   <si>
     <t xml:space="preserve">1.66338467597961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67321765422821</t>
+    <t xml:space="preserve">1.67321753501892</t>
   </si>
   <si>
     <t xml:space="preserve">1.64535784721375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63880264759064</t>
+    <t xml:space="preserve">1.63880276679993</t>
   </si>
   <si>
     <t xml:space="preserve">1.62569212913513</t>
@@ -359,19 +359,19 @@
     <t xml:space="preserve">1.64699673652649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63798320293427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59865188598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62978911399841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58308351039886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59537446498871</t>
+    <t xml:space="preserve">1.63798332214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59865200519562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6297892332077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58308339118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59537434577942</t>
   </si>
   <si>
     <t xml:space="preserve">1.57898640632629</t>
@@ -380,13 +380,13 @@
     <t xml:space="preserve">1.59127748012543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54047453403473</t>
+    <t xml:space="preserve">1.54047441482544</t>
   </si>
   <si>
     <t xml:space="preserve">1.56751477718353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56997299194336</t>
+    <t xml:space="preserve">1.56997287273407</t>
   </si>
   <si>
     <t xml:space="preserve">1.56669533252716</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">1.6027489900589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60356843471527</t>
+    <t xml:space="preserve">1.60356855392456</t>
   </si>
   <si>
     <t xml:space="preserve">1.6060266494751</t>
@@ -410,22 +410,22 @@
     <t xml:space="preserve">1.56177890300751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54539108276367</t>
+    <t xml:space="preserve">1.54539096355438</t>
   </si>
   <si>
     <t xml:space="preserve">1.37659418582916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41264808177948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39462113380432</t>
+    <t xml:space="preserve">1.41264796257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39462101459503</t>
   </si>
   <si>
     <t xml:space="preserve">1.45771491527557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47082531452179</t>
+    <t xml:space="preserve">1.47082543373108</t>
   </si>
   <si>
     <t xml:space="preserve">1.53391933441162</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">1.54211330413818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51179540157318</t>
+    <t xml:space="preserve">1.51179552078247</t>
   </si>
   <si>
     <t xml:space="preserve">1.55522382259369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56505656242371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56423723697662</t>
+    <t xml:space="preserve">1.56505644321442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56423711776733</t>
   </si>
   <si>
     <t xml:space="preserve">1.59291625022888</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">1.52162826061249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5412939786911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50442087650299</t>
+    <t xml:space="preserve">1.54129385948181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5044207572937</t>
   </si>
   <si>
     <t xml:space="preserve">1.51097619533539</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">1.55112671852112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51589238643646</t>
+    <t xml:space="preserve">1.51589250564575</t>
   </si>
   <si>
     <t xml:space="preserve">1.55194628238678</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">1.50851774215698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53228068351746</t>
+    <t xml:space="preserve">1.53228056430817</t>
   </si>
   <si>
     <t xml:space="preserve">1.50933730602264</t>
@@ -500,37 +500,37 @@
     <t xml:space="preserve">1.49540746212006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51015663146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57325053215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58554136753082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59455502033234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60684597492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62159538269043</t>
+    <t xml:space="preserve">1.51015675067902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57325065135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58554148674011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59455513954163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60684585571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62159526348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.57161176204681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54375219345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57243120670319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58718025684357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54621016979218</t>
+    <t xml:space="preserve">1.54375207424164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57243132591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58718037605286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54621028900146</t>
   </si>
   <si>
     <t xml:space="preserve">1.55768203735352</t>
@@ -548,10 +548,10 @@
     <t xml:space="preserve">1.54702973365784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53883564472198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54784905910492</t>
+    <t xml:space="preserve">1.53883576393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54784917831421</t>
   </si>
   <si>
     <t xml:space="preserve">1.55276548862457</t>
@@ -575,97 +575,97 @@
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191316604614</t>
+    <t xml:space="preserve">1.65191304683685</t>
   </si>
   <si>
     <t xml:space="preserve">1.69288313388824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65355181694031</t>
+    <t xml:space="preserve">1.65355169773102</t>
   </si>
   <si>
     <t xml:space="preserve">1.82070958614349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82890391349792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81743216514587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81579351425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87970626354218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79448878765106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80104398727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73876965045929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72729814052582</t>
+    <t xml:space="preserve">1.82890379428864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81743204593658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.815793633461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87970650196075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79448890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80104410648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72729802131653</t>
   </si>
   <si>
     <t xml:space="preserve">1.74696362018585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76335167884827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8469306230545</t>
+    <t xml:space="preserve">1.76335155963898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84693050384521</t>
   </si>
   <si>
     <t xml:space="preserve">1.81087708473206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80923807621002</t>
+    <t xml:space="preserve">1.80923795700073</t>
   </si>
   <si>
     <t xml:space="preserve">1.81251573562622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86167991161346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86495769023895</t>
+    <t xml:space="preserve">1.86168015003204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86495745182037</t>
   </si>
   <si>
     <t xml:space="preserve">1.85840213298798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87642908096313</t>
+    <t xml:space="preserve">1.87642896175385</t>
   </si>
   <si>
     <t xml:space="preserve">1.89937257766724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84856951236725</t>
+    <t xml:space="preserve">1.84856939315796</t>
   </si>
   <si>
     <t xml:space="preserve">1.92479622364044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93679404258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850827217102</t>
+    <t xml:space="preserve">1.93679416179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850839138031</t>
   </si>
   <si>
     <t xml:space="preserve">1.97107374668121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92822420597076</t>
+    <t xml:space="preserve">1.92822432518005</t>
   </si>
   <si>
     <t xml:space="preserve">1.94193625450134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94365012645721</t>
+    <t xml:space="preserve">1.94365000724792</t>
   </si>
   <si>
     <t xml:space="preserve">1.95907580852509</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">1.93336617946625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90594255924225</t>
+    <t xml:space="preserve">1.90594267845154</t>
   </si>
   <si>
     <t xml:space="preserve">1.8939448595047</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">1.8716629743576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92993855476379</t>
+    <t xml:space="preserve">1.92993831634521</t>
   </si>
   <si>
     <t xml:space="preserve">1.90080046653748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91451239585876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88708889484406</t>
+    <t xml:space="preserve">1.91451251506805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">1.87680494785309</t>
@@ -713,16 +713,16 @@
     <t xml:space="preserve">1.8853747844696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86994898319244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88880276679993</t>
+    <t xml:space="preserve">1.86994886398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88880288600922</t>
   </si>
   <si>
     <t xml:space="preserve">1.90937054157257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90251469612122</t>
+    <t xml:space="preserve">1.90251457691193</t>
   </si>
   <si>
     <t xml:space="preserve">1.96421790122986</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">1.98649966716766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97964370250702</t>
+    <t xml:space="preserve">1.97964346408844</t>
   </si>
   <si>
     <t xml:space="preserve">2.12533164024353</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">2.08591032028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05677270889282</t>
+    <t xml:space="preserve">2.0567729473114</t>
   </si>
   <si>
     <t xml:space="preserve">2.07905435562134</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">2.0807683467865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06534242630005</t>
+    <t xml:space="preserve">2.06534266471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.06020045280457</t>
@@ -767,13 +767,13 @@
     <t xml:space="preserve">2.13390159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1081919670105</t>
+    <t xml:space="preserve">2.10819172859192</t>
   </si>
   <si>
     <t xml:space="preserve">2.09962201118469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10304999351501</t>
+    <t xml:space="preserve">2.10304975509644</t>
   </si>
   <si>
     <t xml:space="preserve">2.03963279724121</t>
@@ -788,28 +788,28 @@
     <t xml:space="preserve">2.07391238212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09790802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1167619228363</t>
+    <t xml:space="preserve">2.09790778160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11676168441772</t>
   </si>
   <si>
     <t xml:space="preserve">2.08248209953308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06705641746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12190365791321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10647773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0893383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05163049697876</t>
+    <t xml:space="preserve">2.06705665588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12190389633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10647797584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08933806419373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05163073539734</t>
   </si>
   <si>
     <t xml:space="preserve">2.17675089836121</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">2.14247155189514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1321873664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13047385215759</t>
+    <t xml:space="preserve">2.13218760490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13047361373901</t>
   </si>
   <si>
     <t xml:space="preserve">2.15961122512817</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">2.11847543716431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09105181694031</t>
+    <t xml:space="preserve">2.09105205535889</t>
   </si>
   <si>
     <t xml:space="preserve">2.12361764907837</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">2.15789723396301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15618348121643</t>
+    <t xml:space="preserve">2.15618324279785</t>
   </si>
   <si>
     <t xml:space="preserve">2.1441855430603</t>
@@ -857,10 +857,10 @@
     <t xml:space="preserve">2.14932703971863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13904356956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17503690719604</t>
+    <t xml:space="preserve">2.13904333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17503714561462</t>
   </si>
   <si>
     <t xml:space="preserve">2.15104126930237</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">2.12018966674805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1047637462616</t>
+    <t xml:space="preserve">2.10476398468018</t>
   </si>
   <si>
     <t xml:space="preserve">2.06362843513489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03277707099915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0482029914856</t>
+    <t xml:space="preserve">2.03277683258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04820275306702</t>
   </si>
   <si>
     <t xml:space="preserve">2.07048416137695</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">2.0499165058136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12875962257385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08762431144714</t>
+    <t xml:space="preserve">2.12875938415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08762407302856</t>
   </si>
   <si>
     <t xml:space="preserve">2.02077913284302</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">2.33100891113281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32243895530701</t>
+    <t xml:space="preserve">2.32243919372559</t>
   </si>
   <si>
     <t xml:space="preserve">2.35671830177307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44241738319397</t>
+    <t xml:space="preserve">2.44241714477539</t>
   </si>
   <si>
     <t xml:space="preserve">2.49383664131165</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">2.57953572273254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.596675157547</t>
+    <t xml:space="preserve">2.59667539596558</t>
   </si>
   <si>
     <t xml:space="preserve">2.61381506919861</t>
@@ -68460,7 +68460,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6816203704</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>31010</v>
@@ -68481,6 +68481,32 @@
         <v>790</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.5991203704</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>35531</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>788</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -44,37 +44,37 @@
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9132376909256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109167575836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8849630355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92423319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80642306804657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82998502254486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79856884479523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76715278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85354697704315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86925530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87710916996002</t>
+    <t xml:space="preserve">1.91323757171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109191417694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88496315479279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9242330789566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80642282962799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82998514175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79856896400452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76715302467346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85354721546173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86925518512726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87710905075073</t>
   </si>
   <si>
     <t xml:space="preserve">1.89281713962555</t>
@@ -86,31 +86,31 @@
     <t xml:space="preserve">1.81584763526917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83783900737762</t>
+    <t xml:space="preserve">1.83783888816833</t>
   </si>
   <si>
     <t xml:space="preserve">1.87553822994232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82684350013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8456928730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8189891576767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8362683057785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8598301410675</t>
+    <t xml:space="preserve">1.82684326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84569275379181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81898939609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83626818656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85983026027679</t>
   </si>
   <si>
     <t xml:space="preserve">1.80485212802887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82056021690369</t>
+    <t xml:space="preserve">1.82056045532227</t>
   </si>
   <si>
     <t xml:space="preserve">1.81741845607758</t>
@@ -119,16 +119,16 @@
     <t xml:space="preserve">1.85040545463562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88025081157684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81427705287933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85197603702545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84412217140198</t>
+    <t xml:space="preserve">1.88025069236755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81427693367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85197627544403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84412205219269</t>
   </si>
   <si>
     <t xml:space="preserve">1.84098052978516</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">1.82370173931122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81113529205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82213115692139</t>
+    <t xml:space="preserve">1.81113541126251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8221310377121</t>
   </si>
   <si>
     <t xml:space="preserve">1.93679976463318</t>
@@ -149,22 +149,22 @@
     <t xml:space="preserve">1.94622445106506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95407807826996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.963503241539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96507382392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99334836006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00434422492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98706531524658</t>
+    <t xml:space="preserve">1.95407831668854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96350300312042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9650741815567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99334847927094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00434398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98706543445587</t>
   </si>
   <si>
     <t xml:space="preserve">2.00905680656433</t>
@@ -173,49 +173,49 @@
     <t xml:space="preserve">2.02476477622986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93051648139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9619323015213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994128704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564925670624</t>
+    <t xml:space="preserve">1.93051636219025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96193218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994116783142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564913749695</t>
   </si>
   <si>
     <t xml:space="preserve">1.91637897491455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8739675283432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378698825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017540454865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92231583595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050968647003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656310558319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509159564972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95836925506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739904880524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93542611598969</t>
+    <t xml:space="preserve">1.87396740913391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378722667694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017528533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050944805145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656346321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509135723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95836913585663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739916801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9354259967804</t>
   </si>
   <si>
     <t xml:space="preserve">1.94198131561279</t>
@@ -224,49 +224,49 @@
     <t xml:space="preserve">1.91248285770416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91084408760071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545899391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80268287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84201419353485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83218133449554</t>
+    <t xml:space="preserve">1.91084396839142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545887470245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8026829957962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84201431274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83218145370483</t>
   </si>
   <si>
     <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86823511123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9075665473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88462316989899</t>
+    <t xml:space="preserve">1.86823523044586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90756642818451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90592730045319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88462293148041</t>
   </si>
   <si>
     <t xml:space="preserve">1.90920507907867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87151265144348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89773333072662</t>
+    <t xml:space="preserve">1.87151277065277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8977335691452</t>
   </si>
   <si>
     <t xml:space="preserve">1.82398748397827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75843524932861</t>
+    <t xml:space="preserve">1.75843501091003</t>
   </si>
   <si>
     <t xml:space="preserve">1.76662921905518</t>
@@ -275,58 +275,58 @@
     <t xml:space="preserve">1.78629493713379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77646207809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75188004970551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75351893901825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77973985671997</t>
+    <t xml:space="preserve">1.77646219730377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75188016891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75351905822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77973961830139</t>
   </si>
   <si>
     <t xml:space="preserve">1.75024127960205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72074282169342</t>
+    <t xml:space="preserve">1.72074270248413</t>
   </si>
   <si>
     <t xml:space="preserve">1.66993999481201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72893679141998</t>
+    <t xml:space="preserve">1.72893667221069</t>
   </si>
   <si>
     <t xml:space="preserve">1.69616079330444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76007401943207</t>
+    <t xml:space="preserve">1.76007390022278</t>
   </si>
   <si>
     <t xml:space="preserve">1.70435476303101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73549211025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73385322093964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71254873275757</t>
+    <t xml:space="preserve">1.73549199104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73385310173035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71254861354828</t>
   </si>
   <si>
     <t xml:space="preserve">1.63060867786407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67157876491547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66666233539581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61012375354767</t>
+    <t xml:space="preserve">1.67157864570618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66666221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61012363433838</t>
   </si>
   <si>
     <t xml:space="preserve">1.62241458892822</t>
@@ -338,13 +338,13 @@
     <t xml:space="preserve">1.67321753501892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64535784721375</t>
+    <t xml:space="preserve">1.64535772800446</t>
   </si>
   <si>
     <t xml:space="preserve">1.63880264759064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62569224834442</t>
+    <t xml:space="preserve">1.62569212913513</t>
   </si>
   <si>
     <t xml:space="preserve">1.66830110549927</t>
@@ -365,40 +365,40 @@
     <t xml:space="preserve">1.6297892332077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58308351039886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59537446498871</t>
+    <t xml:space="preserve">1.58308339118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59537434577942</t>
   </si>
   <si>
     <t xml:space="preserve">1.57898640632629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59127748012543</t>
+    <t xml:space="preserve">1.59127736091614</t>
   </si>
   <si>
     <t xml:space="preserve">1.54047453403473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56751465797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56997299194336</t>
+    <t xml:space="preserve">1.56751477718353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56997287273407</t>
   </si>
   <si>
     <t xml:space="preserve">1.56669533252716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55850124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60274887084961</t>
+    <t xml:space="preserve">1.5585013628006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6027489900589</t>
   </si>
   <si>
     <t xml:space="preserve">1.60356843471527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6060266494751</t>
+    <t xml:space="preserve">1.60602676868439</t>
   </si>
   <si>
     <t xml:space="preserve">1.51917004585266</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">1.37659406661987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4126478433609</t>
+    <t xml:space="preserve">1.41264796257019</t>
   </si>
   <si>
     <t xml:space="preserve">1.39462113380432</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">1.45771491527557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47082531452179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53391945362091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6125819683075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61176252365112</t>
+    <t xml:space="preserve">1.47082543373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53391933441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61258172988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61176240444183</t>
   </si>
   <si>
     <t xml:space="preserve">1.59783267974854</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">1.54211330413818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51179540157318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55522382259369</t>
+    <t xml:space="preserve">1.51179552078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5552237033844</t>
   </si>
   <si>
     <t xml:space="preserve">1.56505644321442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56423723697662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59291625022888</t>
+    <t xml:space="preserve">1.56423711776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59291613101959</t>
   </si>
   <si>
     <t xml:space="preserve">1.55686259269714</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">1.54129385948181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50442087650299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5109760761261</t>
+    <t xml:space="preserve">1.5044207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51097619533539</t>
   </si>
   <si>
     <t xml:space="preserve">1.55112683773041</t>
@@ -479,40 +479,40 @@
     <t xml:space="preserve">1.55194616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50851774215698</t>
+    <t xml:space="preserve">1.50851762294769</t>
   </si>
   <si>
     <t xml:space="preserve">1.53228056430817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50933718681335</t>
+    <t xml:space="preserve">1.50933730602264</t>
   </si>
   <si>
     <t xml:space="preserve">1.50769853591919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50278210639954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49540746212006</t>
+    <t xml:space="preserve">1.50278198719025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49540758132935</t>
   </si>
   <si>
     <t xml:space="preserve">1.51015663146973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57325053215027</t>
+    <t xml:space="preserve">1.57325065135956</t>
   </si>
   <si>
     <t xml:space="preserve">1.58554148674011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59455490112305</t>
+    <t xml:space="preserve">1.59455502033234</t>
   </si>
   <si>
     <t xml:space="preserve">1.60684585571289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62159514427185</t>
+    <t xml:space="preserve">1.62159526348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.57161176204681</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">1.57243132591248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58718037605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54621016979218</t>
+    <t xml:space="preserve">1.58718049526215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54621028900146</t>
   </si>
   <si>
     <t xml:space="preserve">1.55768203735352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58799970149994</t>
+    <t xml:space="preserve">1.58799982070923</t>
   </si>
   <si>
     <t xml:space="preserve">1.53473877906799</t>
@@ -548,22 +548,22 @@
     <t xml:space="preserve">1.53883576393127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54784917831421</t>
+    <t xml:space="preserve">1.5478492975235</t>
   </si>
   <si>
     <t xml:space="preserve">1.55276548862457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54948782920837</t>
+    <t xml:space="preserve">1.54948806762695</t>
   </si>
   <si>
     <t xml:space="preserve">1.5380163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.548668384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53637754917145</t>
+    <t xml:space="preserve">1.54866850376129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53637742996216</t>
   </si>
   <si>
     <t xml:space="preserve">1.53965508937836</t>
@@ -575,19 +575,19 @@
     <t xml:space="preserve">1.65191316604614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69288325309753</t>
+    <t xml:space="preserve">1.69288313388824</t>
   </si>
   <si>
     <t xml:space="preserve">1.65355181694031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82070970535278</t>
+    <t xml:space="preserve">1.82070958614349</t>
   </si>
   <si>
     <t xml:space="preserve">1.82890379428864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81743204593658</t>
+    <t xml:space="preserve">1.81743192672729</t>
   </si>
   <si>
     <t xml:space="preserve">1.81579351425171</t>
@@ -602,16 +602,16 @@
     <t xml:space="preserve">1.80104410648346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73876965045929</t>
+    <t xml:space="preserve">1.73876953125</t>
   </si>
   <si>
     <t xml:space="preserve">1.72729802131653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74696362018585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76335155963898</t>
+    <t xml:space="preserve">1.74696373939514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76335144042969</t>
   </si>
   <si>
     <t xml:space="preserve">1.84693050384521</t>
@@ -623,40 +623,40 @@
     <t xml:space="preserve">1.80923795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81251561641693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86167979240417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86495757102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85840201377869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87642908096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89937233924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84856927394867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92479634284973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679392337799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850827217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97107374668121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822420597076</t>
+    <t xml:space="preserve">1.81251573562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86168015003204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86495745182037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85840213298798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87642896175385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89937257766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84856939315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92479622364044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679404258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850839138031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107362747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822432518005</t>
   </si>
   <si>
     <t xml:space="preserve">1.94193613529205</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">1.94364988803864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95907592773438</t>
+    <t xml:space="preserve">1.95907580852509</t>
   </si>
   <si>
     <t xml:space="preserve">1.96764576435089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92651033401489</t>
+    <t xml:space="preserve">1.9265102148056</t>
   </si>
   <si>
     <t xml:space="preserve">1.95393395423889</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">1.93336606025696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90594255924225</t>
+    <t xml:space="preserve">1.90594267845154</t>
   </si>
   <si>
     <t xml:space="preserve">1.8939448595047</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">1.8716629743576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9299384355545</t>
+    <t xml:space="preserve">1.92993831634521</t>
   </si>
   <si>
     <t xml:space="preserve">1.90080046653748</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">1.88708889484406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87680494785309</t>
+    <t xml:space="preserve">1.87680506706238</t>
   </si>
   <si>
     <t xml:space="preserve">1.91794049739838</t>
@@ -710,13 +710,13 @@
     <t xml:space="preserve">1.8853747844696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86994910240173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88880264759064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90937042236328</t>
+    <t xml:space="preserve">1.86994898319244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88880288600922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90937054157257</t>
   </si>
   <si>
     <t xml:space="preserve">1.90251469612122</t>
@@ -728,28 +728,28 @@
     <t xml:space="preserve">1.96250379085541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821365833282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98649954795837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97964358329773</t>
+    <t xml:space="preserve">1.98821341991425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98649966716766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97964346408844</t>
   </si>
   <si>
     <t xml:space="preserve">2.12533164024353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08591032028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05677247047424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07905459403992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0807683467865</t>
+    <t xml:space="preserve">2.0859100818634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05677270889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07905435562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08076810836792</t>
   </si>
   <si>
     <t xml:space="preserve">2.06534242630005</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">2.06020045280457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07219862937927</t>
+    <t xml:space="preserve">2.07219839096069</t>
   </si>
   <si>
     <t xml:space="preserve">2.13390159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10819220542908</t>
+    <t xml:space="preserve">2.1081919670105</t>
   </si>
   <si>
     <t xml:space="preserve">2.09962201118469</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">2.10304975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03963303565979</t>
+    <t xml:space="preserve">2.03963279724121</t>
   </si>
   <si>
     <t xml:space="preserve">2.06877040863037</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">2.09790778160095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1167619228363</t>
+    <t xml:space="preserve">2.11676168441772</t>
   </si>
   <si>
     <t xml:space="preserve">2.08248209953308</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">2.12190365791321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10647797584534</t>
+    <t xml:space="preserve">2.10647773742676</t>
   </si>
   <si>
     <t xml:space="preserve">2.08933806419373</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">2.14247131347656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1321873664856</t>
+    <t xml:space="preserve">2.13218760490417</t>
   </si>
   <si>
     <t xml:space="preserve">2.13047361373901</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">2.11847543716431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09105181694031</t>
+    <t xml:space="preserve">2.09105205535889</t>
   </si>
   <si>
     <t xml:space="preserve">2.12361764907837</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">2.15789699554443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15618348121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14418530464172</t>
+    <t xml:space="preserve">2.15618324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1441855430603</t>
   </si>
   <si>
     <t xml:space="preserve">2.1407573223114</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">2.13904333114624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17503690719604</t>
+    <t xml:space="preserve">2.17503714561462</t>
   </si>
   <si>
     <t xml:space="preserve">2.15104126930237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12018990516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1047637462616</t>
+    <t xml:space="preserve">2.12018966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10476398468018</t>
   </si>
   <si>
     <t xml:space="preserve">2.06362843513489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03277707099915</t>
+    <t xml:space="preserve">2.03277683258057</t>
   </si>
   <si>
     <t xml:space="preserve">2.04820275306702</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">2.00535321235657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16818118095398</t>
+    <t xml:space="preserve">2.1681809425354</t>
   </si>
   <si>
     <t xml:space="preserve">2.18532085418701</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">2.33100891113281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32243895530701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35671830177307</t>
+    <t xml:space="preserve">2.32243919372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35671854019165</t>
   </si>
   <si>
     <t xml:space="preserve">2.44241738319397</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.47669696807861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48526668548584</t>
+    <t xml:space="preserve">2.48526692390442</t>
   </si>
   <si>
     <t xml:space="preserve">2.53668618202209</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">2.59667539596558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61381483078003</t>
+    <t xml:space="preserve">2.61381506919861</t>
   </si>
   <si>
     <t xml:space="preserve">2.55382585525513</t>
@@ -968,13 +968,13 @@
     <t xml:space="preserve">2.52694344520569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43733549118042</t>
+    <t xml:space="preserve">2.437335729599</t>
   </si>
   <si>
     <t xml:space="preserve">2.46421790122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50006103515625</t>
+    <t xml:space="preserve">2.50006127357483</t>
   </si>
   <si>
     <t xml:space="preserve">2.45525717735291</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">2.51798272132874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56278657913208</t>
+    <t xml:space="preserve">2.56278681755066</t>
   </si>
   <si>
     <t xml:space="preserve">2.53590416908264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4911003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48213982582092</t>
+    <t xml:space="preserve">2.49110054969788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48213958740234</t>
   </si>
   <si>
     <t xml:space="preserve">2.50902199745178</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">2.78680658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75992441177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77784562110901</t>
+    <t xml:space="preserve">2.7599241733551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77784585952759</t>
   </si>
   <si>
     <t xml:space="preserve">2.74200248718262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76888489723206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71512007713318</t>
+    <t xml:space="preserve">2.76888513565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71512031555176</t>
   </si>
   <si>
     <t xml:space="preserve">2.75096321105957</t>
@@ -1055,13 +1055,13 @@
     <t xml:space="preserve">2.86745381355286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83161044120789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6434338092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62551236152649</t>
+    <t xml:space="preserve">2.83161067962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64343404769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62551259994507</t>
   </si>
   <si>
     <t xml:space="preserve">2.58070850372314</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">2.607590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41941428184509</t>
+    <t xml:space="preserve">2.41941404342651</t>
   </si>
   <si>
     <t xml:space="preserve">2.66135549545288</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">2.81368899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84057140350342</t>
+    <t xml:space="preserve">2.840571641922</t>
   </si>
   <si>
     <t xml:space="preserve">2.93914008140564</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">2.80472826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90329670906067</t>
+    <t xml:space="preserve">2.90329694747925</t>
   </si>
   <si>
     <t xml:space="preserve">3.12731671333313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16315984725952</t>
+    <t xml:space="preserve">3.16315960884094</t>
   </si>
   <si>
     <t xml:space="preserve">3.13627743721008</t>
@@ -1118,19 +1118,19 @@
     <t xml:space="preserve">3.28861093521118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29757189750671</t>
+    <t xml:space="preserve">3.29757165908813</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33341503143311</t>
+    <t xml:space="preserve">3.33341479301453</t>
   </si>
   <si>
     <t xml:space="preserve">3.34237575531006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42302298545837</t>
+    <t xml:space="preserve">3.42302274703979</t>
   </si>
   <si>
     <t xml:space="preserve">3.3871796131134</t>
@@ -1148,10 +1148,10 @@
     <t xml:space="preserve">3.37821888923645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45886564254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48574876785278</t>
+    <t xml:space="preserve">3.45886588096619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4857485294342</t>
   </si>
   <si>
     <t xml:space="preserve">3.47678756713867</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">3.67392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58431696891785</t>
+    <t xml:space="preserve">3.58431720733643</t>
   </si>
   <si>
     <t xml:space="preserve">3.53055238723755</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">3.55743479728699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52159142494202</t>
+    <t xml:space="preserve">3.5215916633606</t>
   </si>
   <si>
     <t xml:space="preserve">3.51263093948364</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">3.80833721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79041504859924</t>
+    <t xml:space="preserve">3.79041528701782</t>
   </si>
   <si>
     <t xml:space="preserve">3.95170950889587</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">3.97005581855774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00759792327881</t>
+    <t xml:space="preserve">4.00759744644165</t>
   </si>
   <si>
     <t xml:space="preserve">4.0920672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81988835334778</t>
+    <t xml:space="preserve">3.81988859176636</t>
   </si>
   <si>
     <t xml:space="preserve">3.87620115280151</t>
@@ -1259,40 +1259,40 @@
     <t xml:space="preserve">4.03575468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99821257591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97944092750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85743021965027</t>
+    <t xml:space="preserve">3.9982123374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97944116592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85743045806885</t>
   </si>
   <si>
     <t xml:space="preserve">3.84804463386536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81050252914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7448046207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89497232437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94189953804016</t>
+    <t xml:space="preserve">3.81050276756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74480438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89497208595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.941899061203</t>
   </si>
   <si>
     <t xml:space="preserve">3.8668155670166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93251395225525</t>
+    <t xml:space="preserve">3.93251419067383</t>
   </si>
   <si>
     <t xml:space="preserve">4.08268165588379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11083793640137</t>
+    <t xml:space="preserve">4.11083841323853</t>
   </si>
   <si>
     <t xml:space="preserve">4.12022304534912</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">4.18592166900635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19530725479126</t>
+    <t xml:space="preserve">4.1953067779541</t>
   </si>
   <si>
     <t xml:space="preserve">4.20469284057617</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">4.28916215896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26100587844849</t>
+    <t xml:space="preserve">4.26100540161133</t>
   </si>
   <si>
     <t xml:space="preserve">4.2703914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34547472000122</t>
+    <t xml:space="preserve">4.34547519683838</t>
   </si>
   <si>
     <t xml:space="preserve">4.36424589157104</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">4.50502824783325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49564266204834</t>
+    <t xml:space="preserve">4.49564218521118</t>
   </si>
   <si>
     <t xml:space="preserve">4.43932962417603</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">4.5519552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54257011413574</t>
+    <t xml:space="preserve">4.54256963729858</t>
   </si>
   <si>
     <t xml:space="preserve">4.48625707626343</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">4.40178775787354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44871520996094</t>
+    <t xml:space="preserve">4.44871473312378</t>
   </si>
   <si>
     <t xml:space="preserve">4.42994403839111</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">4.41117334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39240169525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24223470687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30793333053589</t>
+    <t xml:space="preserve">4.39240217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2422342300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30793285369873</t>
   </si>
   <si>
     <t xml:space="preserve">4.17653608322144</t>
@@ -1394,28 +1394,28 @@
     <t xml:space="preserve">4.62703895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61765336990356</t>
+    <t xml:space="preserve">4.61765384674072</t>
   </si>
   <si>
     <t xml:space="preserve">4.51441335678101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57072591781616</t>
+    <t xml:space="preserve">4.57072639465332</t>
   </si>
   <si>
     <t xml:space="preserve">4.67396640777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80536270141602</t>
+    <t xml:space="preserve">4.80536317825317</t>
   </si>
   <si>
     <t xml:space="preserve">4.78659200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86167621612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84290504455566</t>
+    <t xml:space="preserve">4.86167573928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84290456771851</t>
   </si>
   <si>
     <t xml:space="preserve">4.89921760559082</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">4.5988826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53318405151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58011150360107</t>
+    <t xml:space="preserve">4.53318452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58011198043823</t>
   </si>
   <si>
     <t xml:space="preserve">4.6927375793457</t>
@@ -1439,16 +1439,16 @@
     <t xml:space="preserve">4.74905014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73027944564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71150827407837</t>
+    <t xml:space="preserve">4.73027896881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71150875091553</t>
   </si>
   <si>
     <t xml:space="preserve">4.76782131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95553112030029</t>
+    <t xml:space="preserve">4.95553064346313</t>
   </si>
   <si>
     <t xml:space="preserve">4.88044691085815</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">4.91798877716064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99307250976562</t>
+    <t xml:space="preserve">4.99307298660278</t>
   </si>
   <si>
     <t xml:space="preserve">4.93675994873047</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">6.60737419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28826808929443</t>
+    <t xml:space="preserve">6.28826761245728</t>
   </si>
   <si>
     <t xml:space="preserve">6.1568717956543</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">5.96916246414185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70636892318726</t>
+    <t xml:space="preserve">5.7063684463501</t>
   </si>
   <si>
     <t xml:space="preserve">5.53743028640747</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">5.87530755996704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66882658004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68759727478027</t>
+    <t xml:space="preserve">5.66882705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68759775161743</t>
   </si>
   <si>
     <t xml:space="preserve">5.83776521682739</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59374284744263</t>
+    <t xml:space="preserve">5.59374332427979</t>
   </si>
   <si>
     <t xml:space="preserve">5.38726234436035</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">5.10569858551025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68335199356079</t>
+    <t xml:space="preserve">4.68335151672363</t>
   </si>
   <si>
     <t xml:space="preserve">4.14837980270386</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">3.62279319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55709481239319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37877082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50078225135803</t>
+    <t xml:space="preserve">3.55709505081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37877106666565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50078201293945</t>
   </si>
   <si>
     <t xml:space="preserve">3.5664803981781</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">3.75418996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70726251602173</t>
+    <t xml:space="preserve">3.70726275444031</t>
   </si>
   <si>
     <t xml:space="preserve">3.71664810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8386595249176</t>
+    <t xml:space="preserve">3.83865928649902</t>
   </si>
   <si>
     <t xml:space="preserve">4.25162029266357</t>
@@ -1580,25 +1580,25 @@
     <t xml:space="preserve">4.12960910797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16715049743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05452537536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76357555389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66972064971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65094995498657</t>
+    <t xml:space="preserve">4.16715097427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05452489852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76357579231262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66972088813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65094971656799</t>
   </si>
   <si>
     <t xml:space="preserve">3.66033530235291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95128512382507</t>
+    <t xml:space="preserve">3.95128488540649</t>
   </si>
   <si>
     <t xml:space="preserve">4.29854726791382</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">4.31731843948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15776491165161</t>
+    <t xml:space="preserve">4.15776538848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.10145235061646</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">4.13899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88558626174927</t>
+    <t xml:space="preserve">3.88558650016785</t>
   </si>
   <si>
     <t xml:space="preserve">4.32670402526855</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">4.27977657318115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.913743019104</t>
+    <t xml:space="preserve">3.91374325752258</t>
   </si>
   <si>
     <t xml:space="preserve">3.92312836647034</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">3.49139666557312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67910623550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38815641403198</t>
+    <t xml:space="preserve">3.67910599708557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3881561756134</t>
   </si>
   <si>
     <t xml:space="preserve">3.35999989509583</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">3.34122896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20044708251953</t>
+    <t xml:space="preserve">3.20044684410095</t>
   </si>
   <si>
     <t xml:space="preserve">3.24737429618835</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">3.47262573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57586574554443</t>
+    <t xml:space="preserve">3.57586598396301</t>
   </si>
   <si>
     <t xml:space="preserve">3.73541903495789</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">3.68849158287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72603368759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52893853187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63217878341675</t>
+    <t xml:space="preserve">3.72603344917297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52893877029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63217854499817</t>
   </si>
   <si>
     <t xml:space="preserve">3.51016759872437</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">3.58525133132935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53832411766052</t>
+    <t xml:space="preserve">3.53832387924194</t>
   </si>
   <si>
     <t xml:space="preserve">3.80111742019653</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">3.48201107978821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46324014663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4444694519043</t>
+    <t xml:space="preserve">3.46324038505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44446921348572</t>
   </si>
   <si>
     <t xml:space="preserve">3.42569851875305</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">3.41631293296814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754199981689</t>
+    <t xml:space="preserve">3.39754176139832</t>
   </si>
   <si>
     <t xml:space="preserve">3.21921801567078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1910617351532</t>
+    <t xml:space="preserve">3.19106149673462</t>
   </si>
   <si>
     <t xml:space="preserve">3.17229056358337</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">3.23798894882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14413404464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25675964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36938524246216</t>
+    <t xml:space="preserve">3.14413380622864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25675988197327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36938548088074</t>
   </si>
   <si>
     <t xml:space="preserve">3.15351939201355</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">3.18167614936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29430174827576</t>
+    <t xml:space="preserve">3.29430150985718</t>
   </si>
   <si>
     <t xml:space="preserve">3.2661452293396</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">3.12536311149597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04089379310608</t>
+    <t xml:space="preserve">3.04089403152466</t>
   </si>
   <si>
     <t xml:space="preserve">3.05027914047241</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">2.93765377998352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95642447471619</t>
+    <t xml:space="preserve">2.95642471313477</t>
   </si>
   <si>
     <t xml:space="preserve">3.03150844573975</t>
@@ -1805,19 +1805,19 @@
     <t xml:space="preserve">3.02212285995483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92826795578003</t>
+    <t xml:space="preserve">2.92826819419861</t>
   </si>
   <si>
     <t xml:space="preserve">2.94703912734985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90011167526245</t>
+    <t xml:space="preserve">2.90011143684387</t>
   </si>
   <si>
     <t xml:space="preserve">2.97519564628601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27553057670593</t>
+    <t xml:space="preserve">3.27553081512451</t>
   </si>
   <si>
     <t xml:space="preserve">3.33184361457825</t>
@@ -68561,7 +68561,7 @@
     </row>
     <row r="2533">
       <c r="A2533" s="1" t="n">
-        <v>46006.6658912037</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2533" t="n">
         <v>35231</v>
@@ -68582,6 +68582,32 @@
         <v>790</v>
       </c>
       <c r="H2533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46007.6692708333</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>36758</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>792</v>
+      </c>
+      <c r="H2534" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85825943946838</t>
+    <t xml:space="preserve">1.85825932025909</t>
   </si>
   <si>
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91323745250702</t>
+    <t xml:space="preserve">1.91323757171631</t>
   </si>
   <si>
     <t xml:space="preserve">1.92109167575836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88496327400208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92423295974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80642282962799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82998490333557</t>
+    <t xml:space="preserve">1.88496315479279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9242330789566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80642306804657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82998502254486</t>
   </si>
   <si>
     <t xml:space="preserve">1.79856884479523</t>
@@ -80,94 +80,94 @@
     <t xml:space="preserve">1.89281725883484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86768412590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81584799289703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83783900737762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8755384683609</t>
+    <t xml:space="preserve">1.86768436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81584763526917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83783888816833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553822994232</t>
   </si>
   <si>
     <t xml:space="preserve">1.82684338092804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84569323062897</t>
+    <t xml:space="preserve">1.84569299221039</t>
   </si>
   <si>
     <t xml:space="preserve">1.81898939609528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8362683057785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85983037948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80485224723816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82056045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81741845607758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85040557384491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88025081157684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81427693367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85197627544403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84412229061127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84098052978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82370173931122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8111355304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82213091850281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9367995262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622445106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407819747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.963503241539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96507441997528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99334847927094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00434422492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98706519603729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905656814575</t>
+    <t xml:space="preserve">1.83626818656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85983002185822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80485212802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82056021690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81741857528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85040545463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88025045394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81427681446075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85197639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84412217140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84098064899445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82370185852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81113541126251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8221310377121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93679976463318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622433185577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407843589783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96350336074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96507394313812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99334859848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00434398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.987065076828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905680656433</t>
   </si>
   <si>
     <t xml:space="preserve">2.0247642993927</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">1.93051624298096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96193242073059</t>
+    <t xml:space="preserve">1.96193253993988</t>
   </si>
   <si>
     <t xml:space="preserve">1.93994116783142</t>
@@ -188,82 +188,82 @@
     <t xml:space="preserve">1.91637921333313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87396728992462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93378698825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95017528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92231547832489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93050968647003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96656346321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509135723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95836913585663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91739916801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9354259967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198107719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91248297691345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91084384918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545911312103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8026829957962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84201431274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83218133449554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88298439979553</t>
+    <t xml:space="preserve">1.87396764755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93378722667694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95017540454865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93050956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96656322479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95836925506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91739904880524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93542587757111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9419811964035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91248285770416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91084408760071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545887470245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80268287658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84201419353485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83218145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
     <t xml:space="preserve">1.86823523044586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90756618976593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281702041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592753887177</t>
+    <t xml:space="preserve">1.9075665473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281713962555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90592741966248</t>
   </si>
   <si>
     <t xml:space="preserve">1.88462293148041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90920507907867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87151265144348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8977335691452</t>
+    <t xml:space="preserve">1.90920519828796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87151277065277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89773344993591</t>
   </si>
   <si>
     <t xml:space="preserve">1.82398748397827</t>
@@ -278,31 +278,31 @@
     <t xml:space="preserve">1.78629493713379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77646195888519</t>
+    <t xml:space="preserve">1.77646219730377</t>
   </si>
   <si>
     <t xml:space="preserve">1.75188004970551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75351905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77973961830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75024127960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72074258327484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6699401140213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72893679141998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69616079330444</t>
+    <t xml:space="preserve">1.75351893901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77973973751068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75024116039276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72074270248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66993999481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72893667221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69616067409515</t>
   </si>
   <si>
     <t xml:space="preserve">1.76007401943207</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">1.73549211025238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73385298252106</t>
+    <t xml:space="preserve">1.73385322093964</t>
   </si>
   <si>
     <t xml:space="preserve">1.71254861354828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63060879707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67157876491547</t>
+    <t xml:space="preserve">1.63060867786407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67157864570618</t>
   </si>
   <si>
     <t xml:space="preserve">1.66666221618652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61012351512909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62241470813751</t>
+    <t xml:space="preserve">1.61012363433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62241458892822</t>
   </si>
   <si>
     <t xml:space="preserve">1.66338467597961</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">1.64535784721375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63880264759064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62569224834442</t>
+    <t xml:space="preserve">1.63880276679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62569212913513</t>
   </si>
   <si>
     <t xml:space="preserve">1.66830110549927</t>
@@ -356,49 +356,49 @@
     <t xml:space="preserve">1.65519070625305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6469966173172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63798320293427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59865212440491</t>
+    <t xml:space="preserve">1.64699673652649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63798332214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59865200519562</t>
   </si>
   <si>
     <t xml:space="preserve">1.6297892332077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58308351039886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.595374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.578986287117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59127736091614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54047453403473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56751489639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56997299194336</t>
+    <t xml:space="preserve">1.58308339118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59537434577942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57898640632629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59127748012543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54047441482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56751477718353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56997287273407</t>
   </si>
   <si>
     <t xml:space="preserve">1.56669533252716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5585013628006</t>
+    <t xml:space="preserve">1.55850124359131</t>
   </si>
   <si>
     <t xml:space="preserve">1.6027489900589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60356831550598</t>
+    <t xml:space="preserve">1.60356855392456</t>
   </si>
   <si>
     <t xml:space="preserve">1.6060266494751</t>
@@ -407,22 +407,22 @@
     <t xml:space="preserve">1.51917004585266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5617790222168</t>
+    <t xml:space="preserve">1.56177890300751</t>
   </si>
   <si>
     <t xml:space="preserve">1.54539096355438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37659406661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4126478433609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39462113380432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45771503448486</t>
+    <t xml:space="preserve">1.37659418582916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41264796257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39462101459503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45771491527557</t>
   </si>
   <si>
     <t xml:space="preserve">1.47082543373108</t>
@@ -434,25 +434,25 @@
     <t xml:space="preserve">1.61258184909821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61176252365112</t>
+    <t xml:space="preserve">1.61176240444183</t>
   </si>
   <si>
     <t xml:space="preserve">1.59783267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54211318492889</t>
+    <t xml:space="preserve">1.54211330413818</t>
   </si>
   <si>
     <t xml:space="preserve">1.51179552078247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5552237033844</t>
+    <t xml:space="preserve">1.55522382259369</t>
   </si>
   <si>
     <t xml:space="preserve">1.56505644321442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56423723697662</t>
+    <t xml:space="preserve">1.56423711776733</t>
   </si>
   <si>
     <t xml:space="preserve">1.59291625022888</t>
@@ -461,16 +461,16 @@
     <t xml:space="preserve">1.55686259269714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52162837982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5412939786911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50442087650299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5109760761261</t>
+    <t xml:space="preserve">1.52162826061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54129385948181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5044207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51097619533539</t>
   </si>
   <si>
     <t xml:space="preserve">1.55112671852112</t>
@@ -479,10 +479,10 @@
     <t xml:space="preserve">1.51589250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55194616317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50851786136627</t>
+    <t xml:space="preserve">1.55194628238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50851774215698</t>
   </si>
   <si>
     <t xml:space="preserve">1.53228056430817</t>
@@ -491,31 +491,31 @@
     <t xml:space="preserve">1.50933730602264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5076984167099</t>
+    <t xml:space="preserve">1.50769853591919</t>
   </si>
   <si>
     <t xml:space="preserve">1.50278198719025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49540758132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51015663146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57325053215027</t>
+    <t xml:space="preserve">1.49540746212006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51015675067902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57325065135956</t>
   </si>
   <si>
     <t xml:space="preserve">1.58554148674011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59455490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60684597492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62159538269043</t>
+    <t xml:space="preserve">1.59455513954163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60684585571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62159526348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.57161176204681</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">1.54375207424164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57243120670319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58718049526215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54621040821075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55768191814423</t>
+    <t xml:space="preserve">1.57243132591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58718037605286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54621028900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55768203735352</t>
   </si>
   <si>
     <t xml:space="preserve">1.58799982070923</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">1.5347386598587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5822639465332</t>
+    <t xml:space="preserve">1.58226406574249</t>
   </si>
   <si>
     <t xml:space="preserve">1.54702973365784</t>
@@ -557,16 +557,16 @@
     <t xml:space="preserve">1.55276548862457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54948806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53801620006561</t>
+    <t xml:space="preserve">1.54948794841766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5380163192749</t>
   </si>
   <si>
     <t xml:space="preserve">1.54866850376129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53637754917145</t>
+    <t xml:space="preserve">1.53637742996216</t>
   </si>
   <si>
     <t xml:space="preserve">1.53965508937836</t>
@@ -575,34 +575,34 @@
     <t xml:space="preserve">1.56915354728699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65191316604614</t>
+    <t xml:space="preserve">1.65191304683685</t>
   </si>
   <si>
     <t xml:space="preserve">1.69288313388824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65355181694031</t>
+    <t xml:space="preserve">1.65355169773102</t>
   </si>
   <si>
     <t xml:space="preserve">1.82070958614349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82890391349792</t>
+    <t xml:space="preserve">1.82890379428864</t>
   </si>
   <si>
     <t xml:space="preserve">1.81743204593658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81579351425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87970638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79448914527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80104434490204</t>
+    <t xml:space="preserve">1.815793633461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87970650196075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79448890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80104410648346</t>
   </si>
   <si>
     <t xml:space="preserve">1.73876953125</t>
@@ -614,28 +614,28 @@
     <t xml:space="preserve">1.74696362018585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76335167884827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8469306230545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81087696552277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80923819541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81251561641693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86168003082275</t>
+    <t xml:space="preserve">1.76335155963898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84693050384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81087708473206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81251573562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86168015003204</t>
   </si>
   <si>
     <t xml:space="preserve">1.86495745182037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85840201377869</t>
+    <t xml:space="preserve">1.85840213298798</t>
   </si>
   <si>
     <t xml:space="preserve">1.87642896175385</t>
@@ -644,28 +644,28 @@
     <t xml:space="preserve">1.89937257766724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84856951236725</t>
+    <t xml:space="preserve">1.84856939315796</t>
   </si>
   <si>
     <t xml:space="preserve">1.92479622364044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93679392337799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93850815296173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97107362747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92822456359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94193637371063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94364988803864</t>
+    <t xml:space="preserve">1.93679416179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93850839138031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97107374668121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92822432518005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94193625450134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94365000724792</t>
   </si>
   <si>
     <t xml:space="preserve">1.95907580852509</t>
@@ -674,46 +674,46 @@
     <t xml:space="preserve">1.96764576435089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9265102148056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95393395423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93336629867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90594255924225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89394462108612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87166309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92993807792664</t>
+    <t xml:space="preserve">1.92651033401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95393407344818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93336617946625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90594267845154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8939448595047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8716629743576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92993831634521</t>
   </si>
   <si>
     <t xml:space="preserve">1.90080046653748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91451263427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88708865642548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87680518627167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9179402589798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88537490367889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86994910240173</t>
+    <t xml:space="preserve">1.91451251506805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88708877563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87680494785309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91794049739838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8853747844696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86994886398315</t>
   </si>
   <si>
     <t xml:space="preserve">1.88880288600922</t>
@@ -722,16 +722,16 @@
     <t xml:space="preserve">1.90937054157257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90251469612122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96421778202057</t>
+    <t xml:space="preserve">1.90251457691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96421790122986</t>
   </si>
   <si>
     <t xml:space="preserve">1.96250379085541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821341991425</t>
+    <t xml:space="preserve">1.98821353912354</t>
   </si>
   <si>
     <t xml:space="preserve">1.98649966716766</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">1.97964346408844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12533140182495</t>
+    <t xml:space="preserve">2.12533164024353</t>
   </si>
   <si>
     <t xml:space="preserve">2.08591032028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05677270889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07905459403992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08076810836792</t>
+    <t xml:space="preserve">2.0567729473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07905435562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0807683467865</t>
   </si>
   <si>
     <t xml:space="preserve">2.06534266471863</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">2.06020045280457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07219862937927</t>
+    <t xml:space="preserve">2.07219839096069</t>
   </si>
   <si>
     <t xml:space="preserve">2.13390159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10819220542908</t>
+    <t xml:space="preserve">2.10819172859192</t>
   </si>
   <si>
     <t xml:space="preserve">2.09962201118469</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">2.06877040863037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11504793167114</t>
+    <t xml:space="preserve">2.11504769325256</t>
   </si>
   <si>
     <t xml:space="preserve">2.07391238212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09790802001953</t>
+    <t xml:space="preserve">2.09790778160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.11676168441772</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">2.08248209953308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06705641746521</t>
+    <t xml:space="preserve">2.06705665588379</t>
   </si>
   <si>
     <t xml:space="preserve">2.12190389633179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10647773742676</t>
+    <t xml:space="preserve">2.10647797584534</t>
   </si>
   <si>
     <t xml:space="preserve">2.08933806419373</t>
@@ -812,28 +812,28 @@
     <t xml:space="preserve">2.05163073539734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17675113677979</t>
+    <t xml:space="preserve">2.17675089836121</t>
   </si>
   <si>
     <t xml:space="preserve">2.14247155189514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1321873664856</t>
+    <t xml:space="preserve">2.13218760490417</t>
   </si>
   <si>
     <t xml:space="preserve">2.13047361373901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15961098670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11847567558289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09105229377747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12361741065979</t>
+    <t xml:space="preserve">2.15961122512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11847543716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09105205535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12361764907837</t>
   </si>
   <si>
     <t xml:space="preserve">2.11161994934082</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">2.15789723396301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15618348121643</t>
+    <t xml:space="preserve">2.15618324279785</t>
   </si>
   <si>
     <t xml:space="preserve">2.1441855430603</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">2.1407573223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14932751655579</t>
+    <t xml:space="preserve">2.14932703971863</t>
   </si>
   <si>
     <t xml:space="preserve">2.13904333114624</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">2.17503714561462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15104150772095</t>
+    <t xml:space="preserve">2.15104126930237</t>
   </si>
   <si>
     <t xml:space="preserve">2.12018966674805</t>
@@ -881,16 +881,16 @@
     <t xml:space="preserve">2.04820275306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07048439979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04991674423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12875986099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08762431144714</t>
+    <t xml:space="preserve">2.07048416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0499165058136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12875938415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08762407302856</t>
   </si>
   <si>
     <t xml:space="preserve">2.02077913284302</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.0224928855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01392316818237</t>
+    <t xml:space="preserve">2.01392292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.00535321235657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1681809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18532061576843</t>
+    <t xml:space="preserve">2.16818118095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18532085418701</t>
   </si>
   <si>
     <t xml:space="preserve">2.29672932624817</t>
@@ -920,19 +920,19 @@
     <t xml:space="preserve">2.33100891113281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32243895530701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35671854019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44241738319397</t>
+    <t xml:space="preserve">2.32243919372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35671830177307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44241714477539</t>
   </si>
   <si>
     <t xml:space="preserve">2.49383664131165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46812701225281</t>
+    <t xml:space="preserve">2.46812725067139</t>
   </si>
   <si>
     <t xml:space="preserve">2.47669696807861</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">2.48526692390442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53668594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57953548431396</t>
+    <t xml:space="preserve">2.53668642044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57953572273254</t>
   </si>
   <si>
     <t xml:space="preserve">2.59667539596558</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">2.61381506919861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55382609367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63447308540344</t>
+    <t xml:space="preserve">2.55382585525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63447332382202</t>
   </si>
   <si>
     <t xml:space="preserve">2.59862995147705</t>
@@ -965,13 +965,10 @@
     <t xml:space="preserve">2.5896692276001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61655163764954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55382585525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52694368362427</t>
+    <t xml:space="preserve">2.61655139923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52694344520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.437335729599</t>
@@ -980,16 +977,16 @@
     <t xml:space="preserve">2.46421790122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50006103515625</t>
+    <t xml:space="preserve">2.50006127357483</t>
   </si>
   <si>
     <t xml:space="preserve">2.45525717735291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54486489295959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57174730300903</t>
+    <t xml:space="preserve">2.54486513137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57174754142761</t>
   </si>
   <si>
     <t xml:space="preserve">2.51798272132874</t>
@@ -1001,7 +998,7 @@
     <t xml:space="preserve">2.53590416908264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4911003112793</t>
+    <t xml:space="preserve">2.49110054969788</t>
   </si>
   <si>
     <t xml:space="preserve">2.48213958740234</t>
@@ -1019,37 +1016,37 @@
     <t xml:space="preserve">2.7599241733551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77784562110901</t>
+    <t xml:space="preserve">2.77784585952759</t>
   </si>
   <si>
     <t xml:space="preserve">2.74200248718262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76888465881348</t>
+    <t xml:space="preserve">2.76888513565063</t>
   </si>
   <si>
     <t xml:space="preserve">2.71512031555176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75096344947815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67031645774841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72408080101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65239453315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68823766708374</t>
+    <t xml:space="preserve">2.75096321105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67031621932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72408103942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65239477157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68823790550232</t>
   </si>
   <si>
     <t xml:space="preserve">2.73304176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69719862937927</t>
+    <t xml:space="preserve">2.69719886779785</t>
   </si>
   <si>
     <t xml:space="preserve">2.67927694320679</t>
@@ -1058,25 +1055,25 @@
     <t xml:space="preserve">2.84953236579895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86745357513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83161044120789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6434338092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62551236152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58070826530457</t>
+    <t xml:space="preserve">2.86745381355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83161067962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64343404769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62551259994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58070850372314</t>
   </si>
   <si>
     <t xml:space="preserve">2.607590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41941428184509</t>
+    <t xml:space="preserve">2.41941404342651</t>
   </si>
   <si>
     <t xml:space="preserve">2.66135549545288</t>
@@ -1085,7 +1082,7 @@
     <t xml:space="preserve">2.81368899345398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84057140350342</t>
+    <t xml:space="preserve">2.840571641922</t>
   </si>
   <si>
     <t xml:space="preserve">2.93914008140564</t>
@@ -1094,7 +1091,7 @@
     <t xml:space="preserve">2.87641453742981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82264995574951</t>
+    <t xml:space="preserve">2.82264971733093</t>
   </si>
   <si>
     <t xml:space="preserve">2.80472826957703</t>
@@ -1106,34 +1103,34 @@
     <t xml:space="preserve">3.12731671333313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16315984725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13627767562866</t>
+    <t xml:space="preserve">3.16315960884094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13627743721008</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004225730896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25276803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26172876358032</t>
+    <t xml:space="preserve">3.25276780128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26172852516174</t>
   </si>
   <si>
     <t xml:space="preserve">3.28861093521118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29757189750671</t>
+    <t xml:space="preserve">3.29757165908813</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33341503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34237551689148</t>
+    <t xml:space="preserve">3.33341479301453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34237575531006</t>
   </si>
   <si>
     <t xml:space="preserve">3.42302274703979</t>
@@ -1148,19 +1145,19 @@
     <t xml:space="preserve">3.41406202316284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36925840377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37821865081787</t>
+    <t xml:space="preserve">3.36925792694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37821888923645</t>
   </si>
   <si>
     <t xml:space="preserve">3.45886588096619</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48574829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47678780555725</t>
+    <t xml:space="preserve">3.4857485294342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47678756713867</t>
   </si>
   <si>
     <t xml:space="preserve">3.49470925331116</t>
@@ -1178,16 +1175,16 @@
     <t xml:space="preserve">3.59327816963196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55743455886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52159142494202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51263070106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53951334953308</t>
+    <t xml:space="preserve">3.55743479728699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5215916633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51263093948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5395131111145</t>
   </si>
   <si>
     <t xml:space="preserve">3.60223865509033</t>
@@ -1196,13 +1193,13 @@
     <t xml:space="preserve">3.65600347518921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66496419906616</t>
+    <t xml:space="preserve">3.66496443748474</t>
   </si>
   <si>
     <t xml:space="preserve">3.72768974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71872901916504</t>
+    <t xml:space="preserve">3.71872925758362</t>
   </si>
   <si>
     <t xml:space="preserve">3.6918466091156</t>
@@ -1211,7 +1208,7 @@
     <t xml:space="preserve">3.70976805686951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68288612365723</t>
+    <t xml:space="preserve">3.68288588523865</t>
   </si>
   <si>
     <t xml:space="preserve">3.7635326385498</t>
@@ -1220,7 +1217,7 @@
     <t xml:space="preserve">3.78145432472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80833697319031</t>
+    <t xml:space="preserve">3.80833721160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.79041528701782</t>
@@ -1229,22 +1226,25 @@
     <t xml:space="preserve">3.95170950889587</t>
   </si>
   <si>
+    <t xml:space="preserve">3.96067070960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97005581855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00759744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0920672416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81988859176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87620115280151</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.96067023277283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97005581855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00759744644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0920672416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81988859176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87620115280151</t>
   </si>
   <si>
     <t xml:space="preserve">4.02636861801147</t>
@@ -18639,7 +18639,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18665,7 +18665,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G613" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18691,7 +18691,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G614" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18717,7 +18717,7 @@
         <v>2.75</v>
       </c>
       <c r="G615" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18743,7 +18743,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G616" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18769,7 +18769,7 @@
         <v>2.75</v>
       </c>
       <c r="G617" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18795,7 +18795,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G618" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18821,7 +18821,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G619" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18847,7 +18847,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G620" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18873,7 +18873,7 @@
         <v>2.75</v>
       </c>
       <c r="G621" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18899,7 +18899,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G622" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18925,7 +18925,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18951,7 +18951,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18977,7 +18977,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19003,7 +19003,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19029,7 +19029,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G627" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19055,7 +19055,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G628" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19081,7 +19081,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G629" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19107,7 +19107,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G630" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19133,7 +19133,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19159,7 +19159,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G632" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19185,7 +19185,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19211,7 +19211,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G634" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19237,7 +19237,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G635" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19263,7 +19263,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G636" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19289,7 +19289,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19315,7 +19315,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19341,7 +19341,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19367,7 +19367,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19393,7 +19393,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19419,7 +19419,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19445,7 +19445,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19471,7 +19471,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19497,7 +19497,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19523,7 +19523,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19549,7 +19549,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G647" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19575,7 +19575,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G648" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19601,7 +19601,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G649" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19627,7 +19627,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G650" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19653,7 +19653,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G651" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19705,7 +19705,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G653" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19757,7 +19757,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19783,7 +19783,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G656" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19809,7 +19809,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -19835,7 +19835,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G658" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -19861,7 +19861,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G659" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19887,7 +19887,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G660" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19913,7 +19913,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G661" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19939,7 +19939,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G662" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19965,7 +19965,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G663" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19991,7 +19991,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G664" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20017,7 +20017,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20043,7 +20043,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20069,7 +20069,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20095,7 +20095,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20147,7 +20147,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G670" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20173,7 +20173,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20199,7 +20199,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G672" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20225,7 +20225,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G673" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20251,7 +20251,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20277,7 +20277,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20303,7 +20303,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G676" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20329,7 +20329,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20355,7 +20355,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20381,7 +20381,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G679" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20407,7 +20407,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20433,7 +20433,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G681" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20459,7 +20459,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20485,7 +20485,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20511,7 +20511,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20537,7 +20537,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20563,7 +20563,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20589,7 +20589,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20615,7 +20615,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20641,7 +20641,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20667,7 +20667,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20693,7 +20693,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20719,7 +20719,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G692" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20745,7 +20745,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20771,7 +20771,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20797,7 +20797,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20823,7 +20823,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20849,7 +20849,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20875,7 +20875,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -20901,7 +20901,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -20927,7 +20927,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -20953,7 +20953,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -20979,7 +20979,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21005,7 +21005,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21031,7 +21031,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21057,7 +21057,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21083,7 +21083,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21109,7 +21109,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21161,7 +21161,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G709" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21187,7 +21187,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G710" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21213,7 +21213,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G711" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21239,7 +21239,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21369,7 +21369,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G717" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21395,7 +21395,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21421,7 +21421,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G719" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21603,7 +21603,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G726" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21707,7 +21707,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21811,7 +21811,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G734" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21837,7 +21837,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G735" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21863,7 +21863,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G736" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21889,7 +21889,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G737" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21915,7 +21915,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21941,7 +21941,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G739" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21967,7 +21967,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21993,7 +21993,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G741" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22019,7 +22019,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G742" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22045,7 +22045,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G743" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22071,7 +22071,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G744" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22097,7 +22097,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G745" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22123,7 +22123,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22149,7 +22149,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22175,7 +22175,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22201,7 +22201,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G749" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22227,7 +22227,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22253,7 +22253,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22279,7 +22279,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22305,7 +22305,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22331,7 +22331,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22357,7 +22357,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22383,7 +22383,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22409,7 +22409,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22435,7 +22435,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22461,7 +22461,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G759" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22487,7 +22487,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G760" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22513,7 +22513,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G761" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22539,7 +22539,7 @@
         <v>2.75</v>
       </c>
       <c r="G762" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22565,7 +22565,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22591,7 +22591,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22617,7 +22617,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22669,7 +22669,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22695,7 +22695,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G768" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22721,7 +22721,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22747,7 +22747,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22773,7 +22773,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22799,7 +22799,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22825,7 +22825,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22851,7 +22851,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22877,7 +22877,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22903,7 +22903,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22929,7 +22929,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22955,7 +22955,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22981,7 +22981,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G779" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23007,7 +23007,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23033,7 +23033,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23059,7 +23059,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G782" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23085,7 +23085,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23111,7 +23111,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G784" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23137,7 +23137,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G785" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23163,7 +23163,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23189,7 +23189,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G787" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23215,7 +23215,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G788" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23241,7 +23241,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G789" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23267,7 +23267,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23293,7 +23293,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G791" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23319,7 +23319,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G792" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23345,7 +23345,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G793" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23371,7 +23371,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23397,7 +23397,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23423,7 +23423,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23449,7 +23449,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G797" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23475,7 +23475,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G798" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23501,7 +23501,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23527,7 +23527,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G800" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23553,7 +23553,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23579,7 +23579,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G802" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23605,7 +23605,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23631,7 +23631,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G804" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23657,7 +23657,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23683,7 +23683,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23709,7 +23709,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G807" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23735,7 +23735,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G808" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23761,7 +23761,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G809" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23787,7 +23787,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G810" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23813,7 +23813,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G811" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23839,7 +23839,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23865,7 +23865,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G813" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23891,7 +23891,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G814" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23917,7 +23917,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23943,7 +23943,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G816" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23969,7 +23969,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23995,7 +23995,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G818" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24021,7 +24021,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24047,7 +24047,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G820" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24073,7 +24073,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G821" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24099,7 +24099,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24125,7 +24125,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G823" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24151,7 +24151,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G824" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24177,7 +24177,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G825" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24203,7 +24203,7 @@
         <v>4</v>
       </c>
       <c r="G826" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24229,7 +24229,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G827" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24255,7 +24255,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G828" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24281,7 +24281,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G829" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24307,7 +24307,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G830" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24333,7 +24333,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24359,7 +24359,7 @@
         <v>4</v>
       </c>
       <c r="G832" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24385,7 +24385,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24411,7 +24411,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24437,7 +24437,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24463,7 +24463,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G836" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24489,7 +24489,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24515,7 +24515,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24541,7 +24541,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G839" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24567,7 +24567,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24593,7 +24593,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G841" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24619,7 +24619,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G842" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24645,7 +24645,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24671,7 +24671,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G844" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24697,7 +24697,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G845" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24723,7 +24723,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24749,7 +24749,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24775,7 +24775,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24801,7 +24801,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24827,7 +24827,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G850" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24853,7 +24853,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24879,7 +24879,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24905,7 +24905,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G853" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24931,7 +24931,7 @@
         <v>4.25</v>
       </c>
       <c r="G854" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24957,7 +24957,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24983,7 +24983,7 @@
         <v>4.25</v>
       </c>
       <c r="G856" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25009,7 +25009,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G857" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25035,7 +25035,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G858" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25061,7 +25061,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G859" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25087,7 +25087,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25113,7 +25113,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G861" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25139,7 +25139,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G862" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25165,7 +25165,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G863" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25191,7 +25191,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G864" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25217,7 +25217,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G865" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25269,7 +25269,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G867" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25373,7 +25373,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25425,7 +25425,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G873" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25555,7 +25555,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G878" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25919,7 +25919,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G892" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25997,7 +25997,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G895" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26231,7 +26231,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G904" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -30417,7 +30417,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1065" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30703,7 +30703,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1076" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30729,7 +30729,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1077" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30963,7 +30963,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1086" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31327,7 +31327,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1100" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31431,7 +31431,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1104" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32939,7 +32939,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1162" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32965,7 +32965,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1163" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33407,7 +33407,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1180" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33537,7 +33537,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1185" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33745,7 +33745,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1193" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -68619,7 +68619,7 @@
     </row>
     <row r="2535">
       <c r="A2535" s="1" t="n">
-        <v>46008.5750925926</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2535" t="n">
         <v>40</v>
@@ -68640,6 +68640,32 @@
         <v>794</v>
       </c>
       <c r="H2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46009.6252314815</v>
+      </c>
+      <c r="B2536" t="n">
+        <v>33000</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>792</v>
+      </c>
+      <c r="H2536" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="796">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,22 +44,22 @@
     <t xml:space="preserve">RAT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91323757171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109167575836</t>
+    <t xml:space="preserve">1.9132376909256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109155654907</t>
   </si>
   <si>
     <t xml:space="preserve">1.88496315479279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9242330789566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80642306804657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82998502254486</t>
+    <t xml:space="preserve">1.92423319816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80642282962799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82998490333557</t>
   </si>
   <si>
     <t xml:space="preserve">1.79856884479523</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">1.76715302467346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85354685783386</t>
+    <t xml:space="preserve">1.85354721546173</t>
   </si>
   <si>
     <t xml:space="preserve">1.86925518512726</t>
@@ -83,34 +83,34 @@
     <t xml:space="preserve">1.86768436431885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81584763526917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83783888816833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87553822994232</t>
+    <t xml:space="preserve">1.81584787368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8378392457962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87553834915161</t>
   </si>
   <si>
     <t xml:space="preserve">1.82684338092804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84569299221039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81898939609528</t>
+    <t xml:space="preserve">1.84569311141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81898951530457</t>
   </si>
   <si>
     <t xml:space="preserve">1.83626818656921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85983002185822</t>
+    <t xml:space="preserve">1.85983037948608</t>
   </si>
   <si>
     <t xml:space="preserve">1.80485212802887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82056021690369</t>
+    <t xml:space="preserve">1.82056033611298</t>
   </si>
   <si>
     <t xml:space="preserve">1.81741857528687</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">1.85040545463562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88025045394897</t>
+    <t xml:space="preserve">1.88025057315826</t>
   </si>
   <si>
     <t xml:space="preserve">1.81427681446075</t>
@@ -128,85 +128,85 @@
     <t xml:space="preserve">1.85197639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84412217140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84098064899445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82370185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81113541126251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8221310377121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93679976463318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94622433185577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407843589783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96350336074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96507394313812</t>
+    <t xml:space="preserve">1.84412240982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84098041057587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82370173931122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81113517284393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82213091850281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9367995262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94622409343719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407819747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.963503241539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96507441997528</t>
   </si>
   <si>
     <t xml:space="preserve">1.99334859848022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00434398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.987065076828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905680656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0247642993927</t>
+    <t xml:space="preserve">2.00434422492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98706531524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905632972717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02476453781128</t>
   </si>
   <si>
     <t xml:space="preserve">1.93051624298096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96193253993988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93994116783142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95564925670624</t>
+    <t xml:space="preserve">1.96193242073059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93994104862213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95564913749695</t>
   </si>
   <si>
     <t xml:space="preserve">1.91637921333313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87396764755249</t>
+    <t xml:space="preserve">1.87396740913391</t>
   </si>
   <si>
     <t xml:space="preserve">1.93378722667694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95017540454865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92231559753418</t>
+    <t xml:space="preserve">1.95017528533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9223153591156</t>
   </si>
   <si>
     <t xml:space="preserve">1.93050956726074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96656322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95509147644043</t>
+    <t xml:space="preserve">1.96656346321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95509135723114</t>
   </si>
   <si>
     <t xml:space="preserve">1.95836925506592</t>
@@ -215,25 +215,25 @@
     <t xml:space="preserve">1.91739904880524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93542587757111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9419811964035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91248285770416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91084408760071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83545887470245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80268287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84201419353485</t>
+    <t xml:space="preserve">1.93542575836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198107719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91248309612274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91084396839142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83545899391174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80268311500549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84201431274414</t>
   </si>
   <si>
     <t xml:space="preserve">1.83218145370483</t>
@@ -242,31 +242,31 @@
     <t xml:space="preserve">1.88298428058624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86823523044586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9075665473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89281713962555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90592741966248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88462293148041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90920519828796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87151277065277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89773344993591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82398748397827</t>
+    <t xml:space="preserve">1.86823499202728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90756618976593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89281690120697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90592765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88462316989899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90920507907867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87151253223419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8977335691452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82398736476898</t>
   </si>
   <si>
     <t xml:space="preserve">1.75843513011932</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">1.76662921905518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78629493713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77646219730377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75188004970551</t>
+    <t xml:space="preserve">1.78629505634308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77646195888519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75187993049622</t>
   </si>
   <si>
     <t xml:space="preserve">1.75351893901825</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">1.77973973751068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75024116039276</t>
+    <t xml:space="preserve">1.75024127960205</t>
   </si>
   <si>
     <t xml:space="preserve">1.72074270248413</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">1.72893667221069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69616067409515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76007401943207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70435476303101</t>
+    <t xml:space="preserve">1.69616079330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76007413864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70435464382172</t>
   </si>
   <si>
     <t xml:space="preserve">1.73549211025238</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">1.73385322093964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71254861354828</t>
+    <t xml:space="preserve">1.71254873275757</t>
   </si>
   <si>
     <t xml:space="preserve">1.63060867786407</t>
@@ -326,67 +326,67 @@
     <t xml:space="preserve">1.67157864570618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66666221618652</t>
+    <t xml:space="preserve">1.66666233539581</t>
   </si>
   <si>
     <t xml:space="preserve">1.61012363433838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62241458892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66338467597961</t>
+    <t xml:space="preserve">1.62241470813751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6633847951889</t>
   </si>
   <si>
     <t xml:space="preserve">1.67321753501892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64535784721375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63880276679993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62569212913513</t>
+    <t xml:space="preserve">1.64535772800446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63880264759064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62569224834442</t>
   </si>
   <si>
     <t xml:space="preserve">1.66830110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65519070625305</t>
+    <t xml:space="preserve">1.65519058704376</t>
   </si>
   <si>
     <t xml:space="preserve">1.64699673652649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63798332214355</t>
+    <t xml:space="preserve">1.63798320293427</t>
   </si>
   <si>
     <t xml:space="preserve">1.59865200519562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6297892332077</t>
+    <t xml:space="preserve">1.62978935241699</t>
   </si>
   <si>
     <t xml:space="preserve">1.58308339118958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59537434577942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57898640632629</t>
+    <t xml:space="preserve">1.59537446498871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.578986287117</t>
   </si>
   <si>
     <t xml:space="preserve">1.59127748012543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54047441482544</t>
+    <t xml:space="preserve">1.54047453403473</t>
   </si>
   <si>
     <t xml:space="preserve">1.56751477718353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56997287273407</t>
+    <t xml:space="preserve">1.56997299194336</t>
   </si>
   <si>
     <t xml:space="preserve">1.56669533252716</t>
@@ -398,19 +398,19 @@
     <t xml:space="preserve">1.6027489900589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60356855392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6060266494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51917004585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56177890300751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54539096355438</t>
+    <t xml:space="preserve">1.60356831550598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60602653026581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51916992664337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5617790222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54539108276367</t>
   </si>
   <si>
     <t xml:space="preserve">1.37659418582916</t>
@@ -422,73 +422,73 @@
     <t xml:space="preserve">1.39462101459503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45771491527557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47082543373108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53391933441162</t>
+    <t xml:space="preserve">1.45771503448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47082531452179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53391921520233</t>
   </si>
   <si>
     <t xml:space="preserve">1.61258184909821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61176240444183</t>
+    <t xml:space="preserve">1.61176252365112</t>
   </si>
   <si>
     <t xml:space="preserve">1.59783267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54211330413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51179552078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55522382259369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56505644321442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56423711776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59291625022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55686259269714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52162826061249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54129385948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5044207572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51097619533539</t>
+    <t xml:space="preserve">1.54211342334747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51179563999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5552237033844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56505656242371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56423723697662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59291613101959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55686247348785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52162837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5412939786911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50442087650299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5109760761261</t>
   </si>
   <si>
     <t xml:space="preserve">1.55112671852112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51589250564575</t>
+    <t xml:space="preserve">1.51589238643646</t>
   </si>
   <si>
     <t xml:space="preserve">1.55194628238678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50851774215698</t>
+    <t xml:space="preserve">1.50851786136627</t>
   </si>
   <si>
     <t xml:space="preserve">1.53228056430817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50933730602264</t>
+    <t xml:space="preserve">1.50933718681335</t>
   </si>
   <si>
     <t xml:space="preserve">1.50769853591919</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">1.50278198719025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49540746212006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51015675067902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57325065135956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58554148674011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">